--- a/Ranking_CNB_500km_2026.xlsx
+++ b/Ranking_CNB_500km_2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,12 +488,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>350,8 km</t>
+          <t>360,8 km</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.805 m</t>
+          <t>4.930 m</t>
         </is>
       </c>
     </row>
@@ -522,12 +522,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>168,6 km</t>
+          <t>173,1 km</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.332 m</t>
+          <t>1.384 m</t>
         </is>
       </c>
     </row>
@@ -539,12 +539,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>160,3 km</t>
+          <t>166,2 km</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.906 m</t>
+          <t>1.973 m</t>
         </is>
       </c>
     </row>
@@ -687,51 +687,51 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Naiane C.</t>
+          <t>Jandson P.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>82,0 km</t>
+          <t>82,3 km</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>711 m</t>
+          <t>1.146 m</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Maria E.</t>
+          <t>Naiane C.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>75,4 km</t>
+          <t>82,0 km</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>959 m</t>
+          <t>711 m</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Jandson P.</t>
+          <t>Maria E.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>72,2 km</t>
+          <t>75,4 km</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.006 m</t>
+          <t>959 m</t>
         </is>
       </c>
     </row>
@@ -823,83 +823,117 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Thaisa V.</t>
+          <t>Alexsia A.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14,0 km</t>
+          <t>21,0 km</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>197 m</t>
+          <t>268 m</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Mariana L.</t>
+          <t>Thaisa V.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>7,9 km</t>
+          <t>19,5 km</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>108 m</t>
+          <t>272 m</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Filipe M.</t>
+          <t>Neydrielle V.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5,0 km</t>
+          <t>18,6 km</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>94 m</t>
+          <t>119 m</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Jhonny E.</t>
+          <t>Filipe M.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0,0 km</t>
+          <t>10,4 km</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0 m</t>
+          <t>169 m</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>Mariana L.</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>7,9 km</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>108 m</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>Marta L.</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>0,0 km</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>0 m</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Jhonny E.</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0,0 km</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
         <is>
           <t>0 m</t>
         </is>
@@ -916,7 +950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A160"/>
+  <dimension ref="A1:A176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -929,1022 +963,1022 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>4692.9_1546_P.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>6345.4_2376_S.</t>
+          <t>4891.7_1690_F.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2504.7_703_🔋.</t>
+          <t>9507.9_2851_M.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5028.5_4433_S.</t>
+          <t>3026.1_1490_A.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10503.6_3278_M.</t>
+          <t>2051.8_860_S.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>5242.7_1657_S.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3735.9_1928_V.</t>
+          <t>2036.1_839_S.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>7992.7_2506_F.</t>
+          <t>4932.4_1545_E.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5100.0_2587_A.</t>
+          <t>5724.1_3694_S.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>8396.0_2595_S.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>9507.9_2851_M.</t>
+          <t>5014.3_1731_F.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>6951.4_2856_S.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5580.0_2471_A.</t>
+          <t>7039.1_2754_S.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3798.9_1319_S.</t>
+          <t>9791.4_3527_G.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10011.5_3070_S.</t>
+          <t>4731.9_1407_T.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5724.1_3694_S.</t>
+          <t>5025.8_1214_P.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5296.8_1844_P.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3010.0_1424_A.</t>
+          <t>6046.5_3239_S.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>6012.6_2984_F.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6007.1_3172_F.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>9209.1_3141_E.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2060.0_802_S.</t>
+          <t>5256.5_1535_S.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5033.4_1976_M.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5242.7_1657_S.</t>
+          <t>14014.7_3537_S.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>10062.5_2886_M.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>6951.4_2856_S.</t>
+          <t>3798.9_1319_S.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>26010.2_9812_F.</t>
+          <t>8187.1_2322_M.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5029.4_1585_P.</t>
+          <t>26010.2_9812_F.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>1002.7_460_S.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5235.4_1766_P.</t>
+          <t>5005.8_1527_S.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>7312.2_2446_G.</t>
+          <t>5579.8_1990_E.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>4000.6_1659_S.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>9562.8_3145_M.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>17003.0_7696_P.</t>
+          <t>9012.4_2700_M.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>7985.2_2173_P.</t>
+          <t>2002.2_938_P.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>6833.7_2100_G.</t>
+          <t>10058.8_3483_F.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2186.2_736_G.</t>
+          <t>5086.0_1810_G.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>6818.2_2036_P.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>6038.2_2121_P.</t>
+          <t>6903.6_2566_G.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>4791.5_1524_E.</t>
+          <t>5580.0_2471_A.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>5004.0_2103_C.</t>
+          <t>7012.1_3931_🔋.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>6903.6_2566_G.</t>
+          <t>5119.6_3153_M.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1002.7_460_S.</t>
+          <t>9013.7_2337_M.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>6536.2_2241_P.</t>
+          <t>4763.8_1720_P.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>5282.8_2392_C.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>5010.3_3392_P.</t>
+          <t>3023.2_962_S.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>5365.6_2437_C.</t>
+          <t>7006.7_5717_S.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>14117.6_3844_M.</t>
+          <t>4000.6_1659_S.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>4028.8_1699_L.</t>
+          <t>1884.9_866_S.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>4797.2_1541_G.</t>
+          <t>5522.8_2716_V.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>4932.4_1545_E.</t>
+          <t>7992.7_2506_F.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>8187.1_2322_M.</t>
+          <t>10011.5_3070_S.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>4735.2_997_S.</t>
+          <t>4896.8_2251_L.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>5296.8_1844_P.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>4768.0_1875_L.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2002.2_938_P.</t>
+          <t>3614.8_970_🔋.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>4028.8_1699_L.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>9006.5_3085_X.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>7039.1_2754_S.</t>
+          <t>8104.2_2652_M.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>14014.7_3537_S.</t>
+          <t>21442.0_7959_F.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>5022.5_1222_P.</t>
+          <t>5004.5_1548_A.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>5365.6_2437_C.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>8351.7_4153_C.</t>
+          <t>8218.3_2327_P.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>8396.0_2595_S.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>3089.9_1508_C.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>5238.0_2781_F.</t>
+          <t>5029.4_1585_P.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>8481.2_2463_🔋.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>10016.9_3028_M.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>12545.4_3039_S.</t>
+          <t>7576.8_2823_P.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>10012.3_3067_S.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>10174.3_3680_S.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>5005.8_1527_S.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>9029.6_4595_P.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>13023.5_5156_L.</t>
+          <t>5085.1_1840_G.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>7576.8_2823_P.</t>
+          <t>6833.7_2100_G.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>5086.0_1810_G.</t>
+          <t>6007.1_3172_F.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>4797.2_1541_G.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>3010.0_1685_A.</t>
+          <t>2305.1_940_S.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>3412.3_1947_C.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>3757.2_1716_A.</t>
+          <t>1011.0_396_L.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>4896.8_2251_L.</t>
+          <t>17003.0_7696_P.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>7312.2_2446_G.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>2783.5_952_S.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>4705.5_1241_G.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>6011.5_2408_A.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>15637.2_5789_G.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2735.8_959_S.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>8481.2_2463_🔋.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>7598.7_2799_S.</t>
+          <t>1443.0_851_A.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>12521.4_4814_M.</t>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1443.0_851_A.</t>
+          <t>10503.6_3278_M.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>8132.9_2716_S.</t>
+          <t>6038.2_2121_P.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>5451.1_1905_T.</t>
+          <t>4017.3_1883_C.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>9791.4_3527_G.</t>
+          <t>12524.7_3259_S.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>8442.5_3038_G.</t>
+          <t>2504.7_703_🔋.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>10012.3_3067_S.</t>
+          <t>2011.7_731_S.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>37036.6_17889_F.</t>
+          <t>4830.1_2569_C.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>1366.2_487_L.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>15194.4_3911_S.</t>
+          <t>531.0_343_A.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>8351.7_4153_C.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>5028.5_4433_S.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>14117.6_3844_M.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>8120.9_2737_G.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>9029.6_4595_P.</t>
+          <t>15194.4_3911_S.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>7874.8_2223_M.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>4692.9_1546_P.</t>
+          <t>7230.5_2794_V.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>5004.0_2103_C.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>7874.8_2223_M.</t>
+          <t>5451.1_1905_T.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>9012.4_2700_M.</t>
+          <t>16397.3_4254_S.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>3089.9_1508_C.</t>
+          <t>2186.2_736_G.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>12524.7_3259_S.</t>
+          <t>8442.5_3038_G.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>10106.6_2889_P.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>5256.5_1535_S.</t>
+          <t>5238.0_2781_F.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>4077.1_1454_S.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>12326.4_4833_S.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>16397.3_4254_S.</t>
+          <t>791.5_266_G.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>4821.0_1857_P.</t>
+          <t>6472.0_2501_S.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>3023.2_962_S.</t>
+          <t>7598.7_2799_S.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>9209.1_3141_E.</t>
+          <t>4791.5_1524_E.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2047.9_924_L.</t>
+          <t>9006.5_3085_X.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2011.7_731_S.</t>
+          <t>657.7_273_S.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>7006.7_5717_S.</t>
+          <t>17012.6_5869_T.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>3412.3_1947_C.</t>
+          <t>12545.4_3039_S.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>37036.6_17889_F.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>7012.1_3931_🔋.</t>
+          <t>10030.0_3041_G.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>4017.3_1883_C.</t>
+          <t>8132.9_2716_S.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>15637.2_5789_G.</t>
+          <t>5008.2_1646_A.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>6818.2_2036_P.</t>
+          <t>5022.5_1222_P.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>6137.8_2406_L.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>5004.9_1790_A.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>10030.0_3041_G.</t>
+          <t>7015.4_2141_T.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2036.1_839_S.</t>
+          <t>15186.5_3866_S.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>3026.1_1490_A.</t>
+          <t>5010.3_3392_P.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>3005.2_1040_L.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>9756.3_2793_M.</t>
+          <t>3757.2_1716_A.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>8218.3_2327_P.</t>
+          <t>8253.0_2972_🔋.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>5282.8_2392_C.</t>
+          <t>7985.2_2173_P.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>531.0_343_A.</t>
+          <t>18665.3_4638_S.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>10348.3_2647_S.</t>
+          <t>10106.6_3354_M.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>10533.4_4020_F.</t>
+          <t>5100.0_2587_A.</t>
         </is>
       </c>
     </row>
@@ -1958,84 +1992,196 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>208.3_85_P.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>4830.1_2569_C.</t>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>1366.2_487_L.</t>
+          <t>3010.0_1685_A.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>10008.1_2966_M.</t>
+          <t>3019.8_1453_F.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>6345.4_2376_S.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>4821.0_1857_P.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>15186.5_3866_S.</t>
+          <t>5235.4_1766_P.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>18665.3_4638_S.</t>
+          <t>5287.4_1835_V.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>10533.4_4020_F.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>5382.2_2690_M.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>5579.8_1990_E.</t>
+          <t>2735.8_959_S.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>5025.8_1214_P.</t>
+          <t>4814.5_1705_🔋.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2060.0_802_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>3010.0_1424_A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>10348.3_2647_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2175.4_712_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>5033.4_1976_M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>12006.9_5463_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>3735.9_1928_V.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>6084.1_2156_V.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>5007.5_3389_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>1027.7_364_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>3580.9_1198_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>13023.5_5156_L.</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2047.9_924_L.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>6536.2_2241_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>4735.2_997_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>9756.3_2793_M.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_500km_2026.xlsx
+++ b/Ranking_CNB_500km_2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,151 +789,168 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Karine F.</t>
+          <t>Pierre P.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>23,4 km</t>
+          <t>27,3 km</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>294 m</t>
+          <t>290 m</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Eduardo T.</t>
+          <t>Karine F.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>22,8 km</t>
+          <t>23,4 km</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>234 m</t>
+          <t>294 m</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Alexsia A.</t>
+          <t>Eduardo T.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>21,0 km</t>
+          <t>22,8 km</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>268 m</t>
+          <t>234 m</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Thaisa V.</t>
+          <t>Alexsia A.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>19,5 km</t>
+          <t>21,0 km</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>272 m</t>
+          <t>268 m</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Neydrielle V.</t>
+          <t>Thaisa V.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>18,6 km</t>
+          <t>19,5 km</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>119 m</t>
+          <t>272 m</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Filipe M.</t>
+          <t>Neydrielle V.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>10,4 km</t>
+          <t>18,6 km</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>169 m</t>
+          <t>119 m</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Mariana L.</t>
+          <t>Filipe M.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>7,9 km</t>
+          <t>10,4 km</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>108 m</t>
+          <t>169 m</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Marta L.</t>
+          <t>Mariana L.</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0,0 km</t>
+          <t>7,9 km</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>0 m</t>
+          <t>108 m</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>Marta L.</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0,0 km</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>0 m</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>Jhonny E.</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>0,0 km</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>0 m</t>
         </is>
@@ -950,7 +967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A176"/>
+  <dimension ref="A1:A181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -963,1085 +980,1085 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4692.9_1546_P.</t>
+          <t>3735.9_1928_V.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>21442.0_7959_F.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>9507.9_2851_M.</t>
+          <t>5022.5_1222_P.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3026.1_1490_A.</t>
+          <t>8396.0_2595_S.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>3614.8_970_🔋.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5242.7_1657_S.</t>
+          <t>7874.8_2223_M.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2036.1_839_S.</t>
+          <t>5904.3_2699_P.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>4932.4_1545_E.</t>
+          <t>17012.6_5869_T.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5724.1_3694_S.</t>
+          <t>1443.0_851_A.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>8396.0_2595_S.</t>
+          <t>12326.4_4833_S.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>4791.5_1524_E.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6951.4_2856_S.</t>
+          <t>4896.8_2251_L.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>7039.1_2754_S.</t>
+          <t>1884.9_866_S.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>9791.4_3527_G.</t>
+          <t>3010.0_1424_A.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>5296.8_1844_P.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5025.8_1214_P.</t>
+          <t>5287.4_1835_V.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>5010.3_3392_P.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>7039.1_2754_S.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>8481.2_2463_🔋.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>5256.5_1535_S.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>9209.1_3141_E.</t>
+          <t>10503.6_3278_M.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5256.5_1535_S.</t>
+          <t>9791.4_3527_G.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>12521.4_4814_M.</t>
+          <t>5235.4_1766_P.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>14014.7_3537_S.</t>
+          <t>4692.9_1546_P.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3798.9_1319_S.</t>
+          <t>5119.6_3153_M.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>8187.1_2322_M.</t>
+          <t>8120.9_2737_G.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>26010.2_9812_F.</t>
+          <t>6012.6_2984_P.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1002.7_460_S.</t>
+          <t>4028.8_1699_L.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5005.8_1527_S.</t>
+          <t>4705.5_1241_G.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5579.8_1990_E.</t>
+          <t>2186.2_736_G.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>5242.7_1657_S.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>4891.7_1690_F.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>15186.5_3866_S.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>9012.4_2700_M.</t>
+          <t>5522.8_2716_V.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2002.2_938_P.</t>
+          <t>7576.8_2823_P.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>8187.1_2322_M.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>5086.0_1810_G.</t>
+          <t>9029.6_4595_P.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>6818.2_2036_P.</t>
+          <t>2060.0_802_S.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>3089.9_1508_C.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>6903.6_2566_G.</t>
+          <t>12545.4_3039_S.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>5580.0_2471_A.</t>
+          <t>2047.9_924_L.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>7012.1_3931_🔋.</t>
+          <t>5014.3_1731_F.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>5580.0_2471_A.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>4077.1_1454_S.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>5282.8_2392_C.</t>
+          <t>3010.0_1685_A.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3023.2_962_S.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>1002.7_460_S.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>7006.7_5717_S.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>4000.6_1659_S.</t>
+          <t>7006.7_5717_S.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>7992.7_2506_F.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>5522.8_2716_V.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>7992.7_2506_F.</t>
+          <t>8253.0_2972_🔋.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>10011.5_3070_S.</t>
+          <t>14117.6_3844_M.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>4896.8_2251_L.</t>
+          <t>9756.3_2793_M.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>5296.8_1844_P.</t>
+          <t>1011.0_396_L.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>5004.5_1548_A.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>10008.1_2966_M.</t>
+          <t>1027.7_364_S.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>4028.8_1699_L.</t>
+          <t>5085.1_1840_G.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>2504.7_703_🔋.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>12524.7_3259_S.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>6007.1_3172_F.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>5004.5_1548_A.</t>
+          <t>1366.2_487_L.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>5365.6_2437_C.</t>
+          <t>15194.4_3911_S.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>8218.3_2327_P.</t>
+          <t>8132.9_2716_S.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>9209.1_3141_E.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>3089.9_1508_C.</t>
+          <t>26010.2_9812_F.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>5029.4_1585_P.</t>
+          <t>3019.8_1453_F.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>8481.2_2463_🔋.</t>
+          <t>5724.1_3694_S.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>10016.9_3028_M.</t>
+          <t>5579.8_1990_E.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>7576.8_2823_P.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>10012.3_3067_S.</t>
+          <t>2036.1_839_S.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>12006.9_5463_P.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>5621.6_2375_P.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>9029.6_4595_P.</t>
+          <t>4017.3_1883_C.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>5085.1_1840_G.</t>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>6833.7_2100_G.</t>
+          <t>10174.3_3680_S.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>6007.1_3172_F.</t>
+          <t>18665.3_4638_S.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>4797.2_1541_G.</t>
+          <t>5238.0_2781_F.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>5028.5_4433_S.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>3412.3_1947_C.</t>
+          <t>5004.0_2103_C.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>6472.0_2501_S.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>17003.0_7696_P.</t>
+          <t>9013.7_2337_M.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>7312.2_2446_G.</t>
+          <t>4763.8_1720_P.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2783.5_952_S.</t>
+          <t>4830.1_2569_C.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>2735.8_959_S.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>6011.5_2408_A.</t>
+          <t>791.5_266_G.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>15637.2_5789_G.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>7012.1_3931_🔋.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>7312.2_2446_G.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1443.0_851_A.</t>
+          <t>6536.2_2241_P.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>3798.9_1319_S.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>10503.6_3278_M.</t>
+          <t>5282.8_2392_C.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>6038.2_2121_P.</t>
+          <t>3757.2_1716_A.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>4017.3_1883_C.</t>
+          <t>10106.6_3354_M.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>12524.7_3259_S.</t>
+          <t>4786.5_1898_P.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2504.7_703_🔋.</t>
+          <t>4797.2_1541_G.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2011.7_731_S.</t>
+          <t>6011.5_2408_A.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>4830.1_2569_C.</t>
+          <t>5005.8_1527_S.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1366.2_487_L.</t>
+          <t>3023.2_962_S.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>531.0_343_A.</t>
+          <t>4000.6_1659_S.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>8351.7_4153_C.</t>
+          <t>208.3_85_P.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>4731.9_1407_T.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>2051.8_860_S.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>5028.5_4433_S.</t>
+          <t>5004.9_1790_A.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>14117.6_3844_M.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>6951.4_2856_S.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>15194.4_3911_S.</t>
+          <t>4768.0_1875_L.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>7874.8_2223_M.</t>
+          <t>6038.2_2121_P.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>7230.5_2794_V.</t>
+          <t>14014.7_3537_S.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>5004.0_2103_C.</t>
+          <t>4735.2_997_S.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>5451.1_1905_T.</t>
+          <t>6137.8_2406_L.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>16397.3_4254_S.</t>
+          <t>5451.1_1905_T.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2186.2_736_G.</t>
+          <t>8351.7_4153_C.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>8442.5_3038_G.</t>
+          <t>9555.5_5689_S.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>10106.6_2889_P.</t>
+          <t>2175.4_712_S.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>5238.0_2781_F.</t>
+          <t>2002.2_938_P.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>10348.3_2647_S.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>2305.1_940_S.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>791.5_266_G.</t>
+          <t>6012.6_2984_F.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>7598.7_2799_S.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>4791.5_1524_E.</t>
+          <t>2783.5_952_S.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>9006.5_3085_X.</t>
+          <t>531.0_343_A.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>657.7_273_S.</t>
+          <t>8218.3_2327_P.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>13023.5_5156_L.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>12545.4_3039_S.</t>
+          <t>5008.2_1646_A.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>37036.6_17889_F.</t>
+          <t>6345.4_2376_S.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>10030.0_3041_G.</t>
+          <t>10016.9_3028_M.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>8132.9_2716_S.</t>
+          <t>5025.8_1214_P.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>5008.2_1646_A.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>5022.5_1222_P.</t>
+          <t>7230.5_2794_V.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>3026.1_1490_A.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>5004.9_1790_A.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>3412.3_1947_C.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>15186.5_3866_S.</t>
+          <t>7015.4_2141_T.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>5010.3_3392_P.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>3580.9_1198_S.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>3757.2_1716_A.</t>
+          <t>7985.2_2173_P.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>16397.3_4254_S.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>7985.2_2173_P.</t>
+          <t>9012.4_2700_M.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>18665.3_4638_S.</t>
+          <t>3005.2_1040_L.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>5100.0_2587_A.</t>
+          <t>10012.3_3067_S.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>9555.5_5689_S.</t>
+          <t>6818.2_2036_P.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>17003.0_7696_P.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>9006.5_3085_X.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>3010.0_1685_A.</t>
+          <t>6833.7_2100_G.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>6903.6_2566_G.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>6345.4_2376_S.</t>
+          <t>7598.7_2799_S.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>4821.0_1857_P.</t>
+          <t>4932.4_1545_E.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>5235.4_1766_P.</t>
+          <t>5365.6_2437_C.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>5287.4_1835_V.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
@@ -2055,133 +2072,168 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>5382.2_2690_M.</t>
+          <t>10058.8_3483_F.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2735.8_959_S.</t>
+          <t>10062.5_2886_M.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>5029.4_1585_P.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2060.0_802_S.</t>
+          <t>10011.5_3070_S.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>3010.0_1424_A.</t>
+          <t>4814.5_1705_🔋.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>10348.3_2647_S.</t>
+          <t>5086.0_1810_G.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>8442.5_3038_G.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>5033.4_1976_M.</t>
+          <t>37036.6_17889_F.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>5033.4_1976_M.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>3735.9_1928_V.</t>
+          <t>2011.7_731_S.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>6084.1_2156_V.</t>
+          <t>5382.2_2690_M.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>657.7_273_S.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>1027.7_364_S.</t>
+          <t>9562.8_3145_M.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>10030.0_3041_G.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>13023.5_5156_L.</t>
+          <t>6084.1_2156_V.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2047.9_924_L.</t>
+          <t>6046.5_3239_S.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>6536.2_2241_P.</t>
+          <t>5008.0_2402_P.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>4735.2_997_S.</t>
+          <t>15637.2_5789_G.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>9756.3_2793_M.</t>
+          <t>4821.0_1857_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>5100.0_2587_A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>3378.9_1292_🔋.</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>9507.9_2851_M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>8104.2_2652_M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>10106.6_2889_P.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_500km_2026.xlsx
+++ b/Ranking_CNB_500km_2026.xlsx
@@ -505,12 +505,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>173,1 km</t>
+          <t>180,6 km</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.384 m</t>
+          <t>1.471 m</t>
         </is>
       </c>
     </row>
@@ -539,12 +539,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>154,8 km</t>
+          <t>164,8 km</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.486 m</t>
+          <t>1.557 m</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>129,0 km</t>
+          <t>131,9 km</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -568,34 +568,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cassia C.</t>
+          <t>Gleydson G.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>117,1 km</t>
+          <t>118,9 km</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.458 m</t>
+          <t>798 m</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Gleydson G.</t>
+          <t>Cassia C.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>113,9 km</t>
+          <t>117,1 km</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>782 m</t>
+          <t>1.458 m</t>
         </is>
       </c>
     </row>
@@ -641,12 +641,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>90,9 km</t>
+          <t>97,7 km</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.252 m</t>
+          <t>1.352 m</t>
         </is>
       </c>
     </row>
@@ -789,51 +789,51 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Karine F.</t>
+          <t>Alexsia A.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>23,4 km</t>
+          <t>29,0 km</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>294 m</t>
+          <t>351 m</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Eduardo T.</t>
+          <t>Karine F.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>22,8 km</t>
+          <t>23,4 km</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>234 m</t>
+          <t>294 m</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Alexsia A.</t>
+          <t>Eduardo T.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>21,0 km</t>
+          <t>22,8 km</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>268 m</t>
+          <t>234 m</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A190"/>
+  <dimension ref="A1:A197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -963,70 +963,70 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1027.7_364_S.</t>
+          <t>12326.4_4833_S.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5004.0_2103_C.</t>
+          <t>6007.1_3172_F.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5005.4_2618_L.</t>
+          <t>791.5_266_G.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>21442.0_7959_F.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>10011.5_3070_S.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>8396.0_2595_S.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5296.8_1844_P.</t>
+          <t>5100.0_2587_A.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>7576.8_2823_P.</t>
+          <t>8351.7_4153_C.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>5282.8_2392_C.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>15637.2_5789_G.</t>
+          <t>2036.1_839_S.</t>
         </is>
       </c>
     </row>
@@ -1040,707 +1040,707 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2735.8_959_S.</t>
+          <t>4791.5_1524_E.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>12521.4_4814_M.</t>
+          <t>5904.3_2699_P.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5086.0_1810_G.</t>
+          <t>5296.8_1844_P.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5033.4_1976_M.</t>
+          <t>6804.1_2088_P.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>5086.0_1810_G.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>9756.3_2793_M.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>6345.4_2376_S.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>7012.1_3931_🔋.</t>
+          <t>2175.4_712_S.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>8187.1_2322_M.</t>
+          <t>4896.8_2251_L.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2011.7_731_S.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>6833.7_2100_G.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>4821.0_1857_P.</t>
+          <t>2002.2_938_P.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>26010.2_9812_F.</t>
+          <t>6951.4_2856_S.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>13023.5_5156_L.</t>
+          <t>17012.6_5869_T.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2504.7_703_🔋.</t>
+          <t>7312.2_2446_G.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5008.2_1646_A.</t>
+          <t>6046.5_3239_S.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1366.2_487_L.</t>
+          <t>10533.4_4020_F.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3412.3_1947_C.</t>
+          <t>9791.4_3527_G.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5010.3_3392_P.</t>
+          <t>3026.1_1490_A.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5451.1_1905_T.</t>
+          <t>3005.2_1040_L.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>6007.1_3172_F.</t>
+          <t>6833.7_2100_G.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>531.0_343_A.</t>
+          <t>4692.9_1546_P.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>5242.7_1657_S.</t>
+          <t>4768.0_1875_L.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10503.6_3278_M.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3089.9_1508_C.</t>
+          <t>5004.9_1790_A.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>8218.3_2327_P.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>12524.7_3259_S.</t>
+          <t>17003.0_7696_P.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>9507.9_2851_M.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>7419.2_3469_F.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>4896.8_2251_L.</t>
+          <t>4028.8_1699_L.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>3010.0_1424_A.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>5033.4_1976_M.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>5238.0_2781_F.</t>
+          <t>3010.0_1685_A.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>12545.4_3039_S.</t>
+          <t>6472.0_2501_S.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>4017.3_1883_C.</t>
+          <t>5242.7_1657_S.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>4028.8_1699_L.</t>
+          <t>9006.5_3085_X.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>8218.3_2327_P.</t>
+          <t>4786.5_1898_P.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>791.5_266_G.</t>
+          <t>5004.5_1548_A.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>14117.6_3844_M.</t>
+          <t>7230.5_2794_V.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>10348.3_2647_S.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>5005.8_1527_S.</t>
+          <t>14117.6_3844_M.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>16397.3_4254_S.</t>
+          <t>12545.4_3039_S.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>37036.6_17889_F.</t>
+          <t>5382.2_2690_M.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>8132.9_2716_S.</t>
+          <t>16397.3_4254_S.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>7985.2_2173_P.</t>
+          <t>8004.6_2357_G.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>6038.2_2121_P.</t>
+          <t>8618.0_2344_P.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>5365.6_2437_C.</t>
+          <t>4891.7_1690_F.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>8004.6_2357_G.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>4932.4_1545_E.</t>
+          <t>3798.9_1319_S.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>5028.5_4433_S.</t>
+          <t>5522.8_2716_V.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>2047.9_924_L.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>2011.7_731_S.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>26010.2_9812_F.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>18665.3_4638_S.</t>
+          <t>4735.2_997_S.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>4797.2_1541_G.</t>
+          <t>5022.5_1222_P.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>6345.4_2376_S.</t>
+          <t>10106.6_2889_P.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>5025.8_1214_P.</t>
+          <t>15504.3_3950_M.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>10106.6_2889_P.</t>
+          <t>3089.9_1508_C.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>6012.6_2984_P.</t>
+          <t>5085.1_1840_G.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>4735.2_997_S.</t>
+          <t>5235.4_1766_P.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>5256.5_1535_S.</t>
+          <t>5004.0_2103_C.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2002.2_938_P.</t>
+          <t>5028.5_4433_S.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>7114.0_2850_S.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>8351.7_4153_C.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>8120.9_2737_G.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>5621.6_2375_P.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>3735.9_1928_V.</t>
+          <t>7985.2_2173_P.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>5022.5_1222_P.</t>
+          <t>5008.2_1646_A.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>10503.6_3278_M.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2060.0_802_S.</t>
+          <t>4705.5_1241_G.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>4791.5_1524_E.</t>
+          <t>8253.0_2972_🔋.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2186.2_736_G.</t>
+          <t>4814.5_1705_🔋.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>5621.6_2375_P.</t>
+          <t>8187.1_2322_M.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>657.7_273_S.</t>
+          <t>9007.1_3080_P.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>5522.8_2716_V.</t>
+          <t>4000.6_1659_S.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>37036.6_17889_F.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>10012.3_3067_S.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>7230.5_2794_V.</t>
+          <t>10012.3_3067_S.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>5238.0_2781_F.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>9555.5_5689_S.</t>
+          <t>5579.8_1990_E.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>5008.0_2402_P.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>5287.4_1835_V.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>2186.2_736_G.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>9013.7_2337_M.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>1884.9_866_S.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>6011.5_2408_A.</t>
+          <t>8481.2_2463_🔋.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>3023.2_962_S.</t>
+          <t>6536.2_2241_P.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>9029.6_4595_P.</t>
+          <t>5005.8_1527_S.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>10012.1_3139_S.</t>
+          <t>5580.0_2471_A.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>3026.1_1490_A.</t>
+          <t>1443.0_851_A.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2036.1_839_S.</t>
+          <t>5256.5_1535_S.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>4763.8_1720_P.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>14014.7_3537_S.</t>
+          <t>6903.6_2566_G.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>10008.1_2966_M.</t>
+          <t>8104.2_2652_M.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1443.0_851_A.</t>
+          <t>531.0_343_A.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>4692.9_1546_P.</t>
+          <t>9012.4_2700_M.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>1011.0_396_L.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>6903.6_2566_G.</t>
+          <t>7598.7_2799_S.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>7006.7_5717_S.</t>
+          <t>6012.6_2984_P.</t>
         </is>
       </c>
     </row>
@@ -1754,532 +1754,581 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1002.7_460_S.</t>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>9006.5_3085_X.</t>
+          <t>2504.7_703_🔋.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>9029.6_4595_P.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>5119.6_3153_M.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>4077.1_1454_S.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>10533.4_4020_F.</t>
+          <t>4731.9_1407_T.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>3010.0_1424_A.</t>
+          <t>9562.8_3145_M.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>4177.9_1557_T.</t>
+          <t>2783.5_952_S.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>6536.2_2241_P.</t>
+          <t>7015.4_2141_T.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>3757.2_1716_A.</t>
+          <t>15194.4_3911_S.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>10001.9_4466_P.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>17003.0_7696_P.</t>
+          <t>4830.1_2569_C.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>4786.5_1898_P.</t>
+          <t>2735.8_959_S.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>5580.0_2471_A.</t>
+          <t>6038.2_2121_P.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>7502.4_3467_P.</t>
+          <t>6012.6_2984_F.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>3735.9_1928_V.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>3757.2_1716_A.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>4000.6_1659_S.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>8008.0_2930_A.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>1027.7_364_S.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>7598.7_2799_S.</t>
+          <t>12524.7_3259_S.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>8396.0_2595_S.</t>
+          <t>3580.9_1198_S.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>9791.4_3527_G.</t>
+          <t>7012.1_3931_🔋.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>4017.3_1883_C.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>5004.5_1548_A.</t>
+          <t>401.2_179_S.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>15504.3_3950_M.</t>
+          <t>3614.8_970_🔋.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>7039.1_2754_S.</t>
+          <t>10016.9_3028_M.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>5724.1_3694_S.</t>
+          <t>5014.3_1731_F.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>7874.8_2223_M.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>3010.0_1685_A.</t>
+          <t>13023.5_5156_L.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>5005.4_2618_L.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>14014.7_3537_S.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>4830.1_2569_C.</t>
+          <t>15637.2_5789_G.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>7312.2_2446_G.</t>
+          <t>10012.1_3139_S.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>5085.1_1840_G.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>6084.1_2156_V.</t>
+          <t>2880.9_1210_L.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>9756.3_2793_M.</t>
+          <t>3023.2_962_S.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>7419.2_3469_F.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>8618.0_2344_P.</t>
+          <t>2305.1_940_S.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>8442.5_3038_G.</t>
+          <t>10058.8_3483_F.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>10011.5_3070_S.</t>
+          <t>7039.1_2754_S.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>1366.2_487_L.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>9007.1_3080_P.</t>
+          <t>3412.3_1947_C.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>5235.4_1766_P.</t>
+          <t>10106.6_3354_M.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>7992.7_2506_F.</t>
+          <t>6084.1_2156_V.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>9507.9_2851_M.</t>
+          <t>7576.8_2823_P.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>5287.4_1835_V.</t>
+          <t>3019.8_1453_F.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>15194.4_3911_S.</t>
+          <t>8442.5_3038_G.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>7992.7_2506_F.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>4177.9_1557_T.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>15186.5_3866_S.</t>
+          <t>12006.9_5463_P.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>7502.4_3467_P.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>5579.8_1990_E.</t>
+          <t>7874.8_2223_M.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2783.5_952_S.</t>
+          <t>2051.8_860_S.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>5008.0_2402_P.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>5029.4_1585_P.</t>
+          <t>5451.1_1905_T.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>5100.0_2587_A.</t>
+          <t>18665.3_4638_S.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2047.9_924_L.</t>
+          <t>10174.3_3680_S.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>15186.5_3866_S.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>5282.8_2392_C.</t>
+          <t>7006.7_5717_S.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>8481.2_2463_🔋.</t>
+          <t>9209.1_3141_E.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>5365.6_2437_C.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>9209.1_3141_E.</t>
+          <t>5029.4_1585_P.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>5382.2_2690_M.</t>
+          <t>4797.2_1541_G.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>5004.9_1790_A.</t>
+          <t>6137.8_2406_L.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>5904.3_2699_P.</t>
+          <t>2060.0_802_S.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>6951.4_2856_S.</t>
+          <t>6011.5_2408_A.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>3798.9_1319_S.</t>
+          <t>5010.3_3392_P.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>5010.3_1888_G.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>10016.9_3028_M.</t>
+          <t>657.7_273_S.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>1002.7_460_S.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>9012.4_2700_M.</t>
+          <t>4932.4_1545_E.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>5724.1_3694_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>8132.9_2716_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>5025.8_1214_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>208.3_85_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>4821.0_1857_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>10062.5_2886_M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>10348.3_2647_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>9555.5_5689_S.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_500km_2026.xlsx
+++ b/Ranking_CNB_500km_2026.xlsx
@@ -454,12 +454,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>391,2 km</t>
+          <t>447,3 km</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>5.617 m</t>
+          <t>6.042 m</t>
         </is>
       </c>
     </row>
@@ -568,34 +568,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Gleydson G.</t>
+          <t>Cassia C.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>118,9 km</t>
+          <t>125,5 km</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>798 m</t>
+          <t>1.569 m</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cassia C.</t>
+          <t>Gleydson G.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>117,1 km</t>
+          <t>118,9 km</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.458 m</t>
+          <t>798 m</t>
         </is>
       </c>
     </row>
@@ -806,68 +806,68 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Karine F.</t>
+          <t>Neydrielle V.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>23,4 km</t>
+          <t>26,2 km</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>294 m</t>
+          <t>182 m</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Eduardo T.</t>
+          <t>Karine F.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>22,8 km</t>
+          <t>23,4 km</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>234 m</t>
+          <t>294 m</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Thaisa V.</t>
+          <t>Eduardo T.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>19,5 km</t>
+          <t>22,8 km</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>272 m</t>
+          <t>234 m</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Neydrielle V.</t>
+          <t>Thaisa V.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>18,6 km</t>
+          <t>19,5 km</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>119 m</t>
+          <t>272 m</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A197"/>
+  <dimension ref="A1:A200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -963,1372 +963,1393 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>5522.8_2716_V.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>6007.1_3172_F.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>791.5_266_G.</t>
+          <t>7419.2_3469_F.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>7569.4_2477_V.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10011.5_3070_S.</t>
+          <t>6345.4_2376_S.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>8396.0_2595_S.</t>
+          <t>401.2_179_S.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5100.0_2587_A.</t>
+          <t>4000.6_1659_S.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>8351.7_4153_C.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5282.8_2392_C.</t>
+          <t>5004.5_1548_A.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2036.1_839_S.</t>
+          <t>12326.4_4833_S.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6818.2_2036_P.</t>
+          <t>3798.9_1319_S.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>4791.5_1524_E.</t>
+          <t>7874.8_2223_M.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5904.3_2699_P.</t>
+          <t>6137.8_2406_L.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5296.8_1844_P.</t>
+          <t>10001.9_4466_P.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>6804.1_2088_P.</t>
+          <t>3019.8_1453_F.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5086.0_1810_G.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>9756.3_2793_M.</t>
+          <t>657.7_273_S.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6345.4_2376_S.</t>
+          <t>10348.3_2647_S.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>1884.9_866_S.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4896.8_2251_L.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>3026.1_1490_A.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>7012.1_3931_🔋.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2002.2_938_P.</t>
+          <t>5004.0_2103_C.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>6951.4_2856_S.</t>
+          <t>9006.5_3085_X.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>4017.3_1883_C.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>7312.2_2446_G.</t>
+          <t>10058.8_3483_F.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>5025.8_1214_P.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10533.4_4020_F.</t>
+          <t>3614.8_970_🔋.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>9791.4_3527_G.</t>
+          <t>5282.8_2392_C.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3026.1_1490_A.</t>
+          <t>5010.3_1888_G.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>2783.5_952_S.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>6833.7_2100_G.</t>
+          <t>5451.1_1905_T.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>4692.9_1546_P.</t>
+          <t>5580.0_2471_A.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>3010.0_1424_A.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>7502.4_3467_P.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5004.9_1790_A.</t>
+          <t>26010.2_9812_F.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>8218.3_2327_P.</t>
+          <t>3023.2_962_S.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>17003.0_7696_P.</t>
+          <t>4821.0_1857_P.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>9507.9_2851_M.</t>
+          <t>13023.5_5156_L.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10008.1_2966_M.</t>
+          <t>5014.3_1731_F.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>4028.8_1699_L.</t>
+          <t>3735.9_1928_V.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>3010.0_1424_A.</t>
+          <t>5008.2_1646_A.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>5033.4_1976_M.</t>
+          <t>4797.2_1541_G.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3010.0_1685_A.</t>
+          <t>4791.5_1524_E.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>4891.7_1690_F.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>5242.7_1657_S.</t>
+          <t>37036.6_17889_F.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>9006.5_3085_X.</t>
+          <t>6903.6_2566_G.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>4786.5_1898_P.</t>
+          <t>5382.2_2690_M.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>5004.5_1548_A.</t>
+          <t>9562.8_3145_M.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>7230.5_2794_V.</t>
+          <t>10011.5_3070_S.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>8218.3_2327_P.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>14117.6_3844_M.</t>
+          <t>2002.2_938_P.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>12545.4_3039_S.</t>
+          <t>5008.0_2402_P.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>5382.2_2690_M.</t>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>16397.3_4254_S.</t>
+          <t>4830.1_2569_C.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>8004.6_2357_G.</t>
+          <t>4731.9_1407_T.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>8618.0_2344_P.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>4177.9_1557_T.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>10503.6_3278_M.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>3798.9_1319_S.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>5522.8_2716_V.</t>
+          <t>9013.7_2337_M.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2047.9_924_L.</t>
+          <t>5005.8_1527_S.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2011.7_731_S.</t>
+          <t>5100.0_2587_A.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>26010.2_9812_F.</t>
+          <t>4786.5_1898_P.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>4735.2_997_S.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>5022.5_1222_P.</t>
+          <t>8351.7_4153_C.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>10106.6_2889_P.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>15504.3_3950_M.</t>
+          <t>4077.1_1454_S.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>3089.9_1508_C.</t>
+          <t>9507.9_2851_M.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>5085.1_1840_G.</t>
+          <t>3580.9_1198_S.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>5235.4_1766_P.</t>
+          <t>9791.4_3527_G.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>5004.0_2103_C.</t>
+          <t>2186.2_736_G.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>5028.5_4433_S.</t>
+          <t>6012.6_2984_P.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>7114.0_2850_S.</t>
+          <t>9209.1_3141_E.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>5296.8_1844_P.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>15194.4_3911_S.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>5621.6_2375_P.</t>
+          <t>9012.4_2700_M.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>7985.2_2173_P.</t>
+          <t>18665.3_4638_S.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>5008.2_1646_A.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10503.6_3278_M.</t>
+          <t>10174.3_3680_S.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>4896.8_2251_L.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>2060.0_802_S.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>6046.5_3239_S.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>8187.1_2322_M.</t>
+          <t>2011.7_731_S.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>9007.1_3080_P.</t>
+          <t>6084.1_2156_V.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>4000.6_1659_S.</t>
+          <t>1011.0_396_L.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>37036.6_17889_F.</t>
+          <t>14117.6_3844_M.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>1027.7_364_S.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>10012.3_3067_S.</t>
+          <t>6833.7_2100_G.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>5238.0_2781_F.</t>
+          <t>7312.2_2446_G.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>4705.5_1241_G.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>6951.4_2856_S.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>5579.8_1990_E.</t>
+          <t>5119.6_3153_M.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>5008.0_2402_P.</t>
+          <t>10106.6_3354_M.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>5287.4_1835_V.</t>
+          <t>8442.5_3038_G.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2186.2_736_G.</t>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>4768.0_1875_L.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>8481.2_2463_🔋.</t>
+          <t>3010.0_1685_A.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>6536.2_2241_P.</t>
+          <t>5365.6_2437_C.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>5005.8_1527_S.</t>
+          <t>7992.7_2506_F.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>5580.0_2471_A.</t>
+          <t>2880.9_1210_L.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1443.0_851_A.</t>
+          <t>8187.1_2322_M.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>5256.5_1535_S.</t>
+          <t>10533.4_4020_F.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>7230.5_2794_V.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>6903.6_2566_G.</t>
+          <t>3757.2_1716_A.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>531.0_343_A.</t>
+          <t>5033.4_1976_M.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>9012.4_2700_M.</t>
+          <t>4028.8_1699_L.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>5085.1_1840_G.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>7598.7_2799_S.</t>
+          <t>10016.9_3028_M.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>6012.6_2984_P.</t>
+          <t>7006.7_5717_S.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>10030.0_3041_G.</t>
+          <t>4735.2_997_S.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>8132.9_2716_S.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2504.7_703_🔋.</t>
+          <t>3089.9_1508_C.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>9029.6_4595_P.</t>
+          <t>14014.7_3537_S.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>5022.5_1222_P.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>7576.8_2823_P.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>3412.3_1947_C.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>6011.5_2408_A.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2783.5_952_S.</t>
+          <t>56121.5_25636_F.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>4814.5_1705_🔋.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>15194.4_3911_S.</t>
+          <t>7015.4_2141_T.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>10001.9_4466_P.</t>
+          <t>5238.0_2781_F.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>4830.1_2569_C.</t>
+          <t>208.3_85_P.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2735.8_959_S.</t>
+          <t>5086.0_1810_G.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>6038.2_2121_P.</t>
+          <t>17012.6_5869_T.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>7598.7_2799_S.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>3735.9_1928_V.</t>
+          <t>2051.8_860_S.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>3757.2_1716_A.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>8481.2_2463_🔋.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>8008.0_2930_A.</t>
+          <t>5010.3_3392_P.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1027.7_364_S.</t>
+          <t>5724.1_3694_S.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>12524.7_3259_S.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>6818.2_2036_P.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>7012.1_3931_🔋.</t>
+          <t>4692.9_1546_P.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>10106.6_2889_P.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>4017.3_1883_C.</t>
+          <t>8120.9_2737_G.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>401.2_179_S.</t>
+          <t>12545.4_3039_S.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>1366.2_487_L.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>10016.9_3028_M.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>9029.6_4595_P.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>12521.4_4814_M.</t>
+          <t>8367.5_4269_C.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>13023.5_5156_L.</t>
+          <t>8253.0_2972_🔋.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>5005.4_2618_L.</t>
+          <t>2175.4_712_S.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>14014.7_3537_S.</t>
+          <t>4932.4_1545_E.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>15637.2_5789_G.</t>
+          <t>15186.5_3866_S.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>10012.1_3139_S.</t>
+          <t>8618.0_2344_P.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>9007.1_3080_P.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2880.9_1210_L.</t>
+          <t>6804.1_2088_P.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>3023.2_962_S.</t>
+          <t>5005.4_2618_L.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>7419.2_3469_F.</t>
+          <t>10012.3_3067_S.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>6038.2_2121_P.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>1002.7_460_S.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>7039.1_2754_S.</t>
+          <t>12524.7_3259_S.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>1366.2_487_L.</t>
+          <t>15637.2_5789_G.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>3412.3_1947_C.</t>
+          <t>5004.9_1790_A.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>5028.5_4433_S.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>6084.1_2156_V.</t>
+          <t>8008.0_2930_A.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>7576.8_2823_P.</t>
+          <t>8004.6_2357_G.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>8104.2_2652_M.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>8442.5_3038_G.</t>
+          <t>3005.2_1040_L.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>7992.7_2506_F.</t>
+          <t>15504.3_3950_M.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>4177.9_1557_T.</t>
+          <t>10030.0_3041_G.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>2305.1_940_S.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>7502.4_3467_P.</t>
+          <t>5242.7_1657_S.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>7874.8_2223_M.</t>
+          <t>7985.2_2173_P.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>6007.1_3172_F.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>5904.3_2699_P.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>5451.1_1905_T.</t>
+          <t>6472.0_2501_S.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>18665.3_4638_S.</t>
+          <t>16397.3_4254_S.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>8396.0_2595_S.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>15186.5_3866_S.</t>
+          <t>5621.6_2375_P.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>7006.7_5717_S.</t>
+          <t>12006.9_5463_P.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>9209.1_3141_E.</t>
+          <t>7114.0_2850_S.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>5365.6_2437_C.</t>
+          <t>2047.9_924_L.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>5029.4_1585_P.</t>
+          <t>2504.7_703_🔋.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>4797.2_1541_G.</t>
+          <t>531.0_343_A.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>5029.4_1585_P.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>9756.3_2793_M.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2060.0_802_S.</t>
+          <t>2036.1_839_S.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>6011.5_2408_A.</t>
+          <t>6012.6_2984_F.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>5010.3_3392_P.</t>
+          <t>791.5_266_G.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>5010.3_1888_G.</t>
+          <t>10062.5_2886_M.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>657.7_273_S.</t>
+          <t>9555.5_5689_S.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>1002.7_460_S.</t>
+          <t>7039.1_2754_S.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>4932.4_1545_E.</t>
+          <t>21442.0_7959_F.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>5724.1_3694_S.</t>
+          <t>2735.8_959_S.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>8132.9_2716_S.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>5025.8_1214_P.</t>
+          <t>17003.0_7696_P.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>6536.2_2241_P.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>4821.0_1857_P.</t>
+          <t>5579.8_1990_E.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>5287.4_1835_V.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>10348.3_2647_S.</t>
+          <t>10012.1_3139_S.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>9555.5_5689_S.</t>
+          <t>5256.5_1535_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>5235.4_1766_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>1443.0_851_A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>4763.8_1720_P.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_500km_2026.xlsx
+++ b/Ranking_CNB_500km_2026.xlsx
@@ -454,12 +454,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>447,3 km</t>
+          <t>467,4 km</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>6.042 m</t>
+          <t>6.339 m</t>
         </is>
       </c>
     </row>
@@ -471,80 +471,80 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>376,3 km</t>
+          <t>394,4 km</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>5.096 m</t>
+          <t>5.301 m</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mateus  M.</t>
+          <t>Hortência  S.</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>181,2 km</t>
+          <t>194,7 km</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.341 m</t>
+          <t>1.602 m</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Hortência  S.</t>
+          <t>Mateus  M.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>180,6 km</t>
+          <t>181,2 km</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.471 m</t>
+          <t>2.341 m</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Fernanda G.</t>
+          <t>Jéssica P.</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>166,2 km</t>
+          <t>174,8 km</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.973 m</t>
+          <t>1.675 m</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Jéssica P.</t>
+          <t>Fernanda G.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>164,8 km</t>
+          <t>166,2 km</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.557 m</t>
+          <t>1.973 m</t>
         </is>
       </c>
     </row>
@@ -556,63 +556,63 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>131,9 km</t>
+          <t>143,9 km</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>882 m</t>
+          <t>980 m</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cassia C.</t>
+          <t>Gleydson G.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>125,5 km</t>
+          <t>133,9 km</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.569 m</t>
+          <t>890 m</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Gleydson G.</t>
+          <t>Cassia C.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>118,9 km</t>
+          <t>125,5 km</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>798 m</t>
+          <t>1.569 m</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Fellipe T.</t>
+          <t>Jandson P.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>111,9 km</t>
+          <t>118,8 km</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>893 m</t>
+          <t>1.655 m</t>
         </is>
       </c>
     </row>
@@ -624,80 +624,80 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>107,6 km</t>
+          <t>117,2 km</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.185 m</t>
+          <t>1.291 m</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Jandson P.</t>
+          <t>Fellipe T.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>97,7 km</t>
+          <t>111,9 km</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.352 m</t>
+          <t>893 m</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Duda X.</t>
+          <t>Naiane C.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>87,6 km</t>
+          <t>90,5 km</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.037 m</t>
+          <t>812 m</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Carlos 🔋.</t>
+          <t>Duda X.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>84,4 km</t>
+          <t>87,6 km</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.050 m</t>
+          <t>1.037 m</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Naiane C.</t>
+          <t>Carlos 🔋.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>82,0 km</t>
+          <t>84,4 km</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>711 m</t>
+          <t>1.050 m</t>
         </is>
       </c>
     </row>
@@ -755,68 +755,68 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Renato C.</t>
+          <t>Pierre P.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>36,2 km</t>
+          <t>40,7 km</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>440 m</t>
+          <t>446 m</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Pierre P.</t>
+          <t>Neydrielle V.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>34,8 km</t>
+          <t>36,2 km</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>372 m</t>
+          <t>193 m</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Alexsia A.</t>
+          <t>Renato C.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>29,0 km</t>
+          <t>36,2 km</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>351 m</t>
+          <t>440 m</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Neydrielle V.</t>
+          <t>Alexsia A.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>26,2 km</t>
+          <t>34,0 km</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>182 m</t>
+          <t>351 m</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A200"/>
+  <dimension ref="A1:A212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -963,1365 +963,1365 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5522.8_2716_V.</t>
+          <t>10106.6_2889_P.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>2504.7_703_🔋.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>7419.2_3469_F.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>7569.4_2477_V.</t>
+          <t>7012.1_3931_🔋.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6345.4_2376_S.</t>
+          <t>14117.6_3844_M.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>401.2_179_S.</t>
+          <t>7114.0_2850_S.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4000.6_1659_S.</t>
+          <t>10012.1_3139_S.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>6137.8_2406_L.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5004.5_1548_A.</t>
+          <t>17012.6_5869_T.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>8132.9_2716_S.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3798.9_1319_S.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>7874.8_2223_M.</t>
+          <t>5010.3_1888_G.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>10348.3_2647_S.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10001.9_4466_P.</t>
+          <t>12326.4_4833_S.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>5010.3_3392_P.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>657.7_273_S.</t>
+          <t>15637.2_5789_G.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10348.3_2647_S.</t>
+          <t>7992.7_2506_F.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>9012.4_2700_M.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>9006.5_3085_X.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3026.1_1490_A.</t>
+          <t>7985.2_2173_P.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>7012.1_3931_🔋.</t>
+          <t>5238.0_2781_F.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5004.0_2103_C.</t>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>9006.5_3085_X.</t>
+          <t>531.0_343_A.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>4017.3_1883_C.</t>
+          <t>5008.2_1646_A.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>21106.2_7925_P.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5025.8_1214_P.</t>
+          <t>4731.9_1407_T.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>5242.7_1657_S.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>5282.8_2392_C.</t>
+          <t>4797.2_1541_G.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5010.3_1888_G.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2783.5_952_S.</t>
+          <t>15504.3_3950_M.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5451.1_1905_T.</t>
+          <t>14119.3_5262_S.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5580.0_2471_A.</t>
+          <t>9639.7_4763_P.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3010.0_1424_A.</t>
+          <t>1443.0_851_A.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>7502.4_3467_P.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>26010.2_9812_F.</t>
+          <t>5282.8_2392_C.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3023.2_962_S.</t>
+          <t>5522.8_2716_V.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>4821.0_1857_P.</t>
+          <t>6038.2_2121_P.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>13023.5_5156_L.</t>
+          <t>3757.2_1716_A.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>12022.7_5417_L.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3735.9_1928_V.</t>
+          <t>3010.0_1685_A.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>5008.2_1646_A.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>4797.2_1541_G.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>4791.5_1524_E.</t>
+          <t>5029.4_1585_P.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>10030.0_3041_G.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>37036.6_17889_F.</t>
+          <t>401.2_179_S.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>6903.6_2566_G.</t>
+          <t>7419.2_3469_F.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>5382.2_2690_M.</t>
+          <t>15194.4_3911_S.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>8004.6_2357_G.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>10011.5_3070_S.</t>
+          <t>17003.0_7696_P.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>8218.3_2327_P.</t>
+          <t>37036.6_17889_F.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2002.2_938_P.</t>
+          <t>6472.0_2501_S.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>5008.0_2402_P.</t>
+          <t>12006.9_5463_P.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>4735.2_997_S.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>4830.1_2569_C.</t>
+          <t>9756.3_2793_M.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>5005.8_1527_S.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>16397.3_4254_S.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>4177.9_1557_T.</t>
+          <t>5004.5_1548_A.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>10503.6_3278_M.</t>
+          <t>15016.9_6221_G.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>2011.7_731_S.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>2783.5_952_S.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>5005.8_1527_S.</t>
+          <t>18102.7_4949_M.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>5100.0_2587_A.</t>
+          <t>7006.7_5717_S.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>4786.5_1898_P.</t>
+          <t>5579.8_1990_E.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>4932.4_1545_E.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>8351.7_4153_C.</t>
+          <t>3412.3_1947_C.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>3580.9_1198_S.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>6804.1_2088_P.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>9507.9_2851_M.</t>
+          <t>8253.0_2972_🔋.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>4814.5_1705_🔋.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>9791.4_3527_G.</t>
+          <t>4791.5_1524_E.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2186.2_736_G.</t>
+          <t>2051.8_860_S.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>6012.6_2984_P.</t>
+          <t>12545.4_3039_S.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>9209.1_3141_E.</t>
+          <t>4077.1_1454_S.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>5296.8_1844_P.</t>
+          <t>14014.7_3537_S.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>15194.4_3911_S.</t>
+          <t>21442.0_7959_F.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>9012.4_2700_M.</t>
+          <t>9555.5_5689_S.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>18665.3_4638_S.</t>
+          <t>5022.5_1222_P.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>3798.9_1319_S.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>6007.1_3172_F.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>4896.8_2251_L.</t>
+          <t>56121.5_25636_F.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2060.0_802_S.</t>
+          <t>13023.5_5156_L.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>4821.0_1857_P.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2011.7_731_S.</t>
+          <t>6012.6_2984_F.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>6084.1_2156_V.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>5365.6_2437_C.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>14117.6_3844_M.</t>
+          <t>3019.8_1453_F.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1027.7_364_S.</t>
+          <t>7569.4_2477_V.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>6833.7_2100_G.</t>
+          <t>3005.2_1040_L.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>7312.2_2446_G.</t>
+          <t>5621.6_2375_P.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>5382.2_2690_M.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>6951.4_2856_S.</t>
+          <t>2186.2_736_G.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>6012.6_2984_P.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>12524.7_3259_S.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>8442.5_3038_G.</t>
+          <t>10001.9_4466_P.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>7039.1_2754_S.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>10058.8_3483_F.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>4692.9_1546_P.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>3010.0_1685_A.</t>
+          <t>5004.9_1790_A.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>5365.6_2437_C.</t>
+          <t>7598.7_2799_S.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>7992.7_2506_F.</t>
+          <t>7576.8_2823_P.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2880.9_1210_L.</t>
+          <t>8218.3_2327_P.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>8187.1_2322_M.</t>
+          <t>7230.5_2794_V.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>10533.4_4020_F.</t>
+          <t>10016.9_3028_M.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>7230.5_2794_V.</t>
+          <t>6818.2_2036_P.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>3757.2_1716_A.</t>
+          <t>9562.8_3145_M.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>6046.5_3239_S.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>5033.4_1976_M.</t>
+          <t>9013.7_2337_M.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>4028.8_1699_L.</t>
+          <t>10002.4_5136_P.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>5085.1_1840_G.</t>
+          <t>10062.5_2886_M.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>10016.9_3028_M.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>7006.7_5717_S.</t>
+          <t>10503.6_3278_M.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>4735.2_997_S.</t>
+          <t>26010.2_9812_F.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>8132.9_2716_S.</t>
+          <t>4891.7_1690_F.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>3089.9_1508_C.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>14014.7_3537_S.</t>
+          <t>8187.1_2322_M.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>5022.5_1222_P.</t>
+          <t>5086.0_1810_G.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>7576.8_2823_P.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>3412.3_1947_C.</t>
+          <t>7874.8_2223_M.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>6011.5_2408_A.</t>
+          <t>7015.4_2141_T.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>56121.5_25636_F.</t>
+          <t>6536.2_2241_P.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>8506.3_4050_C.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>6345.4_2376_S.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>5238.0_2781_F.</t>
+          <t>2047.9_924_L.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>4830.1_2569_C.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>5086.0_1810_G.</t>
+          <t>18665.3_4638_S.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>5085.1_1840_G.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>7598.7_2799_S.</t>
+          <t>10012.3_3067_S.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>8120.9_2737_G.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>4768.0_1875_L.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>8481.2_2463_🔋.</t>
+          <t>6833.7_2100_G.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>5010.3_3392_P.</t>
+          <t>6951.4_2856_S.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>5724.1_3694_S.</t>
+          <t>2060.0_802_S.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>1366.2_487_L.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>6818.2_2036_P.</t>
+          <t>8481.2_2463_🔋.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>4692.9_1546_P.</t>
+          <t>8396.0_2595_S.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>10106.6_2889_P.</t>
+          <t>2735.8_959_S.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>208.3_85_P.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>12545.4_3039_S.</t>
+          <t>5025.8_1214_P.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1366.2_487_L.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>8442.5_3038_G.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>9029.6_4595_P.</t>
+          <t>8367.5_4269_C.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>8367.5_4269_C.</t>
+          <t>9007.1_3080_P.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>1002.7_460_S.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>3023.2_962_S.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>4932.4_1545_E.</t>
+          <t>5287.4_1835_V.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>15186.5_3866_S.</t>
+          <t>5451.1_1905_T.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>8618.0_2344_P.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>9007.1_3080_P.</t>
+          <t>7502.4_3467_P.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>6804.1_2088_P.</t>
+          <t>657.7_273_S.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>5005.4_2618_L.</t>
+          <t>1027.7_364_S.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>10012.3_3067_S.</t>
+          <t>3614.8_970_🔋.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>6038.2_2121_P.</t>
+          <t>5100.0_2587_A.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>1002.7_460_S.</t>
+          <t>9507.9_2851_M.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>12524.7_3259_S.</t>
+          <t>2880.9_1210_L.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>15637.2_5789_G.</t>
+          <t>8008.0_2930_A.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>5004.9_1790_A.</t>
+          <t>5904.3_2699_P.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>5028.5_4433_S.</t>
+          <t>10533.4_4020_F.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>8008.0_2930_A.</t>
+          <t>7312.2_2446_G.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>8004.6_2357_G.</t>
+          <t>5014.3_1731_F.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>4017.3_1883_C.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>10174.3_3680_S.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>15504.3_3950_M.</t>
+          <t>4177.9_1557_T.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>10030.0_3041_G.</t>
+          <t>2002.2_938_P.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>3026.1_1490_A.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>10008.1_2966_M.</t>
+          <t>5119.6_3153_M.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>5242.7_1657_S.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>7985.2_2173_P.</t>
+          <t>2305.1_940_S.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>6007.1_3172_F.</t>
+          <t>2036.1_839_S.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>5904.3_2699_P.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>2175.4_712_S.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>16397.3_4254_S.</t>
+          <t>5869.6_2613_P.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>8396.0_2595_S.</t>
+          <t>3735.9_1928_V.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>5621.6_2375_P.</t>
+          <t>5580.0_2471_A.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>1011.0_396_L.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>7114.0_2850_S.</t>
+          <t>4896.8_2251_L.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2047.9_924_L.</t>
+          <t>15186.5_3866_S.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2504.7_703_🔋.</t>
+          <t>4705.5_1241_G.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>531.0_343_A.</t>
+          <t>5235.4_1766_P.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>5029.4_1585_P.</t>
+          <t>10007.4_3588_V.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>9756.3_2793_M.</t>
+          <t>5004.0_2103_C.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2036.1_839_S.</t>
+          <t>3089.9_1508_C.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>4000.6_1659_S.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>791.5_266_G.</t>
+          <t>6011.5_2408_A.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>8104.2_2652_M.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>9555.5_5689_S.</t>
+          <t>5008.0_2402_P.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>7039.1_2754_S.</t>
+          <t>4028.8_1699_L.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>10011.5_3070_S.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2735.8_959_S.</t>
+          <t>5724.1_3694_S.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>12521.4_4814_M.</t>
+          <t>6084.1_2156_V.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>17003.0_7696_P.</t>
+          <t>5033.4_1976_M.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>6536.2_2241_P.</t>
+          <t>9209.1_3141_E.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>5579.8_1990_E.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>5287.4_1835_V.</t>
+          <t>9791.4_3527_G.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>10012.1_3139_S.</t>
+          <t>4763.8_1720_P.</t>
         </is>
       </c>
     </row>
@@ -2335,21 +2335,105 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>5235.4_1766_P.</t>
+          <t>20105.6_7766_F.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>1443.0_851_A.</t>
+          <t>8351.7_4153_C.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>9029.6_4595_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>5296.8_1844_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>8618.0_2344_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>5028.5_4433_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>3010.0_1424_A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>6903.6_2566_G.</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>1884.9_866_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>5013.9_1673_A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>3079.4_1056_L.</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>10106.6_3354_M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>791.5_266_G.</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>5005.4_2618_L.</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>4786.5_1898_P.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_500km_2026.xlsx
+++ b/Ranking_CNB_500km_2026.xlsx
@@ -471,12 +471,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>394,5 km</t>
+          <t>400,5 km</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>5.301 m</t>
+          <t>5.383 m</t>
         </is>
       </c>
     </row>
@@ -488,12 +488,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>194,7 km</t>
+          <t>203,1 km</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.602 m</t>
+          <t>1.643 m</t>
         </is>
       </c>
     </row>
@@ -607,12 +607,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>118,8 km</t>
+          <t>123,8 km</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.655 m</t>
+          <t>1.703 m</t>
         </is>
       </c>
     </row>
@@ -624,12 +624,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>117,2 km</t>
+          <t>123,8 km</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.291 m</t>
+          <t>1.372 m</t>
         </is>
       </c>
     </row>
@@ -692,12 +692,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>90,5 km</t>
+          <t>95,5 km</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>812 m</t>
+          <t>857 m</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A212"/>
+  <dimension ref="A1:A219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -946,1477 +946,1526 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>7015.4_2141_T.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5282.8_2392_C.</t>
+          <t>7985.2_2173_P.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>10062.5_2886_M.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>15637.2_5789_G.</t>
+          <t>4791.5_1524_E.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>7006.7_5717_S.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1002.7_460_S.</t>
+          <t>4028.8_1699_L.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>17003.0_7696_P.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3798.9_1319_S.</t>
+          <t>14014.7_3537_S.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>1011.0_396_L.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4177.9_1557_T.</t>
+          <t>9013.7_2337_M.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5086.0_1810_G.</t>
+          <t>12545.4_3039_S.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>5522.8_2716_V.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>13023.5_5156_L.</t>
+          <t>1366.2_487_L.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>2186.2_736_G.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5580.0_2471_A.</t>
+          <t>5724.1_3694_S.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5022.5_1222_P.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6011.5_2408_A.</t>
+          <t>5869.6_2613_P.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>12022.7_5417_L.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6833.7_2100_G.</t>
+          <t>16397.3_4254_S.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5010.3_3392_P.</t>
+          <t>5004.0_2103_C.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>2504.7_703_🔋.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>5027.8_1361_P.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2735.8_959_S.</t>
+          <t>3010.0_1685_A.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5522.8_2716_V.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>56121.5_25636_F.</t>
+          <t>8218.3_2327_P.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5100.0_2587_A.</t>
+          <t>4705.5_1241_G.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3735.9_1928_V.</t>
+          <t>10007.4_3588_V.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1443.0_851_A.</t>
+          <t>2051.8_860_S.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>5904.3_2699_P.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3757.2_1716_A.</t>
+          <t>12326.4_4833_S.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>14117.6_3844_M.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10012.1_3139_S.</t>
+          <t>5119.6_3153_M.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>8506.3_4050_C.</t>
+          <t>2002.2_938_P.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>7598.7_2799_S.</t>
+          <t>7114.0_2850_S.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>12022.7_5417_L.</t>
+          <t>8618.0_2344_P.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>9791.4_3527_G.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>8442.5_3038_G.</t>
+          <t>10106.6_2889_P.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2036.1_839_S.</t>
+          <t>5010.3_1888_G.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>4000.6_1659_S.</t>
+          <t>3412.3_1947_C.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>4028.8_1699_L.</t>
+          <t>13023.5_5156_L.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>15504.3_3950_M.</t>
+          <t>3023.2_962_S.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>5010.3_1888_G.</t>
+          <t>9756.3_2793_M.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>5365.6_2437_C.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>6038.2_2121_P.</t>
+          <t>7230.5_2794_V.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>8481.2_2463_🔋.</t>
+          <t>4763.8_1720_P.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>8351.7_4153_C.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>9639.7_4763_P.</t>
+          <t>6011.8_1873_M.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>5235.4_1766_P.</t>
+          <t>9012.4_2700_M.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>15194.4_3911_S.</t>
+          <t>6137.8_2406_L.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>8351.7_4153_C.</t>
+          <t>5579.8_1990_E.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>7012.1_3931_🔋.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>21106.2_7925_P.</t>
+          <t>4797.2_1541_G.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>15016.9_6221_G.</t>
+          <t>3757.2_1716_A.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>14014.7_3537_S.</t>
+          <t>5256.5_1535_S.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>531.0_343_A.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>5004.5_1548_A.</t>
+          <t>5282.8_2392_C.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>4932.4_1545_E.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2783.5_952_S.</t>
+          <t>2011.7_731_S.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>401.2_179_S.</t>
+          <t>9209.1_3141_E.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>4017.3_1883_C.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>6011.5_2408_A.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>5005.8_1527_S.</t>
+          <t>5029.4_1585_P.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>7230.5_2794_V.</t>
+          <t>14117.6_3844_M.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>4821.0_1857_P.</t>
+          <t>4077.1_1454_S.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>5025.8_1214_P.</t>
+          <t>3026.1_1490_A.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>5579.8_1990_E.</t>
+          <t>26010.2_9812_F.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>4797.2_1541_G.</t>
+          <t>4830.1_2569_C.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>5004.0_2103_C.</t>
+          <t>2880.9_1210_L.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>5013.9_1673_A.</t>
+          <t>7992.7_2506_F.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>16397.3_4254_S.</t>
+          <t>10106.6_3354_M.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>14119.3_5262_S.</t>
+          <t>5086.0_1810_G.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>6804.1_2088_P.</t>
+          <t>8481.2_2463_🔋.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>8008.0_2930_A.</t>
+          <t>5451.1_1905_T.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10533.4_4020_F.</t>
+          <t>10348.3_2647_S.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2002.2_938_P.</t>
+          <t>5382.2_2690_M.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2060.0_802_S.</t>
+          <t>5287.4_1835_V.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>3010.0_1424_A.</t>
+          <t>5004.5_1548_A.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>9012.4_2700_M.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>657.7_273_S.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>5382.2_2690_M.</t>
+          <t>12524.7_3259_S.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>6084.1_2156_V.</t>
+          <t>5100.0_2587_A.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>1027.7_364_S.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10012.3_3067_S.</t>
+          <t>6038.2_2121_P.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>3089.9_1508_C.</t>
+          <t>15186.5_3866_S.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>8396.0_2595_S.</t>
+          <t>12006.9_5463_P.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>4786.5_1898_P.</t>
+          <t>4177.9_1557_T.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>4932.4_1545_E.</t>
+          <t>10012.3_3067_S.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>3005.2_1040_L.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>5287.4_1835_V.</t>
+          <t>8104.2_2652_M.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>2185.4_792_S.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>15186.5_3866_S.</t>
+          <t>8396.0_2595_S.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>10058.8_3483_F.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>7985.2_2173_P.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>3010.0_1685_A.</t>
+          <t>4000.6_1659_S.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>7874.8_2223_M.</t>
+          <t>2735.8_959_S.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>6345.4_2376_S.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>5451.1_1905_T.</t>
+          <t>5005.4_2618_L.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>7992.7_2506_F.</t>
+          <t>5008.2_1646_A.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>10030.0_3041_G.</t>
+          <t>3798.9_1319_S.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>8187.1_2322_M.</t>
+          <t>1443.0_851_A.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>10011.5_3070_S.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2047.9_924_L.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>10348.3_2647_S.</t>
+          <t>8004.6_2357_G.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>7114.0_2850_S.</t>
+          <t>9006.5_3085_X.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>5904.3_2699_P.</t>
+          <t>9007.1_3080_P.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>4791.5_1524_E.</t>
+          <t>401.2_179_S.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>26010.2_9812_F.</t>
+          <t>7598.7_2799_S.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>17012.6_5869_T.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>10016.9_3028_M.</t>
+          <t>5005.8_1527_S.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>4896.8_2251_L.</t>
+          <t>3010.0_1424_A.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>3412.3_1947_C.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>5028.5_4433_S.</t>
+          <t>6472.0_2501_S.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>8367.5_4269_C.</t>
+          <t>9507.9_2851_M.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>2060.0_802_S.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>37036.6_17889_F.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>1114.9_359_S.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>9639.7_4763_P.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>5621.6_2375_P.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>8218.3_2327_P.</t>
+          <t>5580.0_2471_A.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2504.7_703_🔋.</t>
+          <t>8253.0_2972_🔋.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>12521.4_4814_M.</t>
+          <t>8442.5_3038_G.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>5724.1_3694_S.</t>
+          <t>6084.1_2156_V.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>18665.3_4638_S.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>5238.0_2781_F.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>10002.4_5136_P.</t>
+          <t>56121.5_25636_F.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>2305.1_940_S.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>9507.9_2851_M.</t>
+          <t>6007.1_3172_F.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>9029.6_4595_P.</t>
+          <t>2047.9_924_L.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>5033.4_1976_M.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>5008.2_1646_A.</t>
+          <t>5013.9_1673_A.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>3089.9_1508_C.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>5256.5_1535_S.</t>
+          <t>5235.4_1766_P.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>6345.4_2376_S.</t>
+          <t>3735.9_1928_V.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>6007.1_3172_F.</t>
+          <t>208.3_85_P.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>2175.4_712_S.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>10001.9_4466_P.</t>
+          <t>6012.6_2984_F.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>37036.6_17889_F.</t>
+          <t>7012.1_3931_🔋.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>5365.6_2437_C.</t>
+          <t>21106.2_7925_P.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>9555.5_5689_S.</t>
+          <t>7502.4_3467_P.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>4830.1_2569_C.</t>
+          <t>6536.2_2241_P.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>18665.3_4638_S.</t>
+          <t>7569.4_2477_V.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>18102.7_4949_M.</t>
+          <t>7576.8_2823_P.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>9756.3_2793_M.</t>
+          <t>5022.5_1222_P.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>20105.6_7766_F.</t>
+          <t>5025.8_1214_P.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>8132.9_2716_S.</t>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>10011.5_3070_S.</t>
+          <t>5072.4_1931_S.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>5005.4_2618_L.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>7874.8_2223_M.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>8618.0_2344_P.</t>
+          <t>5621.6_2375_P.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>5029.4_1585_P.</t>
+          <t>8187.1_2322_M.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>5008.0_2402_P.</t>
+          <t>1884.9_866_S.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>17003.0_7696_P.</t>
+          <t>5014.3_1731_F.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>3023.2_962_S.</t>
+          <t>5010.3_3392_P.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>4735.2_997_S.</t>
+          <t>9029.6_4595_P.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>5296.8_1844_P.</t>
+          <t>4731.9_1407_T.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>657.7_273_S.</t>
+          <t>5085.1_1840_G.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>6012.6_2984_P.</t>
+          <t>4692.9_1546_P.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>15016.9_6221_G.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>7419.2_3469_F.</t>
+          <t>10174.3_3680_S.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>5869.6_2613_P.</t>
+          <t>5242.7_1657_S.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>7576.8_2823_P.</t>
+          <t>7039.1_2754_S.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>9006.5_3085_X.</t>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>6951.4_2856_S.</t>
+          <t>4814.5_1705_🔋.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>6818.2_2036_P.</t>
+          <t>4891.7_1690_F.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>6951.4_2856_S.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>5242.7_1657_S.</t>
+          <t>15504.3_3950_M.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>12524.7_3259_S.</t>
+          <t>6620.4_2477_P.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>7039.1_2754_S.</t>
+          <t>7312.2_2446_G.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>531.0_343_A.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>10007.4_3588_V.</t>
+          <t>10012.1_3139_S.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>5004.9_1790_A.</t>
+          <t>10016.9_3028_M.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>1366.2_487_L.</t>
+          <t>4735.2_997_S.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>9007.1_3080_P.</t>
+          <t>14119.3_5262_S.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>15194.4_3911_S.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>9209.1_3141_E.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2880.9_1210_L.</t>
+          <t>1002.7_460_S.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>6833.7_2100_G.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>4692.9_1546_P.</t>
+          <t>10001.9_4466_P.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>4768.0_1875_L.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>7502.4_3467_P.</t>
+          <t>21442.0_7959_F.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>3026.1_1490_A.</t>
+          <t>3580.9_1198_S.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>5008.0_2402_P.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2011.7_731_S.</t>
+          <t>6903.6_2566_G.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>4017.3_1883_C.</t>
+          <t>4821.0_1857_P.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>10533.4_4020_F.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>5004.9_1790_A.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>5085.1_1840_G.</t>
+          <t>5028.5_4433_S.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>10503.6_3278_M.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>5033.4_1976_M.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>3019.8_1453_F.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>10008.1_2966_M.</t>
+          <t>10002.4_5136_P.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>15637.2_5789_G.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>6536.2_2241_P.</t>
+          <t>4786.5_1898_P.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>9791.4_3527_G.</t>
+          <t>10030.0_3041_G.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>8004.6_2357_G.</t>
+          <t>2783.5_952_S.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>18102.7_4949_M.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>12545.4_3039_S.</t>
+          <t>791.5_266_G.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>791.5_266_G.</t>
+          <t>9555.5_5689_S.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>7569.4_2477_V.</t>
+          <t>20105.6_7766_F.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>7312.2_2446_G.</t>
+          <t>8506.3_4050_C.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>5238.0_2781_F.</t>
+          <t>5296.8_1844_P.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>10503.6_3278_M.</t>
+          <t>6818.2_2036_P.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>6903.6_2566_G.</t>
+          <t>5040.0_2514_C.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>1027.7_364_S.</t>
+          <t>8132.9_2716_S.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>6804.1_2088_P.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2186.2_736_G.</t>
+          <t>4896.8_2251_L.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>10106.6_2889_P.</t>
+          <t>3614.8_970_🔋.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>7006.7_5717_S.</t>
+          <t>2036.1_839_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>8008.0_2930_A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>8120.9_2737_G.</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>6012.6_2984_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>8367.5_4269_C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>9562.8_3145_M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>7419.2_3469_F.</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>6046.5_3239_S.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_500km_2026.xlsx
+++ b/Ranking_CNB_500km_2026.xlsx
@@ -454,12 +454,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>467,4 km</t>
+          <t>489,7 km</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>6.339 m</t>
+          <t>6.968 m</t>
         </is>
       </c>
     </row>
@@ -471,12 +471,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>400,5 km</t>
+          <t>410,5 km</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>5.383 m</t>
+          <t>5.506 m</t>
         </is>
       </c>
     </row>
@@ -539,12 +539,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>166,2 km</t>
+          <t>172,0 km</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.973 m</t>
+          <t>2.045 m</t>
         </is>
       </c>
     </row>
@@ -556,12 +556,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>143,9 km</t>
+          <t>150,9 km</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>980 m</t>
+          <t>1.062 m</t>
         </is>
       </c>
     </row>
@@ -590,36 +590,36 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>125,5 km</t>
+          <t>132,9 km</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.569 m</t>
+          <t>1.669 m</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Jandson P.</t>
+          <t>Mateus P.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>123,8 km</t>
+          <t>129,8 km</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.703 m</t>
+          <t>1.443 m</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Mateus P.</t>
+          <t>Jandson P.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -629,7 +629,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.372 m</t>
+          <t>1.703 m</t>
         </is>
       </c>
     </row>
@@ -658,12 +658,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>104,2 km</t>
+          <t>110,2 km</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.138 m</t>
+          <t>1.208 m</t>
         </is>
       </c>
     </row>
@@ -760,12 +760,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>44,4 km</t>
+          <t>47,4 km</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>427 m</t>
+          <t>443 m</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A219"/>
+  <dimension ref="A1:A227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -946,686 +946,686 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>2011.7_731_S.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>7985.2_2173_P.</t>
+          <t>8253.0_2972_🔋.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>7022.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4791.5_1524_E.</t>
+          <t>4705.5_1241_G.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>7006.7_5717_S.</t>
+          <t>4731.9_1407_T.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4028.8_1699_L.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>17003.0_7696_P.</t>
+          <t>2051.8_860_S.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>6951.4_2856_S.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>14014.7_3537_S.</t>
+          <t>4763.8_1720_P.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>2036.1_839_S.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>18665.3_4638_S.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>12545.4_3039_S.</t>
+          <t>791.5_266_G.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5522.8_2716_V.</t>
+          <t>8004.6_2357_G.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1366.2_487_L.</t>
+          <t>7419.2_3469_F.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2186.2_736_G.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5724.1_3694_S.</t>
+          <t>3010.0_1685_A.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>6038.2_2121_P.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5869.6_2613_P.</t>
+          <t>1443.0_851_A.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>12022.7_5417_L.</t>
+          <t>9555.5_5689_S.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>16397.3_4254_S.</t>
+          <t>10012.1_3139_S.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5004.0_2103_C.</t>
+          <t>8104.2_2652_M.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2504.7_703_🔋.</t>
+          <t>5004.5_1548_A.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5027.8_1361_P.</t>
+          <t>5028.5_4433_S.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3010.0_1685_A.</t>
+          <t>10002.4_5136_P.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>4028.8_1699_L.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>8218.3_2327_P.</t>
+          <t>6345.4_2376_S.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>9791.4_3527_G.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10007.4_3588_V.</t>
+          <t>15504.3_3950_M.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>21442.0_7959_F.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5904.3_2699_P.</t>
+          <t>6818.2_2036_P.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>5027.8_1361_P.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>5119.6_3153_M.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>14117.6_3844_M.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2002.2_938_P.</t>
+          <t>4735.2_997_S.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>7114.0_2850_S.</t>
+          <t>1027.7_364_S.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>8618.0_2344_P.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>9791.4_3527_G.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10106.6_2889_P.</t>
+          <t>9013.7_2337_M.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>5010.3_1888_G.</t>
+          <t>9639.7_4763_P.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3412.3_1947_C.</t>
+          <t>2047.9_924_L.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>13023.5_5156_L.</t>
+          <t>2186.2_736_G.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>3023.2_962_S.</t>
+          <t>15186.5_3866_S.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>9756.3_2793_M.</t>
+          <t>3735.9_1928_V.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>5365.6_2437_C.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>7230.5_2794_V.</t>
+          <t>5904.3_2699_P.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>12326.4_4833_S.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>8351.7_4153_C.</t>
+          <t>5100.0_2587_A.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>6011.8_1873_M.</t>
+          <t>4692.9_1546_P.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>9012.4_2700_M.</t>
+          <t>4077.1_1454_S.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>5040.0_2514_C.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>5579.8_1990_E.</t>
+          <t>4896.8_2251_L.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>10058.8_3483_F.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>4797.2_1541_G.</t>
+          <t>10062.5_2886_M.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>3757.2_1716_A.</t>
+          <t>1366.2_487_L.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>5256.5_1535_S.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>531.0_343_A.</t>
+          <t>17012.6_5869_T.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>5282.8_2392_C.</t>
+          <t>9562.8_3145_M.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>4932.4_1545_E.</t>
+          <t>4821.0_1857_P.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2011.7_731_S.</t>
+          <t>5242.7_1657_S.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>9209.1_3141_E.</t>
+          <t>8367.5_4269_C.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>4017.3_1883_C.</t>
+          <t>1011.0_396_L.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>6011.5_2408_A.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>5029.4_1585_P.</t>
+          <t>5004.9_1790_A.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>14117.6_3844_M.</t>
+          <t>6011.5_2408_A.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>9507.9_2851_M.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>3026.1_1490_A.</t>
+          <t>5010.3_3392_P.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>26010.2_9812_F.</t>
+          <t>3026.1_1490_A.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>4830.1_2569_C.</t>
+          <t>4791.5_1524_E.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2880.9_1210_L.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>7992.7_2506_F.</t>
+          <t>7312.2_2446_G.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>14119.3_5262_S.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>5086.0_1810_G.</t>
+          <t>9012.4_2700_M.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>8481.2_2463_🔋.</t>
+          <t>5282.8_2392_C.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>5451.1_1905_T.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10348.3_2647_S.</t>
+          <t>2002.2_938_P.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>5382.2_2690_M.</t>
+          <t>9007.1_3080_P.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>5287.4_1835_V.</t>
+          <t>8132.9_2716_S.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>5004.5_1548_A.</t>
+          <t>10533.4_4020_F.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>5008.2_1646_A.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>5022.5_1222_P.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>657.7_273_S.</t>
+          <t>12545.4_3039_S.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>12524.7_3259_S.</t>
+          <t>5451.1_1905_T.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>5100.0_2587_A.</t>
+          <t>6833.7_2100_G.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1027.7_364_S.</t>
+          <t>6010.6_2144_A.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>6038.2_2121_P.</t>
+          <t>2783.5_952_S.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>15186.5_3866_S.</t>
+          <t>21106.2_7925_P.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>10012.3_3067_S.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>4177.9_1557_T.</t>
+          <t>13023.5_5156_L.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>10012.3_3067_S.</t>
+          <t>5008.0_2402_P.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>7576.8_2823_P.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>531.0_343_A.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2185.4_792_S.</t>
+          <t>10106.6_3354_M.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>8396.0_2595_S.</t>
+          <t>3010.0_1289_A.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>10030.0_3041_G.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>4000.6_1659_S.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>4000.6_1659_S.</t>
+          <t>10174.3_3680_S.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2735.8_959_S.</t>
+          <t>7598.7_2799_S.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>6345.4_2376_S.</t>
+          <t>10106.6_2889_P.</t>
         </is>
       </c>
     </row>
@@ -1639,350 +1639,350 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>5008.2_1646_A.</t>
+          <t>3757.2_1716_A.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>3798.9_1319_S.</t>
+          <t>3089.9_1508_C.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1443.0_851_A.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>10011.5_3070_S.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>5580.0_2471_A.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>8004.6_2357_G.</t>
+          <t>5382.2_2690_M.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>9006.5_3085_X.</t>
+          <t>8618.0_2344_P.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>9007.1_3080_P.</t>
+          <t>5025.8_1214_P.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>401.2_179_S.</t>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>7598.7_2799_S.</t>
+          <t>56121.5_25636_F.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>1884.9_866_S.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>5005.8_1527_S.</t>
+          <t>3580.9_1198_S.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>3010.0_1424_A.</t>
+          <t>6011.8_1873_M.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>10008.1_2966_M.</t>
+          <t>15637.2_5789_G.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>18102.7_4949_M.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>9507.9_2851_M.</t>
+          <t>20105.6_7766_F.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2060.0_802_S.</t>
+          <t>657.7_273_S.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>37036.6_17889_F.</t>
+          <t>7015.4_2141_T.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1114.9_359_S.</t>
+          <t>5522.8_2716_V.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>9639.7_4763_P.</t>
+          <t>7569.4_2477_V.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>8481.2_2463_🔋.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>5580.0_2471_A.</t>
+          <t>7985.2_2173_P.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>16397.3_4254_S.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>8442.5_3038_G.</t>
+          <t>6536.2_2241_P.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>6084.1_2156_V.</t>
+          <t>15194.4_3911_S.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>18665.3_4638_S.</t>
+          <t>5013.9_1673_A.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>5238.0_2781_F.</t>
+          <t>6012.6_2984_P.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>56121.5_25636_F.</t>
+          <t>5256.5_1535_S.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>6903.6_2566_G.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>6007.1_3172_F.</t>
+          <t>8506.3_4050_C.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2047.9_924_L.</t>
+          <t>5869.6_2613_P.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>5033.4_1976_M.</t>
+          <t>8396.0_2595_S.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>5013.9_1673_A.</t>
+          <t>3412.3_1947_C.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>3089.9_1508_C.</t>
+          <t>10011.5_3070_S.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>5235.4_1766_P.</t>
+          <t>6137.8_2406_L.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>3735.9_1928_V.</t>
+          <t>4177.9_1557_T.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>2175.4_712_S.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>4830.1_2569_C.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>12006.9_5463_P.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>7012.1_3931_🔋.</t>
+          <t>6620.4_2477_P.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>21106.2_7925_P.</t>
+          <t>12524.7_3259_S.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>7502.4_3467_P.</t>
+          <t>10348.3_2647_S.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>6536.2_2241_P.</t>
+          <t>8218.3_2327_P.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>7569.4_2477_V.</t>
+          <t>3005.2_1040_L.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>7576.8_2823_P.</t>
+          <t>7230.5_2794_V.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>5022.5_1222_P.</t>
+          <t>3798.9_1319_S.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>5025.8_1214_P.</t>
+          <t>5621.6_2375_P.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>5579.8_1990_E.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>5072.4_1931_S.</t>
+          <t>6472.0_2501_S.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>12022.7_5417_L.</t>
         </is>
       </c>
     </row>
@@ -1996,63 +1996,63 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>5621.6_2375_P.</t>
+          <t>5014.3_1731_F.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>8187.1_2322_M.</t>
+          <t>4768.0_1875_L.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>2185.4_792_S.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>7012.1_3931_🔋.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>5010.3_3392_P.</t>
+          <t>3023.2_962_S.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>9029.6_4595_P.</t>
+          <t>4786.5_1898_P.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>4891.7_1690_F.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>5085.1_1840_G.</t>
+          <t>5072.4_1931_S.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>4692.9_1546_P.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
@@ -2066,119 +2066,119 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>5086.0_1810_G.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>5242.7_1657_S.</t>
+          <t>7114.0_2850_S.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>7039.1_2754_S.</t>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>26010.2_9812_F.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>10001.9_4466_P.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>1114.9_359_S.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>6951.4_2856_S.</t>
+          <t>4797.2_1541_G.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>15504.3_3950_M.</t>
+          <t>8187.1_2322_M.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>6620.4_2477_P.</t>
+          <t>9209.1_3141_E.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>7312.2_2446_G.</t>
+          <t>6007.1_3172_F.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>2735.8_959_S.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>10012.1_3139_S.</t>
+          <t>7006.7_5717_S.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>10016.9_3028_M.</t>
+          <t>7502.4_3467_P.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>4735.2_997_S.</t>
+          <t>5029.4_1585_P.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>14119.3_5262_S.</t>
+          <t>17003.0_7696_P.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>15194.4_3911_S.</t>
+          <t>8120.9_2737_G.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>6006.6_2009_P.</t>
         </is>
       </c>
     </row>
@@ -2192,280 +2192,336 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>6833.7_2100_G.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>10001.9_4466_P.</t>
+          <t>10503.6_3278_M.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>5365.6_2437_C.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>10007.4_3588_V.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>6046.5_3239_S.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>5008.0_2402_P.</t>
+          <t>2504.7_703_🔋.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>6903.6_2566_G.</t>
+          <t>6804.1_2088_P.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>4821.0_1857_P.</t>
+          <t>9756.3_2793_M.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>9006.5_3085_X.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>10533.4_4020_F.</t>
+          <t>37036.6_17889_F.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>5004.9_1790_A.</t>
+          <t>7992.7_2506_F.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>5028.5_4433_S.</t>
+          <t>6012.6_2984_F.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>10503.6_3278_M.</t>
+          <t>5235.4_1766_P.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>12521.4_4814_M.</t>
+          <t>10016.9_3028_M.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>8351.7_4153_C.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>10002.4_5136_P.</t>
+          <t>8442.5_3038_G.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>15637.2_5789_G.</t>
+          <t>5724.1_3694_S.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>4786.5_1898_P.</t>
+          <t>5085.1_1840_G.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>10030.0_3041_G.</t>
+          <t>5005.8_1527_S.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2783.5_952_S.</t>
+          <t>8008.0_2930_A.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>18102.7_4949_M.</t>
+          <t>4017.3_1883_C.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>791.5_266_G.</t>
+          <t>2060.0_802_S.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>9555.5_5689_S.</t>
+          <t>6084.1_2156_V.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>20105.6_7766_F.</t>
+          <t>5287.4_1835_V.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>8506.3_4050_C.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>5296.8_1844_P.</t>
+          <t>2305.1_940_S.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>6818.2_2036_P.</t>
+          <t>7039.1_2754_S.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>5040.0_2514_C.</t>
+          <t>3019.8_1453_F.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>8132.9_2716_S.</t>
+          <t>4932.4_1545_E.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>6804.1_2088_P.</t>
+          <t>3010.0_1424_A.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>4896.8_2251_L.</t>
+          <t>5033.4_1976_M.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>9029.6_4595_P.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2036.1_839_S.</t>
+          <t>4814.5_1705_🔋.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>8008.0_2930_A.</t>
+          <t>5004.0_2103_C.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>5010.3_1888_G.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>6012.6_2984_P.</t>
+          <t>2880.9_1210_L.</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>8367.5_4269_C.</t>
+          <t>401.2_179_S.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>7419.2_3469_F.</t>
+          <t>14014.7_3537_S.</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>22320.3_9183_F.</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>5296.8_1844_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>208.3_85_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>5770.8_2848_G.</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>10022.1_2875_M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>7420.2_4318_C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>5238.0_2781_F.</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>3614.8_970_🔋.</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_500km_2026.xlsx
+++ b/Ranking_CNB_500km_2026.xlsx
@@ -454,12 +454,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>489,7 km</t>
+          <t>510,8 km</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>6.968 m</t>
+          <t>7.229 m</t>
         </is>
       </c>
     </row>
@@ -471,12 +471,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>410,5 km</t>
+          <t>422,8 km</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>5.506 m</t>
+          <t>5.642 m</t>
         </is>
       </c>
     </row>
@@ -488,12 +488,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>203,1 km</t>
+          <t>207,0 km</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.643 m</t>
+          <t>1.717 m</t>
         </is>
       </c>
     </row>
@@ -568,68 +568,68 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Gleydson G.</t>
+          <t>Mateus P.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>133,9 km</t>
+          <t>145,0 km</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>890 m</t>
+          <t>1.612 m</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cassia C.</t>
+          <t>Gleydson G.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>132,9 km</t>
+          <t>133,9 km</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.669 m</t>
+          <t>890 m</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Mateus P.</t>
+          <t>Jandson P.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>129,8 km</t>
+          <t>133,8 km</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.443 m</t>
+          <t>1.848 m</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Jandson P.</t>
+          <t>Cassia C.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>123,8 km</t>
+          <t>132,9 km</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.703 m</t>
+          <t>1.669 m</t>
         </is>
       </c>
     </row>
@@ -675,12 +675,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>101,7 km</t>
+          <t>106,9 km</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>970 m</t>
+          <t>1.020 m</t>
         </is>
       </c>
     </row>
@@ -692,12 +692,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>95,5 km</t>
+          <t>100,5 km</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>857 m</t>
+          <t>903 m</t>
         </is>
       </c>
     </row>
@@ -777,12 +777,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>40,7 km</t>
+          <t>46,7 km</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>446 m</t>
+          <t>521 m</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A227"/>
+  <dimension ref="A1:A237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -946,378 +946,378 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2011.7_731_S.</t>
+          <t>5004.5_1548_A.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>7022.4_3008_L.</t>
+          <t>5522.8_2716_V.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>6536.2_2241_P.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>208.3_85_P.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>10007.4_3588_V.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>2036.1_839_S.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6951.4_2856_S.</t>
+          <t>9639.7_4763_P.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>8187.1_2322_M.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2036.1_839_S.</t>
+          <t>3614.8_970_🔋.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>18665.3_4638_S.</t>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>791.5_266_G.</t>
+          <t>3580.9_1198_S.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>8004.6_2357_G.</t>
+          <t>1114.9_359_S.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>7419.2_3469_F.</t>
+          <t>1011.0_396_L.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10008.1_2966_M.</t>
+          <t>7569.4_2477_V.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3010.0_1685_A.</t>
+          <t>5119.6_3153_M.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>6038.2_2121_P.</t>
+          <t>15016.9_6221_G.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1443.0_851_A.</t>
+          <t>7420.2_4318_C.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>9555.5_5689_S.</t>
+          <t>4763.8_1720_P.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10012.1_3139_S.</t>
+          <t>6833.7_2100_G.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>5029.4_1585_P.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5004.5_1548_A.</t>
+          <t>791.5_266_G.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5028.5_4433_S.</t>
+          <t>9012.4_2700_M.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10002.4_5136_P.</t>
+          <t>12326.4_4833_S.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>4028.8_1699_L.</t>
+          <t>6345.4_2376_S.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>6345.4_2376_S.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>9791.4_3527_G.</t>
+          <t>10002.4_5136_P.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>15504.3_3950_M.</t>
+          <t>9013.7_2337_M.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>5025.8_1214_P.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>6818.2_2036_P.</t>
+          <t>5013.9_1673_A.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5027.8_1361_P.</t>
+          <t>6472.0_2501_S.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>5086.0_1810_G.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>14117.6_3844_M.</t>
+          <t>5235.4_1766_P.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>4735.2_997_S.</t>
+          <t>14119.3_5262_S.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1027.7_364_S.</t>
+          <t>10016.9_3028_M.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>5004.9_1790_A.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>7312.2_2446_G.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>12006.9_5463_P.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>9639.7_4763_P.</t>
+          <t>5770.8_2848_G.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2047.9_924_L.</t>
+          <t>1002.7_460_S.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2186.2_736_G.</t>
+          <t>4017.3_1883_C.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>15186.5_3866_S.</t>
+          <t>5869.6_2613_P.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3735.9_1928_V.</t>
+          <t>4768.0_1875_L.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>5072.4_1931_S.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>5904.3_2699_P.</t>
+          <t>773.5_238_S.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>5008.2_1646_A.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>5100.0_2587_A.</t>
+          <t>6011.8_1873_M.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>4692.9_1546_P.</t>
+          <t>1884.9_866_S.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>10011.5_3070_S.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>5040.0_2514_C.</t>
+          <t>2002.2_938_P.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>4896.8_2251_L.</t>
+          <t>5242.7_1657_S.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>5040.0_2514_C.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1366.2_487_L.</t>
+          <t>5022.5_1222_P.</t>
         </is>
       </c>
     </row>
@@ -1331,77 +1331,77 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>20105.6_7766_F.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>5028.5_4433_S.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>4821.0_1857_P.</t>
+          <t>9029.6_4595_P.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>5242.7_1657_S.</t>
+          <t>7012.1_3931_🔋.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>8367.5_4269_C.</t>
+          <t>5008.0_2402_P.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>7598.7_2799_S.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>7006.7_5717_S.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>5004.9_1790_A.</t>
+          <t>2783.5_952_S.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>6011.5_2408_A.</t>
+          <t>18102.7_4949_M.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>9507.9_2851_M.</t>
+          <t>5100.0_2587_A.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>5010.3_3392_P.</t>
+          <t>3005.2_1040_L.</t>
         </is>
       </c>
     </row>
@@ -1415,1113 +1415,1183 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>4791.5_1524_E.</t>
+          <t>553.2_224_S.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>7312.2_2446_G.</t>
+          <t>4705.5_1241_G.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>14119.3_5262_S.</t>
+          <t>12022.7_5417_L.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>9012.4_2700_M.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>5282.8_2392_C.</t>
+          <t>10001.9_4466_P.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>15194.4_3911_S.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2002.2_938_P.</t>
+          <t>6012.6_2984_F.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>9007.1_3080_P.</t>
+          <t>9756.3_2793_M.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>8132.9_2716_S.</t>
+          <t>6038.2_2121_P.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>10533.4_4020_F.</t>
+          <t>5621.6_2375_P.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>5008.2_1646_A.</t>
+          <t>531.0_343_A.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>5022.5_1222_P.</t>
+          <t>2558.7_905_S.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>12545.4_3039_S.</t>
+          <t>5580.0_2471_A.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>5451.1_1905_T.</t>
+          <t>8008.0_2930_A.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>6833.7_2100_G.</t>
+          <t>9209.1_3141_E.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>6010.6_2144_A.</t>
+          <t>9007.1_3080_P.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2783.5_952_S.</t>
+          <t>6004.0_2559_P.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>21106.2_7925_P.</t>
+          <t>10174.3_3680_S.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10012.3_3067_S.</t>
+          <t>5010.3_3392_P.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>13023.5_5156_L.</t>
+          <t>5256.5_1535_S.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>5008.0_2402_P.</t>
+          <t>6006.6_2009_P.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>7576.8_2823_P.</t>
+          <t>5014.3_1731_F.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>531.0_343_A.</t>
+          <t>4932.4_1545_E.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>8104.2_2652_M.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>3010.0_1289_A.</t>
+          <t>15186.5_3866_S.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>10030.0_3041_G.</t>
+          <t>4786.5_1898_P.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>4000.6_1659_S.</t>
+          <t>8004.6_2357_G.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>5365.6_2437_C.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>7598.7_2799_S.</t>
+          <t>10533.4_4020_F.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>10106.6_2889_P.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>5005.4_2618_L.</t>
+          <t>4731.9_1407_T.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>3757.2_1716_A.</t>
+          <t>6951.4_2856_S.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>3089.9_1508_C.</t>
+          <t>5238.0_2781_F.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>2305.1_940_S.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>6046.5_3239_S.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>5580.0_2471_A.</t>
+          <t>10012.3_3067_S.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>5382.2_2690_M.</t>
+          <t>2504.7_703_🔋.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>8618.0_2344_P.</t>
+          <t>16397.3_4254_S.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>5025.8_1214_P.</t>
+          <t>10058.8_3483_F.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>7230.5_2794_V.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>56121.5_25636_F.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>5005.8_1527_S.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>4735.2_997_S.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>6011.8_1873_M.</t>
+          <t>5382.2_2690_M.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>15637.2_5789_G.</t>
+          <t>6012.6_2984_P.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>18102.7_4949_M.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>20105.6_7766_F.</t>
+          <t>1443.0_851_A.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>657.7_273_S.</t>
+          <t>2186.2_736_G.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>9562.8_3145_M.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>5522.8_2716_V.</t>
+          <t>3010.0_1424_A.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>7569.4_2477_V.</t>
+          <t>10348.3_2647_S.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>8481.2_2463_🔋.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>7985.2_2173_P.</t>
+          <t>10012.1_3139_S.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>16397.3_4254_S.</t>
+          <t>10503.6_3278_M.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>6536.2_2241_P.</t>
+          <t>6084.1_2156_V.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>15194.4_3911_S.</t>
+          <t>10106.6_2889_P.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>5013.9_1673_A.</t>
+          <t>8132.9_2716_S.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>6012.6_2984_P.</t>
+          <t>6903.6_2566_G.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>5256.5_1535_S.</t>
+          <t>9555.5_5689_S.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>6903.6_2566_G.</t>
+          <t>6010.6_2144_A.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>8506.3_4050_C.</t>
+          <t>26010.2_9812_F.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>5869.6_2613_P.</t>
+          <t>10027.3_2906_P.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>8396.0_2595_S.</t>
+          <t>3010.0_1289_A.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>3412.3_1947_C.</t>
+          <t>3735.9_1928_V.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>10011.5_3070_S.</t>
+          <t>3412.3_1947_C.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>21442.0_7959_F.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>4177.9_1557_T.</t>
+          <t>4791.5_1524_E.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>3010.0_1685_A.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>4830.1_2569_C.</t>
+          <t>5451.1_1905_T.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>4692.9_1546_P.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>6620.4_2477_P.</t>
+          <t>21106.2_7925_P.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>12524.7_3259_S.</t>
+          <t>5579.8_1990_E.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>10348.3_2647_S.</t>
+          <t>5033.4_1976_M.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>8218.3_2327_P.</t>
+          <t>401.2_179_S.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>9791.4_3527_G.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>7230.5_2794_V.</t>
+          <t>10062.5_2886_M.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>3798.9_1319_S.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>5621.6_2375_P.</t>
+          <t>8367.5_4269_C.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>5579.8_1990_E.</t>
+          <t>2735.8_959_S.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>6007.1_3172_F.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>12022.7_5417_L.</t>
+          <t>13023.5_5156_L.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>7874.8_2223_M.</t>
+          <t>8396.0_2595_S.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>8218.3_2327_P.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>2060.0_802_S.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2185.4_792_S.</t>
+          <t>8442.5_3038_G.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>7012.1_3931_🔋.</t>
+          <t>17012.6_5869_T.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>3023.2_962_S.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>4786.5_1898_P.</t>
+          <t>2880.9_1210_L.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>5005.4_2618_L.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>5072.4_1931_S.</t>
+          <t>1027.7_364_S.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>7114.0_2850_S.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>15016.9_6221_G.</t>
+          <t>10022.1_2875_M.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>5086.0_1810_G.</t>
+          <t>4028.8_1699_L.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>7114.0_2850_S.</t>
+          <t>8120.9_2737_G.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>4891.7_1690_F.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>26010.2_9812_F.</t>
+          <t>21141.5_8155_F.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>10001.9_4466_P.</t>
+          <t>7022.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1114.9_359_S.</t>
+          <t>6137.8_2406_L.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>4797.2_1541_G.</t>
+          <t>4000.6_1659_S.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>8187.1_2322_M.</t>
+          <t>6620.4_2477_P.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>9209.1_3141_E.</t>
+          <t>4830.1_2569_C.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>6007.1_3172_F.</t>
+          <t>2051.8_860_S.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2735.8_959_S.</t>
+          <t>7039.1_2754_S.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>7006.7_5717_S.</t>
+          <t>9006.5_3085_X.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>7502.4_3467_P.</t>
+          <t>2185.4_792_S.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>5029.4_1585_P.</t>
+          <t>4814.5_1705_🔋.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>17003.0_7696_P.</t>
+          <t>657.7_273_S.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>15637.2_5789_G.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>6006.6_2009_P.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>1002.7_460_S.</t>
+          <t>22320.3_9183_F.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>12524.7_3259_S.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>10503.6_3278_M.</t>
+          <t>7502.4_3467_P.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>5365.6_2437_C.</t>
+          <t>3019.8_1453_F.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>10007.4_3588_V.</t>
+          <t>8253.0_2972_🔋.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>6011.5_2408_A.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2504.7_703_🔋.</t>
+          <t>6804.1_2088_P.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>6804.1_2088_P.</t>
+          <t>14014.7_3537_S.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>9756.3_2793_M.</t>
+          <t>4077.1_1454_S.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>9006.5_3085_X.</t>
+          <t>2047.9_924_L.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>37036.6_17889_F.</t>
+          <t>7874.8_2223_M.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>7992.7_2506_F.</t>
+          <t>7015.4_2141_T.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>8481.2_2463_🔋.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>5235.4_1766_P.</t>
+          <t>5296.8_1844_P.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>10016.9_3028_M.</t>
+          <t>5904.3_2699_P.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>8351.7_4153_C.</t>
+          <t>8618.0_2344_P.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>8442.5_3038_G.</t>
+          <t>8506.3_4050_C.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>5724.1_3694_S.</t>
+          <t>3798.9_1319_S.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>5085.1_1840_G.</t>
+          <t>5287.4_1835_V.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>5005.8_1527_S.</t>
+          <t>5163.5_1775_V.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>8008.0_2930_A.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>4017.3_1883_C.</t>
+          <t>3023.2_962_S.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2060.0_802_S.</t>
+          <t>10030.0_3041_G.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>6084.1_2156_V.</t>
+          <t>7985.2_2173_P.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>5287.4_1835_V.</t>
+          <t>14117.6_3844_M.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>17003.0_7696_P.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>7039.1_2754_S.</t>
+          <t>9507.9_2851_M.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>56121.5_25636_F.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>4932.4_1545_E.</t>
+          <t>4896.8_2251_L.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>3010.0_1424_A.</t>
+          <t>4177.9_1557_T.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>5033.4_1976_M.</t>
+          <t>1366.2_487_L.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>9029.6_4595_P.</t>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>5020.4_2167_C.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>5004.0_2103_C.</t>
+          <t>3757.2_1716_A.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>5010.3_1888_G.</t>
+          <t>7992.7_2506_F.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2880.9_1210_L.</t>
+          <t>7576.8_2823_P.</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>401.2_179_S.</t>
+          <t>4821.0_1857_P.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>37036.6_17889_F.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>14014.7_3537_S.</t>
+          <t>4797.2_1541_G.</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>22320.3_9183_F.</t>
+          <t>12545.4_3039_S.</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>5296.8_1844_P.</t>
+          <t>5724.1_3694_S.</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>15504.3_3950_M.</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>5770.8_2848_G.</t>
+          <t>2175.4_712_S.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>10022.1_2875_M.</t>
+          <t>5010.3_1888_G.</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>7420.2_4318_C.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>5238.0_2781_F.</t>
+          <t>7419.2_3469_F.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>18665.3_4638_S.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>5282.8_2392_C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>8351.7_4153_C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>15223.0_6245_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>5027.8_1361_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>6818.2_2036_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2011.7_731_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>5085.1_1840_G.</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>12342.9_3211_M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>10106.6_3354_M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>3089.9_1508_C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>5004.0_2103_C.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_500km_2026.xlsx
+++ b/Ranking_CNB_500km_2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,12 +454,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>531,9 km</t>
+          <t>537,2 km</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>7.535 m</t>
+          <t>7.595 m</t>
         </is>
       </c>
     </row>
@@ -488,12 +488,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>207,0 km</t>
+          <t>215,0 km</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.717 m</t>
+          <t>1.747 m</t>
         </is>
       </c>
     </row>
@@ -505,12 +505,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>181,5 km</t>
+          <t>187,1 km</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.714 m</t>
+          <t>1.782 m</t>
         </is>
       </c>
     </row>
@@ -636,34 +636,34 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Alexsia A.</t>
+          <t>Fellipe T.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>119,2 km</t>
+          <t>120,1 km</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.301 m</t>
+          <t>1.005 m</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Fellipe T.</t>
+          <t>Alexsia A.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>111,9 km</t>
+          <t>119,2 km</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>893 m</t>
+          <t>1.301 m</t>
         </is>
       </c>
     </row>
@@ -704,34 +704,34 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Duda X.</t>
+          <t>Jhonatas V.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>87,6 km</t>
+          <t>93,0 km</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.037 m</t>
+          <t>909 m</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Jhonatas V.</t>
+          <t>Duda X.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>83,0 km</t>
+          <t>87,6 km</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>827 m</t>
+          <t>1.037 m</t>
         </is>
       </c>
     </row>
@@ -772,202 +772,219 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Eduarda A.</t>
+          <t>Pierre P.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>47,4 km</t>
+          <t>50,7 km</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>443 m</t>
+          <t>530 m</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Pierre P.</t>
+          <t>Eduarda A.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>46,7 km</t>
+          <t>47,4 km</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>521 m</t>
+          <t>443 m</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Renato C.</t>
+          <t>Alexsandro A.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>36,2 km</t>
+          <t>41,6 km</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>440 m</t>
+          <t>346 m</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Alexsandro A.</t>
+          <t>Renato C.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>34,1 km</t>
+          <t>36,2 km</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>284 m</t>
+          <t>440 m</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Karine F.</t>
+          <t>Jhonny E.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>23,4 km</t>
+          <t>27,3 km</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>294 m</t>
+          <t>317 m</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Eduardo T.</t>
+          <t>Edivânia M.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>22,8 km</t>
+          <t>25,6 km</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>234 m</t>
+          <t>283 m</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Thaisa V.</t>
+          <t>Karine F.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>19,5 km</t>
+          <t>23,4 km</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>272 m</t>
+          <t>294 m</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Filipe M.</t>
+          <t>Eduardo T.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>10,4 km</t>
+          <t>22,8 km</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>169 m</t>
+          <t>234 m</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Mariana L.</t>
+          <t>Thaisa V.</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>7,9 km</t>
+          <t>19,5 km</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>108 m</t>
+          <t>272 m</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>José E.</t>
+          <t>Filipe M.</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>7,1 km</t>
+          <t>13,4 km</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>100 m</t>
+          <t>215 m</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Jhonny E.</t>
+          <t>Mariana L.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>4,6 km</t>
+          <t>7,9 km</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>27 m</t>
+          <t>108 m</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>José E.</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>7,1 km</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>100 m</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>Marta L.</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>0,0 km</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>0 m</t>
         </is>
@@ -984,7 +1001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A263"/>
+  <dimension ref="A1:A280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -997,1834 +1014,1953 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>7015.4_2141_T.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>6833.7_2100_G.</t>
+          <t>7516.9_3203_A.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>8351.7_4153_C.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5021.7_1930_A.</t>
+          <t>3005.2_1040_L.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>7312.2_2446_G.</t>
+          <t>10006.0_2772_V.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4786.5_1898_P.</t>
+          <t>7598.7_2799_S.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5451.1_1905_T.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>7419.2_3469_F.</t>
+          <t>6833.7_2100_G.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>9209.1_3141_E.</t>
+          <t>6007.4_1804_G.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>6536.2_2241_P.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5382.2_2690_M.</t>
+          <t>2305.1_940_S.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>9029.6_4595_P.</t>
+          <t>7022.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6661.8_3736_P.</t>
+          <t>18665.3_4638_S.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5904.3_2699_P.</t>
+          <t>9013.7_2337_M.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10003.7_2721_V.</t>
+          <t>4850.9_2239_C.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10012.1_3139_S.</t>
+          <t>37036.6_17889_F.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4078.1_1810_A.</t>
+          <t>22320.3_9183_F.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>56121.5_25636_F.</t>
+          <t>10174.3_3680_S.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>7992.7_2506_F.</t>
+          <t>553.2_224_S.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6951.4_2856_S.</t>
+          <t>9006.5_3085_X.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5020.4_2167_C.</t>
+          <t>25020.8_7832_V.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>4028.8_1699_L.</t>
+          <t>8008.0_2930_A.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>15504.3_3950_M.</t>
+          <t>7420.2_4318_C.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5085.1_1840_G.</t>
+          <t>3026.1_1490_A.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>10002.4_5136_P.</t>
+          <t>7880.9_2433_E.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>5163.5_1775_V.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5014.8_2009_A.</t>
+          <t>9209.1_3141_E.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2880.9_1210_L.</t>
+          <t>5013.9_1673_A.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>7114.0_2850_S.</t>
+          <t>5010.3_3392_P.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>2047.9_924_L.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>791.5_266_G.</t>
+          <t>5238.0_2781_F.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10030.0_3041_G.</t>
+          <t>7006.7_5717_S.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>12022.7_5417_L.</t>
+          <t>2036.1_839_S.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>13023.5_5156_L.</t>
+          <t>5028.5_4433_S.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5296.8_1844_P.</t>
+          <t>4700.4_1216_V.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5027.8_1361_P.</t>
+          <t>4692.9_1546_P.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10010.0_2910_V.</t>
+          <t>8196.1_2807_T.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>5028.5_4433_S.</t>
+          <t>21141.5_8155_F.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1114.9_359_S.</t>
+          <t>5256.5_1535_S.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>14117.6_3844_M.</t>
+          <t>9507.9_2851_M.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>4821.0_1857_P.</t>
+          <t>2011.7_731_S.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>12524.7_3259_S.</t>
+          <t>2558.7_905_S.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>6012.6_2984_P.</t>
+          <t>3614.8_970_🔋.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>9006.5_3085_X.</t>
+          <t>10003.3_3845_P.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>10001.9_4466_P.</t>
+          <t>9012.4_2700_M.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>5040.0_2514_C.</t>
+          <t>15186.5_3866_S.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>7985.2_2173_P.</t>
+          <t>9756.3_2793_M.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>4705.5_1241_G.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2186.2_736_G.</t>
+          <t>2002.2_938_P.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>5282.8_2392_C.</t>
+          <t>6472.0_2501_S.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>3735.9_1928_V.</t>
+          <t>5242.7_1657_S.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>5287.4_1835_V.</t>
+          <t>6012.6_2984_P.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>5256.5_1535_S.</t>
+          <t>3958.9_1777_P.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>6010.6_2144_A.</t>
+          <t>10016.9_3028_M.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>15223.0_6245_P.</t>
+          <t>7992.7_2506_F.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>10027.3_2906_P.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1002.7_460_S.</t>
+          <t>2186.2_736_G.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>5010.3_1888_G.</t>
+          <t>2175.4_712_S.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>8351.7_4153_C.</t>
+          <t>10012.1_3139_S.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>8481.2_2463_🔋.</t>
+          <t>12326.4_4833_S.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>15186.5_3866_S.</t>
+          <t>2880.9_1210_L.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>3004.6_746_V.</t>
+          <t>4791.5_1524_E.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>4017.3_1883_C.</t>
+          <t>6011.5_2408_A.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>12342.9_3211_M.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>3597.6_2910_E.</t>
+          <t>8367.5_4269_C.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1012.0_375_E.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>5235.4_1766_P.</t>
+          <t>14117.6_3844_M.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>6004.0_2559_P.</t>
+          <t>2051.8_860_S.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>6345.4_2376_S.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>10016.9_3028_M.</t>
+          <t>5005.4_2618_L.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>8506.3_4050_C.</t>
+          <t>4177.9_1557_T.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>6007.4_1804_G.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>3089.9_1508_C.</t>
+          <t>3010.0_1685_A.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>5770.8_2848_G.</t>
+          <t>17012.6_5869_T.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>6006.6_2009_P.</t>
+          <t>4821.0_1857_P.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>6804.1_2088_P.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>7025.4_3008_L.</t>
+          <t>7001.2_3357_M.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>791.5_266_G.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>37036.6_17889_F.</t>
+          <t>7230.5_2794_V.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>7022.4_3008_L.</t>
+          <t>5581.6_3687_P.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>4017.3_1883_C.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>7569.4_2477_V.</t>
+          <t>5014.3_1731_F.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>5010.3_3392_P.</t>
+          <t>7985.2_2173_P.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>12521.4_4814_M.</t>
+          <t>21106.2_7925_P.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>20105.6_7766_F.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>12545.4_3039_S.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>6011.8_1873_M.</t>
+          <t>5008.2_1646_A.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>3412.3_1947_C.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>5100.0_2587_A.</t>
+          <t>7114.0_2850_S.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>22320.3_9183_F.</t>
+          <t>4814.5_1705_🔋.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>12545.4_3039_S.</t>
+          <t>18102.7_4949_M.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>10503.6_3278_M.</t>
+          <t>8004.6_2357_G.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2060.0_802_S.</t>
+          <t>3010.0_1424_A.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>4013.7_1173_V.</t>
+          <t>10106.6_2889_P.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>5724.1_3694_S.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>8396.0_2595_S.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>21141.5_8155_F.</t>
+          <t>21207.4_6474_V.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>7039.1_2754_S.</t>
+          <t>12022.7_5417_L.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>8132.9_2716_S.</t>
+          <t>3597.6_2910_E.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>15194.4_3911_S.</t>
+          <t>3023.2_962_S.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>611.2_221_M.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>9012.4_2700_M.</t>
+          <t>4864.8_1353_E.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>8004.6_2357_G.</t>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>7502.4_3467_P.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>5033.4_1976_M.</t>
+          <t>5580.0_2471_A.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>10011.5_3070_S.</t>
+          <t>10533.4_4020_F.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>5004.0_2103_C.</t>
+          <t>10011.5_3070_S.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>5869.6_2613_P.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>7576.8_2823_P.</t>
+          <t>5085.1_1840_G.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>7006.7_5717_S.</t>
+          <t>15194.4_3911_S.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>10020.8_2989_M.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>6345.4_2376_S.</t>
+          <t>5003.2_1389_E.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>9005.3_4344_A.</t>
+          <t>5004.5_1548_A.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>4613.1_1806_A.</t>
+          <t>5005.8_1527_S.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1443.0_851_A.</t>
+          <t>10503.6_3278_M.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>15223.0_6245_P.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>6011.5_2408_A.</t>
+          <t>4013.7_1173_V.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>4700.4_1216_V.</t>
+          <t>401.2_179_S.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>12342.9_3211_M.</t>
+          <t>10106.6_3354_M.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>4932.4_1545_E.</t>
+          <t>6137.8_2406_L.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2047.9_924_L.</t>
+          <t>4214.8_2018_A.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>15637.2_5789_G.</t>
+          <t>10030.0_3041_G.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>5029.4_1585_P.</t>
+          <t>5004.9_1790_A.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>3010.0_1289_A.</t>
+          <t>9029.6_4595_P.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1366.2_487_L.</t>
+          <t>5869.6_2613_P.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>3757.2_1716_A.</t>
+          <t>3580.9_1198_S.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>5072.4_1931_S.</t>
+          <t>6016.7_2122_M.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>6007.1_3172_F.</t>
+          <t>4896.8_2251_L.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>14119.3_5262_S.</t>
+          <t>21124.1_8011_F.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>4797.2_1541_G.</t>
+          <t>5100.0_2587_A.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>5382.2_2690_M.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>10027.3_2906_P.</t>
+          <t>9007.1_3080_P.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>10348.3_2647_S.</t>
+          <t>5025.8_1214_P.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>5621.6_2375_P.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>5004.9_1790_A.</t>
+          <t>8506.3_4050_C.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>8218.3_2327_P.</t>
+          <t>9791.4_3527_G.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>5522.8_2716_V.</t>
+          <t>1011.0_396_L.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2036.1_839_S.</t>
+          <t>6011.8_1873_M.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>7145.5_2856_E.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>6536.2_2241_P.</t>
+          <t>6818.2_2036_P.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>6084.1_2156_V.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>26010.2_9812_F.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>1443.0_851_A.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>10007.4_3588_V.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>7025.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>9756.3_2793_M.</t>
+          <t>12006.9_5463_P.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>6903.6_2566_G.</t>
+          <t>5119.6_3153_M.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>7874.8_2223_M.</t>
+          <t>1884.9_866_S.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>10022.1_2875_M.</t>
+          <t>7576.8_2823_P.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>5004.5_1548_A.</t>
+          <t>2060.0_802_S.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>6006.6_2009_P.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>8024.4_2933_S.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>7502.4_3467_P.</t>
+          <t>7039.1_2754_S.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>18665.3_4638_S.</t>
+          <t>6004.0_2559_P.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>10106.6_2889_P.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>17003.0_7696_P.</t>
+          <t>5522.8_2716_V.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>5086.0_1810_G.</t>
+          <t>8481.2_2463_🔋.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>3412.3_1947_C.</t>
+          <t>15637.2_5789_G.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>25020.8_7832_V.</t>
+          <t>773.5_238_S.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>2185.4_792_S.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>12524.7_3259_S.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>9639.7_4763_P.</t>
+          <t>1012.0_375_E.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>7419.2_3469_F.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>16397.3_4254_S.</t>
+          <t>5365.6_2437_C.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>21124.1_8011_F.</t>
+          <t>4891.7_1690_F.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>4000.6_1659_S.</t>
+          <t>17003.0_7696_P.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>5008.2_1646_A.</t>
+          <t>3798.9_1319_S.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2735.8_959_S.</t>
+          <t>4028.8_1699_L.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2185.4_792_S.</t>
+          <t>2783.5_952_S.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>7230.5_2794_V.</t>
+          <t>3019.8_1453_F.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>4797.2_1541_G.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>5238.0_2781_F.</t>
+          <t>10007.4_3588_V.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>1114.9_359_S.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>5365.6_2437_C.</t>
+          <t>4830.1_2569_C.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>9007.1_3080_P.</t>
+          <t>6661.8_3736_P.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>5005.4_2618_L.</t>
+          <t>21442.0_7959_F.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>5013.9_1673_A.</t>
+          <t>7145.5_2856_E.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>10533.4_4020_F.</t>
+          <t>10012.3_3067_S.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>6010.6_2144_A.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>3010.0_1289_A.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>3010.0_1424_A.</t>
+          <t>1027.7_364_S.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>6046.5_3239_S.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>4078.1_1810_A.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>10003.3_3845_P.</t>
+          <t>15504.3_3950_M.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>4786.5_1898_P.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>6518.4_2914_A.</t>
+          <t>5904.3_2699_P.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>1027.7_364_S.</t>
+          <t>3089.9_1508_C.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>6818.2_2036_P.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>10008.1_2966_M.</t>
+          <t>4768.0_1875_L.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>8218.3_2327_P.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>8008.0_2930_A.</t>
+          <t>4735.2_997_S.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>2504.7_703_🔋.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>6620.4_2477_P.</t>
+          <t>5027.8_1361_P.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>10348.3_2647_S.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>3010.0_1685_A.</t>
+          <t>4613.1_1806_A.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>21106.2_7925_P.</t>
+          <t>4678.8_1840_A.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>5004.0_2103_C.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>5579.8_1990_E.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>401.2_179_S.</t>
+          <t>6012.6_2984_F.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>9507.9_2851_M.</t>
+          <t>5621.6_2375_P.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>8367.5_4269_C.</t>
+          <t>5008.0_2402_P.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>5022.5_1222_P.</t>
+          <t>3735.9_1928_V.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>8396.0_2595_S.</t>
+          <t>5072.4_1931_S.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>8104.2_2652_M.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>531.0_343_A.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>10020.8_2989_M.</t>
+          <t>5022.5_1222_P.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>4678.8_1840_A.</t>
+          <t>10062.5_2886_M.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2783.5_952_S.</t>
+          <t>6084.1_2156_V.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>3026.1_1490_A.</t>
+          <t>5235.4_1766_P.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>773.5_238_S.</t>
+          <t>5301.0_2064_F.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>5025.8_1214_P.</t>
+          <t>4077.1_1454_S.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>9791.4_3527_G.</t>
+          <t>13023.5_5156_L.</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>6038.2_2121_P.</t>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>3023.2_962_S.</t>
+          <t>10022.1_2875_M.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>18102.7_4949_M.</t>
+          <t>6951.4_2856_S.</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>5724.1_3694_S.</t>
+          <t>9555.5_5689_S.</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>8618.0_2344_P.</t>
+          <t>9639.7_4763_P.</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>7420.2_4318_C.</t>
+          <t>8187.1_2322_M.</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>4735.2_997_S.</t>
+          <t>10001.9_4466_P.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>5580.0_2471_A.</t>
+          <t>26010.2_9812_F.</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>5242.7_1657_S.</t>
+          <t>4763.8_1720_P.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>4692.9_1546_P.</t>
+          <t>5021.7_1930_A.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2002.2_938_P.</t>
+          <t>56121.5_25636_F.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>4850.9_2239_C.</t>
+          <t>5020.4_2167_C.</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>7598.7_2799_S.</t>
+          <t>5040.0_2514_C.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>5579.8_1990_E.</t>
+          <t>8120.9_2737_G.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2011.7_731_S.</t>
+          <t>7874.8_2223_M.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>531.0_343_A.</t>
+          <t>9562.8_3145_M.</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>553.2_224_S.</t>
+          <t>10010.0_2910_V.</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>10012.3_3067_S.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>8442.5_3038_G.</t>
+          <t>10003.7_2721_V.</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>5287.4_1835_V.</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>6518.4_2914_A.</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>6804.1_2088_P.</t>
+          <t>5282.8_2392_C.</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>3004.6_746_V.</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>7569.4_2477_V.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>15016.9_6221_G.</t>
+          <t>8442.5_3038_G.</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>3798.9_1319_S.</t>
+          <t>1002.7_460_S.</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2504.7_703_🔋.</t>
+          <t>5770.8_2848_G.</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>657.7_273_S.</t>
+          <t>14119.3_5262_S.</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>14014.7_3537_S.</t>
+          <t>4932.4_1545_E.</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>4896.8_2251_L.</t>
+          <t>8253.0_2972_🔋.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>4177.9_1557_T.</t>
+          <t>16397.3_4254_S.</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>4791.5_1524_E.</t>
+          <t>10002.4_5136_P.</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>208.3_85_P.</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>5029.4_1585_P.</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>7012.1_3931_🔋.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>5008.0_2402_P.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>2558.7_905_S.</t>
+          <t>7312.2_2446_G.</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>5005.8_1527_S.</t>
+          <t>9005.3_4344_A.</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>21207.4_6474_V.</t>
+          <t>6007.1_3172_F.</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>5000.2_1932_E.</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>8187.1_2322_M.</t>
+          <t>5086.0_1810_G.</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>5001.9_1291_V.</t>
+          <t>5033.4_1976_M.</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>5163.5_1775_V.</t>
+          <t>6903.6_2566_G.</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>9555.5_5689_S.</t>
+          <t>5014.8_2009_A.</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>4214.8_2018_A.</t>
+          <t>2735.8_959_S.</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>4830.1_2569_C.</t>
+          <t>8618.0_2344_P.</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>20105.6_7766_F.</t>
+          <t>7012.1_3931_🔋.</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>5001.9_1291_V.</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>6003.3_2987_M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>3757.2_1716_A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>5451.1_1905_T.</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>1366.2_487_L.</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>4000.6_1659_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>6620.4_2477_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>6038.2_2121_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>15016.9_6221_G.</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>14014.7_3537_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>6007.1_2393_M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>8132.9_2716_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>5296.8_1844_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>3006.0_1286_M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>5010.3_1888_G.</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>10058.8_3483_F.</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>4731.9_1407_T.</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>657.7_273_S.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_500km_2026.xlsx
+++ b/Ranking_CNB_500km_2026.xlsx
@@ -454,12 +454,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>537,2 km</t>
+          <t>592,6 km</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>7.595 m</t>
+          <t>9.495 m</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A280"/>
+  <dimension ref="A1:A282"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1014,315 +1014,315 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>9005.3_4344_A.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>7516.9_3203_A.</t>
+          <t>5621.6_2375_P.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>8351.7_4153_C.</t>
+          <t>5013.9_1673_A.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>9555.5_5689_S.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10006.0_2772_V.</t>
+          <t>8004.6_2357_G.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>7598.7_2799_S.</t>
+          <t>9029.6_4595_P.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>4864.8_1353_E.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6833.7_2100_G.</t>
+          <t>1629.5_671_F.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6007.4_1804_G.</t>
+          <t>6833.7_2100_G.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>6536.2_2241_P.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>21207.4_6474_V.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>7022.4_3008_L.</t>
+          <t>4731.9_1407_T.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>18665.3_4638_S.</t>
+          <t>5724.1_3694_S.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>5100.0_2587_A.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4850.9_2239_C.</t>
+          <t>15016.9_6221_G.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>37036.6_17889_F.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>22320.3_9183_F.</t>
+          <t>7022.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>5027.8_1361_P.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>553.2_224_S.</t>
+          <t>14014.7_3537_S.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>9006.5_3085_X.</t>
+          <t>4896.8_2251_L.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>25020.8_7832_V.</t>
+          <t>17003.0_7696_P.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>8008.0_2930_A.</t>
+          <t>3023.2_962_S.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>7420.2_4318_C.</t>
+          <t>15504.3_3950_M.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3026.1_1490_A.</t>
+          <t>3597.6_2910_E.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>7880.9_2433_E.</t>
+          <t>9562.8_3145_M.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5163.5_1775_V.</t>
+          <t>553.2_224_S.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>9209.1_3141_E.</t>
+          <t>9006.5_3085_X.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5013.9_1673_A.</t>
+          <t>21106.2_7925_P.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>5010.3_3392_P.</t>
+          <t>3010.0_1685_A.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2047.9_924_L.</t>
+          <t>6804.1_2088_P.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5238.0_2781_F.</t>
+          <t>15223.0_6245_P.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>7006.7_5717_S.</t>
+          <t>4013.7_1173_V.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2036.1_839_S.</t>
+          <t>12342.9_3211_M.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>5028.5_4433_S.</t>
+          <t>7145.5_2856_E.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>4700.4_1216_V.</t>
+          <t>4791.5_1524_E.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>4692.9_1546_P.</t>
+          <t>10001.9_4466_P.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>8196.1_2807_T.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>21141.5_8155_F.</t>
+          <t>8396.0_2595_S.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>5256.5_1535_S.</t>
+          <t>10011.5_3070_S.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>9507.9_2851_M.</t>
+          <t>5004.5_1548_A.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2011.7_731_S.</t>
+          <t>5282.8_2392_C.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2558.7_905_S.</t>
+          <t>5014.8_2009_A.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>10503.6_3278_M.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>10003.3_3845_P.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>9012.4_2700_M.</t>
+          <t>2558.7_905_S.</t>
         </is>
       </c>
     </row>
@@ -1336,1309 +1336,1309 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>9756.3_2793_M.</t>
+          <t>4891.7_1690_F.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>6012.6_2984_P.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>6007.1_2393_M.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2002.2_938_P.</t>
+          <t>9209.1_3141_E.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>2186.2_736_G.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>5242.7_1657_S.</t>
+          <t>5029.4_1585_P.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>6012.6_2984_P.</t>
+          <t>10003.3_3845_P.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>3958.9_1777_P.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>10016.9_3028_M.</t>
+          <t>5451.1_1905_T.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>7992.7_2506_F.</t>
+          <t>1884.9_866_S.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>10027.3_2906_P.</t>
+          <t>15637.2_5789_G.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2186.2_736_G.</t>
+          <t>4214.8_2018_A.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>5028.5_4433_S.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>10012.1_3139_S.</t>
+          <t>12022.7_5417_L.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>12006.9_5463_P.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2880.9_1210_L.</t>
+          <t>6084.1_2156_V.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>4791.5_1524_E.</t>
+          <t>6011.8_1873_M.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>6011.5_2408_A.</t>
+          <t>7569.4_2477_V.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>12342.9_3211_M.</t>
+          <t>6007.1_3172_F.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>8367.5_4269_C.</t>
+          <t>2305.1_940_S.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>8104.2_2652_M.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>14117.6_3844_M.</t>
+          <t>10012.1_3139_S.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>7114.0_2850_S.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>6345.4_2376_S.</t>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>5005.4_2618_L.</t>
+          <t>10062.5_2886_M.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>4177.9_1557_T.</t>
+          <t>8120.9_2737_G.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>10008.1_2966_M.</t>
+          <t>8618.0_2344_P.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>3010.0_1685_A.</t>
+          <t>2036.1_839_S.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>10003.7_2721_V.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>4821.0_1857_P.</t>
+          <t>4077.1_1454_S.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>6804.1_2088_P.</t>
+          <t>17012.6_5869_T.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>7001.2_3357_M.</t>
+          <t>5085.1_1840_G.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>791.5_266_G.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>7230.5_2794_V.</t>
+          <t>1366.2_487_L.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>5581.6_3687_P.</t>
+          <t>9756.3_2793_M.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>4017.3_1883_C.</t>
+          <t>5242.7_1657_S.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>7985.2_2173_P.</t>
+          <t>10533.4_4020_F.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>21106.2_7925_P.</t>
+          <t>1114.9_359_S.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>20105.6_7766_F.</t>
+          <t>8008.0_2930_A.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>12545.4_3039_S.</t>
+          <t>3958.9_1777_P.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>5008.2_1646_A.</t>
+          <t>10030.0_3041_G.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>3412.3_1947_C.</t>
+          <t>5163.5_1775_V.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>7114.0_2850_S.</t>
+          <t>9507.9_2851_M.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>5004.0_2103_C.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>18102.7_4949_M.</t>
+          <t>10027.3_2906_P.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>8004.6_2357_G.</t>
+          <t>2175.4_712_S.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>3010.0_1424_A.</t>
+          <t>2060.0_802_S.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>10106.6_2889_P.</t>
+          <t>5904.3_2699_P.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>5724.1_3694_S.</t>
+          <t>8253.0_2972_🔋.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>8396.0_2595_S.</t>
+          <t>5522.8_2716_V.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>21207.4_6474_V.</t>
+          <t>9013.7_2337_M.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>12022.7_5417_L.</t>
+          <t>13023.5_5156_L.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>3597.6_2910_E.</t>
+          <t>3004.6_746_V.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>3023.2_962_S.</t>
+          <t>2047.9_924_L.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>611.2_221_M.</t>
+          <t>5869.6_2613_P.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>4864.8_1353_E.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>6818.2_2036_P.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>7502.4_3467_P.</t>
+          <t>7576.8_2823_P.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>5580.0_2471_A.</t>
+          <t>5021.7_1930_A.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>10533.4_4020_F.</t>
+          <t>5770.8_2848_G.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>10011.5_3070_S.</t>
+          <t>8351.7_4153_C.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>5000.2_1932_E.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>5085.1_1840_G.</t>
+          <t>3026.1_1490_A.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>15194.4_3911_S.</t>
+          <t>4786.5_1898_P.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>10020.8_2989_M.</t>
+          <t>6010.6_2144_A.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>5003.2_1389_E.</t>
+          <t>8506.3_4050_C.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>5004.5_1548_A.</t>
+          <t>4613.1_1806_A.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>5005.8_1527_S.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>10503.6_3278_M.</t>
+          <t>1012.0_375_E.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>15223.0_6245_P.</t>
+          <t>6536.2_2241_P.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>4013.7_1173_V.</t>
+          <t>25020.8_7832_V.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>401.2_179_S.</t>
+          <t>2880.9_1210_L.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>611.2_221_M.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>10010.0_2910_V.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>4214.8_2018_A.</t>
+          <t>6620.4_2477_P.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>10030.0_3041_G.</t>
+          <t>21442.0_7959_F.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>5004.9_1790_A.</t>
+          <t>5033.4_1976_M.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>9029.6_4595_P.</t>
+          <t>2504.7_703_🔋.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>5869.6_2613_P.</t>
+          <t>8442.5_3038_G.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>56121.5_25636_F.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>6016.7_2122_M.</t>
+          <t>7874.8_2223_M.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>4896.8_2251_L.</t>
+          <t>6011.5_2408_A.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>21124.1_8011_F.</t>
+          <t>5581.6_3687_P.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>5100.0_2587_A.</t>
+          <t>4705.5_1241_G.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>5382.2_2690_M.</t>
+          <t>4700.4_1216_V.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>9007.1_3080_P.</t>
+          <t>10012.3_3067_S.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>5025.8_1214_P.</t>
+          <t>6038.2_2121_P.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>8481.2_2463_🔋.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>8506.3_4050_C.</t>
+          <t>7516.9_3203_A.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>9791.4_3527_G.</t>
+          <t>5365.6_2437_C.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>5014.3_1731_F.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>6011.8_1873_M.</t>
+          <t>4932.4_1545_E.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>8196.1_2807_T.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>6818.2_2036_P.</t>
+          <t>6661.8_3736_P.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>5010.3_1888_G.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>4735.2_997_S.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1443.0_851_A.</t>
+          <t>4797.2_1541_G.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>7025.4_3008_L.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>9007.1_3080_P.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>5579.8_1990_E.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>7576.8_2823_P.</t>
+          <t>7015.4_2141_T.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2060.0_802_S.</t>
+          <t>6012.6_2984_F.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>6006.6_2009_P.</t>
+          <t>5020.4_2167_C.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>8024.4_2933_S.</t>
+          <t>4000.6_1659_S.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>7039.1_2754_S.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>6004.0_2559_P.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>12326.4_4833_S.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>5522.8_2716_V.</t>
+          <t>7230.5_2794_V.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>8481.2_2463_🔋.</t>
+          <t>14117.6_3844_M.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>15637.2_5789_G.</t>
+          <t>6903.6_2566_G.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>773.5_238_S.</t>
+          <t>1002.7_460_S.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2185.4_792_S.</t>
+          <t>4692.9_1546_P.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>12524.7_3259_S.</t>
+          <t>9012.4_2700_M.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>1012.0_375_E.</t>
+          <t>6004.0_2559_P.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>7419.2_3469_F.</t>
+          <t>3089.9_1508_C.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>5365.6_2437_C.</t>
+          <t>3614.8_970_🔋.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>2002.2_938_P.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>17003.0_7696_P.</t>
+          <t>4830.1_2569_C.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>21124.1_8011_F.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>3798.9_1319_S.</t>
+          <t>2735.8_959_S.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>4028.8_1699_L.</t>
+          <t>5004.9_1790_A.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2783.5_952_S.</t>
+          <t>5025.8_1214_P.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>7420.2_4318_C.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>4797.2_1541_G.</t>
+          <t>2051.8_860_S.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>10007.4_3588_V.</t>
+          <t>6137.8_2406_L.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1114.9_359_S.</t>
+          <t>401.2_179_S.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>4830.1_2569_C.</t>
+          <t>6003.3_2987_M.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>6661.8_3736_P.</t>
+          <t>10058.8_3483_F.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>4821.0_1857_P.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>7145.5_2856_E.</t>
+          <t>6951.4_2856_S.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>10012.3_3067_S.</t>
+          <t>6007.4_1804_G.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>6010.6_2144_A.</t>
+          <t>5040.0_2514_C.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>3010.0_1289_A.</t>
+          <t>3006.0_1286_M.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>1027.7_364_S.</t>
+          <t>10022.1_2875_M.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>10348.3_2647_S.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>4078.1_1810_A.</t>
+          <t>5301.0_2064_F.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>15504.3_3950_M.</t>
+          <t>8187.1_2322_M.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>4786.5_1898_P.</t>
+          <t>15194.4_3911_S.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>5904.3_2699_P.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>3089.9_1508_C.</t>
+          <t>18665.3_4638_S.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>2011.7_731_S.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>5003.2_1389_E.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>8218.3_2327_P.</t>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>4735.2_997_S.</t>
+          <t>5382.2_2690_M.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2504.7_703_🔋.</t>
+          <t>3005.2_1040_L.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>5027.8_1361_P.</t>
+          <t>10016.9_3028_M.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>10348.3_2647_S.</t>
+          <t>53755.6_36604_F.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>4613.1_1806_A.</t>
+          <t>6472.0_2501_S.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>4678.8_1840_A.</t>
+          <t>7006.7_5717_S.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>5004.0_2103_C.</t>
+          <t>7985.2_2173_P.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>5579.8_1990_E.</t>
+          <t>4850.9_2239_C.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>5008.2_1646_A.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>5621.6_2375_P.</t>
+          <t>4678.8_1840_A.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>5008.0_2402_P.</t>
+          <t>4768.0_1875_L.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>3735.9_1928_V.</t>
+          <t>4177.9_1557_T.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>5072.4_1931_S.</t>
+          <t>5005.8_1527_S.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>7992.7_2506_F.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>531.0_343_A.</t>
+          <t>2185.4_792_S.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>5022.5_1222_P.</t>
+          <t>7312.2_2446_G.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>6046.5_3239_S.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>6084.1_2156_V.</t>
+          <t>21141.5_8155_F.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>5235.4_1766_P.</t>
+          <t>5001.9_1291_V.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>5301.0_2064_F.</t>
+          <t>5296.8_1844_P.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>8024.4_2933_S.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>13023.5_5156_L.</t>
+          <t>791.5_266_G.</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>3757.2_1716_A.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>10022.1_2875_M.</t>
+          <t>5580.0_2471_A.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>6951.4_2856_S.</t>
+          <t>6006.6_2009_P.</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>9555.5_5689_S.</t>
+          <t>26010.2_9812_F.</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>9639.7_4763_P.</t>
+          <t>10106.6_2889_P.</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>8187.1_2322_M.</t>
+          <t>18102.7_4949_M.</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>10001.9_4466_P.</t>
+          <t>5005.4_2618_L.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>26010.2_9812_F.</t>
+          <t>3580.9_1198_S.</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>7502.4_3467_P.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>5021.7_1930_A.</t>
+          <t>2783.5_952_S.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>56121.5_25636_F.</t>
+          <t>6016.7_2122_M.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>5020.4_2167_C.</t>
+          <t>10020.8_2989_M.</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>5040.0_2514_C.</t>
+          <t>9791.4_3527_G.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>20105.6_7766_F.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>7874.8_2223_M.</t>
+          <t>8367.5_4269_C.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>7039.1_2754_S.</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>10010.0_2910_V.</t>
+          <t>3019.8_1453_F.</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>5256.5_1535_S.</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>10003.7_2721_V.</t>
+          <t>5008.0_2402_P.</t>
         </is>
       </c>
     </row>
@@ -2652,140 +2652,140 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>6518.4_2914_A.</t>
+          <t>3412.3_1947_C.</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>5282.8_2392_C.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>3004.6_746_V.</t>
+          <t>7001.2_3357_M.</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>7569.4_2477_V.</t>
+          <t>4028.8_1699_L.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>8442.5_3038_G.</t>
+          <t>3010.0_1289_A.</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>1002.7_460_S.</t>
+          <t>10106.6_3354_M.</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>5770.8_2848_G.</t>
+          <t>10002.4_5136_P.</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>14119.3_5262_S.</t>
+          <t>10174.3_3680_S.</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>4932.4_1545_E.</t>
+          <t>657.7_273_S.</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>22320.3_9183_F.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>16397.3_4254_S.</t>
+          <t>6518.4_2914_A.</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>10002.4_5136_P.</t>
+          <t>16397.3_4254_S.</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>10006.0_2772_V.</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>5029.4_1585_P.</t>
+          <t>773.5_238_S.</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>12521.4_4814_M.</t>
+          <t>3010.0_1424_A.</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>4078.1_1810_A.</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>7312.2_2446_G.</t>
+          <t>6345.4_2376_S.</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>9005.3_4344_A.</t>
+          <t>9639.7_4763_P.</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>6007.1_3172_F.</t>
+          <t>14119.3_5262_S.</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>5000.2_1932_E.</t>
+          <t>1443.0_851_A.</t>
         </is>
       </c>
     </row>
@@ -2799,168 +2799,182 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>5033.4_1976_M.</t>
+          <t>531.0_343_A.</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>6903.6_2566_G.</t>
+          <t>7419.2_3469_F.</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>5014.8_2009_A.</t>
+          <t>5022.5_1222_P.</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>2735.8_959_S.</t>
+          <t>208.3_85_P.</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>8618.0_2344_P.</t>
+          <t>37036.6_17889_F.</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>7012.1_3931_🔋.</t>
+          <t>5238.0_2781_F.</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>5001.9_1291_V.</t>
+          <t>7880.9_2433_E.</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>6003.3_2987_M.</t>
+          <t>12545.4_3039_S.</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>3757.2_1716_A.</t>
+          <t>5119.6_3153_M.</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>5451.1_1905_T.</t>
+          <t>12524.7_3259_S.</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>1366.2_487_L.</t>
+          <t>10007.4_3588_V.</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>4000.6_1659_S.</t>
+          <t>3798.9_1319_S.</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>6620.4_2477_P.</t>
+          <t>5010.3_3392_P.</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>6038.2_2121_P.</t>
+          <t>3735.9_1928_V.</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>15016.9_6221_G.</t>
+          <t>7598.7_2799_S.</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>14014.7_3537_S.</t>
+          <t>4017.3_1883_C.</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>6007.1_2393_M.</t>
+          <t>7025.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>8132.9_2716_S.</t>
+          <t>4814.5_1705_🔋.</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>5296.8_1844_P.</t>
+          <t>1027.7_364_S.</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>3006.0_1286_M.</t>
+          <t>5235.4_1766_P.</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>5010.3_1888_G.</t>
+          <t>7012.1_3931_🔋.</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>8132.9_2716_S.</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>4763.8_1720_P.</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>657.7_273_S.</t>
+          <t>8218.3_2327_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>1011.0_396_L.</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>5072.4_1931_S.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_500km_2026.xlsx
+++ b/Ranking_CNB_500km_2026.xlsx
@@ -454,12 +454,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>592,6 km</t>
+          <t>602,5 km</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>9.495 m</t>
+          <t>9.596 m</t>
         </is>
       </c>
     </row>
@@ -471,12 +471,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>432,8 km</t>
+          <t>450,9 km</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>5.820 m</t>
+          <t>6.013 m</t>
         </is>
       </c>
     </row>
@@ -488,12 +488,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>215,0 km</t>
+          <t>231,0 km</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.747 m</t>
+          <t>1.875 m</t>
         </is>
       </c>
     </row>
@@ -505,46 +505,46 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>187,1 km</t>
+          <t>194,7 km</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.782 m</t>
+          <t>1.848 m</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Mateus  M.</t>
+          <t>Fernanda G.</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>181,2 km</t>
+          <t>181,4 km</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.341 m</t>
+          <t>2.164 m</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Fernanda G.</t>
+          <t>Mateus  M.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>172,0 km</t>
+          <t>181,2 km</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.045 m</t>
+          <t>2.341 m</t>
         </is>
       </c>
     </row>
@@ -556,12 +556,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>157,9 km</t>
+          <t>171,9 km</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.117 m</t>
+          <t>1.199 m</t>
         </is>
       </c>
     </row>
@@ -573,12 +573,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>155,0 km</t>
+          <t>159,8 km</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.730 m</t>
+          <t>1.788 m</t>
         </is>
       </c>
     </row>
@@ -590,12 +590,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>139,9 km</t>
+          <t>151,9 km</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>942 m</t>
+          <t>1.026 m</t>
         </is>
       </c>
     </row>
@@ -607,12 +607,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>137,8 km</t>
+          <t>142,8 km</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.732 m</t>
+          <t>1.765 m</t>
         </is>
       </c>
     </row>
@@ -641,12 +641,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>120,1 km</t>
+          <t>125,1 km</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.005 m</t>
+          <t>1.063 m</t>
         </is>
       </c>
     </row>
@@ -658,63 +658,63 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>119,2 km</t>
+          <t>124,0 km</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.301 m</t>
+          <t>1.359 m</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Neydrielle V.</t>
+          <t>Naiane C.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>106,9 km</t>
+          <t>110,5 km</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.020 m</t>
+          <t>1.026 m</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Naiane C.</t>
+          <t>Jhonatas V.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>100,5 km</t>
+          <t>107,0 km</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>903 m</t>
+          <t>1.169 m</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Jhonatas V.</t>
+          <t>Neydrielle V.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>93,0 km</t>
+          <t>106,9 km</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>909 m</t>
+          <t>1.020 m</t>
         </is>
       </c>
     </row>
@@ -726,12 +726,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>87,6 km</t>
+          <t>92,6 km</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.037 m</t>
+          <t>1.095 m</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>75,4 km</t>
+          <t>83,0 km</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>959 m</t>
+          <t>1.030 m</t>
         </is>
       </c>
     </row>
@@ -772,34 +772,34 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Pierre P.</t>
+          <t>Eduarda A.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>50,7 km</t>
+          <t>54,8 km</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>530 m</t>
+          <t>522 m</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Eduarda A.</t>
+          <t>Pierre P.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>47,4 km</t>
+          <t>50,7 km</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>443 m</t>
+          <t>530 m</t>
         </is>
       </c>
     </row>
@@ -811,12 +811,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>41,6 km</t>
+          <t>46,1 km</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>346 m</t>
+          <t>404 m</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A282"/>
+  <dimension ref="A1:A305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1014,1925 +1014,1925 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>9005.3_4344_A.</t>
+          <t>21106.2_7925_P.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5621.6_2375_P.</t>
+          <t>3005.2_1040_L.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5013.9_1673_A.</t>
+          <t>4017.3_1883_C.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>9555.5_5689_S.</t>
+          <t>2504.7_703_🔋.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>8004.6_2357_G.</t>
+          <t>9029.6_4595_P.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>9029.6_4595_P.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4864.8_1353_E.</t>
+          <t>5724.1_3694_S.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1629.5_671_F.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6833.7_2100_G.</t>
+          <t>21442.0_7959_F.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>4735.2_997_S.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>21207.4_6474_V.</t>
+          <t>10007.4_3588_V.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>8367.5_4269_C.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5724.1_3694_S.</t>
+          <t>10003.3_3845_P.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5100.0_2587_A.</t>
+          <t>5040.0_2514_C.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>15016.9_6221_G.</t>
+          <t>5301.0_2064_F.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>12521.4_4814_M.</t>
+          <t>53755.6_36604_F.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>7022.4_3008_L.</t>
+          <t>2060.0_802_S.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5027.8_1361_P.</t>
+          <t>1114.9_359_S.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>14014.7_3537_S.</t>
+          <t>7576.8_2823_P.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4896.8_2251_L.</t>
+          <t>10010.0_2910_V.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>17003.0_7696_P.</t>
+          <t>3757.2_1716_A.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3023.2_962_S.</t>
+          <t>20105.6_7766_F.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>15504.3_3950_M.</t>
+          <t>3010.0_1685_A.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3597.6_2910_E.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>56121.5_25636_F.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>553.2_224_S.</t>
+          <t>5579.8_1990_E.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>9006.5_3085_X.</t>
+          <t>4028.8_1699_L.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>21106.2_7925_P.</t>
+          <t>25020.8_7832_V.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3010.0_1685_A.</t>
+          <t>4788.2_1476_P.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>6804.1_2088_P.</t>
+          <t>4613.1_1806_A.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>15223.0_6245_P.</t>
+          <t>4731.9_1407_T.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>4013.7_1173_V.</t>
+          <t>7114.0_2850_S.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>12342.9_3211_M.</t>
+          <t>12326.4_4833_S.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>7145.5_2856_E.</t>
+          <t>10027.3_2906_P.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>4791.5_1524_E.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10001.9_4466_P.</t>
+          <t>4830.1_2569_C.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>12022.7_5417_L.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>8396.0_2595_S.</t>
+          <t>6137.8_2406_L.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10011.5_3070_S.</t>
+          <t>1443.0_851_A.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5004.5_1548_A.</t>
+          <t>6046.5_3239_S.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>5282.8_2392_C.</t>
+          <t>2002.2_938_P.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>5014.8_2009_A.</t>
+          <t>1380.0_562_A.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>10503.6_3278_M.</t>
+          <t>5007.1_1751_T.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>6804.1_2088_P.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2558.7_905_S.</t>
+          <t>5004.0_2103_C.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>15186.5_3866_S.</t>
+          <t>5770.8_2848_G.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>4821.0_1857_P.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>6012.6_2984_P.</t>
+          <t>8442.5_3038_G.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>6007.1_2393_M.</t>
+          <t>5008.0_2402_P.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>9209.1_3141_E.</t>
+          <t>6345.4_2376_S.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2186.2_736_G.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>5029.4_1585_P.</t>
+          <t>9791.4_3527_G.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>10003.3_3845_P.</t>
+          <t>7419.2_3469_F.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>5100.0_2587_A.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>5451.1_1905_T.</t>
+          <t>10012.1_3139_S.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>6833.7_2100_G.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>15637.2_5789_G.</t>
+          <t>5014.3_1731_F.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>4214.8_2018_A.</t>
+          <t>7985.2_2173_P.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>5028.5_4433_S.</t>
+          <t>5027.8_1361_P.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>12022.7_5417_L.</t>
+          <t>3012.4_1258_P.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>4013.7_1173_V.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>6084.1_2156_V.</t>
+          <t>9012.4_2700_M.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>6011.8_1873_M.</t>
+          <t>7039.1_2754_S.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>7569.4_2477_V.</t>
+          <t>8008.0_2930_A.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>6007.1_3172_F.</t>
+          <t>5522.8_2716_V.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>5014.8_2009_A.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>5242.7_1657_S.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>10012.1_3139_S.</t>
+          <t>22320.3_9183_F.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>7114.0_2850_S.</t>
+          <t>9756.3_2793_M.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>14119.3_5262_S.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>611.2_221_M.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>8618.0_2344_P.</t>
+          <t>6620.4_2477_P.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2036.1_839_S.</t>
+          <t>15186.5_3866_S.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10003.7_2721_V.</t>
+          <t>9209.1_3141_E.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>6011.5_2408_A.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>13023.5_5156_L.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>5085.1_1840_G.</t>
+          <t>5005.4_2618_L.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>12008.4_3832_G.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1366.2_487_L.</t>
+          <t>960.0_1109_A.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>9756.3_2793_M.</t>
+          <t>1629.5_671_F.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>5242.7_1657_S.</t>
+          <t>7145.5_2856_E.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>4932.4_1545_E.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10533.4_4020_F.</t>
+          <t>6004.0_2559_P.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1114.9_359_S.</t>
+          <t>8187.1_2322_M.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>8008.0_2930_A.</t>
+          <t>419.0_180_P.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>3958.9_1777_P.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>10030.0_3041_G.</t>
+          <t>5580.0_2471_A.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>5163.5_1775_V.</t>
+          <t>14014.7_3537_S.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>9507.9_2851_M.</t>
+          <t>6012.6_2984_P.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>5004.0_2103_C.</t>
+          <t>8120.9_2737_G.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>10027.3_2906_P.</t>
+          <t>3023.2_962_S.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>4000.6_1659_S.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2060.0_802_S.</t>
+          <t>4891.7_1690_F.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>5904.3_2699_P.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>1884.9_866_S.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>5522.8_2716_V.</t>
+          <t>5581.6_3687_P.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>5256.5_1535_S.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>13023.5_5156_L.</t>
+          <t>4540.8_1823_A.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>3004.6_746_V.</t>
+          <t>7230.5_2794_V.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2047.9_924_L.</t>
+          <t>2185.4_792_S.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>5869.6_2613_P.</t>
+          <t>5033.4_1976_M.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>5072.4_1931_S.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>6818.2_2036_P.</t>
+          <t>18107.4_4577_M.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>7576.8_2823_P.</t>
+          <t>4781.2_1507_A.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>5021.7_1930_A.</t>
+          <t>10503.6_3278_M.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>5770.8_2848_G.</t>
+          <t>12342.9_3211_M.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>8351.7_4153_C.</t>
+          <t>5869.6_2613_P.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>5000.2_1932_E.</t>
+          <t>2783.5_952_S.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>3026.1_1490_A.</t>
+          <t>2036.1_839_S.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>4786.5_1898_P.</t>
+          <t>9006.5_3085_X.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>6010.6_2144_A.</t>
+          <t>6661.8_3736_P.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>8506.3_4050_C.</t>
+          <t>8196.1_2807_T.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>4613.1_1806_A.</t>
+          <t>4921.0_2491_A.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>10008.1_2966_M.</t>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1012.0_375_E.</t>
+          <t>6011.8_1873_M.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>6536.2_2241_P.</t>
+          <t>10006.0_2772_V.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>25020.8_7832_V.</t>
+          <t>17012.6_5869_T.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2880.9_1210_L.</t>
+          <t>12524.7_3259_S.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>611.2_221_M.</t>
+          <t>26010.2_9812_F.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>10010.0_2910_V.</t>
+          <t>5029.4_1585_P.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>6620.4_2477_P.</t>
+          <t>10003.7_2721_V.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>5033.4_1976_M.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2504.7_703_🔋.</t>
+          <t>6951.4_2856_S.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>8442.5_3038_G.</t>
+          <t>3026.1_1490_A.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>56121.5_25636_F.</t>
+          <t>10030.0_3041_G.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>7874.8_2223_M.</t>
+          <t>6084.1_2156_V.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>6011.5_2408_A.</t>
+          <t>6003.3_2987_M.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>5581.6_3687_P.</t>
+          <t>791.5_266_G.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>18102.7_4949_M.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>4700.4_1216_V.</t>
+          <t>6518.4_2914_A.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>10012.3_3067_S.</t>
+          <t>7569.4_2477_V.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>6038.2_2121_P.</t>
+          <t>10533.4_4020_F.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>8481.2_2463_🔋.</t>
+          <t>8132.9_2716_S.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>7516.9_3203_A.</t>
+          <t>1011.0_396_L.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>5365.6_2437_C.</t>
+          <t>10030.5_4765_C.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>5021.7_1930_A.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>4932.4_1545_E.</t>
+          <t>8506.3_4050_C.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>8196.1_2807_T.</t>
+          <t>5904.3_2699_P.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>6661.8_3736_P.</t>
+          <t>7598.7_2799_S.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>5010.3_1888_G.</t>
+          <t>8218.3_2327_P.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>4735.2_997_S.</t>
+          <t>5013.9_1673_A.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>4797.2_1541_G.</t>
+          <t>5020.4_2167_C.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>10058.8_3483_F.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>4763.8_1720_P.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>9007.1_3080_P.</t>
+          <t>5621.6_2375_P.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>5451.1_1905_T.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>5579.8_1990_E.</t>
+          <t>7025.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>17003.0_7696_P.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>5085.1_1840_G.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>5020.4_2167_C.</t>
+          <t>9007.1_3080_P.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>4000.6_1659_S.</t>
+          <t>7006.7_5717_S.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>5008.2_1646_A.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>1012.0_375_E.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>21124.1_8011_F.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>7230.5_2794_V.</t>
+          <t>2305.1_940_S.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>14117.6_3844_M.</t>
+          <t>5287.4_1835_V.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>6903.6_2566_G.</t>
+          <t>5086.0_1810_G.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>1002.7_460_S.</t>
+          <t>5163.5_1775_V.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>4692.9_1546_P.</t>
+          <t>9507.9_2851_M.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>9012.4_2700_M.</t>
+          <t>3089.9_1508_C.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>6004.0_2559_P.</t>
+          <t>6007.4_1804_G.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>3089.9_1508_C.</t>
+          <t>7992.7_2506_F.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2002.2_938_P.</t>
+          <t>7880.9_2433_E.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>4830.1_2569_C.</t>
+          <t>10002.4_5136_P.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>21124.1_8011_F.</t>
+          <t>10012.3_3067_S.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2735.8_959_S.</t>
+          <t>5028.5_4433_S.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>5004.9_1790_A.</t>
+          <t>8024.4_2933_S.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>5025.8_1214_P.</t>
+          <t>4786.5_1898_P.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>7420.2_4318_C.</t>
+          <t>3958.9_1777_P.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>21141.5_8155_F.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>4153.2_3559_P.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>401.2_179_S.</t>
+          <t>8253.0_2972_🔋.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>6003.3_2987_M.</t>
+          <t>4768.0_1875_L.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>10020.8_2989_M.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>4821.0_1857_P.</t>
+          <t>10022.1_2875_M.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>6951.4_2856_S.</t>
+          <t>7502.4_3467_P.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>6007.4_1804_G.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>5040.0_2514_C.</t>
+          <t>4177.9_1557_T.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>3006.0_1286_M.</t>
+          <t>2880.9_1210_L.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>10022.1_2875_M.</t>
+          <t>8396.0_2595_S.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>10348.3_2647_S.</t>
+          <t>4896.8_2251_L.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>5301.0_2064_F.</t>
+          <t>10106.6_3354_M.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>8187.1_2322_M.</t>
+          <t>4705.5_1241_G.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>15194.4_3911_S.</t>
+          <t>10016.9_3028_M.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>3597.6_2910_E.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>18665.3_4638_S.</t>
+          <t>12545.4_3039_S.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2011.7_731_S.</t>
+          <t>14019.6_6253_L.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>5003.2_1389_E.</t>
+          <t>6010.6_2144_A.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>10011.5_3070_S.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>5382.2_2690_M.</t>
+          <t>15194.4_3911_S.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>4791.5_1524_E.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>10016.9_3028_M.</t>
+          <t>7022.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>53755.6_36604_F.</t>
+          <t>12006.9_5463_P.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>9562.8_3145_M.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>7006.7_5717_S.</t>
+          <t>5025.8_1214_P.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>7985.2_2173_P.</t>
+          <t>3006.0_1286_M.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>4850.9_2239_C.</t>
+          <t>18665.3_4638_S.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>5008.2_1646_A.</t>
+          <t>7015.4_2141_T.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>4678.8_1840_A.</t>
+          <t>7312.2_2446_G.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>9639.7_4763_P.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>4177.9_1557_T.</t>
+          <t>6472.0_2501_S.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>5005.8_1527_S.</t>
+          <t>10174.3_3680_S.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>7992.7_2506_F.</t>
+          <t>6903.6_2566_G.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2185.4_792_S.</t>
+          <t>4814.5_1705_🔋.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>7312.2_2446_G.</t>
+          <t>2186.2_736_G.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>21141.5_8155_F.</t>
+          <t>8351.7_4153_C.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>5001.9_1291_V.</t>
+          <t>3010.0_1424_A.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>5296.8_1844_P.</t>
+          <t>7516.9_3203_A.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>8024.4_2933_S.</t>
+          <t>5009.1_2246_C.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>791.5_266_G.</t>
+          <t>5235.4_1766_P.</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>3757.2_1716_A.</t>
+          <t>657.7_273_S.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>5580.0_2471_A.</t>
+          <t>5004.5_1548_A.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>6006.6_2009_P.</t>
+          <t>5003.2_1389_E.</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>26010.2_9812_F.</t>
+          <t>5010.3_1888_G.</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>10106.6_2889_P.</t>
+          <t>6006.6_2009_P.</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>18102.7_4949_M.</t>
+          <t>6016.7_2122_M.</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>5005.4_2618_L.</t>
+          <t>3614.8_970_🔋.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>531.0_343_A.</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>7502.4_3467_P.</t>
+          <t>7420.2_4318_C.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2783.5_952_S.</t>
+          <t>14117.6_3844_M.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>6016.7_2122_M.</t>
+          <t>4850.9_2239_C.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>10020.8_2989_M.</t>
+          <t>5004.9_1790_A.</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>9791.4_3527_G.</t>
+          <t>5382.2_2690_M.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>20105.6_7766_F.</t>
+          <t>5005.9_1755_X.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>8367.5_4269_C.</t>
+          <t>4078.1_1810_A.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>7039.1_2754_S.</t>
+          <t>5296.8_1844_P.</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>5282.8_2392_C.</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>5256.5_1535_S.</t>
+          <t>2558.7_905_S.</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>5008.0_2402_P.</t>
+          <t>6007.1_2393_M.</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>5287.4_1835_V.</t>
+          <t>16008.9_5968_S.</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>3412.3_1947_C.</t>
+          <t>208.3_85_P.</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>7001.2_3357_M.</t>
+          <t>4700.4_1216_V.</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>4028.8_1699_L.</t>
+          <t>4214.8_2018_A.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>3010.0_1289_A.</t>
+          <t>9005.3_4344_A.</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>3412.3_1947_C.</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>10002.4_5136_P.</t>
+          <t>6818.2_2036_P.</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>8104.2_2652_M.</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>657.7_273_S.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>22320.3_9183_F.</t>
+          <t>6007.1_3172_F.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>6518.4_2914_A.</t>
+          <t>7001.2_3357_M.</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>16397.3_4254_S.</t>
+          <t>2175.4_712_S.</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>10006.0_2772_V.</t>
+          <t>5022.5_1222_P.</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>773.5_238_S.</t>
+          <t>4790.7_1897_F.</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>3010.0_1424_A.</t>
+          <t>5010.3_3392_P.</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>4078.1_1810_A.</t>
+          <t>15637.2_5789_G.</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>6345.4_2376_S.</t>
+          <t>9013.7_2337_M.</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>9639.7_4763_P.</t>
+          <t>5365.6_2437_C.</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>14119.3_5262_S.</t>
+          <t>37036.6_17889_F.</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>1443.0_851_A.</t>
+          <t>14009.7_4401_V.</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>5086.0_1810_G.</t>
+          <t>9415.9_3699_G.</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>531.0_343_A.</t>
+          <t>10001.9_4466_P.</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>7419.2_3469_F.</t>
+          <t>3019.8_1453_F.</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>5022.5_1222_P.</t>
+          <t>15016.9_6221_G.</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>4797.2_1541_G.</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>37036.6_17889_F.</t>
+          <t>1366.2_487_L.</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>5238.0_2781_F.</t>
+          <t>8481.2_2463_🔋.</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>7880.9_2433_E.</t>
+          <t>4864.8_1353_E.</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>12545.4_3039_S.</t>
+          <t>553.2_224_S.</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>3735.9_1928_V.</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>12524.7_3259_S.</t>
+          <t>2047.9_924_L.</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>10007.4_3588_V.</t>
+          <t>2011.7_731_S.</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>3798.9_1319_S.</t>
+          <t>16397.3_4254_S.</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>5010.3_3392_P.</t>
+          <t>6038.2_2121_P.</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>3735.9_1928_V.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>7598.7_2799_S.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>4017.3_1883_C.</t>
+          <t>6536.2_2241_P.</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>7025.4_3008_L.</t>
+          <t>6012.6_2984_F.</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>5001.9_1291_V.</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>1027.7_364_S.</t>
+          <t>3010.0_1289_A.</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>5235.4_1766_P.</t>
+          <t>1027.7_364_S.</t>
         </is>
       </c>
     </row>
@@ -2946,35 +2946,196 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>8132.9_2716_S.</t>
+          <t>5005.8_1527_S.</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>5064.3_1832_F.</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>8218.3_2327_P.</t>
+          <t>401.2_179_S.</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>10348.3_2647_S.</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>5072.4_1931_S.</t>
+          <t>4678.8_1840_A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>7874.8_2223_M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>123.0_5992_A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>10106.6_2889_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>10062.5_2886_M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2735.8_959_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>5238.0_2781_F.</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>7593.7_2701_E.</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2051.8_860_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>3004.6_746_V.</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>4692.9_1546_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>3580.9_1198_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>15504.3_3950_M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>5119.6_3153_M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>5000.2_1932_E.</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>3798.9_1319_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>8004.6_2357_G.</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>9555.5_5689_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>8618.0_2344_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>773.5_238_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>15223.0_6245_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>4077.1_1454_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>1002.7_460_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>21207.4_6474_V.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_500km_2026.xlsx
+++ b/Ranking_CNB_500km_2026.xlsx
@@ -454,12 +454,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>602,5 km</t>
+          <t>617,6 km</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>9.596 m</t>
+          <t>9.785 m</t>
         </is>
       </c>
     </row>
@@ -522,12 +522,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>181,4 km</t>
+          <t>188,5 km</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.164 m</t>
+          <t>2.250 m</t>
         </is>
       </c>
     </row>
@@ -675,12 +675,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>110,5 km</t>
+          <t>115,5 km</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.026 m</t>
+          <t>1.071 m</t>
         </is>
       </c>
     </row>
@@ -772,34 +772,34 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Eduarda A.</t>
+          <t>Pierre P.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>54,8 km</t>
+          <t>55,8 km</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>522 m</t>
+          <t>584 m</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Pierre P.</t>
+          <t>Eduarda A.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>50,7 km</t>
+          <t>54,8 km</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>530 m</t>
+          <t>522 m</t>
         </is>
       </c>
     </row>
@@ -930,12 +930,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>13,4 km</t>
+          <t>18,5 km</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>215 m</t>
+          <t>280 m</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A305"/>
+  <dimension ref="A1:A310"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1014,1540 +1014,1540 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>21106.2_7925_P.</t>
+          <t>7312.2_2446_G.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>6012.6_2984_P.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4017.3_1883_C.</t>
+          <t>2002.2_938_P.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2504.7_703_🔋.</t>
+          <t>22320.3_9183_F.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>9029.6_4595_P.</t>
+          <t>1027.7_364_S.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>9209.1_3141_E.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5724.1_3694_S.</t>
+          <t>6518.4_2914_A.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>4821.0_1857_P.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>7039.1_2754_S.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>4735.2_997_S.</t>
+          <t>6007.1_2393_M.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10007.4_3588_V.</t>
+          <t>4896.8_2251_L.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>8367.5_4269_C.</t>
+          <t>960.0_1109_A.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10003.3_3845_P.</t>
+          <t>4692.9_1546_P.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5040.0_2514_C.</t>
+          <t>4153.2_3559_P.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5301.0_2064_F.</t>
+          <t>7516.9_3203_A.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>53755.6_36604_F.</t>
+          <t>4028.8_1699_L.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2060.0_802_S.</t>
+          <t>4000.6_1659_S.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1114.9_359_S.</t>
+          <t>10503.6_3278_M.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>7576.8_2823_P.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10010.0_2910_V.</t>
+          <t>9012.4_2700_M.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3757.2_1716_A.</t>
+          <t>26010.2_9812_F.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20105.6_7766_F.</t>
+          <t>5005.8_1527_S.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3010.0_1685_A.</t>
+          <t>5770.8_2848_G.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>14117.6_3844_M.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>56121.5_25636_F.</t>
+          <t>4613.1_1806_A.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5579.8_1990_E.</t>
+          <t>16397.3_4254_S.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>4028.8_1699_L.</t>
+          <t>1380.0_562_A.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>25020.8_7832_V.</t>
+          <t>2060.0_802_S.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>4788.2_1476_P.</t>
+          <t>2186.2_736_G.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>4613.1_1806_A.</t>
+          <t>10030.0_3041_G.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>10003.3_3845_P.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>7114.0_2850_S.</t>
+          <t>9555.5_5689_S.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>3757.2_1716_A.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10027.3_2906_P.</t>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>17003.0_7696_P.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>4830.1_2569_C.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>12022.7_5417_L.</t>
+          <t>4788.2_1476_P.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>9756.3_2793_M.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1443.0_851_A.</t>
+          <t>5010.3_3392_P.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>4891.7_1690_F.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2002.2_938_P.</t>
+          <t>10012.3_3067_S.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1380.0_562_A.</t>
+          <t>7145.5_2856_E.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>5007.1_1751_T.</t>
+          <t>3010.0_1685_A.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>6804.1_2088_P.</t>
+          <t>5009.1_2246_C.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>5004.0_2103_C.</t>
+          <t>21442.0_7959_F.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>5770.8_2848_G.</t>
+          <t>2504.7_703_🔋.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>4821.0_1857_P.</t>
+          <t>3006.0_1286_M.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>8442.5_3038_G.</t>
+          <t>8104.2_2652_M.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>5008.0_2402_P.</t>
+          <t>5451.1_1905_T.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>6345.4_2376_S.</t>
+          <t>8004.6_2357_G.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>5085.1_1840_G.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>9791.4_3527_G.</t>
+          <t>4781.2_1507_A.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>7419.2_3469_F.</t>
+          <t>5119.6_3153_M.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>5100.0_2587_A.</t>
+          <t>5008.2_1646_A.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>10012.1_3139_S.</t>
+          <t>2558.7_905_S.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>6833.7_2100_G.</t>
+          <t>8481.2_2463_🔋.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>7593.7_2701_E.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>7985.2_2173_P.</t>
+          <t>9006.5_3085_X.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>5027.8_1361_P.</t>
+          <t>3010.0_1424_A.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>3012.4_1258_P.</t>
+          <t>5579.8_1990_E.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>4013.7_1173_V.</t>
+          <t>2880.9_1210_L.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>9012.4_2700_M.</t>
+          <t>7502.4_3467_P.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>7039.1_2754_S.</t>
+          <t>18102.7_4949_M.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>8008.0_2930_A.</t>
+          <t>5013.9_1673_A.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>5522.8_2716_V.</t>
+          <t>4177.9_1557_T.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>5014.8_2009_A.</t>
+          <t>10062.5_2886_M.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>5242.7_1657_S.</t>
+          <t>9562.8_3145_M.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>22320.3_9183_F.</t>
+          <t>7992.7_2506_F.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>9756.3_2793_M.</t>
+          <t>7001.2_3357_M.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>15186.5_3866_S.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>14119.3_5262_S.</t>
+          <t>5005.4_2618_L.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>611.2_221_M.</t>
+          <t>2011.7_731_S.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>6620.4_2477_P.</t>
+          <t>5051.4_1993_M.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>15186.5_3866_S.</t>
+          <t>21141.5_8155_F.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>9209.1_3141_E.</t>
+          <t>6903.6_2566_G.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>6011.5_2408_A.</t>
+          <t>5163.5_1775_V.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>13023.5_5156_L.</t>
+          <t>2047.9_924_L.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>5005.4_2618_L.</t>
+          <t>7985.2_2173_P.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>12008.4_3832_G.</t>
+          <t>18107.4_4577_M.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>960.0_1109_A.</t>
+          <t>4735.2_997_S.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1629.5_671_F.</t>
+          <t>5301.0_2064_F.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>7145.5_2856_E.</t>
+          <t>5021.7_1930_A.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>4932.4_1545_E.</t>
+          <t>3004.6_746_V.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>6004.0_2559_P.</t>
+          <t>8196.1_2807_T.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>8187.1_2322_M.</t>
+          <t>5014.3_1731_F.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>419.0_180_P.</t>
+          <t>10174.3_3680_S.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>5022.5_1222_P.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>5580.0_2471_A.</t>
+          <t>7015.4_2141_T.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>14014.7_3537_S.</t>
+          <t>7569.4_2477_V.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>6012.6_2984_P.</t>
+          <t>401.2_179_S.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>5724.1_3694_S.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>3023.2_962_S.</t>
+          <t>14019.6_6253_L.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>4000.6_1659_S.</t>
+          <t>6007.1_3172_F.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>7419.2_3469_F.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>5904.3_2699_P.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>5256.5_1535_S.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>5581.6_3687_P.</t>
+          <t>4864.8_1353_E.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>5256.5_1535_S.</t>
+          <t>10001.9_4466_P.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>4540.8_1823_A.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>7230.5_2794_V.</t>
+          <t>10003.7_2721_V.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2185.4_792_S.</t>
+          <t>10058.8_3483_F.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>5033.4_1976_M.</t>
+          <t>9005.3_4344_A.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>5072.4_1931_S.</t>
+          <t>6536.2_2241_P.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>18107.4_4577_M.</t>
+          <t>18665.3_4638_S.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>4781.2_1507_A.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>10503.6_3278_M.</t>
+          <t>4013.7_1173_V.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>12342.9_3211_M.</t>
+          <t>7598.7_2799_S.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>5869.6_2613_P.</t>
+          <t>5005.9_1755_X.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2783.5_952_S.</t>
+          <t>10106.6_2889_P.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2036.1_839_S.</t>
+          <t>8120.9_2737_G.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>9006.5_3085_X.</t>
+          <t>25020.8_7832_V.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>6661.8_3736_P.</t>
+          <t>21106.2_7925_P.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>8196.1_2807_T.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>4921.0_2491_A.</t>
+          <t>5287.4_1835_V.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>6011.8_1873_M.</t>
+          <t>5144.4_2349_P.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>10006.0_2772_V.</t>
+          <t>3597.6_2910_E.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>2036.1_839_S.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>12524.7_3259_S.</t>
+          <t>10348.3_2647_S.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>26010.2_9812_F.</t>
+          <t>12022.7_5417_L.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>5029.4_1585_P.</t>
+          <t>3019.8_1453_F.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>10003.7_2721_V.</t>
+          <t>2735.8_959_S.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>12521.4_4814_M.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>10008.1_2966_M.</t>
+          <t>6137.8_2406_L.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>6951.4_2856_S.</t>
+          <t>6472.0_2501_S.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>3026.1_1490_A.</t>
+          <t>7012.1_3931_🔋.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>10030.0_3041_G.</t>
+          <t>7576.8_2823_P.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>6084.1_2156_V.</t>
+          <t>3580.9_1198_S.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>6003.3_2987_M.</t>
+          <t>5001.9_1291_V.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>791.5_266_G.</t>
+          <t>7025.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>18102.7_4949_M.</t>
+          <t>4017.3_1883_C.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>6518.4_2914_A.</t>
+          <t>5580.0_2471_A.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>7569.4_2477_V.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>10533.4_4020_F.</t>
+          <t>5043.1_2254_C.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>8132.9_2716_S.</t>
+          <t>14014.7_3537_S.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>5100.0_2587_A.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>10030.5_4765_C.</t>
+          <t>4797.2_1541_G.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>5021.7_1930_A.</t>
+          <t>7880.9_2433_E.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>8506.3_4050_C.</t>
+          <t>4768.0_1875_L.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>5904.3_2699_P.</t>
+          <t>6003.3_2987_M.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>7598.7_2799_S.</t>
+          <t>1443.0_851_A.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>8218.3_2327_P.</t>
+          <t>20105.6_7766_F.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>5013.9_1673_A.</t>
+          <t>1629.5_671_F.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>5020.4_2167_C.</t>
+          <t>8506.3_4050_C.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>14009.7_4401_V.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>6016.7_2122_M.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>5621.6_2375_P.</t>
+          <t>2051.8_860_S.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>5451.1_1905_T.</t>
+          <t>1884.9_866_S.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>7025.4_3008_L.</t>
+          <t>10106.6_3354_M.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>17003.0_7696_P.</t>
+          <t>8008.0_2930_A.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>5085.1_1840_G.</t>
+          <t>4078.1_1810_A.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>9007.1_3080_P.</t>
+          <t>10012.1_3139_S.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>7006.7_5717_S.</t>
+          <t>10002.4_5136_P.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>5008.2_1646_A.</t>
+          <t>5020.4_2167_C.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>1012.0_375_E.</t>
+          <t>5522.8_2716_V.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>21124.1_8011_F.</t>
+          <t>2305.1_940_S.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>5004.5_1548_A.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>5287.4_1835_V.</t>
+          <t>4700.4_1216_V.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>5086.0_1810_G.</t>
+          <t>8351.7_4153_C.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>5163.5_1775_V.</t>
+          <t>6006.6_2009_P.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>9507.9_2851_M.</t>
+          <t>10022.1_2875_M.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>3089.9_1508_C.</t>
+          <t>6661.8_3736_P.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>6007.4_1804_G.</t>
+          <t>6012.6_2984_F.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>7992.7_2506_F.</t>
+          <t>1012.0_375_E.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>5010.3_1888_G.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>7880.9_2433_E.</t>
+          <t>10007.4_3588_V.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>10002.4_5136_P.</t>
+          <t>7127.8_1843_G.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>10012.3_3067_S.</t>
+          <t>5003.2_1389_E.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>5028.5_4433_S.</t>
+          <t>7874.8_2223_M.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>8024.4_2933_S.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>4786.5_1898_P.</t>
+          <t>4540.8_1823_A.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>3958.9_1777_P.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>21141.5_8155_F.</t>
+          <t>5382.2_2690_M.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>4153.2_3559_P.</t>
+          <t>5869.6_2613_P.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>4763.8_1720_P.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>6046.5_3239_S.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>10020.8_2989_M.</t>
+          <t>5033.4_1976_M.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>10022.1_2875_M.</t>
+          <t>6345.4_2376_S.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>7502.4_3467_P.</t>
+          <t>2185.4_792_S.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>9415.9_3699_G.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>4177.9_1557_T.</t>
+          <t>5029.4_1585_P.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2880.9_1210_L.</t>
+          <t>3005.2_1040_L.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>8396.0_2595_S.</t>
+          <t>5296.8_1844_P.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>4896.8_2251_L.</t>
+          <t>3010.0_1289_A.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>5004.0_2103_C.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>8396.0_2595_S.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>10016.9_3028_M.</t>
+          <t>53755.6_36604_F.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>3597.6_2910_E.</t>
+          <t>21124.1_8011_F.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>12545.4_3039_S.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>14019.6_6253_L.</t>
+          <t>10010.0_2910_V.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>6010.6_2144_A.</t>
+          <t>4790.7_1897_F.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>10011.5_3070_S.</t>
+          <t>7022.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>15194.4_3911_S.</t>
+          <t>12006.9_5463_P.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>4791.5_1524_E.</t>
+          <t>5064.3_1832_F.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>7022.4_3008_L.</t>
+          <t>56121.5_25636_F.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>5004.9_1790_A.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>5621.6_2375_P.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>5025.8_1214_P.</t>
+          <t>7230.5_2794_V.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>3006.0_1286_M.</t>
+          <t>419.0_180_P.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>18665.3_4638_S.</t>
+          <t>3735.9_1928_V.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>6011.5_2408_A.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>7312.2_2446_G.</t>
+          <t>10027.3_2906_P.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>9639.7_4763_P.</t>
+          <t>5282.8_2392_C.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>657.7_273_S.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>4850.9_2239_C.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>6903.6_2566_G.</t>
+          <t>4077.1_1454_S.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>5025.8_1214_P.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2186.2_736_G.</t>
+          <t>5365.6_2437_C.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>10020.8_2989_M.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>8351.7_4153_C.</t>
+          <t>12326.4_4833_S.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>3010.0_1424_A.</t>
+          <t>3958.9_1777_P.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>7516.9_3203_A.</t>
+          <t>10030.5_4765_C.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>5009.1_2246_C.</t>
+          <t>10016.9_3028_M.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>5235.4_1766_P.</t>
+          <t>9791.4_3527_G.</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>657.7_273_S.</t>
+          <t>21207.4_6474_V.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>5004.5_1548_A.</t>
+          <t>14119.3_5262_S.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>5003.2_1389_E.</t>
+          <t>5238.0_2781_F.</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>5010.3_1888_G.</t>
+          <t>3798.9_1319_S.</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>6006.6_2009_P.</t>
+          <t>8618.0_2344_P.</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>6016.7_2122_M.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
@@ -2561,567 +2561,567 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>531.0_343_A.</t>
+          <t>3012.4_1258_P.</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>7420.2_4318_C.</t>
+          <t>6833.7_2100_G.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>14117.6_3844_M.</t>
+          <t>10011.5_3070_S.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>4850.9_2239_C.</t>
+          <t>3089.9_1508_C.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>5004.9_1790_A.</t>
+          <t>3026.1_1490_A.</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>5382.2_2690_M.</t>
+          <t>4932.4_1545_E.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>5005.9_1755_X.</t>
+          <t>8187.1_2322_M.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>4078.1_1810_A.</t>
+          <t>5242.7_1657_S.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>5296.8_1844_P.</t>
+          <t>15223.0_6245_P.</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>5282.8_2392_C.</t>
+          <t>5000.2_1932_E.</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2558.7_905_S.</t>
+          <t>6010.6_2144_A.</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>6007.1_2393_M.</t>
+          <t>7420.2_4318_C.</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>16008.9_5968_S.</t>
+          <t>9029.6_4595_P.</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>12545.4_3039_S.</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>1114.9_359_S.</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>4700.4_1216_V.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>4214.8_2018_A.</t>
+          <t>10006.0_2772_V.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>9005.3_4344_A.</t>
+          <t>611.2_221_M.</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>3412.3_1947_C.</t>
+          <t>6804.1_2088_P.</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>6818.2_2036_P.</t>
+          <t>5014.8_2009_A.</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>4705.5_1241_G.</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>4786.5_1898_P.</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>6007.1_3172_F.</t>
+          <t>5027.8_1361_P.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>7001.2_3357_M.</t>
+          <t>9007.1_3080_P.</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>5008.0_2402_P.</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>5022.5_1222_P.</t>
+          <t>791.5_266_G.</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>4790.7_1897_F.</t>
+          <t>6011.8_1873_M.</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>5010.3_3392_P.</t>
+          <t>13023.5_5156_L.</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>15637.2_5789_G.</t>
+          <t>2175.4_712_S.</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>5365.6_2437_C.</t>
+          <t>3412.3_1947_C.</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>37036.6_17889_F.</t>
+          <t>1366.2_487_L.</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>14009.7_4401_V.</t>
+          <t>5028.5_4433_S.</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>9415.9_3699_G.</t>
+          <t>6038.2_2121_P.</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>10001.9_4466_P.</t>
+          <t>4214.8_2018_A.</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>6084.1_2156_V.</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>15016.9_6221_G.</t>
+          <t>773.5_238_S.</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>4797.2_1541_G.</t>
+          <t>15016.9_6221_G.</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>1366.2_487_L.</t>
+          <t>12524.7_3259_S.</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>8481.2_2463_🔋.</t>
+          <t>8132.9_2716_S.</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>4864.8_1353_E.</t>
+          <t>9507.9_2851_M.</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>553.2_224_S.</t>
+          <t>1011.0_396_L.</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>3735.9_1928_V.</t>
+          <t>15504.3_3950_M.</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>2047.9_924_L.</t>
+          <t>15057.9_8625_F.</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>2011.7_731_S.</t>
+          <t>5040.0_2514_C.</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>16397.3_4254_S.</t>
+          <t>37036.6_17889_F.</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>6038.2_2121_P.</t>
+          <t>4678.8_1840_A.</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>553.2_224_S.</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>5581.6_3687_P.</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>6536.2_2241_P.</t>
+          <t>3023.2_962_S.</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>8024.4_2933_S.</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>5001.9_1291_V.</t>
+          <t>531.0_343_A.</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>3010.0_1289_A.</t>
+          <t>8367.5_4269_C.</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>1027.7_364_S.</t>
+          <t>9639.7_4763_P.</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>7012.1_3931_🔋.</t>
+          <t>17012.6_5869_T.</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>5005.8_1527_S.</t>
+          <t>7006.7_5717_S.</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>5064.3_1832_F.</t>
+          <t>15637.2_5789_G.</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>401.2_179_S.</t>
+          <t>8442.5_3038_G.</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>10348.3_2647_S.</t>
+          <t>4830.1_2569_C.</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>4678.8_1840_A.</t>
+          <t>16008.9_5968_S.</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>7874.8_2223_M.</t>
+          <t>123.0_5992_A.</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>123.0_5992_A.</t>
+          <t>5072.4_1931_S.</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>10106.6_2889_P.</t>
+          <t>6004.0_2559_P.</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>8218.3_2327_P.</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>2735.8_959_S.</t>
+          <t>5007.1_1751_T.</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>5238.0_2781_F.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>7593.7_2701_E.</t>
+          <t>5235.4_1766_P.</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>12008.4_3832_G.</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>3004.6_746_V.</t>
+          <t>6951.4_2856_S.</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>4692.9_1546_P.</t>
+          <t>6818.2_2036_P.</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>4814.5_1705_🔋.</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>15504.3_3950_M.</t>
+          <t>6620.4_2477_P.</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>4921.0_2491_A.</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>5000.2_1932_E.</t>
+          <t>15194.4_3911_S.</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>3798.9_1319_S.</t>
+          <t>12342.9_3211_M.</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>8004.6_2357_G.</t>
+          <t>4731.9_1407_T.</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>9555.5_5689_S.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>8618.0_2344_P.</t>
+          <t>7114.0_2850_S.</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>773.5_238_S.</t>
+          <t>5086.0_1810_G.</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>15223.0_6245_P.</t>
+          <t>10533.4_4020_F.</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3135,42 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>21207.4_6474_V.</t>
+          <t>2783.5_952_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>9013.7_2337_M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>208.3_85_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>8253.0_2972_🔋.</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>6007.4_1804_G.</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>4791.5_1524_E.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_500km_2026.xlsx
+++ b/Ranking_CNB_500km_2026.xlsx
@@ -454,12 +454,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>617,6 km</t>
+          <t>627,6 km</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>9.785 m</t>
+          <t>9.908 m</t>
         </is>
       </c>
     </row>
@@ -471,12 +471,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>450,9 km</t>
+          <t>467,4 km</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>6.013 m</t>
+          <t>6.241 m</t>
         </is>
       </c>
     </row>
@@ -488,12 +488,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>231,0 km</t>
+          <t>237,4 km</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.875 m</t>
+          <t>1.905 m</t>
         </is>
       </c>
     </row>
@@ -539,12 +539,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>181,2 km</t>
+          <t>187,8 km</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.341 m</t>
+          <t>2.423 m</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>171,9 km</t>
+          <t>178,9 km</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -573,12 +573,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>159,8 km</t>
+          <t>166,8 km</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.788 m</t>
+          <t>1.870 m</t>
         </is>
       </c>
     </row>
@@ -607,12 +607,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>142,8 km</t>
+          <t>147,5 km</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.765 m</t>
+          <t>1.845 m</t>
         </is>
       </c>
     </row>
@@ -624,80 +624,80 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>133,8 km</t>
+          <t>140,4 km</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.848 m</t>
+          <t>1.926 m</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Fellipe T.</t>
+          <t>Alexsia A.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>125,1 km</t>
+          <t>129,0 km</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.063 m</t>
+          <t>1.412 m</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Alexsia A.</t>
+          <t>Fellipe T.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>124,0 km</t>
+          <t>126,1 km</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.359 m</t>
+          <t>1.063 m</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Naiane C.</t>
+          <t>Jhonatas V.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>115,5 km</t>
+          <t>117,0 km</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.071 m</t>
+          <t>1.247 m</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Jhonatas V.</t>
+          <t>Naiane C.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>107,0 km</t>
+          <t>115,5 km</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.169 m</t>
+          <t>1.071 m</t>
         </is>
       </c>
     </row>
@@ -726,12 +726,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>92,6 km</t>
+          <t>102,6 km</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.095 m</t>
+          <t>1.218 m</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>83,0 km</t>
+          <t>89,6 km</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.030 m</t>
+          <t>1.112 m</t>
         </is>
       </c>
     </row>
@@ -772,34 +772,34 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Pierre P.</t>
+          <t>Eduarda A.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>55,8 km</t>
+          <t>56,8 km</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>584 m</t>
+          <t>522 m</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Eduarda A.</t>
+          <t>Pierre P.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>54,8 km</t>
+          <t>55,8 km</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>522 m</t>
+          <t>584 m</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>27,3 km</t>
+          <t>34,1 km</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>317 m</t>
+          <t>399 m</t>
         </is>
       </c>
     </row>
@@ -862,12 +862,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>25,6 km</t>
+          <t>30,6 km</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>283 m</t>
+          <t>337 m</t>
         </is>
       </c>
     </row>
@@ -879,7 +879,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>23,4 km</t>
+          <t>25,1 km</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1001,7 +1001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A310"/>
+  <dimension ref="A1:A329"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1014,112 +1014,112 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>7312.2_2446_G.</t>
+          <t>5004.0_2103_C.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>6012.6_2984_P.</t>
+          <t>7516.9_3203_A.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2002.2_938_P.</t>
+          <t>5904.3_2699_P.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>22320.3_9183_F.</t>
+          <t>10020.8_2989_M.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1027.7_364_S.</t>
+          <t>1012.0_375_E.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>9209.1_3141_E.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6518.4_2914_A.</t>
+          <t>123.0_5992_A.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>4821.0_1857_P.</t>
+          <t>6472.0_2501_S.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>7039.1_2754_S.</t>
+          <t>8396.0_2595_S.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>6007.1_2393_M.</t>
+          <t>4786.5_1898_P.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4896.8_2251_L.</t>
+          <t>3005.2_1040_L.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>960.0_1109_A.</t>
+          <t>10030.0_3041_G.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4692.9_1546_P.</t>
+          <t>3010.0_1289_A.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4153.2_3559_P.</t>
+          <t>2186.2_736_G.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>7516.9_3203_A.</t>
+          <t>9029.6_4595_P.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>4028.8_1699_L.</t>
+          <t>419.0_180_P.</t>
         </is>
       </c>
     </row>
@@ -1133,2044 +1133,2177 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10503.6_3278_M.</t>
+          <t>7022.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>8004.6_2357_G.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>9012.4_2700_M.</t>
+          <t>2064.3_708_S.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>26010.2_9812_F.</t>
+          <t>3597.6_2910_E.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5005.8_1527_S.</t>
+          <t>2002.2_938_P.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5770.8_2848_G.</t>
+          <t>5028.5_4433_S.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>14117.6_3844_M.</t>
+          <t>4705.5_1241_G.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>4613.1_1806_A.</t>
+          <t>6600.2_1915_M.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>16397.3_4254_S.</t>
+          <t>7576.8_2823_P.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1380.0_562_A.</t>
+          <t>16397.3_4254_S.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2060.0_802_S.</t>
+          <t>6010.6_2144_A.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2186.2_736_G.</t>
+          <t>16008.9_5968_S.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10030.0_3041_G.</t>
+          <t>7593.7_2701_E.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10003.3_3845_P.</t>
+          <t>14009.7_4401_V.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>9555.5_5689_S.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3757.2_1716_A.</t>
+          <t>3798.9_1319_S.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>4678.8_1840_A.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>17003.0_7696_P.</t>
+          <t>10348.3_2647_S.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>4700.4_1216_V.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>4788.2_1476_P.</t>
+          <t>5522.8_2716_V.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>9756.3_2793_M.</t>
+          <t>8132.9_2716_S.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>5010.3_3392_P.</t>
+          <t>10003.3_3845_P.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>3006.0_1286_M.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>10012.3_3067_S.</t>
+          <t>9415.9_3699_G.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>7145.5_2856_E.</t>
+          <t>5724.1_3694_S.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3010.0_1685_A.</t>
+          <t>14117.6_3844_M.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>5009.1_2246_C.</t>
+          <t>10174.3_3680_S.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>5009.1_2246_C.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2504.7_703_🔋.</t>
+          <t>6620.4_2477_P.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3006.0_1286_M.</t>
+          <t>8351.7_4153_C.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>5005.8_1527_S.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>5451.1_1905_T.</t>
+          <t>10106.6_2889_P.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>8004.6_2357_G.</t>
+          <t>4788.2_1476_P.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>5085.1_1840_G.</t>
+          <t>6016.7_2122_M.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>4781.2_1507_A.</t>
+          <t>5119.6_3153_M.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>7024.3_3266_L.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>5008.2_1646_A.</t>
+          <t>12008.4_3832_G.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2558.7_905_S.</t>
+          <t>7419.2_3469_F.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>8481.2_2463_🔋.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>7593.7_2701_E.</t>
+          <t>6610.9_1738_P.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>9006.5_3085_X.</t>
+          <t>21124.1_8011_F.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>3010.0_1424_A.</t>
+          <t>10030.5_4765_C.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>5579.8_1990_E.</t>
+          <t>4688.1_2291_C.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2880.9_1210_L.</t>
+          <t>4214.8_2018_A.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>7502.4_3467_P.</t>
+          <t>2000.0_724_A.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>18102.7_4949_M.</t>
+          <t>18107.4_4577_M.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>5013.9_1673_A.</t>
+          <t>5010.3_3392_P.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>4177.9_1557_T.</t>
+          <t>10007.4_3588_V.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>5003.2_1389_E.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>4763.8_1720_P.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>7992.7_2506_F.</t>
+          <t>5027.8_1361_P.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>7001.2_3357_M.</t>
+          <t>10533.4_4020_F.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>15186.5_3866_S.</t>
+          <t>12342.9_3211_M.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>5005.4_2618_L.</t>
+          <t>5296.8_1844_P.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2011.7_731_S.</t>
+          <t>8506.3_4050_C.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>5051.4_1993_M.</t>
+          <t>5010.3_1888_G.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>21141.5_8155_F.</t>
+          <t>5144.4_2349_P.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>6903.6_2566_G.</t>
+          <t>5287.4_1835_V.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>5163.5_1775_V.</t>
+          <t>10006.9_3646_F.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2047.9_924_L.</t>
+          <t>5000.6_1856_M.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>7985.2_2173_P.</t>
+          <t>15057.9_8625_F.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>18107.4_4577_M.</t>
+          <t>2185.4_792_S.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>4735.2_997_S.</t>
+          <t>791.5_266_G.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>5301.0_2064_F.</t>
+          <t>16520.2_4844_M.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>5021.7_1930_A.</t>
+          <t>10062.5_2886_M.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>3004.6_746_V.</t>
+          <t>3580.9_1198_S.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>8196.1_2807_T.</t>
+          <t>4028.8_1699_L.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>4768.0_1875_L.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>10002.4_5136_P.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>5022.5_1222_P.</t>
+          <t>9507.9_2851_M.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>2355.5_726_S.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>7569.4_2477_V.</t>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>401.2_179_S.</t>
+          <t>10503.6_3278_M.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>5724.1_3694_S.</t>
+          <t>4735.2_997_S.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>14019.6_6253_L.</t>
+          <t>10016.9_3028_M.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>6007.1_3172_F.</t>
+          <t>20105.6_7766_F.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>7419.2_3469_F.</t>
+          <t>4153.2_3559_P.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>5904.3_2699_P.</t>
+          <t>5085.1_1840_G.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>5256.5_1535_S.</t>
+          <t>4790.7_1897_F.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>4864.8_1353_E.</t>
+          <t>12022.7_5417_L.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>10001.9_4466_P.</t>
+          <t>8253.0_2972_🔋.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>10001.9_4466_P.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>10003.7_2721_V.</t>
+          <t>7039.1_2754_S.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>3089.9_1508_C.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>9005.3_4344_A.</t>
+          <t>3026.1_1490_A.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>6536.2_2241_P.</t>
+          <t>10006.9_3646_X.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>18665.3_4638_S.</t>
+          <t>7003.6_2437_P.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>7015.4_2141_T.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>4013.7_1173_V.</t>
+          <t>4791.5_1524_E.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>7598.7_2799_S.</t>
+          <t>8104.2_2652_M.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>5005.9_1755_X.</t>
+          <t>7001.2_3357_M.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>10106.6_2889_P.</t>
+          <t>6661.8_3736_P.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>2558.7_905_S.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>25020.8_7832_V.</t>
+          <t>1020.0_679_T.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>21106.2_7925_P.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>10007.8_2733_V.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>5287.4_1835_V.</t>
+          <t>12326.4_4833_S.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>9209.1_3141_E.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>5144.4_2349_P.</t>
+          <t>4850.9_2239_C.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>3597.6_2910_E.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2036.1_839_S.</t>
+          <t>8442.5_3038_G.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>10348.3_2647_S.</t>
+          <t>9756.3_2793_M.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>12022.7_5417_L.</t>
+          <t>15186.5_3866_S.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>7114.0_2850_S.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2735.8_959_S.</t>
+          <t>2004.9_754_S.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>6779.9_2003_E.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>6046.5_3239_S.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>26010.2_9812_F.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>7012.1_3931_🔋.</t>
+          <t>10012.3_3067_S.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>7576.8_2823_P.</t>
+          <t>6084.1_2156_V.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>8481.2_2463_🔋.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>5001.9_1291_V.</t>
+          <t>7992.7_2506_F.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>7025.4_3008_L.</t>
+          <t>4814.5_1705_🔋.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>4017.3_1883_C.</t>
+          <t>5033.4_1976_M.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>5580.0_2471_A.</t>
+          <t>208.3_85_P.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>5014.3_1731_F.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>5043.1_2254_C.</t>
+          <t>531.0_343_A.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>14014.7_3537_S.</t>
+          <t>8367.5_4269_C.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>5100.0_2587_A.</t>
+          <t>3012.4_1258_P.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>4797.2_1541_G.</t>
+          <t>3735.9_1928_V.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>7880.9_2433_E.</t>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>7420.2_4318_C.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>6003.3_2987_M.</t>
+          <t>3412.3_1947_C.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>1443.0_851_A.</t>
+          <t>5008.2_1646_A.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>20105.6_7766_F.</t>
+          <t>3958.9_1777_P.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1629.5_671_F.</t>
+          <t>9006.5_3085_X.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>8506.3_4050_C.</t>
+          <t>3019.8_1453_F.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>14009.7_4401_V.</t>
+          <t>15223.0_6245_P.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>6016.7_2122_M.</t>
+          <t>37036.6_17889_F.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>5621.6_2375_P.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>5238.0_2781_F.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>8008.0_2930_A.</t>
+          <t>4891.7_1690_F.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>4078.1_1810_A.</t>
+          <t>3757.2_1716_A.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>10012.1_3139_S.</t>
+          <t>5580.0_2471_A.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>10002.4_5136_P.</t>
+          <t>6345.4_2376_S.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>5020.4_2167_C.</t>
+          <t>7012.1_3931_🔋.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>5522.8_2716_V.</t>
+          <t>2060.0_802_S.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>56121.5_25636_F.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>5004.5_1548_A.</t>
+          <t>6012.6_2984_P.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>4700.4_1216_V.</t>
+          <t>1027.7_364_S.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>8351.7_4153_C.</t>
+          <t>13023.5_5156_L.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>6006.6_2009_P.</t>
+          <t>6622.5_2224_E.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>10022.1_2875_M.</t>
+          <t>7025.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>6661.8_3736_P.</t>
+          <t>5051.4_1993_M.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>9791.4_3527_G.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>1012.0_375_E.</t>
+          <t>6012.6_2984_F.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>5010.3_1888_G.</t>
+          <t>4932.4_1545_E.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>10007.4_3588_V.</t>
+          <t>4078.1_1810_A.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>7127.8_1843_G.</t>
+          <t>5010.0_1872_A.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>5003.2_1389_E.</t>
+          <t>6007.1_3172_F.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>7874.8_2223_M.</t>
+          <t>5282.8_2392_C.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>4540.8_1823_A.</t>
+          <t>611.2_221_M.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>4177.9_1557_T.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>5382.2_2690_M.</t>
+          <t>1701.7_720_F.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>5869.6_2613_P.</t>
+          <t>2735.8_959_S.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>6004.0_2559_P.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>5869.6_2613_P.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>5033.4_1976_M.</t>
+          <t>4830.1_2569_C.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>6345.4_2376_S.</t>
+          <t>5072.4_1931_S.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2185.4_792_S.</t>
+          <t>5021.7_1930_A.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>9415.9_3699_G.</t>
+          <t>21207.4_6474_V.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>5029.4_1585_P.</t>
+          <t>4864.8_1353_E.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>10022.1_2875_M.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>5296.8_1844_P.</t>
+          <t>8618.0_2344_P.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>3010.0_1289_A.</t>
+          <t>9639.7_4763_P.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>5004.0_2103_C.</t>
+          <t>12524.7_3259_S.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>8396.0_2595_S.</t>
+          <t>5382.2_2690_M.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>53755.6_36604_F.</t>
+          <t>10027.3_2906_P.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>21124.1_8011_F.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>4731.9_1407_T.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>10010.0_2910_V.</t>
+          <t>5451.1_1905_T.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>4790.7_1897_F.</t>
+          <t>15637.2_5789_G.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>7022.4_3008_L.</t>
+          <t>3023.2_962_S.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>5064.3_1832_F.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>5064.3_1832_F.</t>
+          <t>3010.0_1424_A.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>56121.5_25636_F.</t>
+          <t>4797.2_1541_G.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>5004.9_1790_A.</t>
+          <t>6818.2_2036_P.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>5621.6_2375_P.</t>
+          <t>3614.8_970_🔋.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>7230.5_2794_V.</t>
+          <t>5043.1_2254_C.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>419.0_180_P.</t>
+          <t>5005.9_1755_X.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>3735.9_1928_V.</t>
+          <t>6137.8_2406_L.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>6011.5_2408_A.</t>
+          <t>1629.5_671_F.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>10027.3_2906_P.</t>
+          <t>4017.3_1883_C.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>5282.8_2392_C.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>657.7_273_S.</t>
+          <t>4692.9_1546_P.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>4850.9_2239_C.</t>
+          <t>12006.9_5463_P.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>5001.9_1291_V.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>5025.8_1214_P.</t>
+          <t>5008.0_2402_P.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>5365.6_2437_C.</t>
+          <t>4077.1_1454_S.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>10020.8_2989_M.</t>
+          <t>12545.4_3039_S.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>5007.1_1751_T.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>3958.9_1777_P.</t>
+          <t>9013.7_2337_M.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>10030.5_4765_C.</t>
+          <t>4821.0_1857_P.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>10016.9_3028_M.</t>
+          <t>10003.7_2721_V.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>9791.4_3527_G.</t>
+          <t>15504.3_3950_M.</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>21207.4_6474_V.</t>
+          <t>5256.5_1535_S.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>14119.3_5262_S.</t>
+          <t>9005.3_4344_A.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>5238.0_2781_F.</t>
+          <t>5025.8_1214_P.</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>3798.9_1319_S.</t>
+          <t>1011.0_396_L.</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>8618.0_2344_P.</t>
+          <t>4781.2_1507_A.</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>14119.3_5262_S.</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>5000.2_1932_E.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>3012.4_1258_P.</t>
+          <t>7598.7_2799_S.</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>6833.7_2100_G.</t>
+          <t>6518.4_2914_A.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>10011.5_3070_S.</t>
+          <t>6003.3_2987_M.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>3089.9_1508_C.</t>
+          <t>18102.7_4949_M.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>3026.1_1490_A.</t>
+          <t>1002.7_460_S.</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>4932.4_1545_E.</t>
+          <t>8024.4_2933_S.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>8187.1_2322_M.</t>
+          <t>2880.9_1210_L.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>5242.7_1657_S.</t>
+          <t>53755.6_36604_F.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>15223.0_6245_P.</t>
+          <t>6007.1_2393_M.</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>5000.2_1932_E.</t>
+          <t>5020.4_2167_C.</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>6010.6_2144_A.</t>
+          <t>21141.5_8155_F.</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>7420.2_4318_C.</t>
+          <t>7985.2_2173_P.</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>9029.6_4595_P.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>12545.4_3039_S.</t>
+          <t>2783.5_952_S.</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>1114.9_359_S.</t>
+          <t>8008.0_2930_A.</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>9007.1_3080_P.</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>10006.0_2772_V.</t>
+          <t>960.0_1109_A.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>611.2_221_M.</t>
+          <t>7569.4_2477_V.</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>6804.1_2088_P.</t>
+          <t>25020.8_7832_V.</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>5014.8_2009_A.</t>
+          <t>1884.9_866_S.</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>22320.3_9183_F.</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>4786.5_1898_P.</t>
+          <t>10058.8_3483_F.</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>5027.8_1361_P.</t>
+          <t>9012.4_2700_M.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>9007.1_3080_P.</t>
+          <t>7874.8_2223_M.</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>5008.0_2402_P.</t>
+          <t>4540.8_1823_A.</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>791.5_266_G.</t>
+          <t>4013.7_1173_V.</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>6011.8_1873_M.</t>
+          <t>9555.5_5689_S.</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>13023.5_5156_L.</t>
+          <t>4921.0_2491_A.</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>7145.5_2856_E.</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>10008.1_2966_M.</t>
+          <t>2305.1_940_S.</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>3412.3_1947_C.</t>
+          <t>1366.2_487_L.</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>1366.2_487_L.</t>
+          <t>8196.1_2807_T.</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>5028.5_4433_S.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>6038.2_2121_P.</t>
+          <t>18665.3_4638_S.</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>4214.8_2018_A.</t>
+          <t>7006.7_5717_S.</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>6084.1_2156_V.</t>
+          <t>4896.8_2251_L.</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>773.5_238_S.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>15016.9_6221_G.</t>
+          <t>401.2_179_S.</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>12524.7_3259_S.</t>
+          <t>2036.1_839_S.</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>8132.9_2716_S.</t>
+          <t>7880.9_2433_E.</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>9507.9_2851_M.</t>
+          <t>6011.5_2408_A.</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>5040.0_2514_C.</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>15504.3_3950_M.</t>
+          <t>5004.5_1548_A.</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>15057.9_8625_F.</t>
+          <t>21106.2_7925_P.</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>5040.0_2514_C.</t>
+          <t>10012.1_3139_S.</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>37036.6_17889_F.</t>
+          <t>3004.6_746_V.</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>4678.8_1840_A.</t>
+          <t>6903.6_2566_G.</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>553.2_224_S.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>5581.6_3687_P.</t>
+          <t>5579.8_1990_E.</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>3023.2_962_S.</t>
+          <t>773.5_238_S.</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>8024.4_2933_S.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>531.0_343_A.</t>
+          <t>5029.4_1585_P.</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>8367.5_4269_C.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>9639.7_4763_P.</t>
+          <t>2051.8_860_S.</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>4613.1_1806_A.</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>7006.7_5717_S.</t>
+          <t>5014.8_2009_A.</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>15637.2_5789_G.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>8442.5_3038_G.</t>
+          <t>1443.0_851_A.</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>4830.1_2569_C.</t>
+          <t>3010.0_1685_A.</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>16008.9_5968_S.</t>
+          <t>2504.7_703_🔋.</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>123.0_5992_A.</t>
+          <t>5770.8_2848_G.</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>5072.4_1931_S.</t>
+          <t>10010.0_2910_V.</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>6004.0_2559_P.</t>
+          <t>10006.0_2772_V.</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>8218.3_2327_P.</t>
+          <t>1380.0_562_A.</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>5007.1_1751_T.</t>
+          <t>2175.4_712_S.</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>6011.8_1873_M.</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>5235.4_1766_P.</t>
+          <t>5100.0_2587_A.</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>12008.4_3832_G.</t>
+          <t>6804.1_2088_P.</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>6951.4_2856_S.</t>
+          <t>6833.7_2100_G.</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>6818.2_2036_P.</t>
+          <t>15194.4_3911_S.</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>5365.6_2437_C.</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>6620.4_2477_P.</t>
+          <t>5581.6_3687_P.</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>4921.0_2491_A.</t>
+          <t>21442.0_7959_F.</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>15194.4_3911_S.</t>
+          <t>1114.9_359_S.</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>12342.9_3211_M.</t>
+          <t>15016.9_6221_G.</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>2011.7_731_S.</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>12521.4_4814_M.</t>
+          <t>5242.7_1657_S.</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>7114.0_2850_S.</t>
+          <t>8218.3_2327_P.</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>5086.0_1810_G.</t>
+          <t>9562.8_3145_M.</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>10533.4_4020_F.</t>
+          <t>8120.9_2737_G.</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>17003.0_7696_P.</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>1002.7_460_S.</t>
+          <t>5163.5_1775_V.</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>2783.5_952_S.</t>
+          <t>5005.4_2618_L.</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>5004.9_1790_A.</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>5235.4_1766_P.</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>2047.9_924_L.</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>6007.4_1804_G.</t>
+          <t>6006.6_2009_P.</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>4791.5_1524_E.</t>
+          <t>10106.6_3354_M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>17012.6_5869_T.</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>5301.0_2064_F.</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>14014.7_3537_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>7502.4_3467_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>6038.2_2121_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>14019.6_6253_L.</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>7127.8_1843_G.</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>6007.4_1804_G.</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>5013.9_1673_A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>7230.5_2794_V.</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>657.7_273_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>6951.4_2856_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>7312.2_2446_G.</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>5022.5_1222_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>6536.2_2241_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>553.2_224_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>5086.0_1810_G.</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>10011.5_3070_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>8187.1_2322_M.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_500km_2026.xlsx
+++ b/Ranking_CNB_500km_2026.xlsx
@@ -454,12 +454,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>627,7 km</t>
+          <t>642,9 km</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>9.913 m</t>
+          <t>10.089 m</t>
         </is>
       </c>
     </row>
@@ -471,12 +471,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>467,5 km</t>
+          <t>481,8 km</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>6.241 m</t>
+          <t>6.411 m</t>
         </is>
       </c>
     </row>
@@ -505,12 +505,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>237,4 km</t>
+          <t>243,2 km</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.907 m</t>
+          <t>1.948 m</t>
         </is>
       </c>
     </row>
@@ -534,34 +534,34 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Fernanda G.</t>
+          <t>Mateus  M.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>188,5 km</t>
+          <t>192,8 km</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.251 m</t>
+          <t>2.481 m</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Mateus  M.</t>
+          <t>Fernanda G.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>187,8 km</t>
+          <t>188,5 km</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.423 m</t>
+          <t>2.251 m</t>
         </is>
       </c>
     </row>
@@ -590,46 +590,46 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>166,9 km</t>
+          <t>171,9 km</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.870 m</t>
+          <t>1.929 m</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Gleydson G.</t>
+          <t>Cassia C.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>152,0 km</t>
+          <t>152,7 km</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.027 m</t>
+          <t>1.901 m</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cassia C.</t>
+          <t>Gleydson G.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>147,5 km</t>
+          <t>152,0 km</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.845 m</t>
+          <t>1.027 m</t>
         </is>
       </c>
     </row>
@@ -641,12 +641,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>140,5 km</t>
+          <t>150,5 km</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.930 m</t>
+          <t>2.028 m</t>
         </is>
       </c>
     </row>
@@ -658,12 +658,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>129,0 km</t>
+          <t>134,0 km</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.412 m</t>
+          <t>1.472 m</t>
         </is>
       </c>
     </row>
@@ -692,12 +692,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>115,6 km</t>
+          <t>120,9 km</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.071 m</t>
+          <t>1.127 m</t>
         </is>
       </c>
     </row>
@@ -811,12 +811,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>65,8 km</t>
+          <t>70,8 km</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>740 m</t>
+          <t>796 m</t>
         </is>
       </c>
     </row>
@@ -828,12 +828,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>55,8 km</t>
+          <t>60,8 km</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>584 m</t>
+          <t>642 m</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>55,7 km</t>
+          <t>60,7 km</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>501 m</t>
+          <t>554 m</t>
         </is>
       </c>
     </row>
@@ -891,68 +891,68 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Karine F.</t>
+          <t>Thaisa V.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>25,1 km</t>
+          <t>25,5 km</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>294 m</t>
+          <t>352 m</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Eduardo T.</t>
+          <t>Karine F.</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>22,8 km</t>
+          <t>25,1 km</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>234 m</t>
+          <t>294 m</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Thaisa V.</t>
+          <t>Filipe M.</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>19,5 km</t>
+          <t>24,6 km</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>272 m</t>
+          <t>358 m</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Filipe M.</t>
+          <t>Eduardo T.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>18,4 km</t>
+          <t>22,8 km</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>280 m</t>
+          <t>234 m</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A329"/>
+  <dimension ref="A1:A345"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1014,2177 +1014,2177 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>9007.1_3080_P.</t>
+          <t>4850.9_2239_C.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>7576.8_2823_P.</t>
+          <t>18107.4_4577_M.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>6010.6_2144_A.</t>
+          <t>531.0_343_A.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4078.1_1810_A.</t>
+          <t>4731.9_1407_T.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5008.0_2402_P.</t>
+          <t>9756.3_2793_M.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5296.8_1844_P.</t>
+          <t>5287.4_1835_V.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10348.3_2647_S.</t>
+          <t>8196.1_2807_T.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>9555.5_5689_S.</t>
+          <t>1629.5_671_F.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6779.9_2003_E.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5770.8_2848_G.</t>
+          <t>10016.9_3028_M.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>5086.0_1810_G.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5029.4_1585_P.</t>
+          <t>5904.3_2699_P.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6011.5_2408_A.</t>
+          <t>7576.8_2823_P.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>17003.0_7696_P.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>8396.0_2595_S.</t>
+          <t>5029.4_1585_P.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>4013.7_1173_V.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>2735.8_959_S.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>6036.4_2875_V.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5579.8_1990_E.</t>
+          <t>10006.9_3646_F.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5000.6_1856_M.</t>
+          <t>6004.0_2559_P.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2880.9_1210_L.</t>
+          <t>2305.1_940_S.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>8187.1_2322_M.</t>
+          <t>12022.7_5417_L.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>8008.0_2930_A.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5005.9_1755_X.</t>
+          <t>4821.0_1857_P.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>6518.4_2914_A.</t>
+          <t>6007.1_3172_F.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3026.1_1490_A.</t>
+          <t>7230.5_2794_V.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5451.1_1905_T.</t>
+          <t>4613.1_1806_A.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1027.7_364_S.</t>
+          <t>7569.4_2477_V.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>10030.5_4765_C.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>5008.2_1646_A.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>4932.4_1545_E.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>419.0_180_P.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>6007.1_2393_M.</t>
+          <t>10503.6_3278_M.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10002.4_5136_P.</t>
+          <t>5522.8_2716_V.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5238.0_2781_F.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>17003.0_7696_P.</t>
+          <t>5020.4_2167_C.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>4692.9_1546_P.</t>
+          <t>611.2_221_M.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>5072.4_1931_S.</t>
+          <t>7502.4_3467_P.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>8618.0_2344_P.</t>
+          <t>9013.7_2337_M.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3010.0_1424_A.</t>
+          <t>8187.1_2322_M.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>8351.7_4153_C.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>8351.7_4153_C.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>8481.2_2463_🔋.</t>
+          <t>15016.9_6221_G.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>5003.2_1389_E.</t>
+          <t>3012.4_1258_P.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>8618.0_2344_P.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>6804.1_2088_P.</t>
+          <t>123.0_5992_A.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>12008.4_3832_G.</t>
+          <t>10007.4_3588_V.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>4688.1_2291_C.</t>
+          <t>1011.0_396_L.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>9012.4_2700_M.</t>
+          <t>1366.2_487_L.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>9209.1_3141_E.</t>
+          <t>4000.6_1659_S.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3412.3_1947_C.</t>
+          <t>960.0_1109_A.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>8132.9_2716_S.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>4078.1_1810_A.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1114.9_359_S.</t>
+          <t>4814.5_1705_🔋.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1012.0_375_E.</t>
+          <t>7992.7_2506_F.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>5580.0_2471_A.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>6006.6_2009_P.</t>
+          <t>7880.9_2433_E.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>1027.7_364_S.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>15186.5_3866_S.</t>
+          <t>8253.0_2972_🔋.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>4678.8_1840_A.</t>
+          <t>4700.4_1216_V.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>5051.4_1993_M.</t>
+          <t>6012.6_2984_F.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>9029.6_4595_P.</t>
+          <t>6007.1_2393_M.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>12326.4_4833_S.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>553.2_224_S.</t>
+          <t>14019.6_6253_L.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>13023.5_5156_L.</t>
+          <t>10002.4_5136_P.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2504.7_703_🔋.</t>
+          <t>3597.6_2910_E.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>8442.5_3038_G.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>4896.8_2251_L.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>5382.2_2690_M.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>5085.1_1840_G.</t>
+          <t>1114.9_359_S.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>6536.2_2241_P.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>10106.6_2889_P.</t>
+          <t>9562.8_3145_M.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>4790.7_1897_F.</t>
+          <t>5009.1_2246_C.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>15637.2_5789_G.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>960.0_1109_A.</t>
+          <t>16397.3_4254_S.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>5004.9_1790_A.</t>
+          <t>6472.0_2501_S.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>5287.4_1835_V.</t>
+          <t>2186.2_736_G.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>5010.0_1872_A.</t>
+          <t>1443.0_851_A.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>9006.5_3085_X.</t>
+          <t>6007.4_1804_G.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>4153.2_3559_P.</t>
+          <t>4028.8_1699_L.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>5256.5_1535_S.</t>
+          <t>37036.6_17889_F.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2004.9_754_S.</t>
+          <t>15637.2_5789_G.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>7569.4_2477_V.</t>
+          <t>4540.8_1823_A.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>6007.1_3172_F.</t>
+          <t>10001.9_4466_P.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>4781.2_1507_A.</t>
+          <t>2064.3_708_S.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>10011.5_3070_S.</t>
+          <t>21106.2_7925_P.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>15194.4_3911_S.</t>
+          <t>21124.1_8011_F.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>10533.4_4020_F.</t>
+          <t>7145.5_2856_E.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1380.0_562_A.</t>
+          <t>14117.6_3844_M.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>7312.2_2446_G.</t>
+          <t>5008.0_2402_P.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>7039.1_2754_S.</t>
+          <t>9639.7_4763_P.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>4214.8_2018_A.</t>
+          <t>13023.5_5156_L.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>5010.3_1888_G.</t>
+          <t>5014.3_1731_F.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>4932.4_1545_E.</t>
+          <t>4692.9_1546_P.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1629.5_671_F.</t>
+          <t>5163.5_1775_V.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>5027.8_1361_P.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>6661.8_3736_P.</t>
+          <t>3089.9_1508_C.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>5021.7_1930_A.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>3010.0_1289_A.</t>
+          <t>2504.7_703_🔋.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>4700.4_1216_V.</t>
+          <t>553.2_224_S.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>5025.8_1214_P.</t>
+          <t>8442.5_3038_G.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>6011.8_1873_M.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>3958.9_1777_P.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>5004.5_1548_A.</t>
+          <t>5014.8_2009_A.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>4000.6_1659_S.</t>
+          <t>5072.4_1931_S.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>5064.3_1832_F.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>4613.1_1806_A.</t>
+          <t>10058.8_3483_F.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>6007.4_1804_G.</t>
+          <t>6011.5_2408_A.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>7992.7_2506_F.</t>
+          <t>25020.8_7832_V.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>18102.7_4949_M.</t>
+          <t>5013.9_1673_A.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>123.0_5992_A.</t>
+          <t>10007.8_2733_V.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>7420.2_4318_C.</t>
+          <t>6016.7_2122_M.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>10020.8_2989_M.</t>
+          <t>5224.2_2340_C.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>5119.6_3153_M.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>10012.3_3067_S.</t>
+          <t>1012.0_375_E.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>5009.1_2246_C.</t>
+          <t>208.3_85_P.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>10020.8_2989_M.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>6833.7_2100_G.</t>
+          <t>5100.0_2587_A.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>3012.4_1258_P.</t>
+          <t>5581.6_3687_P.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>10016.9_3028_M.</t>
+          <t>3023.2_962_S.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>773.5_238_S.</t>
+          <t>7003.6_2437_P.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>14014.7_3537_S.</t>
+          <t>21442.0_7959_F.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>7003.6_2437_P.</t>
+          <t>21141.5_8155_F.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>5382.2_2690_M.</t>
+          <t>5451.1_1905_T.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>6818.2_2036_P.</t>
+          <t>10348.3_2647_S.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2186.2_736_G.</t>
+          <t>7598.7_2799_S.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>5010.0_1872_A.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>657.7_273_S.</t>
+          <t>4705.5_1241_G.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>25020.8_7832_V.</t>
+          <t>5242.7_1657_S.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>5282.8_2392_C.</t>
+          <t>8506.3_4050_C.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>3735.9_1928_V.</t>
+          <t>15223.0_6245_P.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>791.5_266_G.</t>
+          <t>8120.9_2737_G.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>4735.2_997_S.</t>
+          <t>7022.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>5040.0_2971_A.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2355.5_726_S.</t>
+          <t>9012.4_2700_M.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>9005.3_4344_A.</t>
+          <t>5004.9_1790_A.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>3614.8_970_🔋.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>10022.1_2875_M.</t>
+          <t>4791.5_1524_E.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1002.7_460_S.</t>
+          <t>18102.7_4949_M.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>3023.2_962_S.</t>
+          <t>2051.8_860_S.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>7114.0_2850_S.</t>
+          <t>6779.9_2003_E.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>5163.5_1775_V.</t>
+          <t>4790.7_1897_F.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>5028.5_4433_S.</t>
+          <t>4077.1_1454_S.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>5100.0_2587_A.</t>
+          <t>53755.6_36604_F.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>5242.7_1657_S.</t>
+          <t>6620.4_2477_P.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>7419.2_3469_F.</t>
+          <t>7114.0_2850_S.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>7001.2_3357_M.</t>
+          <t>12342.9_3211_M.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>791.5_266_G.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>9791.4_3527_G.</t>
+          <t>6804.1_2088_P.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>5869.6_2613_P.</t>
+          <t>5238.0_2781_F.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>4921.0_2491_A.</t>
+          <t>2000.0_724_A.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2783.5_952_S.</t>
+          <t>18665.3_4638_S.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>8367.5_4269_C.</t>
+          <t>3004.6_746_V.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>10011.5_3070_S.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>15504.3_3950_M.</t>
+          <t>5007.4_1601_A.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>5005.8_1527_S.</t>
+          <t>10533.4_4020_F.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>5000.2_1932_E.</t>
+          <t>6046.5_3239_S.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>1443.0_851_A.</t>
+          <t>3757.2_1716_A.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>611.2_221_M.</t>
+          <t>8024.4_2933_S.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>5580.0_2471_A.</t>
+          <t>6600.2_1915_M.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>21106.2_7925_P.</t>
+          <t>5296.8_1844_P.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>6345.4_2376_S.</t>
+          <t>6903.6_2566_G.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>21207.4_6474_V.</t>
+          <t>15194.4_3911_S.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>10003.7_2721_V.</t>
+          <t>5003.2_1389_E.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>3580.9_1198_S.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>5022.5_1222_P.</t>
+          <t>7312.2_2446_G.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>3089.9_1508_C.</t>
+          <t>9555.5_5689_S.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>1366.2_487_L.</t>
+          <t>5022.5_1222_P.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>7598.7_2799_S.</t>
+          <t>7420.2_4318_C.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>6084.1_2156_V.</t>
+          <t>9507.9_2851_M.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>16008.9_5968_S.</t>
+          <t>5144.4_2349_P.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>419.0_180_P.</t>
+          <t>6006.6_2009_P.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>10012.1_3139_S.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2060.0_802_S.</t>
+          <t>6173.6_2865_M.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>8196.1_2807_T.</t>
+          <t>9415.9_3699_G.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>4017.3_1883_C.</t>
+          <t>10006.0_2772_V.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>10012.1_3139_S.</t>
+          <t>5001.9_1291_V.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>5144.4_2349_P.</t>
+          <t>4972.5_2522_S.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>7006.7_5717_S.</t>
+          <t>7874.8_2223_M.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>10010.0_2910_V.</t>
+          <t>5724.1_3694_S.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>7127.8_1843_G.</t>
+          <t>9007.1_3080_P.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>401.2_179_S.</t>
+          <t>6661.8_3736_P.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>4830.1_2569_C.</t>
+          <t>6137.8_2406_L.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>8218.3_2327_P.</t>
+          <t>6833.7_2100_G.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>7874.8_2223_M.</t>
+          <t>2783.5_952_S.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>6003.3_2987_M.</t>
+          <t>4153.2_3559_P.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>4788.2_1476_P.</t>
+          <t>16008.9_5968_S.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>6620.4_2477_P.</t>
+          <t>2047.9_924_L.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>5004.0_2103_C.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>4540.8_1823_A.</t>
+          <t>4864.8_1353_E.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>16520.2_4844_M.</t>
+          <t>3798.9_1319_S.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>8132.9_2716_S.</t>
+          <t>4797.2_1541_G.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>9507.9_2851_M.</t>
+          <t>10031.8_2663_P.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>7127.8_1843_G.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>4797.2_1541_G.</t>
+          <t>8218.3_2327_P.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>14014.7_3537_S.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>16397.3_4254_S.</t>
+          <t>5000.2_1932_E.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>7516.9_3203_A.</t>
+          <t>8481.2_2463_🔋.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>10007.4_3588_V.</t>
+          <t>6818.2_2036_P.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>3757.2_1716_A.</t>
+          <t>10003.3_3845_P.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>5235.4_1766_P.</t>
+          <t>5000.6_1856_M.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2011.7_731_S.</t>
+          <t>5299.8_2406_C.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>5033.4_1976_M.</t>
+          <t>7985.2_2173_P.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>7419.2_3469_F.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2064.3_708_S.</t>
+          <t>10006.9_3646_X.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>10030.0_3041_G.</t>
+          <t>2355.5_726_S.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>6038.2_2121_P.</t>
+          <t>401.2_179_S.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>20105.6_7766_F.</t>
+          <t>7012.1_3931_🔋.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>1701.7_720_F.</t>
+          <t>5010.3_3392_P.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2000.0_724_A.</t>
+          <t>4768.0_1875_L.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>12022.7_5417_L.</t>
+          <t>6610.9_1738_P.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>14009.7_4401_V.</t>
+          <t>15186.5_3866_S.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>531.0_343_A.</t>
+          <t>5025.8_1214_P.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>9639.7_4763_P.</t>
+          <t>4969.4_2146_P.</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>7985.2_2173_P.</t>
+          <t>7024.3_3266_L.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>8008.0_2930_A.</t>
+          <t>10174.3_3680_S.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>15223.0_6245_P.</t>
+          <t>15200.8_10718_F.</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>9029.6_4595_P.</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>5086.0_1810_G.</t>
+          <t>4781.2_1507_A.</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>10027.3_2906_P.</t>
+          <t>5365.6_2437_C.</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>3798.9_1319_S.</t>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>53755.6_36604_F.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>7022.4_3008_L.</t>
+          <t>8200.5_2738_M.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>21141.5_8155_F.</t>
+          <t>5017.7_1147_M.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>5040.0_2514_C.</t>
+          <t>3005.2_1040_L.</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>3010.0_1685_A.</t>
+          <t>2060.0_802_S.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>5043.1_2254_C.</t>
+          <t>8004.6_2357_G.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>10503.6_3278_M.</t>
+          <t>12008.4_3832_G.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>15057.9_8625_F.</t>
+          <t>6622.5_2224_E.</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>12521.4_4814_M.</t>
+          <t>1002.7_460_S.</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>15016.9_6221_G.</t>
+          <t>3006.0_1286_M.</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>6600.2_1915_M.</t>
+          <t>5085.1_1840_G.</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>18107.4_4577_M.</t>
+          <t>2175.4_712_S.</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>5235.4_1766_P.</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>5014.8_2009_A.</t>
+          <t>17012.6_5869_T.</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>7880.9_2433_E.</t>
+          <t>4830.1_2569_C.</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>10003.3_3845_P.</t>
+          <t>5005.9_1755_X.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>21124.1_8011_F.</t>
+          <t>5282.8_2392_C.</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2185.4_792_S.</t>
+          <t>6012.6_2984_P.</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>5013.9_1673_A.</t>
+          <t>3010.0_1424_A.</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>5581.6_3687_P.</t>
+          <t>2004.9_754_S.</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>16520.2_4844_M.</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>7145.5_2856_E.</t>
+          <t>14009.7_4401_V.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>6004.0_2559_P.</t>
+          <t>5011.9_1594_P.</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>10022.1_2875_M.</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>10001.9_4466_P.</t>
+          <t>2036.1_839_S.</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>2735.8_959_S.</t>
+          <t>10012.3_3067_S.</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>15057.9_8625_F.</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>9415.9_3699_G.</t>
+          <t>8396.0_2595_S.</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>1020.0_679_T.</t>
+          <t>9006.5_3085_X.</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>10008.1_2966_M.</t>
+          <t>4786.5_1898_P.</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>5005.8_1527_S.</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>3010.0_1289_A.</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>5020.4_2167_C.</t>
+          <t>5020.6_1328_M.</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>5001.9_1291_V.</t>
+          <t>22320.3_9183_F.</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>56121.5_25636_F.</t>
+          <t>10106.6_3354_M.</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>4177.9_1557_T.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>4821.0_1857_P.</t>
+          <t>10030.0_3041_G.</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>4850.9_2239_C.</t>
+          <t>10010.0_2910_V.</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>6536.2_2241_P.</t>
+          <t>10003.7_2721_V.</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>5256.5_1535_S.</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>6951.4_2856_S.</t>
+          <t>3026.1_1490_A.</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>5021.7_1930_A.</t>
+          <t>6038.2_2121_P.</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>3597.6_2910_E.</t>
+          <t>1884.9_866_S.</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>2558.7_905_S.</t>
+          <t>3735.9_1928_V.</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>4864.8_1353_E.</t>
+          <t>4763.8_1720_P.</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>7024.3_3266_L.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>7593.7_2701_E.</t>
+          <t>1083.2_390_M.</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>6903.6_2566_G.</t>
+          <t>5004.5_1548_A.</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>8506.3_4050_C.</t>
+          <t>10027.3_2906_P.</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>2002.2_938_P.</t>
+          <t>5869.6_2613_P.</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>10106.6_2889_P.</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>4896.8_2251_L.</t>
+          <t>1380.0_562_A.</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>2002.2_938_P.</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>10030.5_4765_C.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>4786.5_1898_P.</t>
+          <t>2558.7_905_S.</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>10006.9_3646_F.</t>
+          <t>4891.7_1690_F.</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>4791.5_1524_E.</t>
+          <t>5040.0_2514_C.</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>3004.6_746_V.</t>
+          <t>6345.4_2376_S.</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>12342.9_3211_M.</t>
+          <t>5770.8_2848_G.</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>5004.0_2103_C.</t>
+          <t>4214.8_2018_A.</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>4013.7_1173_V.</t>
+          <t>4735.2_997_S.</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>5064.3_1832_F.</t>
+          <t>5827.8_2106_S.</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>14019.6_6253_L.</t>
+          <t>5579.8_1990_E.</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>3006.0_1286_M.</t>
+          <t>657.7_273_S.</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>5301.0_2064_F.</t>
+          <t>4177.9_1557_T.</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>8024.4_2933_S.</t>
+          <t>8367.5_4269_C.</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>12545.4_3039_S.</t>
+          <t>15504.3_3950_M.</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>2047.9_924_L.</t>
+          <t>14119.3_5262_S.</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>8004.6_2357_G.</t>
+          <t>7593.7_2701_E.</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>6622.5_2224_E.</t>
+          <t>1020.0_679_T.</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>14119.3_5262_S.</t>
+          <t>20105.6_7766_F.</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>5365.6_2437_C.</t>
+          <t>6084.1_2156_V.</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>37036.6_17889_F.</t>
+          <t>4921.0_2491_A.</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>6610.9_1738_P.</t>
+          <t>8104.2_2652_M.</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>22320.3_9183_F.</t>
+          <t>7006.7_5717_S.</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>7230.5_2794_V.</t>
+          <t>5033.4_1976_M.</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>5904.3_2699_P.</t>
+          <t>5010.3_1888_G.</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>12006.9_5463_P.</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>7012.1_3931_🔋.</t>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>10007.8_2733_V.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>14117.6_3844_M.</t>
+          <t>3412.3_1947_C.</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>6012.6_2984_P.</t>
+          <t>5051.4_1993_M.</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>9756.3_2793_M.</t>
+          <t>2880.9_1210_L.</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>10006.0_2772_V.</t>
+          <t>5621.6_2375_P.</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>7502.4_3467_P.</t>
+          <t>4678.8_1840_A.</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>5621.6_2375_P.</t>
+          <t>3019.8_1453_F.</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>5301.0_2064_F.</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>5010.3_3392_P.</t>
+          <t>6010.6_2144_A.</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>12524.7_3259_S.</t>
+          <t>2011.7_731_S.</t>
         </is>
       </c>
     </row>
@@ -3198,112 +3198,224 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>26010.2_9812_F.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>2036.1_839_S.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>5522.8_2716_V.</t>
+          <t>12545.4_3039_S.</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>5724.1_3694_S.</t>
+          <t>10062.5_2886_M.</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>7025.4_3008_L.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>3958.9_1777_P.</t>
+          <t>9791.4_3527_G.</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>18665.3_4638_S.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>4688.1_2291_C.</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>9005.3_4344_A.</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>5027.8_1361_P.</t>
+          <t>2185.4_792_S.</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>4028.8_1699_L.</t>
+          <t>7001.2_3357_M.</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>5007.1_1751_T.</t>
+          <t>7015.4_2141_T.</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>21207.4_6474_V.</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>10006.9_3646_X.</t>
+          <t>7516.9_3203_A.</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>5008.2_1646_A.</t>
+          <t>6011.8_1873_M.</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>6016.7_2122_M.</t>
+          <t>773.5_238_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>5007.1_1751_T.</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>12524.7_3259_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>6518.4_2914_A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>26010.2_9812_F.</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>5028.5_4433_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>9209.1_3141_E.</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>4788.2_1476_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>6951.4_2856_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>1701.7_720_F.</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>5043.1_2254_C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>7025.4_3008_L.</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>3010.0_1685_A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>4017.3_1883_C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>6003.3_2987_M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>56121.5_25636_F.</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>7039.1_2754_S.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_500km_2026.xlsx
+++ b/Ranking_CNB_500km_2026.xlsx
@@ -471,12 +471,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>481,8 km</t>
+          <t>491,8 km</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>6.411 m</t>
+          <t>6.543 m</t>
         </is>
       </c>
     </row>
@@ -522,46 +522,46 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>194,7 km</t>
+          <t>202,8 km</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.848 m</t>
+          <t>1.921 m</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Mateus  M.</t>
+          <t>Fernanda G.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>192,8 km</t>
+          <t>193,6 km</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.481 m</t>
+          <t>2.310 m</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Fernanda G.</t>
+          <t>Mateus  M.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>188,5 km</t>
+          <t>192,8 km</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.251 m</t>
+          <t>2.481 m</t>
         </is>
       </c>
     </row>
@@ -590,12 +590,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>171,9 km</t>
+          <t>177,9 km</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.929 m</t>
+          <t>2.007 m</t>
         </is>
       </c>
     </row>
@@ -789,34 +789,34 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Jhonny E.</t>
+          <t>Izac S.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>73,1 km</t>
+          <t>81,4 km</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>728 m</t>
+          <t>924 m</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Izac S.</t>
+          <t>Jhonny E.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>70,8 km</t>
+          <t>73,1 km</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>796 m</t>
+          <t>728 m</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A345"/>
+  <dimension ref="A1:A350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1014,2408 +1014,2443 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4850.9_2239_C.</t>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>18107.4_4577_M.</t>
+          <t>10007.8_2733_V.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>531.0_343_A.</t>
+          <t>4921.0_2491_A.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>5004.9_1790_A.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>9756.3_2793_M.</t>
+          <t>6010.6_2144_A.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5287.4_1835_V.</t>
+          <t>12326.4_4833_S.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>8196.1_2807_T.</t>
+          <t>6011.8_1873_M.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1629.5_671_F.</t>
+          <t>10002.4_5136_P.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>5025.8_1214_P.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10016.9_3028_M.</t>
+          <t>3412.3_1947_C.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5086.0_1810_G.</t>
+          <t>25020.8_7832_V.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5904.3_2699_P.</t>
+          <t>6012.6_2984_F.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>7576.8_2823_P.</t>
+          <t>1380.0_562_A.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>17003.0_7696_P.</t>
+          <t>6661.8_3736_P.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5029.4_1585_P.</t>
+          <t>15194.4_3911_S.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>4013.7_1173_V.</t>
+          <t>3798.9_1319_S.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2735.8_959_S.</t>
+          <t>14019.6_6253_L.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6036.4_2875_V.</t>
+          <t>7003.6_2437_P.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10006.9_3646_F.</t>
+          <t>5827.8_2106_S.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6004.0_2559_P.</t>
+          <t>5579.8_1990_E.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>8008.0_2930_A.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>12022.7_5417_L.</t>
+          <t>5029.4_1585_P.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>8008.0_2930_A.</t>
+          <t>4678.8_1840_A.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>4821.0_1857_P.</t>
+          <t>8196.1_2807_T.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>6007.1_3172_F.</t>
+          <t>960.0_1109_A.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>7230.5_2794_V.</t>
+          <t>4896.8_2251_L.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>4613.1_1806_A.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>7569.4_2477_V.</t>
+          <t>7419.2_3469_F.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10030.5_4765_C.</t>
+          <t>5724.1_3694_S.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5008.2_1646_A.</t>
+          <t>17003.0_7696_P.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>4932.4_1545_E.</t>
+          <t>14119.3_5262_S.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>419.0_180_P.</t>
+          <t>10003.7_2721_V.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10503.6_3278_M.</t>
+          <t>5451.1_1905_T.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>5522.8_2716_V.</t>
+          <t>9029.6_4595_P.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>4763.8_1720_P.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5020.4_2167_C.</t>
+          <t>12545.4_3039_S.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>611.2_221_M.</t>
+          <t>2064.3_708_S.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>7502.4_3467_P.</t>
+          <t>6804.1_2088_P.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>8187.1_2322_M.</t>
+          <t>5022.5_1222_P.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>8351.7_4153_C.</t>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>6038.2_2121_P.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>15016.9_6221_G.</t>
+          <t>6903.6_2566_G.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3012.4_1258_P.</t>
+          <t>6035.0_2481_P.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>8618.0_2344_P.</t>
+          <t>21124.1_8011_F.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>123.0_5992_A.</t>
+          <t>7874.8_2223_M.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>10007.4_3588_V.</t>
+          <t>8024.4_2933_S.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>5235.4_1766_P.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1366.2_487_L.</t>
+          <t>4821.0_1857_P.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>4000.6_1659_S.</t>
+          <t>8253.0_2972_🔋.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>960.0_1109_A.</t>
+          <t>1002.7_460_S.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>8132.9_2716_S.</t>
+          <t>4797.2_1541_G.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>4078.1_1810_A.</t>
+          <t>10012.3_3067_S.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>6011.5_2408_A.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>7992.7_2506_F.</t>
+          <t>2175.4_712_S.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>5580.0_2471_A.</t>
+          <t>1020.0_679_T.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>7880.9_2433_E.</t>
+          <t>7114.0_2850_S.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1027.7_364_S.</t>
+          <t>6007.4_1804_G.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>6173.6_2865_M.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>4700.4_1216_V.</t>
+          <t>4786.5_1898_P.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>8618.0_2344_P.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>6007.1_2393_M.</t>
+          <t>5008.2_1646_A.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>5100.0_2587_A.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>14019.6_6253_L.</t>
+          <t>10030.5_4765_C.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>10002.4_5136_P.</t>
+          <t>8351.7_4153_C.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>3597.6_2910_E.</t>
+          <t>7880.9_2433_E.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>6818.2_2036_P.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>4896.8_2251_L.</t>
+          <t>3958.9_1777_P.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>5382.2_2690_M.</t>
+          <t>5299.8_2406_C.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1114.9_359_S.</t>
+          <t>8120.9_2737_G.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>6536.2_2241_P.</t>
+          <t>657.7_273_S.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>5081.5_1647_G.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>5009.1_2246_C.</t>
+          <t>5365.6_2437_C.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>10020.8_2989_M.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>16397.3_4254_S.</t>
+          <t>1027.7_364_S.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>3006.0_1286_M.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2186.2_736_G.</t>
+          <t>7006.7_5717_S.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1443.0_851_A.</t>
+          <t>8187.1_2322_M.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>6007.4_1804_G.</t>
+          <t>7598.7_2799_S.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>4028.8_1699_L.</t>
+          <t>9791.4_3527_G.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>37036.6_17889_F.</t>
+          <t>2004.9_754_S.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>15637.2_5789_G.</t>
+          <t>4791.5_1524_E.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>4540.8_1823_A.</t>
+          <t>4078.1_1810_A.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10001.9_4466_P.</t>
+          <t>18665.3_4638_S.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2064.3_708_S.</t>
+          <t>3089.9_1508_C.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>21106.2_7925_P.</t>
+          <t>8481.2_2463_🔋.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>21124.1_8011_F.</t>
+          <t>5017.7_1147_M.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>7145.5_2856_E.</t>
+          <t>10106.6_3354_M.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>14117.6_3844_M.</t>
+          <t>4688.1_2291_C.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>5008.0_2402_P.</t>
+          <t>4017.3_1883_C.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>9639.7_4763_P.</t>
+          <t>2735.8_959_S.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>13023.5_5156_L.</t>
+          <t>5072.4_1931_S.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>5064.3_1832_F.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>4692.9_1546_P.</t>
+          <t>6016.7_2122_M.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>5163.5_1775_V.</t>
+          <t>553.2_224_S.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>5027.8_1361_P.</t>
+          <t>7312.2_2446_G.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>3089.9_1508_C.</t>
+          <t>4731.9_1407_T.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>5021.7_1930_A.</t>
+          <t>4932.4_1545_E.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2504.7_703_🔋.</t>
+          <t>3023.2_962_S.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>553.2_224_S.</t>
+          <t>4540.8_1823_A.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>8442.5_3038_G.</t>
+          <t>10062.5_2886_M.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>12521.4_4814_M.</t>
+          <t>2185.4_792_S.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>3958.9_1777_P.</t>
+          <t>5028.5_4433_S.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>5014.8_2009_A.</t>
+          <t>123.0_5992_A.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>5072.4_1931_S.</t>
+          <t>9012.4_2700_M.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>5064.3_1832_F.</t>
+          <t>4177.9_1557_T.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>53755.6_36604_F.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>6011.5_2408_A.</t>
+          <t>5027.8_1361_P.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>25020.8_7832_V.</t>
+          <t>5007.4_1601_A.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>5013.9_1673_A.</t>
+          <t>14117.6_3844_M.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>10007.8_2733_V.</t>
+          <t>6833.7_2100_G.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>6016.7_2122_M.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>5224.2_2340_C.</t>
+          <t>12524.7_3259_S.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>16397.3_4254_S.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1012.0_375_E.</t>
+          <t>5242.7_1657_S.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>10348.3_2647_S.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>10020.8_2989_M.</t>
+          <t>5040.0_2514_C.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>5100.0_2587_A.</t>
+          <t>6472.0_2501_S.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>5581.6_3687_P.</t>
+          <t>5008.0_2402_P.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>3023.2_962_S.</t>
+          <t>3005.2_1040_L.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>7003.6_2437_P.</t>
+          <t>4613.1_1806_A.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>5020.4_2167_C.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>21141.5_8155_F.</t>
+          <t>4768.0_1875_L.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>5451.1_1905_T.</t>
+          <t>8104.2_2652_M.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>10348.3_2647_S.</t>
+          <t>9507.9_2851_M.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>7598.7_2799_S.</t>
+          <t>9005.3_4344_A.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>5010.0_1872_A.</t>
+          <t>10058.8_3483_F.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>2002.2_938_P.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>5242.7_1657_S.</t>
+          <t>8200.5_2738_M.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>8506.3_4050_C.</t>
+          <t>21141.5_8155_F.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>15223.0_6245_P.</t>
+          <t>5010.3_1888_G.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>401.2_179_S.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>7022.4_3008_L.</t>
+          <t>7576.8_2823_P.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>5040.0_2971_A.</t>
+          <t>9756.3_2793_M.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>9012.4_2700_M.</t>
+          <t>7015.4_2141_T.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>5004.9_1790_A.</t>
+          <t>17012.6_5869_T.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>3757.2_1716_A.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>4791.5_1524_E.</t>
+          <t>7502.4_3467_P.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>18102.7_4949_M.</t>
+          <t>1011.0_396_L.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>10106.6_2889_P.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>6779.9_2003_E.</t>
+          <t>6610.9_1738_P.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>4790.7_1897_F.</t>
+          <t>4788.2_1476_P.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>15057.9_8625_F.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>53755.6_36604_F.</t>
+          <t>8506.3_4050_C.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>6620.4_2477_P.</t>
+          <t>3580.9_1198_S.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>7114.0_2850_S.</t>
+          <t>9006.5_3085_X.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>12342.9_3211_M.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>791.5_266_G.</t>
+          <t>5013.9_1673_A.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>6804.1_2088_P.</t>
+          <t>5282.8_2392_C.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>5238.0_2781_F.</t>
+          <t>2060.0_802_S.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2000.0_724_A.</t>
+          <t>6003.3_2987_M.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>18665.3_4638_S.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>3004.6_746_V.</t>
+          <t>5770.8_2848_G.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>10011.5_3070_S.</t>
+          <t>5000.6_1856_M.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>5007.4_1601_A.</t>
+          <t>10006.9_3646_F.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>10533.4_4020_F.</t>
+          <t>4214.8_2018_A.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>4972.5_2522_S.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>3757.2_1716_A.</t>
+          <t>5382.2_2690_M.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>8024.4_2933_S.</t>
+          <t>4864.8_1353_E.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>6600.2_1915_M.</t>
+          <t>21207.4_6474_V.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>5296.8_1844_P.</t>
+          <t>12008.4_3832_G.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>6903.6_2566_G.</t>
+          <t>14014.7_3537_S.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>15194.4_3911_S.</t>
+          <t>5287.4_1835_V.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>5003.2_1389_E.</t>
+          <t>7569.4_2477_V.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>9639.7_4763_P.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>7312.2_2446_G.</t>
+          <t>10011.5_3070_S.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>9555.5_5689_S.</t>
+          <t>10012.1_3139_S.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>5022.5_1222_P.</t>
+          <t>15200.8_10718_F.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>7420.2_4318_C.</t>
+          <t>2036.1_839_S.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>9507.9_2851_M.</t>
+          <t>6007.1_3172_F.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>5144.4_2349_P.</t>
+          <t>26010.2_9812_F.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>6006.6_2009_P.</t>
+          <t>4814.5_1705_🔋.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>10012.1_3139_S.</t>
+          <t>1012.0_375_E.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>6173.6_2865_M.</t>
+          <t>7024.3_3266_L.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>9415.9_3699_G.</t>
+          <t>5051.4_1993_M.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>10006.0_2772_V.</t>
+          <t>4000.6_1659_S.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>5001.9_1291_V.</t>
+          <t>7230.5_2794_V.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>4972.5_2522_S.</t>
+          <t>3004.6_746_V.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>7874.8_2223_M.</t>
+          <t>1083.2_390_M.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>5724.1_3694_S.</t>
+          <t>21106.2_7925_P.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>9007.1_3080_P.</t>
+          <t>4891.7_1690_F.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>6661.8_3736_P.</t>
+          <t>5224.2_2340_C.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>4692.9_1546_P.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>6833.7_2100_G.</t>
+          <t>9007.1_3080_P.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2783.5_952_S.</t>
+          <t>2305.1_940_S.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>4153.2_3559_P.</t>
+          <t>20105.6_7766_F.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>16008.9_5968_S.</t>
+          <t>10030.0_3041_G.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2047.9_924_L.</t>
+          <t>6137.8_2406_L.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>5004.0_2103_C.</t>
+          <t>5301.0_2064_F.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>4864.8_1353_E.</t>
+          <t>10030.1_3124_M.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>3798.9_1319_S.</t>
+          <t>4781.2_1507_A.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>4797.2_1541_G.</t>
+          <t>5005.4_2618_L.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>10031.8_2663_P.</t>
+          <t>5020.6_1328_M.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>7127.8_1843_G.</t>
+          <t>56121.5_25636_F.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>8218.3_2327_P.</t>
+          <t>6622.5_2224_E.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>14014.7_3537_S.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>5000.2_1932_E.</t>
+          <t>10016.9_3028_M.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>8481.2_2463_🔋.</t>
+          <t>7012.1_3931_🔋.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>6818.2_2036_P.</t>
+          <t>6779.9_2003_E.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>10003.3_3845_P.</t>
+          <t>10174.3_3680_S.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>5000.6_1856_M.</t>
+          <t>3010.0_1289_A.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>5299.8_2406_C.</t>
+          <t>6007.1_2393_M.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>7985.2_2173_P.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>7419.2_3469_F.</t>
+          <t>4077.1_1454_S.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>10006.9_3646_X.</t>
+          <t>2000.0_724_A.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2355.5_726_S.</t>
+          <t>18107.4_4577_M.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>401.2_179_S.</t>
+          <t>15186.5_3866_S.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>7012.1_3931_🔋.</t>
+          <t>10006.9_3646_X.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>5010.3_3392_P.</t>
+          <t>7420.2_4318_C.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>7593.7_2701_E.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>6610.9_1738_P.</t>
+          <t>5007.1_1751_T.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>15186.5_3866_S.</t>
+          <t>7039.1_2754_S.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>5025.8_1214_P.</t>
+          <t>208.3_85_P.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>4969.4_2146_P.</t>
+          <t>5085.1_1840_G.</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>7024.3_3266_L.</t>
+          <t>5014.3_1731_F.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>2880.9_1210_L.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>15200.8_10718_F.</t>
+          <t>611.2_221_M.</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>9029.6_4595_P.</t>
+          <t>6084.1_2156_V.</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>4781.2_1507_A.</t>
+          <t>5904.3_2699_P.</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>5365.6_2437_C.</t>
+          <t>5621.6_2375_P.</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>773.5_238_S.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>6518.4_2914_A.</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>8092.0_4532_P.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>8200.5_2738_M.</t>
+          <t>10003.3_3845_P.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>5017.7_1147_M.</t>
+          <t>10643.3_3263_S.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>5014.8_2009_A.</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2060.0_802_S.</t>
+          <t>3019.8_1453_F.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>8004.6_2357_G.</t>
+          <t>5000.2_1932_E.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>12008.4_3832_G.</t>
+          <t>8004.6_2357_G.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>6622.5_2224_E.</t>
+          <t>9013.7_2337_M.</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>1002.7_460_S.</t>
+          <t>5086.0_1810_G.</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>3006.0_1286_M.</t>
+          <t>4850.9_2239_C.</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>5085.1_1840_G.</t>
+          <t>37036.6_17889_F.</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>12006.9_5463_P.</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>5235.4_1766_P.</t>
+          <t>8132.9_2716_S.</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>4830.1_2569_C.</t>
+          <t>5040.0_2971_A.</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>5005.9_1755_X.</t>
+          <t>419.0_180_P.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>5282.8_2392_C.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>6012.6_2984_P.</t>
+          <t>531.0_343_A.</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>3010.0_1424_A.</t>
+          <t>10533.4_4020_F.</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2004.9_754_S.</t>
+          <t>2047.9_924_L.</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>16520.2_4844_M.</t>
+          <t>10031.8_2663_P.</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>14009.7_4401_V.</t>
+          <t>10006.0_2772_V.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>5011.9_1594_P.</t>
+          <t>791.5_266_G.</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>10022.1_2875_M.</t>
+          <t>5009.1_2246_C.</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>2036.1_839_S.</t>
+          <t>10022.1_2875_M.</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>10012.3_3067_S.</t>
+          <t>5256.5_1535_S.</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>15057.9_8625_F.</t>
+          <t>4735.2_997_S.</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>8396.0_2595_S.</t>
+          <t>7985.2_2173_P.</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>9006.5_3085_X.</t>
+          <t>4013.7_1173_V.</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>4786.5_1898_P.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>5005.8_1527_S.</t>
+          <t>5011.9_1594_P.</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>3010.0_1289_A.</t>
+          <t>4969.4_2146_P.</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>5020.6_1328_M.</t>
+          <t>3012.4_1258_P.</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>22320.3_9183_F.</t>
+          <t>10010.0_2910_V.</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>15223.0_6245_P.</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>14009.7_4401_V.</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>10030.0_3041_G.</t>
+          <t>5010.0_1872_A.</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>10010.0_2910_V.</t>
+          <t>5004.0_2103_C.</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>10003.7_2721_V.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>5256.5_1535_S.</t>
+          <t>4028.8_1699_L.</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>3026.1_1490_A.</t>
+          <t>5005.9_1755_X.</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>6038.2_2121_P.</t>
+          <t>6004.0_2559_P.</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>7516.9_3203_A.</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>3735.9_1928_V.</t>
+          <t>5033.4_1976_M.</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>12342.9_3211_M.</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>8396.0_2595_S.</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>1083.2_390_M.</t>
+          <t>9209.1_3141_E.</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>5004.5_1548_A.</t>
+          <t>16008.9_5968_S.</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>10027.3_2906_P.</t>
+          <t>8218.3_2327_P.</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>5869.6_2613_P.</t>
+          <t>5021.7_1930_A.</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>10106.6_2889_P.</t>
+          <t>2355.5_726_S.</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>1380.0_562_A.</t>
+          <t>16520.2_4844_M.</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>2002.2_938_P.</t>
+          <t>6036.4_2875_V.</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>3026.1_1490_A.</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>2558.7_905_S.</t>
+          <t>3010.0_1685_A.</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>9415.9_3699_G.</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>5040.0_2514_C.</t>
+          <t>3010.0_1424_A.</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>6345.4_2376_S.</t>
+          <t>3614.8_970_🔋.</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>5770.8_2848_G.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>4214.8_2018_A.</t>
+          <t>9555.5_5689_S.</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>4735.2_997_S.</t>
+          <t>1443.0_851_A.</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>5827.8_2106_S.</t>
+          <t>5003.2_1389_E.</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>5579.8_1990_E.</t>
+          <t>7022.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>657.7_273_S.</t>
+          <t>5004.5_1548_A.</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>4177.9_1557_T.</t>
+          <t>10503.6_3278_M.</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>8367.5_4269_C.</t>
+          <t>4830.1_2569_C.</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>15504.3_3950_M.</t>
+          <t>5010.3_3392_P.</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>14119.3_5262_S.</t>
+          <t>5296.8_1844_P.</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>7593.7_2701_E.</t>
+          <t>5144.4_2349_P.</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>1020.0_679_T.</t>
+          <t>5005.8_1527_S.</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>20105.6_7766_F.</t>
+          <t>3735.9_1928_V.</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>6084.1_2156_V.</t>
+          <t>6006.6_2009_P.</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>4921.0_2491_A.</t>
+          <t>2504.7_703_🔋.</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>2558.7_905_S.</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>7006.7_5717_S.</t>
+          <t>6046.5_3239_S.</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>5033.4_1976_M.</t>
+          <t>7127.8_1843_G.</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>5010.3_1888_G.</t>
+          <t>4705.5_1241_G.</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>4790.7_1897_F.</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>1884.9_866_S.</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>3412.3_1947_C.</t>
+          <t>1701.7_720_F.</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>5051.4_1993_M.</t>
+          <t>3597.6_2910_E.</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>2880.9_1210_L.</t>
+          <t>8442.5_3038_G.</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>5621.6_2375_P.</t>
+          <t>1114.9_359_S.</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>4678.8_1840_A.</t>
+          <t>10007.4_3588_V.</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>9562.8_3145_M.</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>5301.0_2064_F.</t>
+          <t>15016.9_6221_G.</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>6010.6_2144_A.</t>
+          <t>1629.5_671_F.</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>2011.7_731_S.</t>
+          <t>5580.0_2471_A.</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>5005.4_2618_L.</t>
+          <t>8367.5_4269_C.</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>10008.1_2966_M.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>6012.6_2984_P.</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>12545.4_3039_S.</t>
+          <t>6951.4_2856_S.</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>7025.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>7992.7_2506_F.</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>9791.4_3527_G.</t>
+          <t>6536.2_2241_P.</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>5001.9_1291_V.</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>4688.1_2291_C.</t>
+          <t>15504.3_3950_M.</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>9005.3_4344_A.</t>
+          <t>5043.1_2254_C.</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>2185.4_792_S.</t>
+          <t>10001.9_4466_P.</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>7001.2_3357_M.</t>
+          <t>5869.6_2613_P.</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>7145.5_2856_E.</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>21207.4_6474_V.</t>
+          <t>6345.4_2376_S.</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>7516.9_3203_A.</t>
+          <t>4153.2_3559_P.</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>6011.8_1873_M.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>773.5_238_S.</t>
+          <t>5581.6_3687_P.</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>5007.1_1751_T.</t>
+          <t>7001.2_3357_M.</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>12524.7_3259_S.</t>
+          <t>2186.2_736_G.</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>6518.4_2914_A.</t>
+          <t>4700.4_1216_V.</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>26010.2_9812_F.</t>
+          <t>22320.3_9183_F.</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>5028.5_4433_S.</t>
+          <t>5238.0_2781_F.</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>9209.1_3141_E.</t>
+          <t>2051.8_860_S.</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>4788.2_1476_P.</t>
+          <t>2783.5_952_S.</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>6951.4_2856_S.</t>
+          <t>10027.3_2906_P.</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>1701.7_720_F.</t>
+          <t>5522.8_2716_V.</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>5043.1_2254_C.</t>
+          <t>5119.6_3153_M.</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>7025.4_3008_L.</t>
+          <t>2011.7_731_S.</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>3010.0_1685_A.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>4017.3_1883_C.</t>
+          <t>6600.2_1915_M.</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>6003.3_2987_M.</t>
+          <t>1366.2_487_L.</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>56121.5_25636_F.</t>
+          <t>13023.5_5156_L.</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>7039.1_2754_S.</t>
+          <t>12022.7_5417_L.</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>5163.5_1775_V.</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>18102.7_4949_M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>15637.2_5789_G.</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>21442.0_7959_F.</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>6620.4_2477_P.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_500km_2026.xlsx
+++ b/Ranking_CNB_500km_2026.xlsx
@@ -471,12 +471,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>491,8 km</t>
+          <t>493,2 km</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>6.543 m</t>
+          <t>6.551 m</t>
         </is>
       </c>
     </row>
@@ -488,12 +488,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>289,9 km</t>
+          <t>299,9 km</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.775 m</t>
+          <t>2.875 m</t>
         </is>
       </c>
     </row>
@@ -505,12 +505,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>243,2 km</t>
+          <t>250,9 km</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.948 m</t>
+          <t>2.078 m</t>
         </is>
       </c>
     </row>
@@ -522,12 +522,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>202,8 km</t>
+          <t>211,2 km</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.921 m</t>
+          <t>1.986 m</t>
         </is>
       </c>
     </row>
@@ -539,12 +539,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>193,6 km</t>
+          <t>198,7 km</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.310 m</t>
+          <t>2.369 m</t>
         </is>
       </c>
     </row>
@@ -658,12 +658,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>134,0 km</t>
+          <t>148,0 km</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.472 m</t>
+          <t>1.606 m</t>
         </is>
       </c>
     </row>
@@ -675,7 +675,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>126,1 km</t>
+          <t>129,2 km</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -692,12 +692,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>120,9 km</t>
+          <t>127,0 km</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.127 m</t>
+          <t>1.182 m</t>
         </is>
       </c>
     </row>
@@ -709,12 +709,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>112,0 km</t>
+          <t>126,0 km</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.242 m</t>
+          <t>1.374 m</t>
         </is>
       </c>
     </row>
@@ -726,12 +726,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>106,9 km</t>
+          <t>112,9 km</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.020 m</t>
+          <t>1.071 m</t>
         </is>
       </c>
     </row>
@@ -760,12 +760,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>94,3 km</t>
+          <t>101,4 km</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>714 m</t>
+          <t>779 m</t>
         </is>
       </c>
     </row>
@@ -828,12 +828,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>60,8 km</t>
+          <t>66,8 km</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>642 m</t>
+          <t>721 m</t>
         </is>
       </c>
     </row>
@@ -874,68 +874,68 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>José E.</t>
+          <t>Thaisa V.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>27,2 km</t>
+          <t>28,1 km</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>287 m</t>
+          <t>391 m</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Thaisa V.</t>
+          <t>José E.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>25,5 km</t>
+          <t>27,2 km</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>352 m</t>
+          <t>287 m</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Karine F.</t>
+          <t>Filipe M.</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>25,1 km</t>
+          <t>27,2 km</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>294 m</t>
+          <t>398 m</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Filipe M.</t>
+          <t>Karine F.</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>24,6 km</t>
+          <t>25,1 km</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>358 m</t>
+          <t>294 m</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A350"/>
+  <dimension ref="A1:A365"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1014,28 +1014,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>960.0_1109_A.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10007.8_2733_V.</t>
+          <t>10030.1_3124_M.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4921.0_2491_A.</t>
+          <t>5014.8_2009_A.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5004.9_1790_A.</t>
+          <t>2051.8_860_S.</t>
         </is>
       </c>
     </row>
@@ -1049,1722 +1049,1722 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>12008.4_3832_G.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6011.8_1873_M.</t>
+          <t>5013.9_1673_A.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10002.4_5136_P.</t>
+          <t>18102.7_4949_M.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5025.8_1214_P.</t>
+          <t>4830.1_2569_C.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3412.3_1947_C.</t>
+          <t>1366.2_487_L.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>25020.8_7832_V.</t>
+          <t>15057.9_8625_F.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>5064.2_1636_G.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1380.0_562_A.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6661.8_3736_P.</t>
+          <t>4763.8_1720_P.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>15194.4_3911_S.</t>
+          <t>5296.8_1844_P.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3798.9_1319_S.</t>
+          <t>4540.8_1823_A.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>14019.6_6253_L.</t>
+          <t>5007.1_1751_T.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>7003.6_2437_P.</t>
+          <t>10030.0_3041_G.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5827.8_2106_S.</t>
+          <t>5040.0_2971_A.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5579.8_1990_E.</t>
+          <t>5081.5_1647_G.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>8008.0_2930_A.</t>
+          <t>6622.5_2224_E.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5029.4_1585_P.</t>
+          <t>10643.3_3263_S.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>4678.8_1840_A.</t>
+          <t>6036.4_2875_V.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>8196.1_2807_T.</t>
+          <t>9791.4_3527_G.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>960.0_1109_A.</t>
+          <t>18665.3_4638_S.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>4896.8_2251_L.</t>
+          <t>123.0_5992_A.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>1380.0_562_A.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>7419.2_3469_F.</t>
+          <t>14019.6_6253_L.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>5724.1_3694_S.</t>
+          <t>4768.0_1875_L.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>17003.0_7696_P.</t>
+          <t>7420.2_4318_C.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>14119.3_5262_S.</t>
+          <t>9209.1_3141_E.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10003.7_2721_V.</t>
+          <t>5051.4_1993_M.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5451.1_1905_T.</t>
+          <t>14004.5_5478_M.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>9029.6_4595_P.</t>
+          <t>3019.8_1453_F.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>12545.4_3039_S.</t>
+          <t>9562.8_3145_M.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2064.3_708_S.</t>
+          <t>3412.3_1947_C.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>6804.1_2088_P.</t>
+          <t>10030.5_4765_C.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>12521.4_4814_M.</t>
+          <t>10016.9_3028_M.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5022.5_1222_P.</t>
+          <t>10003.3_3845_P.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>8132.9_2716_S.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>6038.2_2121_P.</t>
+          <t>5027.8_1361_P.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>6903.6_2566_G.</t>
+          <t>2185.4_792_S.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>6035.0_2481_P.</t>
+          <t>53755.6_36604_F.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>21124.1_8011_F.</t>
+          <t>3757.2_1716_A.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>7874.8_2223_M.</t>
+          <t>10006.9_3646_F.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>8024.4_2933_S.</t>
+          <t>5365.6_2437_C.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>5235.4_1766_P.</t>
+          <t>5010.3_1888_G.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>4821.0_1857_P.</t>
+          <t>6173.6_2865_M.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>26010.2_9812_F.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1002.7_460_S.</t>
+          <t>15194.4_3911_S.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>4797.2_1541_G.</t>
+          <t>1012.0_375_E.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>10012.3_3067_S.</t>
+          <t>10007.8_2733_V.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>6011.5_2408_A.</t>
+          <t>4864.8_1353_E.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>8196.1_2807_T.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1020.0_679_T.</t>
+          <t>5001.9_1291_V.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>7114.0_2850_S.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>6007.4_1804_G.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>6173.6_2865_M.</t>
+          <t>1884.9_866_S.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>4786.5_1898_P.</t>
+          <t>8416.2_4091_P.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>8618.0_2344_P.</t>
+          <t>10058.8_3483_F.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>5008.2_1646_A.</t>
+          <t>5299.8_2406_C.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>5100.0_2587_A.</t>
+          <t>5580.0_2471_A.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>10030.5_4765_C.</t>
+          <t>12022.7_5417_L.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>8351.7_4153_C.</t>
+          <t>5072.4_1931_S.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>7880.9_2433_E.</t>
+          <t>4214.8_2018_A.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>6818.2_2036_P.</t>
+          <t>5100.0_2587_A.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>3958.9_1777_P.</t>
+          <t>3059.2_956_T.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>5299.8_2406_C.</t>
+          <t>5235.4_1766_P.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>17012.6_5869_T.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>657.7_273_S.</t>
+          <t>5904.3_2699_P.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>5081.5_1647_G.</t>
+          <t>12545.4_3039_S.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>5365.6_2437_C.</t>
+          <t>3958.9_1777_P.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>10020.8_2989_M.</t>
+          <t>4821.0_1857_P.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1027.7_364_S.</t>
+          <t>4790.7_1897_F.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>3006.0_1286_M.</t>
+          <t>1083.2_390_M.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>7006.7_5717_S.</t>
+          <t>5621.6_2375_P.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>8187.1_2322_M.</t>
+          <t>5004.9_1790_A.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>7598.7_2799_S.</t>
+          <t>2880.9_1210_L.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>9791.4_3527_G.</t>
+          <t>2047.9_924_L.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2004.9_754_S.</t>
+          <t>7090.6_3340_A.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>4791.5_1524_E.</t>
+          <t>7419.2_3469_F.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>4078.1_1810_A.</t>
+          <t>10031.8_2663_P.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>18665.3_4638_S.</t>
+          <t>4969.4_2146_P.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>3089.9_1508_C.</t>
+          <t>6035.0_2481_P.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>8481.2_2463_🔋.</t>
+          <t>8442.5_3038_G.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>5017.7_1147_M.</t>
+          <t>1020.0_679_T.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>531.0_343_A.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>4688.1_2291_C.</t>
+          <t>6003.3_2987_M.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>4017.3_1883_C.</t>
+          <t>1432.9_3942_M.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2735.8_959_S.</t>
+          <t>5008.2_1646_A.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>5072.4_1931_S.</t>
+          <t>7039.1_2754_S.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>5064.3_1832_F.</t>
+          <t>2558.7_905_S.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>6016.7_2122_M.</t>
+          <t>2557.8_1206_V.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>553.2_224_S.</t>
+          <t>4078.1_1810_A.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>7312.2_2446_G.</t>
+          <t>10106.6_2889_P.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>9006.5_3085_X.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>4932.4_1545_E.</t>
+          <t>6833.7_2100_G.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>3023.2_962_S.</t>
+          <t>2504.7_703_🔋.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>4540.8_1823_A.</t>
+          <t>5021.7_1930_A.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>6011.5_2408_A.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2185.4_792_S.</t>
+          <t>5020.6_1328_M.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>5028.5_4433_S.</t>
+          <t>56121.5_25636_F.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>123.0_5992_A.</t>
+          <t>8618.0_2344_P.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>9012.4_2700_M.</t>
+          <t>5022.5_1222_P.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>4177.9_1557_T.</t>
+          <t>16397.3_4254_S.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>53755.6_36604_F.</t>
+          <t>5005.8_1527_S.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>5027.8_1361_P.</t>
+          <t>8367.5_4269_C.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>5007.4_1601_A.</t>
+          <t>5040.0_2514_C.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>14117.6_3844_M.</t>
+          <t>8092.0_4532_P.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>6833.7_2100_G.</t>
+          <t>15504.3_3950_M.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>2186.2_736_G.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>12524.7_3259_S.</t>
+          <t>4613.1_1806_A.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>16397.3_4254_S.</t>
+          <t>12006.9_5463_P.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>5242.7_1657_S.</t>
+          <t>9756.3_2793_M.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>10348.3_2647_S.</t>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>5040.0_2514_C.</t>
+          <t>6600.2_1915_M.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>10533.4_4020_F.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>5008.0_2402_P.</t>
+          <t>4013.7_1173_V.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>3023.2_962_S.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>4613.1_1806_A.</t>
+          <t>12326.4_4833_S.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>5020.4_2167_C.</t>
+          <t>5029.4_1585_P.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>3614.8_970_🔋.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>3010.0_1685_A.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>9507.9_2851_M.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>9005.3_4344_A.</t>
+          <t>9507.9_2851_M.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>8218.3_2327_P.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2002.2_938_P.</t>
+          <t>5010.0_1872_A.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>8200.5_2738_M.</t>
+          <t>21207.4_6474_V.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>21141.5_8155_F.</t>
+          <t>6536.2_2241_P.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>5010.3_1888_G.</t>
+          <t>5981.9_2551_P.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>401.2_179_S.</t>
+          <t>10011.5_3070_S.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>7576.8_2823_P.</t>
+          <t>4932.4_1545_E.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>9756.3_2793_M.</t>
+          <t>6006.6_2009_P.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>5724.1_3694_S.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>4797.2_1541_G.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>3757.2_1716_A.</t>
+          <t>15186.5_3866_S.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>7502.4_3467_P.</t>
+          <t>2735.8_959_S.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>5003.2_1389_E.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>10106.6_2889_P.</t>
+          <t>9007.1_3080_P.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>6610.9_1738_P.</t>
+          <t>10062.5_2886_M.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>4788.2_1476_P.</t>
+          <t>3798.9_1319_S.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>15057.9_8625_F.</t>
+          <t>7003.6_2437_P.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>8506.3_4050_C.</t>
+          <t>6006.1_2236_V.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>6620.4_2477_P.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>9006.5_3085_X.</t>
+          <t>8004.6_2357_G.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>10008.1_2966_M.</t>
+          <t>9555.5_5689_S.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>5013.9_1673_A.</t>
+          <t>6518.4_2914_A.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>5282.8_2392_C.</t>
+          <t>8200.5_2738_M.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2060.0_802_S.</t>
+          <t>5827.8_2106_S.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>6003.3_2987_M.</t>
+          <t>3010.0_1289_A.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>2011.7_731_S.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>5770.8_2848_G.</t>
+          <t>7006.7_5717_S.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>5000.6_1856_M.</t>
+          <t>9639.7_4763_P.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>10006.9_3646_F.</t>
+          <t>7576.8_2823_P.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>4214.8_2018_A.</t>
+          <t>5144.4_2349_P.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>4972.5_2522_S.</t>
+          <t>5020.4_2167_C.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>5382.2_2690_M.</t>
+          <t>12524.7_3259_S.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>4864.8_1353_E.</t>
+          <t>14009.0_5498_A.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>21207.4_6474_V.</t>
+          <t>7012.1_3931_🔋.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>12008.4_3832_G.</t>
+          <t>14009.7_4401_V.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>14014.7_3537_S.</t>
+          <t>2556.5_1160_M.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>5287.4_1835_V.</t>
+          <t>15637.2_5789_G.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>7569.4_2477_V.</t>
+          <t>2064.3_708_S.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>9639.7_4763_P.</t>
+          <t>21124.1_8011_F.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>10011.5_3070_S.</t>
+          <t>3138.1_1120_S.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>10012.1_3139_S.</t>
+          <t>5119.6_3153_M.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>15200.8_10718_F.</t>
+          <t>8187.1_2322_M.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2036.1_839_S.</t>
+          <t>12342.9_3211_M.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>6007.1_3172_F.</t>
+          <t>7874.8_2223_M.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>26010.2_9812_F.</t>
+          <t>6951.4_2856_S.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>8253.0_2972_🔋.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>1012.0_375_E.</t>
+          <t>4678.8_1840_A.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>7024.3_3266_L.</t>
+          <t>10106.6_3354_M.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>5051.4_1993_M.</t>
+          <t>5256.5_1535_S.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>4000.6_1659_S.</t>
+          <t>1629.5_671_F.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>7230.5_2794_V.</t>
+          <t>6012.6_2984_F.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>3004.6_746_V.</t>
+          <t>5282.8_2392_C.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>1083.2_390_M.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>21106.2_7925_P.</t>
+          <t>1701.7_720_F.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>10503.6_3278_M.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>5224.2_2340_C.</t>
+          <t>6779.9_2003_E.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>4692.9_1546_P.</t>
+          <t>7024.3_3266_L.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>9007.1_3080_P.</t>
+          <t>6610.9_1738_P.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>4705.5_1241_G.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>20105.6_7766_F.</t>
+          <t>3735.9_1928_V.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>10030.0_3041_G.</t>
+          <t>4028.8_1699_L.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>5301.0_2064_F.</t>
+          <t>7985.2_2173_P.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>10030.1_3124_M.</t>
+          <t>4177.9_1557_T.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>4781.2_1507_A.</t>
+          <t>791.5_266_G.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>5005.4_2618_L.</t>
+          <t>5011.9_1594_P.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>5020.6_1328_M.</t>
+          <t>4791.5_1524_E.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>56121.5_25636_F.</t>
+          <t>4735.2_997_S.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>6622.5_2224_E.</t>
+          <t>5008.0_2402_P.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>10016.9_3028_M.</t>
+          <t>7502.4_3467_P.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>7012.1_3931_🔋.</t>
+          <t>5000.2_1932_E.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>6779.9_2003_E.</t>
+          <t>6137.8_2406_L.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>4921.0_2491_A.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>3010.0_1289_A.</t>
+          <t>6016.7_2122_M.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>6007.1_2393_M.</t>
+          <t>4000.6_1659_S.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>5028.5_4433_S.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>3580.9_1198_S.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2000.0_724_A.</t>
+          <t>3089.9_1508_C.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>18107.4_4577_M.</t>
+          <t>5579.8_1990_E.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>15186.5_3866_S.</t>
+          <t>8008.0_2930_A.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>10006.9_3646_X.</t>
+          <t>10003.7_2721_V.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>7420.2_4318_C.</t>
+          <t>21141.5_8155_F.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>7593.7_2701_E.</t>
+          <t>4781.2_1507_A.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>5007.1_1751_T.</t>
+          <t>6046.5_3239_S.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>7039.1_2754_S.</t>
+          <t>7022.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>25020.8_7832_V.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>5085.1_1840_G.</t>
+          <t>9005.3_4344_A.</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>1011.0_396_L.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2880.9_1210_L.</t>
+          <t>611.2_221_M.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>611.2_221_M.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>6084.1_2156_V.</t>
+          <t>4688.1_2291_C.</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>5904.3_2699_P.</t>
+          <t>6472.0_2501_S.</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>5621.6_2375_P.</t>
+          <t>7593.7_2701_E.</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>773.5_238_S.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>6518.4_2914_A.</t>
+          <t>17003.0_7696_P.</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>8092.0_4532_P.</t>
+          <t>401.2_179_S.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>10003.3_3845_P.</t>
+          <t>10174.3_3680_S.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>10643.3_3263_S.</t>
+          <t>10001.9_4466_P.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>5014.8_2009_A.</t>
+          <t>5010.3_3392_P.</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>15200.8_10718_F.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>5000.2_1932_E.</t>
+          <t>14014.7_3537_S.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>8004.6_2357_G.</t>
+          <t>10010.0_2910_V.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>9012.4_2700_M.</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>5086.0_1810_G.</t>
+          <t>37036.6_17889_F.</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>4850.9_2239_C.</t>
+          <t>10006.0_2772_V.</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>37036.6_17889_F.</t>
+          <t>6084.1_2156_V.</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>6007.1_2393_M.</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>8132.9_2716_S.</t>
+          <t>7992.7_2506_F.</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>4153.2_3559_P.</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>5040.0_2971_A.</t>
+          <t>4850.9_2239_C.</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>419.0_180_P.</t>
+          <t>5224.2_2340_C.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>5005.9_1755_X.</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>531.0_343_A.</t>
+          <t>6818.2_2036_P.</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>10533.4_4020_F.</t>
+          <t>4017.3_1883_C.</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2047.9_924_L.</t>
+          <t>7598.7_2799_S.</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>10031.8_2663_P.</t>
+          <t>5869.6_2613_P.</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>10006.0_2772_V.</t>
+          <t>2002.2_938_P.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>791.5_266_G.</t>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>5009.1_2246_C.</t>
+          <t>773.5_238_S.</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>10022.1_2875_M.</t>
+          <t>6011.8_1873_M.</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>5256.5_1535_S.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>4735.2_997_S.</t>
+          <t>419.0_180_P.</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>7985.2_2173_P.</t>
+          <t>7516.9_3203_A.</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>4013.7_1173_V.</t>
+          <t>7230.5_2794_V.</t>
         </is>
       </c>
     </row>
@@ -2778,679 +2778,784 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>5011.9_1594_P.</t>
+          <t>5522.8_2716_V.</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>4969.4_2146_P.</t>
+          <t>5301.0_2064_F.</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>3012.4_1258_P.</t>
+          <t>4972.5_2522_S.</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>10010.0_2910_V.</t>
+          <t>5085.1_1840_G.</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>15223.0_6245_P.</t>
+          <t>2355.5_726_S.</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>14009.7_4401_V.</t>
+          <t>5287.4_1835_V.</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>5010.0_1872_A.</t>
+          <t>5242.7_1657_S.</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>5004.0_2103_C.</t>
+          <t>5004.5_1548_A.</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>5086.0_1810_G.</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>4028.8_1699_L.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>5005.9_1755_X.</t>
+          <t>1114.9_359_S.</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>6004.0_2559_P.</t>
+          <t>4896.8_2251_L.</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>7516.9_3203_A.</t>
+          <t>5451.1_1905_T.</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>5033.4_1976_M.</t>
+          <t>21106.2_7925_P.</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>12342.9_3211_M.</t>
+          <t>8506.3_4050_C.</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>8396.0_2595_S.</t>
+          <t>6113.5_2883_C.</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>9209.1_3141_E.</t>
+          <t>14119.3_5262_S.</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>16008.9_5968_S.</t>
+          <t>10012.1_3139_S.</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>8218.3_2327_P.</t>
+          <t>8024.4_2933_S.</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>5021.7_1930_A.</t>
+          <t>7114.0_2850_S.</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>2355.5_726_S.</t>
+          <t>15016.9_6221_G.</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>16520.2_4844_M.</t>
+          <t>208.3_85_P.</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>6036.4_2875_V.</t>
+          <t>4692.9_1546_P.</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>3026.1_1490_A.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>3010.0_1685_A.</t>
+          <t>6004.0_2559_P.</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>9415.9_3699_G.</t>
+          <t>7015.4_2141_T.</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>3010.0_1424_A.</t>
+          <t>4576.3_2084_S.</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>6903.6_2566_G.</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>10022.1_2875_M.</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>9555.5_5689_S.</t>
+          <t>4814.5_1705_🔋.</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>1443.0_851_A.</t>
+          <t>553.2_224_S.</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>5003.2_1389_E.</t>
+          <t>5163.5_1775_V.</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>7022.4_3008_L.</t>
+          <t>3010.0_1424_A.</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>5004.5_1548_A.</t>
+          <t>4788.2_1476_P.</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>10503.6_3278_M.</t>
+          <t>5017.7_1147_M.</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>4830.1_2569_C.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>5010.3_3392_P.</t>
+          <t>6345.4_2376_S.</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>5296.8_1844_P.</t>
+          <t>1027.7_364_S.</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>5144.4_2349_P.</t>
+          <t>6007.4_1804_G.</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>5005.8_1527_S.</t>
+          <t>5033.4_1976_M.</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>3735.9_1928_V.</t>
+          <t>10007.8_2668_V.</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>6006.6_2009_P.</t>
+          <t>10012.3_3067_S.</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>2504.7_703_🔋.</t>
+          <t>6012.6_2984_P.</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>2558.7_905_S.</t>
+          <t>5064.3_1832_F.</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>2783.5_952_S.</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>7127.8_1843_G.</t>
+          <t>1443.0_851_A.</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>4790.7_1897_F.</t>
+          <t>13023.5_5156_L.</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>3005.2_1040_L.</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>6804.1_2088_P.</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>1701.7_720_F.</t>
+          <t>7312.2_2446_G.</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>3597.6_2910_E.</t>
+          <t>2175.4_712_S.</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>8442.5_3038_G.</t>
+          <t>4077.1_1454_S.</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>1114.9_359_S.</t>
+          <t>7569.4_2477_V.</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>10007.4_3588_V.</t>
+          <t>2000.0_724_A.</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>8481.2_2463_🔋.</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>15016.9_6221_G.</t>
+          <t>10006.9_3646_X.</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>1629.5_671_F.</t>
+          <t>4786.5_1898_P.</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>5580.0_2471_A.</t>
+          <t>7025.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>8367.5_4269_C.</t>
+          <t>3006.0_1286_M.</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>1002.7_460_S.</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>6012.6_2984_P.</t>
+          <t>5007.4_1601_A.</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>6951.4_2856_S.</t>
+          <t>5382.2_2690_M.</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>7025.4_3008_L.</t>
+          <t>4731.9_1407_T.</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>7992.7_2506_F.</t>
+          <t>7880.9_2433_E.</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>6536.2_2241_P.</t>
+          <t>5005.4_2618_L.</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>5001.9_1291_V.</t>
+          <t>16520.2_4844_M.</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>15504.3_3950_M.</t>
+          <t>7145.5_2856_E.</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>5043.1_2254_C.</t>
+          <t>18107.4_4577_M.</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>10001.9_4466_P.</t>
+          <t>8104.2_2652_M.</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>5869.6_2613_P.</t>
+          <t>5004.0_2103_C.</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>7145.5_2856_E.</t>
+          <t>10027.3_2906_P.</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>6345.4_2376_S.</t>
+          <t>4700.4_1216_V.</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>4153.2_3559_P.</t>
+          <t>6007.1_3172_F.</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>9029.6_4595_P.</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>5581.6_3687_P.</t>
+          <t>5770.8_2848_G.</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>7001.2_3357_M.</t>
+          <t>16008.9_5968_S.</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>2186.2_736_G.</t>
+          <t>7127.8_1843_G.</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>4700.4_1216_V.</t>
+          <t>9013.7_2337_M.</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>22320.3_9183_F.</t>
+          <t>3004.6_746_V.</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>5238.0_2781_F.</t>
+          <t>10020.8_2989_M.</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>5000.6_1856_M.</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>2783.5_952_S.</t>
+          <t>20105.6_7766_F.</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>10027.3_2906_P.</t>
+          <t>10348.3_2647_S.</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>5522.8_2716_V.</t>
+          <t>22320.3_9183_F.</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>21442.0_7959_F.</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>2011.7_731_S.</t>
+          <t>9415.9_3699_G.</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>5581.6_3687_P.</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>6600.2_1915_M.</t>
+          <t>8396.0_2595_S.</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>1366.2_487_L.</t>
+          <t>6038.2_2121_P.</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>13023.5_5156_L.</t>
+          <t>5009.1_2246_C.</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>12022.7_5417_L.</t>
+          <t>5238.0_2781_F.</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>5163.5_1775_V.</t>
+          <t>10002.4_5136_P.</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>18102.7_4949_M.</t>
+          <t>2060.0_802_S.</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>15637.2_5789_G.</t>
+          <t>5014.3_1731_F.</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>657.7_273_S.</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>6620.4_2477_P.</t>
+          <t>2036.1_839_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>10007.4_3588_V.</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>5025.8_1214_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>14117.6_3844_M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>15223.0_6245_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>3026.1_1490_A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2305.1_940_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>4891.7_1690_F.</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>5043.1_2254_C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>3597.6_2910_E.</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2004.9_754_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>8120.9_2737_G.</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>3012.4_1258_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>8351.7_4153_C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>7001.2_3357_M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>6661.8_3736_P.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_500km_2026.xlsx
+++ b/Ranking_CNB_500km_2026.xlsx
@@ -517,34 +517,34 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Jéssica P.</t>
+          <t>Fernanda G.</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>211,2 km</t>
+          <t>217,2 km</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.986 m</t>
+          <t>2.550 m</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Fernanda G.</t>
+          <t>Jéssica P.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>198,7 km</t>
+          <t>211,2 km</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.369 m</t>
+          <t>1.986 m</t>
         </is>
       </c>
     </row>
@@ -879,80 +879,80 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>28,1 km</t>
+          <t>30,6 km</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>391 m</t>
+          <t>430 m</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>José E.</t>
+          <t>Filipe M.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>27,2 km</t>
+          <t>28,2 km</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>287 m</t>
+          <t>408 m</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Filipe M.</t>
+          <t>Eduardo T.</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>27,2 km</t>
+          <t>27,7 km</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>398 m</t>
+          <t>295 m</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Karine F.</t>
+          <t>José E.</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>25,1 km</t>
+          <t>27,2 km</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>294 m</t>
+          <t>287 m</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Eduardo T.</t>
+          <t>Karine F.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>22,8 km</t>
+          <t>25,1 km</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>234 m</t>
+          <t>294 m</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A365"/>
+  <dimension ref="A1:A369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1014,56 +1014,56 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>960.0_1109_A.</t>
+          <t>5072.4_1931_S.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10030.1_3124_M.</t>
+          <t>6004.0_2559_P.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5014.8_2009_A.</t>
+          <t>12326.4_4833_S.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>5014.3_1731_F.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6010.6_2144_A.</t>
+          <t>8200.5_2738_M.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>12008.4_3832_G.</t>
+          <t>22320.3_9183_F.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5013.9_1673_A.</t>
+          <t>10007.8_2733_V.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>18102.7_4949_M.</t>
+          <t>1629.5_671_F.</t>
         </is>
       </c>
     </row>
@@ -1077,2485 +1077,2513 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1366.2_487_L.</t>
+          <t>3597.6_2910_E.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>15057.9_8625_F.</t>
+          <t>21442.0_7959_F.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5064.2_1636_G.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>553.2_224_S.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>5299.8_2406_C.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5296.8_1844_P.</t>
+          <t>611.2_221_M.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>4540.8_1823_A.</t>
+          <t>3026.1_1490_A.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5007.1_1751_T.</t>
+          <t>5064.2_1636_G.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10030.0_3041_G.</t>
+          <t>1884.9_866_S.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5040.0_2971_A.</t>
+          <t>5064.3_1832_F.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5081.5_1647_G.</t>
+          <t>1114.9_359_S.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>6622.5_2224_E.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10643.3_3263_S.</t>
+          <t>10174.3_3680_S.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6036.4_2875_V.</t>
+          <t>9209.1_3141_E.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>9791.4_3527_G.</t>
+          <t>12006.9_5463_P.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>18665.3_4638_S.</t>
+          <t>6010.6_2144_A.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>123.0_5992_A.</t>
+          <t>657.7_273_S.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1380.0_562_A.</t>
+          <t>8104.2_2652_M.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>14019.6_6253_L.</t>
+          <t>6007.1_3172_F.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>3010.0_1289_A.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>7420.2_4318_C.</t>
+          <t>5365.6_2437_C.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>9209.1_3141_E.</t>
+          <t>5009.1_2246_C.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5051.4_1993_M.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>14004.5_5478_M.</t>
+          <t>6038.2_2121_P.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>6113.5_2883_C.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>4932.4_1545_E.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>7025.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3412.3_1947_C.</t>
+          <t>3006.0_1286_M.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10030.5_4765_C.</t>
+          <t>5119.6_3153_M.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10016.9_3028_M.</t>
+          <t>10010.0_2910_V.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10003.3_3845_P.</t>
+          <t>12545.4_3039_S.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>8132.9_2716_S.</t>
+          <t>2060.0_802_S.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>5027.8_1361_P.</t>
+          <t>6903.6_2566_G.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2185.4_792_S.</t>
+          <t>8442.5_3038_G.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>53755.6_36604_F.</t>
+          <t>10007.8_2668_V.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3757.2_1716_A.</t>
+          <t>10012.3_3067_S.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>10006.9_3646_F.</t>
+          <t>5621.6_2375_P.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>5365.6_2437_C.</t>
+          <t>2504.7_703_🔋.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>5010.3_1888_G.</t>
+          <t>8196.1_2807_T.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>6173.6_2865_M.</t>
+          <t>5580.0_2471_A.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>26010.2_9812_F.</t>
+          <t>10031.8_2663_P.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>15194.4_3911_S.</t>
+          <t>8618.0_2344_P.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1012.0_375_E.</t>
+          <t>7230.5_2794_V.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>10007.8_2733_V.</t>
+          <t>7145.5_2856_E.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>4864.8_1353_E.</t>
+          <t>6804.1_2088_P.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>8196.1_2807_T.</t>
+          <t>5005.9_1755_X.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>5001.9_1291_V.</t>
+          <t>7569.4_2477_V.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>15504.3_3950_M.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>10008.1_2966_M.</t>
+          <t>10020.8_2989_M.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>4017.3_1883_C.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>8416.2_4091_P.</t>
+          <t>7127.8_1843_G.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>5051.4_1993_M.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>5299.8_2406_C.</t>
+          <t>4790.7_1897_F.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>5580.0_2471_A.</t>
+          <t>10106.6_3354_M.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>12022.7_5417_L.</t>
+          <t>6472.0_2501_S.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>5072.4_1931_S.</t>
+          <t>2557.8_1206_V.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>4214.8_2018_A.</t>
+          <t>5007.4_1601_A.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>5100.0_2587_A.</t>
+          <t>5004.9_1790_A.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>3059.2_956_T.</t>
+          <t>8008.0_2930_A.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>5235.4_1766_P.</t>
+          <t>4821.0_1857_P.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>773.5_238_S.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>5904.3_2699_P.</t>
+          <t>8004.6_2357_G.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>12545.4_3039_S.</t>
+          <t>1002.7_460_S.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>3958.9_1777_P.</t>
+          <t>7012.1_3931_🔋.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>4821.0_1857_P.</t>
+          <t>4917.5_2381_T.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>4790.7_1897_F.</t>
+          <t>5238.0_2781_F.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1083.2_390_M.</t>
+          <t>10006.0_2772_V.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>5621.6_2375_P.</t>
+          <t>2305.1_940_S.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>5004.9_1790_A.</t>
+          <t>9005.3_4344_A.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2880.9_1210_L.</t>
+          <t>4576.3_2084_S.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2047.9_924_L.</t>
+          <t>4153.2_3559_P.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>7090.6_3340_A.</t>
+          <t>2011.7_731_S.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>7419.2_3469_F.</t>
+          <t>1432.9_3942_M.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10031.8_2663_P.</t>
+          <t>6007.1_2393_M.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>4969.4_2146_P.</t>
+          <t>10006.9_3646_F.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>6035.0_2481_P.</t>
+          <t>7598.7_2799_S.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>8442.5_3038_G.</t>
+          <t>9006.5_3085_X.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1020.0_679_T.</t>
+          <t>5008.0_2402_P.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>531.0_343_A.</t>
+          <t>3004.6_746_V.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>6003.3_2987_M.</t>
+          <t>10503.6_3278_M.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1432.9_3942_M.</t>
+          <t>4791.5_1524_E.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>5008.2_1646_A.</t>
+          <t>6003.3_2987_M.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>7039.1_2754_S.</t>
+          <t>8120.9_2737_G.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2558.7_905_S.</t>
+          <t>4786.5_1898_P.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2557.8_1206_V.</t>
+          <t>9562.8_3145_M.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>4078.1_1810_A.</t>
+          <t>3757.2_1716_A.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>10106.6_2889_P.</t>
+          <t>7022.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>9006.5_3085_X.</t>
+          <t>5010.0_1872_A.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>6833.7_2100_G.</t>
+          <t>419.0_180_P.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2504.7_703_🔋.</t>
+          <t>10058.8_3483_F.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>5021.7_1930_A.</t>
+          <t>3010.0_1685_A.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>6011.5_2408_A.</t>
+          <t>7880.9_2433_E.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>5020.6_1328_M.</t>
+          <t>8481.2_2463_🔋.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>56121.5_25636_F.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>8618.0_2344_P.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>5022.5_1222_P.</t>
+          <t>2783.5_952_S.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>16397.3_4254_S.</t>
+          <t>15186.5_3866_S.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>5005.8_1527_S.</t>
+          <t>4864.8_1353_E.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>8367.5_4269_C.</t>
+          <t>3023.2_962_S.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>5040.0_2514_C.</t>
+          <t>7114.0_2850_S.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>8092.0_4532_P.</t>
+          <t>5033.4_1976_M.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>15504.3_3950_M.</t>
+          <t>7874.8_2223_M.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2186.2_736_G.</t>
+          <t>531.0_343_A.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>4613.1_1806_A.</t>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>9756.3_2793_M.</t>
+          <t>3412.3_1947_C.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>6600.2_1915_M.</t>
+          <t>3059.2_956_T.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>10533.4_4020_F.</t>
+          <t>2002.2_938_P.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>4013.7_1173_V.</t>
+          <t>5451.1_1905_T.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>3023.2_962_S.</t>
+          <t>7024.3_3266_L.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>1027.7_364_S.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>5029.4_1585_P.</t>
+          <t>960.0_1109_A.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>7992.7_2506_F.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>3010.0_1685_A.</t>
+          <t>1366.2_487_L.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>5086.0_1810_G.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>9507.9_2851_M.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>8218.3_2327_P.</t>
+          <t>8187.1_2322_M.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>5010.0_1872_A.</t>
+          <t>5004.5_1548_A.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>21207.4_6474_V.</t>
+          <t>3012.4_1258_P.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>6536.2_2241_P.</t>
+          <t>5043.1_2254_C.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>5981.9_2551_P.</t>
+          <t>15200.8_10718_F.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>10011.5_3070_S.</t>
+          <t>37036.6_17889_F.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>4932.4_1545_E.</t>
+          <t>5020.4_2167_C.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>6006.6_2009_P.</t>
+          <t>7015.4_2141_T.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>5724.1_3694_S.</t>
+          <t>4921.0_2491_A.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>4797.2_1541_G.</t>
+          <t>1011.0_396_L.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>15186.5_3866_S.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2735.8_959_S.</t>
+          <t>5981.9_2551_P.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>5003.2_1389_E.</t>
+          <t>5011.9_1594_P.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>9007.1_3080_P.</t>
+          <t>5040.0_2971_A.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>6661.8_3736_P.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>3798.9_1319_S.</t>
+          <t>5163.5_1775_V.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>7003.6_2437_P.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>6006.1_2236_V.</t>
+          <t>1443.0_851_A.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>6620.4_2477_P.</t>
+          <t>2004.9_754_S.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>8004.6_2357_G.</t>
+          <t>5282.8_2392_C.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>9555.5_5689_S.</t>
+          <t>6016.7_2122_M.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>6518.4_2914_A.</t>
+          <t>6084.1_2156_V.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>8200.5_2738_M.</t>
+          <t>14119.3_5262_S.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>5827.8_2106_S.</t>
+          <t>4692.9_1546_P.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>3010.0_1289_A.</t>
+          <t>5382.2_2690_M.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2011.7_731_S.</t>
+          <t>5000.6_1856_M.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>7006.7_5717_S.</t>
+          <t>5010.3_3392_P.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>9639.7_4763_P.</t>
+          <t>9791.4_3527_G.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>7576.8_2823_P.</t>
+          <t>9029.6_4595_P.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>5144.4_2349_P.</t>
+          <t>5001.9_1291_V.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>5020.4_2167_C.</t>
+          <t>6137.8_2406_L.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>12524.7_3259_S.</t>
+          <t>5003.2_1389_E.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>14009.0_5498_A.</t>
+          <t>10062.5_2886_M.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>7012.1_3931_🔋.</t>
+          <t>7001.2_3357_M.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>14009.7_4401_V.</t>
+          <t>14117.6_3844_M.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2556.5_1160_M.</t>
+          <t>6345.4_2376_S.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>15637.2_5789_G.</t>
+          <t>12008.4_3832_G.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2064.3_708_S.</t>
+          <t>4768.0_1875_L.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>21124.1_8011_F.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>3138.1_1120_S.</t>
+          <t>2047.9_924_L.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>3138.1_1120_S.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>8187.1_2322_M.</t>
+          <t>6833.7_2100_G.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>12342.9_3211_M.</t>
+          <t>2185.4_792_S.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>7874.8_2223_M.</t>
+          <t>12342.9_3211_M.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>6951.4_2856_S.</t>
+          <t>3005.2_1040_L.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>15637.2_5789_G.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>4678.8_1840_A.</t>
+          <t>7312.2_2446_G.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>2186.2_736_G.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>5256.5_1535_S.</t>
+          <t>5724.1_3694_S.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>1629.5_671_F.</t>
+          <t>2735.8_959_S.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>8218.3_2327_P.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>5282.8_2392_C.</t>
+          <t>6518.4_2914_A.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>5081.5_1647_G.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>1701.7_720_F.</t>
+          <t>4850.9_2239_C.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>10503.6_3278_M.</t>
+          <t>3798.9_1319_S.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>6779.9_2003_E.</t>
+          <t>10003.3_3845_P.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>7024.3_3266_L.</t>
+          <t>7039.1_2754_S.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>6610.9_1738_P.</t>
+          <t>1380.0_562_A.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>3010.0_1424_A.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>3735.9_1928_V.</t>
+          <t>5581.6_3687_P.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>4028.8_1699_L.</t>
+          <t>9555.5_5689_S.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>2175.4_712_S.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>7985.2_2173_P.</t>
+          <t>2355.5_726_S.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>4177.9_1557_T.</t>
+          <t>7516.9_3203_A.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>791.5_266_G.</t>
+          <t>1034.3_279_M.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>5011.9_1594_P.</t>
+          <t>8367.5_4269_C.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>4791.5_1524_E.</t>
+          <t>53755.6_36604_F.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>4735.2_997_S.</t>
+          <t>1083.2_390_M.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>5008.0_2402_P.</t>
+          <t>5010.3_1888_G.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>15057.9_8625_F.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>7502.4_3467_P.</t>
+          <t>7090.6_3340_A.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>5000.2_1932_E.</t>
+          <t>5028.5_4433_S.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>21141.5_8155_F.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>4921.0_2491_A.</t>
+          <t>10007.4_3588_V.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>6016.7_2122_M.</t>
+          <t>4678.8_1840_A.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>4000.6_1659_S.</t>
+          <t>10348.3_2647_S.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>5028.5_4433_S.</t>
+          <t>10533.4_4020_F.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>4735.2_997_S.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>3089.9_1508_C.</t>
+          <t>4763.8_1720_P.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>5579.8_1990_E.</t>
+          <t>12524.7_3259_S.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>8008.0_2930_A.</t>
+          <t>10027.3_2906_P.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>10003.7_2721_V.</t>
+          <t>5014.8_2009_A.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>21141.5_8155_F.</t>
+          <t>9756.3_2793_M.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>4781.2_1507_A.</t>
+          <t>8253.0_2972_🔋.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>17003.0_7696_P.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>7022.4_3008_L.</t>
+          <t>10016.9_3028_M.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>25020.8_7832_V.</t>
+          <t>5904.3_2699_P.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>9005.3_4344_A.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>611.2_221_M.</t>
+          <t>6035.0_2481_P.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>10030.0_3041_G.</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>4688.1_2291_C.</t>
+          <t>3958.9_1777_P.</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>14014.7_3537_S.</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>7593.7_2701_E.</t>
+          <t>7419.2_3469_F.</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>10022.1_2875_M.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>17003.0_7696_P.</t>
+          <t>15194.4_3911_S.</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>401.2_179_S.</t>
+          <t>6007.4_1804_G.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>6779.9_2003_E.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>10001.9_4466_P.</t>
+          <t>18102.7_4949_M.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>5010.3_3392_P.</t>
+          <t>4613.1_1806_A.</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>15200.8_10718_F.</t>
+          <t>3735.9_1928_V.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>14014.7_3537_S.</t>
+          <t>9507.9_2851_M.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>10010.0_2910_V.</t>
+          <t>15016.9_6221_G.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>9012.4_2700_M.</t>
+          <t>6036.4_2875_V.</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>37036.6_17889_F.</t>
+          <t>4000.6_1659_S.</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>10006.0_2772_V.</t>
+          <t>2051.8_860_S.</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>6084.1_2156_V.</t>
+          <t>5040.0_2514_C.</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>6007.1_2393_M.</t>
+          <t>8396.0_2595_S.</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>7992.7_2506_F.</t>
+          <t>18665.3_4638_S.</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>4153.2_3559_P.</t>
+          <t>5770.8_2848_G.</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>4850.9_2239_C.</t>
+          <t>5100.0_2587_A.</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>5224.2_2340_C.</t>
+          <t>13023.5_5156_L.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>5005.9_1755_X.</t>
+          <t>5020.6_1328_M.</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>6818.2_2036_P.</t>
+          <t>7420.2_4318_C.</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>4017.3_1883_C.</t>
+          <t>6011.8_1873_M.</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>7598.7_2799_S.</t>
+          <t>12022.7_5417_L.</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>5869.6_2613_P.</t>
+          <t>5021.7_1930_A.</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>2002.2_938_P.</t>
+          <t>5144.4_2349_P.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>4705.5_1241_G.</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>773.5_238_S.</t>
+          <t>10030.5_4765_C.</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>6011.8_1873_M.</t>
+          <t>18107.4_4577_M.</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>12521.4_4814_M.</t>
+          <t>16520.2_4844_M.</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>419.0_180_P.</t>
+          <t>123.0_5992_A.</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>7516.9_3203_A.</t>
+          <t>14019.6_6253_L.</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>7230.5_2794_V.</t>
+          <t>8092.0_4532_P.</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>5522.8_2716_V.</t>
+          <t>6951.4_2856_S.</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>5301.0_2064_F.</t>
+          <t>6620.4_2477_P.</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>4972.5_2522_S.</t>
+          <t>7593.7_2701_E.</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>5085.1_1840_G.</t>
+          <t>10002.4_5136_P.</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>2355.5_726_S.</t>
+          <t>4731.9_1407_T.</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>5287.4_1835_V.</t>
+          <t>5301.0_2064_F.</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>5242.7_1657_S.</t>
+          <t>5085.1_1840_G.</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>5004.5_1548_A.</t>
+          <t>2510.2_1366_V.</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>5086.0_1810_G.</t>
+          <t>6818.2_2036_P.</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>1114.9_359_S.</t>
+          <t>16008.9_5968_S.</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>4896.8_2251_L.</t>
+          <t>5029.4_1585_P.</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>5451.1_1905_T.</t>
+          <t>3580.9_1198_S.</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>21106.2_7925_P.</t>
+          <t>8132.9_2716_S.</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>8506.3_4050_C.</t>
+          <t>6012.6_2984_F.</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>6113.5_2883_C.</t>
+          <t>8351.7_4153_C.</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>14119.3_5262_S.</t>
+          <t>2000.0_724_A.</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>10012.1_3139_S.</t>
+          <t>9012.4_2700_M.</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>8024.4_2933_S.</t>
+          <t>7006.7_5717_S.</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>7114.0_2850_S.</t>
+          <t>5579.8_1990_E.</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>15016.9_6221_G.</t>
+          <t>14004.5_5478_M.</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>5296.8_1844_P.</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>4692.9_1546_P.</t>
+          <t>9013.7_2337_M.</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>4077.1_1454_S.</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>6004.0_2559_P.</t>
+          <t>5005.8_1527_S.</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>15223.0_6245_P.</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>4576.3_2084_S.</t>
+          <t>18516.8_6699_G.</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>6903.6_2566_G.</t>
+          <t>10106.6_2889_P.</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>10022.1_2875_M.</t>
+          <t>7003.6_2437_P.</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>2064.3_708_S.</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>553.2_224_S.</t>
+          <t>10012.1_3139_S.</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>5163.5_1775_V.</t>
+          <t>21207.4_6474_V.</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>3010.0_1424_A.</t>
+          <t>5004.0_2103_C.</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>4788.2_1476_P.</t>
+          <t>14009.0_5498_A.</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>5017.7_1147_M.</t>
+          <t>5022.5_1222_P.</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>7502.4_3467_P.</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>6345.4_2376_S.</t>
+          <t>6011.5_2408_A.</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>1027.7_364_S.</t>
+          <t>6536.2_2241_P.</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>6007.4_1804_G.</t>
+          <t>10001.9_4466_P.</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>5033.4_1976_M.</t>
+          <t>1701.7_720_F.</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>10007.8_2668_V.</t>
+          <t>6622.5_2224_E.</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>10012.3_3067_S.</t>
+          <t>4540.8_1823_A.</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>6012.6_2984_P.</t>
+          <t>8024.4_2933_S.</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>5064.3_1832_F.</t>
+          <t>401.2_179_S.</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>2783.5_952_S.</t>
+          <t>4177.9_1557_T.</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>1443.0_851_A.</t>
+          <t>16397.3_4254_S.</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>5235.4_1766_P.</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>13023.5_5156_L.</t>
+          <t>26010.2_9812_F.</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>5000.2_1932_E.</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>6804.1_2088_P.</t>
+          <t>10011.5_3070_S.</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>7312.2_2446_G.</t>
+          <t>6046.5_3239_S.</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>5007.1_1751_T.</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>5827.8_2106_S.</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>7569.4_2477_V.</t>
+          <t>4781.2_1507_A.</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>2000.0_724_A.</t>
+          <t>3614.8_970_🔋.</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>8481.2_2463_🔋.</t>
+          <t>4969.4_2146_P.</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>10006.9_3646_X.</t>
+          <t>4013.7_1173_V.</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>4786.5_1898_P.</t>
+          <t>6600.2_1915_M.</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>7025.4_3008_L.</t>
+          <t>2556.5_1160_M.</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>3006.0_1286_M.</t>
+          <t>4972.5_2522_S.</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>1002.7_460_S.</t>
+          <t>1012.0_375_E.</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>5007.4_1601_A.</t>
+          <t>4078.1_1810_A.</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>5382.2_2690_M.</t>
+          <t>5224.2_2340_C.</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>9415.9_3699_G.</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>7880.9_2433_E.</t>
+          <t>6006.6_2009_P.</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>5005.4_2618_L.</t>
+          <t>6610.9_1738_P.</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>16520.2_4844_M.</t>
+          <t>10643.3_3263_S.</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>7145.5_2856_E.</t>
+          <t>10006.9_3646_X.</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>18107.4_4577_M.</t>
+          <t>6173.6_2865_M.</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>791.5_266_G.</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>5004.0_2103_C.</t>
+          <t>208.3_85_P.</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>10027.3_2906_P.</t>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>4700.4_1216_V.</t>
+          <t>25020.8_7832_V.</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>6007.1_3172_F.</t>
+          <t>6006.1_2236_V.</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>9029.6_4595_P.</t>
+          <t>1020.0_679_T.</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>5770.8_2848_G.</t>
+          <t>7576.8_2823_P.</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>16008.9_5968_S.</t>
+          <t>4214.8_2018_A.</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>7127.8_1843_G.</t>
+          <t>6012.6_2984_P.</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>5025.8_1214_P.</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>3004.6_746_V.</t>
+          <t>5242.7_1657_S.</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>10020.8_2989_M.</t>
+          <t>8506.3_4050_C.</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>5000.6_1856_M.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>20105.6_7766_F.</t>
+          <t>2880.9_1210_L.</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>10348.3_2647_S.</t>
+          <t>5869.6_2613_P.</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>22320.3_9183_F.</t>
+          <t>20105.6_7766_F.</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>4788.2_1476_P.</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>9415.9_3699_G.</t>
+          <t>4700.4_1216_V.</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>5581.6_3687_P.</t>
+          <t>21124.1_8011_F.</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>8396.0_2595_S.</t>
+          <t>4891.7_1690_F.</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>6038.2_2121_P.</t>
+          <t>17012.6_5869_T.</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>5009.1_2246_C.</t>
+          <t>9007.1_3080_P.</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>5238.0_2781_F.</t>
+          <t>5017.7_1147_M.</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>10002.4_5136_P.</t>
+          <t>5008.2_1646_A.</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>2060.0_802_S.</t>
+          <t>5256.5_1535_S.</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>5522.8_2716_V.</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>657.7_273_S.</t>
+          <t>3019.8_1453_F.</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>2036.1_839_S.</t>
+          <t>5005.4_2618_L.</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>10007.4_3588_V.</t>
+          <t>7985.2_2173_P.</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>5025.8_1214_P.</t>
+          <t>56121.5_25636_F.</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>14117.6_3844_M.</t>
+          <t>10030.1_3124_M.</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>15223.0_6245_P.</t>
+          <t>4797.2_1541_G.</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>3026.1_1490_A.</t>
+          <t>10003.7_2721_V.</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>5287.4_1835_V.</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>2558.7_905_S.</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>5043.1_2254_C.</t>
+          <t>2036.1_839_S.</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>3597.6_2910_E.</t>
+          <t>14009.7_4401_V.</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>2004.9_754_S.</t>
+          <t>3089.9_1508_C.</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>5013.9_1673_A.</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>3012.4_1258_P.</t>
+          <t>4896.8_2251_L.</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>8351.7_4153_C.</t>
+          <t>9639.7_4763_P.</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>7001.2_3357_M.</t>
+          <t>4028.8_1699_L.</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>6661.8_3736_P.</t>
+          <t>4688.1_2291_C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>4814.5_1705_🔋.</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>8416.2_4091_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>21106.2_7925_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>5027.8_1361_P.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_500km_2026.xlsx
+++ b/Ranking_CNB_500km_2026.xlsx
@@ -454,12 +454,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>642,9 km</t>
+          <t>664,9 km</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>10.089 m</t>
+          <t>10.327 m</t>
         </is>
       </c>
     </row>
@@ -471,12 +471,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>493,2 km</t>
+          <t>498,2 km</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>6.551 m</t>
+          <t>6.613 m</t>
         </is>
       </c>
     </row>
@@ -488,12 +488,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>299,9 km</t>
+          <t>309,9 km</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.875 m</t>
+          <t>3.067 m</t>
         </is>
       </c>
     </row>
@@ -505,46 +505,46 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>250,9 km</t>
+          <t>262,9 km</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.078 m</t>
+          <t>2.174 m</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Fernanda G.</t>
+          <t>Jéssica P.</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>217,2 km</t>
+          <t>224,2 km</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.550 m</t>
+          <t>2.093 m</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Jéssica P.</t>
+          <t>Fernanda G.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>211,2 km</t>
+          <t>222,2 km</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.986 m</t>
+          <t>2.608 m</t>
         </is>
       </c>
     </row>
@@ -556,12 +556,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>192,8 km</t>
+          <t>214,8 km</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.481 m</t>
+          <t>2.722 m</t>
         </is>
       </c>
     </row>
@@ -573,12 +573,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>179,0 km</t>
+          <t>189,3 km</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.202 m</t>
+          <t>1.284 m</t>
         </is>
       </c>
     </row>
@@ -590,29 +590,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>177,9 km</t>
+          <t>182,9 km</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.007 m</t>
+          <t>2.066 m</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cassia C.</t>
+          <t>Jandson P.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>152,7 km</t>
+          <t>171,6 km</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.901 m</t>
+          <t>2.249 m</t>
         </is>
       </c>
     </row>
@@ -624,46 +624,46 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>152,0 km</t>
+          <t>162,0 km</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.027 m</t>
+          <t>1.120 m</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Jandson P.</t>
+          <t>Alexsia A.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>150,5 km</t>
+          <t>152,9 km</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2.028 m</t>
+          <t>1.662 m</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Alexsia A.</t>
+          <t>Cassia C.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>148,0 km</t>
+          <t>152,7 km</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.606 m</t>
+          <t>1.901 m</t>
         </is>
       </c>
     </row>
@@ -675,80 +675,80 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>129,2 km</t>
+          <t>141,2 km</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.065 m</t>
+          <t>1.210 m</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Naiane C.</t>
+          <t>Duda X.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>127,0 km</t>
+          <t>136,6 km</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.182 m</t>
+          <t>1.627 m</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Edivânia M.</t>
+          <t>Naiane C.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>126,0 km</t>
+          <t>132,0 km</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.374 m</t>
+          <t>1.234 m</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Neydrielle V.</t>
+          <t>Edivânia M.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>112,9 km</t>
+          <t>131,0 km</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.071 m</t>
+          <t>1.432 m</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Duda X.</t>
+          <t>Neydrielle V.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>102,6 km</t>
+          <t>124,1 km</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.218 m</t>
+          <t>1.219 m</t>
         </is>
       </c>
     </row>
@@ -760,12 +760,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>101,4 km</t>
+          <t>106,3 km</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>779 m</t>
+          <t>836 m</t>
         </is>
       </c>
     </row>
@@ -777,12 +777,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>89,6 km</t>
+          <t>94,6 km</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.112 m</t>
+          <t>1.170 m</t>
         </is>
       </c>
     </row>
@@ -794,12 +794,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>81,4 km</t>
+          <t>92,1 km</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>924 m</t>
+          <t>1.058 m</t>
         </is>
       </c>
     </row>
@@ -828,12 +828,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>66,8 km</t>
+          <t>71,8 km</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>721 m</t>
+          <t>782 m</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>60,7 km</t>
+          <t>65,7 km</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>554 m</t>
+          <t>610 m</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A369"/>
+  <dimension ref="A1:A393"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1014,2282 +1014,2282 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5072.4_1931_S.</t>
+          <t>3010.0_1685_A.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>6004.0_2559_P.</t>
+          <t>6007.1_2393_M.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>2060.0_802_S.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>7039.1_2754_S.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>8200.5_2738_M.</t>
+          <t>4013.7_1173_V.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>22320.3_9183_F.</t>
+          <t>9007.1_3080_P.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10007.8_2733_V.</t>
+          <t>5020.6_1328_M.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1629.5_671_F.</t>
+          <t>7593.7_2701_E.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4830.1_2569_C.</t>
+          <t>21114.4_6098_P.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3597.6_2910_E.</t>
+          <t>4899.2_1459_A.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>4028.8_1699_L.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>6006.1_2236_V.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>553.2_224_S.</t>
+          <t>6345.4_2376_S.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5299.8_2406_C.</t>
+          <t>10006.9_3646_F.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>611.2_221_M.</t>
+          <t>5027.8_1361_P.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3026.1_1490_A.</t>
+          <t>6010.6_2144_A.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5064.2_1636_G.</t>
+          <t>5365.6_2437_C.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>1443.0_851_A.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5064.3_1832_F.</t>
+          <t>4937.4_1783_A.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1114.9_359_S.</t>
+          <t>7006.7_5717_S.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>12022.7_5417_L.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>5581.6_3687_P.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>9209.1_3141_E.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>6011.8_1873_M.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>6010.6_2144_A.</t>
+          <t>4768.0_1875_L.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>657.7_273_S.</t>
+          <t>8481.2_2463_🔋.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>5238.0_2781_F.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>6007.1_3172_F.</t>
+          <t>16520.2_4844_M.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3010.0_1289_A.</t>
+          <t>6003.3_2987_M.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5365.6_2437_C.</t>
+          <t>8104.2_2652_M.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5009.1_2246_C.</t>
+          <t>791.5_266_G.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>4786.5_1898_P.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>6038.2_2121_P.</t>
+          <t>3580.9_1198_S.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>6113.5_2883_C.</t>
+          <t>7576.8_2823_P.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>4932.4_1545_E.</t>
+          <t>21106.2_7925_P.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>7025.4_3008_L.</t>
+          <t>5064.3_1832_F.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3006.0_1286_M.</t>
+          <t>6600.2_1915_M.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>5579.8_1990_E.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10010.0_2910_V.</t>
+          <t>10006.0_2772_V.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>12545.4_3039_S.</t>
+          <t>2305.1_940_S.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2060.0_802_S.</t>
+          <t>5017.7_1147_M.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>6903.6_2566_G.</t>
+          <t>5049.0_2240_C.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>8442.5_3038_G.</t>
+          <t>53755.6_36604_F.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>10007.8_2668_V.</t>
+          <t>15016.9_6221_G.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>10012.3_3067_S.</t>
+          <t>9029.6_4595_P.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>5621.6_2375_P.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2504.7_703_🔋.</t>
+          <t>5287.4_1835_V.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>8196.1_2807_T.</t>
+          <t>6012.6_2984_P.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>5580.0_2471_A.</t>
+          <t>6536.2_2241_P.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>10031.8_2663_P.</t>
+          <t>3138.1_1120_S.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>8618.0_2344_P.</t>
+          <t>5296.8_1844_P.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>7230.5_2794_V.</t>
+          <t>123.0_5992_A.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>7145.5_2856_E.</t>
+          <t>6951.4_2856_S.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>6804.1_2088_P.</t>
+          <t>5006.8_1080_M.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>5005.9_1755_X.</t>
+          <t>5007.4_1601_A.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>7569.4_2477_V.</t>
+          <t>5004.1_1610_M.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>15504.3_3950_M.</t>
+          <t>5014.3_1731_F.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>10020.8_2989_M.</t>
+          <t>3010.0_1289_A.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>4017.3_1883_C.</t>
+          <t>15200.8_10718_F.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>7127.8_1843_G.</t>
+          <t>4932.4_1545_E.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>5051.4_1993_M.</t>
+          <t>5005.4_2618_L.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>4790.7_1897_F.</t>
+          <t>4678.8_1840_A.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>10030.1_3124_M.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>10030.0_3041_G.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2557.8_1206_V.</t>
+          <t>5028.5_4433_S.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>5007.4_1601_A.</t>
+          <t>17003.0_7696_P.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>5004.9_1790_A.</t>
+          <t>18665.3_4638_S.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>8008.0_2930_A.</t>
+          <t>9555.5_5689_S.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>4821.0_1857_P.</t>
+          <t>4788.2_1476_P.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>773.5_238_S.</t>
+          <t>4735.2_997_S.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>8004.6_2357_G.</t>
+          <t>15194.4_3911_S.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1002.7_460_S.</t>
+          <t>8200.5_2738_M.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>7012.1_3931_🔋.</t>
+          <t>7025.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>4917.5_2381_T.</t>
+          <t>5382.2_2690_M.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>5238.0_2781_F.</t>
+          <t>7419.2_3469_F.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>10006.0_2772_V.</t>
+          <t>7015.4_2141_T.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>1027.7_364_S.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>9005.3_4344_A.</t>
+          <t>14014.7_3537_S.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>4576.3_2084_S.</t>
+          <t>5005.9_1755_X.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>4153.2_3559_P.</t>
+          <t>10718.1_9873_S.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2011.7_731_S.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1432.9_3942_M.</t>
+          <t>4781.2_1507_A.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>6007.1_2393_M.</t>
+          <t>20105.6_7766_F.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10006.9_3646_F.</t>
+          <t>10027.3_2906_P.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>7598.7_2799_S.</t>
+          <t>10174.3_3680_S.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>9006.5_3085_X.</t>
+          <t>1629.5_671_F.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>5008.0_2402_P.</t>
+          <t>14009.7_4401_V.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>3004.6_746_V.</t>
+          <t>14009.0_5498_A.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>10503.6_3278_M.</t>
+          <t>5022.5_1222_P.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>4791.5_1524_E.</t>
+          <t>6137.8_2406_L.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>6003.3_2987_M.</t>
+          <t>2002.2_938_P.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>7880.9_2433_E.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>4786.5_1898_P.</t>
+          <t>5064.2_1636_G.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>21124.1_8011_F.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>3757.2_1716_A.</t>
+          <t>12006.9_5463_P.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>7022.4_3008_L.</t>
+          <t>8092.0_4532_P.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>5010.0_1872_A.</t>
+          <t>12006.1_5290_X.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>419.0_180_P.</t>
+          <t>9791.4_3527_G.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>8351.7_4153_C.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>3010.0_1685_A.</t>
+          <t>10001.3_4206_G.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>7880.9_2433_E.</t>
+          <t>3004.6_746_V.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>8481.2_2463_🔋.</t>
+          <t>9639.7_4763_P.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>2036.1_839_S.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>5040.0_2514_C.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2783.5_952_S.</t>
+          <t>6472.0_2501_S.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>15186.5_3866_S.</t>
+          <t>8506.3_4050_C.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>4864.8_1353_E.</t>
+          <t>17012.6_5869_T.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>3023.2_962_S.</t>
+          <t>6518.4_2914_A.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>7114.0_2850_S.</t>
+          <t>4917.5_2381_T.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>5033.4_1976_M.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>7874.8_2223_M.</t>
+          <t>7312.2_2446_G.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>531.0_343_A.</t>
+          <t>5051.4_1993_M.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>1034.3_279_M.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>3026.1_1490_A.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>3412.3_1947_C.</t>
+          <t>9507.9_2851_M.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>4688.1_2291_C.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>3059.2_956_T.</t>
+          <t>2051.8_860_S.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2002.2_938_P.</t>
+          <t>4972.5_2522_S.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>5451.1_1905_T.</t>
+          <t>12545.4_3039_S.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>7024.3_3266_L.</t>
+          <t>6006.6_2009_P.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1027.7_364_S.</t>
+          <t>5004.0_2103_C.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>960.0_1109_A.</t>
+          <t>8187.1_2322_M.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>7992.7_2506_F.</t>
+          <t>10003.7_2721_V.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1366.2_487_L.</t>
+          <t>4078.1_1810_A.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>5086.0_1810_G.</t>
+          <t>8416.2_4091_P.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>5299.8_2406_C.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>8187.1_2322_M.</t>
+          <t>10006.9_3646_X.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>5004.5_1548_A.</t>
+          <t>10277.3_4318_L.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>3012.4_1258_P.</t>
+          <t>15186.5_3866_S.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>5043.1_2254_C.</t>
+          <t>4077.1_1454_S.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>15200.8_10718_F.</t>
+          <t>4017.3_1883_C.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>37036.6_17889_F.</t>
+          <t>7502.4_3467_P.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>5020.4_2167_C.</t>
+          <t>4790.7_1897_F.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>14117.6_3844_M.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>4921.0_2491_A.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>10007.8_2733_V.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>5981.9_2551_P.</t>
+          <t>5301.0_2064_F.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>5011.9_1594_P.</t>
+          <t>5040.0_2299_A.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>5040.0_2971_A.</t>
+          <t>1011.0_396_L.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>6661.8_3736_P.</t>
+          <t>531.0_343_A.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>5163.5_1775_V.</t>
+          <t>6622.5_2224_E.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>10007.8_2668_V.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1443.0_851_A.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2004.9_754_S.</t>
+          <t>4797.2_1541_G.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>5282.8_2392_C.</t>
+          <t>3010.0_1424_A.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>6016.7_2122_M.</t>
+          <t>8396.0_2595_S.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>6084.1_2156_V.</t>
+          <t>1366.2_487_L.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>14119.3_5262_S.</t>
+          <t>5033.4_1976_M.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>4692.9_1546_P.</t>
+          <t>10006.5_3648_X.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>5382.2_2690_M.</t>
+          <t>7985.2_2173_P.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>5000.6_1856_M.</t>
+          <t>4700.4_1216_V.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>5010.3_3392_P.</t>
+          <t>2355.5_726_S.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>9791.4_3527_G.</t>
+          <t>2510.2_1366_V.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>9029.6_4595_P.</t>
+          <t>5072.4_1931_S.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>5001.9_1291_V.</t>
+          <t>15057.9_8625_F.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>8367.5_4269_C.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>5003.2_1389_E.</t>
+          <t>12013.5_4635_X.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>37036.6_17889_F.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>7001.2_3357_M.</t>
+          <t>1380.0_562_A.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>14117.6_3844_M.</t>
+          <t>5004.9_1790_A.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>6345.4_2376_S.</t>
+          <t>8120.9_2737_G.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>12008.4_3832_G.</t>
+          <t>3798.9_1319_S.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>4969.4_2146_P.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2047.9_924_L.</t>
+          <t>5020.4_2167_C.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>3138.1_1120_S.</t>
+          <t>26010.2_9812_F.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>6833.7_2100_G.</t>
+          <t>11214.0_4224_V.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2185.4_792_S.</t>
+          <t>4153.2_3559_P.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>12342.9_3211_M.</t>
+          <t>4791.5_1524_E.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>6113.5_2883_C.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>15637.2_5789_G.</t>
+          <t>5163.5_1775_V.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>7312.2_2446_G.</t>
+          <t>6084.1_2156_V.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2186.2_736_G.</t>
+          <t>9013.7_2337_M.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>5724.1_3694_S.</t>
+          <t>9415.9_3699_G.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2735.8_959_S.</t>
+          <t>2004.9_754_S.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>8218.3_2327_P.</t>
+          <t>10022.1_2875_M.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>6518.4_2914_A.</t>
+          <t>5000.2_1932_E.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>5081.5_1647_G.</t>
+          <t>8132.9_2716_S.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>4850.9_2239_C.</t>
+          <t>6007.1_3172_F.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>3798.9_1319_S.</t>
+          <t>2047.9_924_L.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>10003.3_3845_P.</t>
+          <t>401.2_179_S.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>7039.1_2754_S.</t>
+          <t>2185.4_792_S.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>1380.0_562_A.</t>
+          <t>5008.2_1646_A.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>3010.0_1424_A.</t>
+          <t>7012.1_3931_🔋.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>5581.6_3687_P.</t>
+          <t>1884.9_866_S.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>9555.5_5689_S.</t>
+          <t>21442.0_7959_F.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>10031.8_2663_P.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2355.5_726_S.</t>
+          <t>5004.5_1548_A.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>7516.9_3203_A.</t>
+          <t>1083.2_390_M.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>1034.3_279_M.</t>
+          <t>10106.6_2889_P.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>8367.5_4269_C.</t>
+          <t>3958.9_1777_P.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>53755.6_36604_F.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>1083.2_390_M.</t>
+          <t>2558.7_905_S.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>5010.3_1888_G.</t>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>15057.9_8625_F.</t>
+          <t>8618.0_2344_P.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>7090.6_3340_A.</t>
+          <t>7420.2_4318_C.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>5028.5_4433_S.</t>
+          <t>5000.6_1856_M.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>21141.5_8155_F.</t>
+          <t>4000.6_1659_S.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>10007.4_3588_V.</t>
+          <t>5282.8_2392_C.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>4678.8_1840_A.</t>
+          <t>16008.9_5968_S.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>10348.3_2647_S.</t>
+          <t>10003.1_5062_V.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>10533.4_4020_F.</t>
+          <t>8253.0_2972_🔋.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>4735.2_997_S.</t>
+          <t>611.2_221_M.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>10016.9_3028_M.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>12524.7_3259_S.</t>
+          <t>3597.6_2910_E.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>10027.3_2906_P.</t>
+          <t>3735.9_1928_V.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>5014.8_2009_A.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>9756.3_2793_M.</t>
+          <t>6038.2_2121_P.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>553.2_224_S.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>17003.0_7696_P.</t>
+          <t>5040.0_2971_A.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>10016.9_3028_M.</t>
+          <t>6620.4_2477_P.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>5904.3_2699_P.</t>
+          <t>2735.8_959_S.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>5451.1_1905_T.</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>12521.4_4814_M.</t>
+          <t>6046.5_3239_S.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>6035.0_2481_P.</t>
+          <t>5981.9_2551_P.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>10030.0_3041_G.</t>
+          <t>18102.7_4949_M.</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>3958.9_1777_P.</t>
+          <t>9209.1_3141_E.</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>14014.7_3537_S.</t>
+          <t>10010.0_2910_V.</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>7419.2_3469_F.</t>
+          <t>4576.3_2084_S.</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>10022.1_2875_M.</t>
+          <t>4830.1_2569_C.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>15194.4_3911_S.</t>
+          <t>7022.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>6007.4_1804_G.</t>
+          <t>10533.4_4020_F.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>6779.9_2003_E.</t>
+          <t>3023.2_962_S.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>18102.7_4949_M.</t>
+          <t>10012.3_3067_S.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>4613.1_1806_A.</t>
+          <t>5119.6_3153_M.</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>3735.9_1928_V.</t>
+          <t>10503.6_3278_M.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>9507.9_2851_M.</t>
+          <t>3006.0_1286_M.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>15016.9_6221_G.</t>
+          <t>5007.1_1751_T.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>6036.4_2875_V.</t>
+          <t>5256.5_1535_S.</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>4000.6_1659_S.</t>
+          <t>15637.2_5789_G.</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>960.0_1109_A.</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>5040.0_2514_C.</t>
+          <t>2556.5_1160_M.</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>8396.0_2595_S.</t>
+          <t>657.7_273_S.</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>18665.3_4638_S.</t>
+          <t>6036.4_2875_V.</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>5770.8_2848_G.</t>
+          <t>14019.6_6253_L.</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>5100.0_2587_A.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>13023.5_5156_L.</t>
+          <t>6610.9_1738_P.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>5020.6_1328_M.</t>
+          <t>5005.8_1527_S.</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>7420.2_4318_C.</t>
+          <t>4814.5_1705_🔋.</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>6011.8_1873_M.</t>
+          <t>6016.7_2122_M.</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>12022.7_5417_L.</t>
+          <t>10348.3_2647_S.</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>5021.7_1930_A.</t>
+          <t>10003.3_3845_P.</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>5144.4_2349_P.</t>
+          <t>2064.3_708_S.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>5522.8_2716_V.</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>10030.5_4765_C.</t>
+          <t>9005.3_4344_A.</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>18107.4_4577_M.</t>
+          <t>2880.9_1210_L.</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>16520.2_4844_M.</t>
+          <t>7001.2_3357_M.</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>123.0_5992_A.</t>
+          <t>7127.8_1843_G.</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>14019.6_6253_L.</t>
+          <t>10007.4_3588_V.</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>8092.0_4532_P.</t>
+          <t>13008.2_4958_P.</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>2557.8_1206_V.</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>6951.4_2856_S.</t>
+          <t>5144.4_2349_P.</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>6620.4_2477_P.</t>
+          <t>3614.8_970_🔋.</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>7593.7_2701_E.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>10002.4_5136_P.</t>
+          <t>21207.4_6474_V.</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>3012.4_1258_P.</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>5301.0_2064_F.</t>
+          <t>3019.8_1453_F.</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>5085.1_1840_G.</t>
+          <t>5224.2_2340_C.</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>2510.2_1366_V.</t>
+          <t>1432.9_3942_M.</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>6818.2_2036_P.</t>
+          <t>2783.5_952_S.</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>10008.1_2966_M.</t>
+          <t>3412.3_1947_C.</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>16008.9_5968_S.</t>
+          <t>22008.4_8412_F.</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>5029.4_1585_P.</t>
+          <t>8218.3_2327_P.</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>8196.1_2807_T.</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>8132.9_2716_S.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>8351.7_4153_C.</t>
+          <t>7003.6_2437_P.</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>2000.0_724_A.</t>
+          <t>8024.4_2933_S.</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>9012.4_2700_M.</t>
+          <t>7024.3_3266_L.</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>7006.7_5717_S.</t>
+          <t>4850.9_2239_C.</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>5579.8_1990_E.</t>
+          <t>5000.5_1919_P.</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>14004.5_5478_M.</t>
+          <t>5242.7_1657_S.</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>5296.8_1844_P.</t>
+          <t>4821.0_1857_P.</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>10002.4_5136_P.</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>18516.8_6699_G.</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>5005.8_1527_S.</t>
+          <t>7145.5_2856_E.</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>15223.0_6245_P.</t>
+          <t>1012.0_375_E.</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>18516.8_6699_G.</t>
+          <t>2504.7_703_🔋.</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>10106.6_2889_P.</t>
+          <t>6007.4_1804_G.</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>7003.6_2437_P.</t>
+          <t>1002.7_460_S.</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>2064.3_708_S.</t>
+          <t>10001.9_4466_P.</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>10012.1_3139_S.</t>
+          <t>15223.0_6245_P.</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>21207.4_6474_V.</t>
+          <t>4705.5_1241_G.</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>5004.0_2103_C.</t>
+          <t>12008.4_3832_G.</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>14009.0_5498_A.</t>
+          <t>6004.0_2559_P.</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>5022.5_1222_P.</t>
+          <t>12342.9_3211_M.</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>7502.4_3467_P.</t>
+          <t>6779.9_2003_E.</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>6011.5_2408_A.</t>
+          <t>5085.1_1840_G.</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>6536.2_2241_P.</t>
+          <t>4896.8_2251_L.</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>10001.9_4466_P.</t>
+          <t>5014.5_1497_G.</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>1701.7_720_F.</t>
+          <t>25020.8_7832_V.</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>6622.5_2224_E.</t>
+          <t>4763.8_1720_P.</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>4540.8_1823_A.</t>
+          <t>5580.0_2471_A.</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>8024.4_2933_S.</t>
+          <t>12524.7_3259_S.</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>401.2_179_S.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>4177.9_1557_T.</t>
+          <t>5724.1_3694_S.</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>16397.3_4254_S.</t>
+          <t>7992.7_2506_F.</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>5235.4_1766_P.</t>
+          <t>10058.8_3483_F.</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>26010.2_9812_F.</t>
+          <t>8004.6_2357_G.</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>5000.2_1932_E.</t>
+          <t>4692.9_1546_P.</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>10011.5_3070_S.</t>
+          <t>2011.7_731_S.</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>8008.0_2930_A.</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>5007.1_1751_T.</t>
+          <t>3059.2_956_T.</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>5827.8_2106_S.</t>
+          <t>5001.9_1291_V.</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>4781.2_1507_A.</t>
+          <t>18107.4_4577_M.</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>5021.7_1930_A.</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>4969.4_2146_P.</t>
+          <t>12326.4_4833_S.</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>4013.7_1173_V.</t>
+          <t>4177.9_1557_T.</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>6600.2_1915_M.</t>
+          <t>22002.4_8469_M.</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>2556.5_1160_M.</t>
+          <t>5043.1_2254_C.</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>4972.5_2522_S.</t>
+          <t>10011.5_3070_S.</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>1012.0_375_E.</t>
+          <t>6903.6_2566_G.</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>4078.1_1810_A.</t>
+          <t>7516.9_3203_A.</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>5224.2_2340_C.</t>
+          <t>56121.5_25636_F.</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>9415.9_3699_G.</t>
+          <t>12002.7_4232_S.</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>6006.6_2009_P.</t>
+          <t>5770.8_2848_G.</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>6610.9_1738_P.</t>
+          <t>5235.4_1766_P.</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>10643.3_3263_S.</t>
+          <t>7114.0_2850_S.</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>10006.9_3646_X.</t>
+          <t>6012.6_2984_F.</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>6173.6_2865_M.</t>
+          <t>5025.8_1214_P.</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>791.5_266_G.</t>
+          <t>14004.5_5478_M.</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>10106.6_3354_M.</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>5086.0_1810_G.</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>25020.8_7832_V.</t>
+          <t>2175.4_712_S.</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>6006.1_2236_V.</t>
+          <t>5009.1_2246_C.</t>
         </is>
       </c>
     </row>
@@ -3303,287 +3303,455 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>7576.8_2823_P.</t>
+          <t>3089.9_1508_C.</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>4214.8_2018_A.</t>
+          <t>4921.0_2491_A.</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>6012.6_2984_P.</t>
+          <t>773.5_238_S.</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>5025.8_1214_P.</t>
+          <t>4864.8_1353_E.</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>5242.7_1657_S.</t>
+          <t>6011.5_2408_A.</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>8506.3_4050_C.</t>
+          <t>5010.3_1888_G.</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>21141.5_8155_F.</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>2880.9_1210_L.</t>
+          <t>10030.5_4765_C.</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>5869.6_2613_P.</t>
+          <t>10643.3_3263_S.</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>20105.6_7766_F.</t>
+          <t>5003.2_1389_E.</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>4788.2_1476_P.</t>
+          <t>5904.3_2699_P.</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>4700.4_1216_V.</t>
+          <t>3757.2_1716_A.</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>21124.1_8011_F.</t>
+          <t>6818.2_2036_P.</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>5013.9_1673_A.</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>12006.1_5290_T.</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>9007.1_3080_P.</t>
+          <t>4974.4_1533_E.</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>5017.7_1147_M.</t>
+          <t>5827.8_2106_S.</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>5008.2_1646_A.</t>
+          <t>4214.8_2018_A.</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>5256.5_1535_S.</t>
+          <t>6173.6_2865_M.</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>5522.8_2716_V.</t>
+          <t>6661.8_3736_P.</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>5029.4_1585_P.</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>5005.4_2618_L.</t>
+          <t>8442.5_3038_G.</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>7985.2_2173_P.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>56121.5_25636_F.</t>
+          <t>5010.3_3392_P.</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>10030.1_3124_M.</t>
+          <t>22320.3_9183_F.</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>4797.2_1541_G.</t>
+          <t>7569.4_2477_V.</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>10003.7_2721_V.</t>
+          <t>13023.5_5156_L.</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>5287.4_1835_V.</t>
+          <t>7230.5_2794_V.</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>2558.7_905_S.</t>
+          <t>4731.9_1407_T.</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>2036.1_839_S.</t>
+          <t>7598.7_2799_S.</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>14009.7_4401_V.</t>
+          <t>10020.8_2989_M.</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>3089.9_1508_C.</t>
+          <t>5081.5_1647_G.</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>5013.9_1673_A.</t>
+          <t>5869.6_2613_P.</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>4896.8_2251_L.</t>
+          <t>4891.7_1690_F.</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>9639.7_4763_P.</t>
+          <t>6035.0_2481_P.</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>4028.8_1699_L.</t>
+          <t>7874.8_2223_M.</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>4688.1_2291_C.</t>
+          <t>4540.8_1823_A.</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>16397.3_4254_S.</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>8416.2_4091_P.</t>
+          <t>419.0_180_P.</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>21106.2_7925_P.</t>
+          <t>1701.7_720_F.</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>5027.8_1361_P.</t>
+          <t>5100.0_2587_A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>5002.9_1487_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>15504.3_3950_M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>5014.8_2009_A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>5008.0_2402_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>5621.6_2375_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>6804.1_2088_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>9756.3_2793_M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>10012.1_3139_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>9012.4_2700_M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>3005.2_1040_L.</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>5011.9_1594_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>7090.6_3340_A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>2000.0_724_A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>9562.8_3145_M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>9006.5_3085_X.</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>14119.3_5262_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>4613.1_1806_A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>6833.7_2100_G.</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>1114.9_359_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>5010.0_1872_A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>2186.2_736_G.</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>208.3_85_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>10062.5_2886_M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_500km_2026.xlsx
+++ b/Ranking_CNB_500km_2026.xlsx
@@ -471,12 +471,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>498,2 km</t>
+          <t>505,5 km</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>6.613 m</t>
+          <t>6.716 m</t>
         </is>
       </c>
     </row>
@@ -488,12 +488,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>309,9 km</t>
+          <t>314,0 km</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.067 m</t>
+          <t>3.107 m</t>
         </is>
       </c>
     </row>
@@ -505,46 +505,46 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>262,9 km</t>
+          <t>270,1 km</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.174 m</t>
+          <t>2.219 m</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Jéssica P.</t>
+          <t>Fernanda G.</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>224,2 km</t>
+          <t>227,4 km</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.093 m</t>
+          <t>2.666 m</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Fernanda G.</t>
+          <t>Jéssica P.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>222,2 km</t>
+          <t>224,2 km</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.608 m</t>
+          <t>2.093 m</t>
         </is>
       </c>
     </row>
@@ -568,34 +568,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Gabriele L.</t>
+          <t>Mateus P.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>189,3 km</t>
+          <t>204,2 km</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.284 m</t>
+          <t>2.304 m</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Mateus P.</t>
+          <t>Gabriele L.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>182,9 km</t>
+          <t>189,3 km</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.066 m</t>
+          <t>1.284 m</t>
         </is>
       </c>
     </row>
@@ -874,17 +874,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Thaisa V.</t>
+          <t>Eduardo T.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>30,6 km</t>
+          <t>33,7 km</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>430 m</t>
+          <t>376 m</t>
         </is>
       </c>
     </row>
@@ -896,29 +896,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>28,2 km</t>
+          <t>33,2 km</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>408 m</t>
+          <t>464 m</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Eduardo T.</t>
+          <t>Thaisa V.</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>27,7 km</t>
+          <t>30,6 km</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>295 m</t>
+          <t>430 m</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A393"/>
+  <dimension ref="A1:A401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1014,1036 +1014,1036 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3010.0_1685_A.</t>
+          <t>5051.4_1993_M.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>6007.1_2393_M.</t>
+          <t>5005.9_1755_X.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2060.0_802_S.</t>
+          <t>15637.2_5789_G.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>7039.1_2754_S.</t>
+          <t>2880.9_1210_L.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4013.7_1173_V.</t>
+          <t>4891.7_1690_F.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>9007.1_3080_P.</t>
+          <t>6011.5_2408_A.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5020.6_1328_M.</t>
+          <t>2002.2_938_P.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>7593.7_2701_E.</t>
+          <t>7598.7_2799_S.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>21114.4_6098_P.</t>
+          <t>6622.5_2224_E.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>4899.2_1459_A.</t>
+          <t>5011.9_1594_P.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4028.8_1699_L.</t>
+          <t>10348.3_2647_S.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6006.1_2236_V.</t>
+          <t>4763.8_1720_P.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6345.4_2376_S.</t>
+          <t>4899.2_1459_A.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10006.9_3646_F.</t>
+          <t>3580.9_1198_S.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5027.8_1361_P.</t>
+          <t>4821.0_1857_P.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>6010.6_2144_A.</t>
+          <t>5014.8_2009_A.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5365.6_2437_C.</t>
+          <t>15057.9_8625_F.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1443.0_851_A.</t>
+          <t>8200.5_2738_M.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4937.4_1783_A.</t>
+          <t>6007.4_1804_G.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>7006.7_5717_S.</t>
+          <t>5724.1_3694_S.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>12022.7_5417_L.</t>
+          <t>531.0_343_A.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5581.6_3687_P.</t>
+          <t>7015.4_2141_T.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>4974.4_1533_E.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>6011.8_1873_M.</t>
+          <t>2000.0_724_A.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>18107.4_4577_M.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>8481.2_2463_🔋.</t>
+          <t>17003.0_7696_P.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5238.0_2781_F.</t>
+          <t>5296.8_1844_P.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>16520.2_4844_M.</t>
+          <t>6047.4_2816_T.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>6003.3_2987_M.</t>
+          <t>3010.0_1424_A.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>1012.0_375_E.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>791.5_266_G.</t>
+          <t>6779.9_2003_E.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>4786.5_1898_P.</t>
+          <t>2036.1_839_S.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>8132.9_2716_S.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>7576.8_2823_P.</t>
+          <t>9639.7_4763_P.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>21106.2_7925_P.</t>
+          <t>14019.6_6253_L.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5064.3_1832_F.</t>
+          <t>5002.9_1487_P.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>6600.2_1915_M.</t>
+          <t>6610.9_1738_P.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>5579.8_1990_E.</t>
+          <t>2064.3_708_S.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10006.0_2772_V.</t>
+          <t>3010.0_1685_A.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>10003.7_2721_V.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>5017.7_1147_M.</t>
+          <t>8196.1_2807_T.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>5049.0_2240_C.</t>
+          <t>6345.4_2376_S.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>53755.6_36604_F.</t>
+          <t>16520.2_4844_M.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>15016.9_6221_G.</t>
+          <t>6036.4_2875_V.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>9029.6_4595_P.</t>
+          <t>8351.7_4153_C.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>5040.0_2299_A.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>5287.4_1835_V.</t>
+          <t>1366.2_487_L.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>6012.6_2984_P.</t>
+          <t>10016.9_3028_M.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>6536.2_2241_P.</t>
+          <t>5086.0_1810_G.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3138.1_1120_S.</t>
+          <t>8506.3_4050_C.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>5296.8_1844_P.</t>
+          <t>8396.0_2595_S.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>123.0_5992_A.</t>
+          <t>5579.8_1990_E.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>6951.4_2856_S.</t>
+          <t>5010.3_3392_P.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>5006.8_1080_M.</t>
+          <t>2305.1_940_S.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>5007.4_1601_A.</t>
+          <t>5004.0_2103_C.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>5004.1_1610_M.</t>
+          <t>7874.8_2223_M.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>5581.6_3687_P.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>3010.0_1289_A.</t>
+          <t>4791.5_1524_E.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>15200.8_10718_F.</t>
+          <t>4692.9_1546_P.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>4932.4_1545_E.</t>
+          <t>4797.2_1541_G.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>5005.4_2618_L.</t>
+          <t>6016.7_2122_M.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>4678.8_1840_A.</t>
+          <t>8004.6_2357_G.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>10030.1_3124_M.</t>
+          <t>25020.8_7832_V.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>10030.0_3041_G.</t>
+          <t>6173.6_2865_M.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>5028.5_4433_S.</t>
+          <t>8367.5_4269_C.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>17003.0_7696_P.</t>
+          <t>15200.8_10718_F.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>18665.3_4638_S.</t>
+          <t>4896.8_2251_L.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>9555.5_5689_S.</t>
+          <t>5003.2_1389_E.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>4788.2_1476_P.</t>
+          <t>21141.5_8155_F.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>4735.2_997_S.</t>
+          <t>8092.0_4532_P.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>15194.4_3911_S.</t>
+          <t>4972.5_2522_S.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>8200.5_2738_M.</t>
+          <t>5224.2_2340_C.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>7025.4_3008_L.</t>
+          <t>208.3_85_P.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>5382.2_2690_M.</t>
+          <t>10006.9_3646_F.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>7419.2_3469_F.</t>
+          <t>18665.3_4638_S.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>10174.3_3680_S.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1027.7_364_S.</t>
+          <t>4000.6_1659_S.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>14014.7_3537_S.</t>
+          <t>8187.1_2322_M.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>5005.9_1755_X.</t>
+          <t>8416.2_4091_P.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10718.1_9873_S.</t>
+          <t>9005.3_4344_A.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>3614.8_970_🔋.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>4781.2_1507_A.</t>
+          <t>5040.0_2971_A.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>20105.6_7766_F.</t>
+          <t>9012.4_2700_M.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10027.3_2906_P.</t>
+          <t>2011.7_731_S.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>1114.9_359_S.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1629.5_671_F.</t>
+          <t>123.0_5992_A.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>14009.7_4401_V.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>14009.0_5498_A.</t>
+          <t>5064.3_1832_F.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>5022.5_1222_P.</t>
+          <t>10106.6_3354_M.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>4153.2_3559_P.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2002.2_938_P.</t>
+          <t>10030.1_3124_M.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>7880.9_2433_E.</t>
+          <t>657.7_273_S.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>5064.2_1636_G.</t>
+          <t>10020.8_2989_M.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>21124.1_8011_F.</t>
+          <t>8481.2_2463_🔋.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>3004.6_746_V.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>8092.0_4532_P.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>12006.1_5290_X.</t>
+          <t>12545.4_3039_S.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>9791.4_3527_G.</t>
+          <t>1020.0_679_T.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>8351.7_4153_C.</t>
+          <t>4786.5_1898_P.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>10001.3_4206_G.</t>
+          <t>4678.8_1840_A.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>3004.6_746_V.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>9639.7_4763_P.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2036.1_839_S.</t>
+          <t>18102.7_4949_M.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>5040.0_2514_C.</t>
+          <t>6012.6_2984_F.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>8218.3_2327_P.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>8506.3_4050_C.</t>
+          <t>1443.0_851_A.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>6518.4_2914_A.</t>
+          <t>5025.8_1214_P.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>4917.5_2381_T.</t>
+          <t>5008.0_2402_P.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>5621.6_2375_P.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>7312.2_2446_G.</t>
+          <t>2051.8_860_S.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>5051.4_1993_M.</t>
+          <t>7039.1_2754_S.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1034.3_279_M.</t>
+          <t>3006.0_1286_M.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>3026.1_1490_A.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>9507.9_2851_M.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>4688.1_2291_C.</t>
+          <t>11214.0_4224_V.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>401.2_179_S.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>4972.5_2522_S.</t>
+          <t>17012.6_5869_T.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>12545.4_3039_S.</t>
+          <t>12002.7_4232_S.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>6006.6_2009_P.</t>
+          <t>5020.4_2167_C.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>5004.0_2103_C.</t>
+          <t>10007.8_2733_V.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>8187.1_2322_M.</t>
+          <t>10010.0_2910_V.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>10003.7_2721_V.</t>
+          <t>6804.1_2088_P.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>4078.1_1810_A.</t>
+          <t>5014.3_1731_F.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>8416.2_4091_P.</t>
+          <t>15504.3_3950_M.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>5299.8_2406_C.</t>
+          <t>5029.4_1585_P.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>10006.9_3646_X.</t>
+          <t>14009.7_4401_V.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>10277.3_4318_L.</t>
+          <t>6003.3_2987_M.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>15186.5_3866_S.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>5242.7_1657_S.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>4017.3_1883_C.</t>
+          <t>10012.3_3067_S.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>7502.4_3467_P.</t>
+          <t>1034.3_279_M.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>4790.7_1897_F.</t>
+          <t>8442.5_3038_G.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>14117.6_3844_M.</t>
+          <t>1629.5_671_F.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>9013.7_2337_M.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>5144.4_2349_P.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>10007.8_2733_V.</t>
+          <t>4850.9_2239_C.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>5301.0_2064_F.</t>
+          <t>4932.4_1545_E.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>5040.0_2299_A.</t>
+          <t>5007.1_1751_T.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>12524.7_3259_S.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>531.0_343_A.</t>
+          <t>7024.3_3266_L.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>6622.5_2224_E.</t>
+          <t>12013.5_4635_X.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>10007.8_2668_V.</t>
+          <t>56121.5_25636_F.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>12521.4_4814_M.</t>
+          <t>6137.8_2406_L.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>4797.2_1541_G.</t>
+          <t>53755.6_36604_F.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>3010.0_1424_A.</t>
+          <t>9209.1_3141_E.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>8396.0_2595_S.</t>
+          <t>10027.3_2906_P.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>1366.2_487_L.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>
@@ -2057,210 +2057,210 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>10006.5_3648_X.</t>
+          <t>6903.6_2566_G.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>7985.2_2173_P.</t>
+          <t>18516.8_6699_G.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>4700.4_1216_V.</t>
+          <t>16397.3_4254_S.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2355.5_726_S.</t>
+          <t>12326.4_4833_S.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2510.2_1366_V.</t>
+          <t>4028.8_1699_L.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>5072.4_1931_S.</t>
+          <t>4969.4_2146_P.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>15057.9_8625_F.</t>
+          <t>6046.5_3239_S.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>8367.5_4269_C.</t>
+          <t>1027.7_364_S.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>12013.5_4635_X.</t>
+          <t>10533.4_4020_F.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>37036.6_17889_F.</t>
+          <t>7593.7_2701_E.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>1380.0_562_A.</t>
+          <t>4177.9_1557_T.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>5004.9_1790_A.</t>
+          <t>9007.1_3080_P.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>7516.9_3203_A.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>3798.9_1319_S.</t>
+          <t>7022.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>7569.4_2477_V.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>4969.4_2146_P.</t>
+          <t>5008.1_1825_M.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>5020.4_2167_C.</t>
+          <t>9507.9_2851_M.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>26010.2_9812_F.</t>
+          <t>6661.8_3736_P.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>11214.0_4224_V.</t>
+          <t>14004.5_5478_M.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>4153.2_3559_P.</t>
+          <t>5008.2_1646_A.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>4791.5_1524_E.</t>
+          <t>10277.3_4318_L.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>6113.5_2883_C.</t>
+          <t>7230.5_2794_V.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>5163.5_1775_V.</t>
+          <t>7992.7_2506_F.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>6084.1_2156_V.</t>
+          <t>7420.2_4318_C.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>10030.0_3041_G.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>9415.9_3699_G.</t>
+          <t>12008.4_3832_G.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2004.9_754_S.</t>
+          <t>5238.0_2781_F.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>10022.1_2875_M.</t>
+          <t>7576.8_2823_P.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>5000.2_1932_E.</t>
+          <t>3138.1_1120_S.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>8132.9_2716_S.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
@@ -2274,1484 +2274,1540 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2047.9_924_L.</t>
+          <t>4705.5_1241_G.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>401.2_179_S.</t>
+          <t>4788.2_1476_P.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2185.4_792_S.</t>
+          <t>2047.9_924_L.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>5008.2_1646_A.</t>
+          <t>6818.2_2036_P.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>7012.1_3931_🔋.</t>
+          <t>26010.2_9812_F.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>3958.9_1777_P.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>3012.4_1258_P.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>10031.8_2663_P.</t>
+          <t>7006.7_5717_S.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>5004.5_1548_A.</t>
+          <t>5770.8_2848_G.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>1083.2_390_M.</t>
+          <t>10031.8_2663_P.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>10106.6_2889_P.</t>
+          <t>37036.6_17889_F.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>3958.9_1777_P.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>10008.1_2966_M.</t>
+          <t>9006.5_3085_X.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2558.7_905_S.</t>
+          <t>10106.6_2889_P.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>6010.6_2144_A.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>8618.0_2344_P.</t>
+          <t>791.5_266_G.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>7420.2_4318_C.</t>
+          <t>21124.1_8011_F.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>5000.6_1856_M.</t>
+          <t>5013.9_1673_A.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>4000.6_1659_S.</t>
+          <t>9555.5_5689_S.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>5282.8_2392_C.</t>
+          <t>5000.2_1932_E.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>16008.9_5968_S.</t>
+          <t>960.0_1109_A.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>10003.1_5062_V.</t>
+          <t>9029.6_4595_P.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>5040.0_2514_C.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>611.2_221_M.</t>
+          <t>6084.1_2156_V.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>10016.9_3028_M.</t>
+          <t>6007.1_2393_M.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>3597.6_2910_E.</t>
+          <t>5004.1_1610_M.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>3735.9_1928_V.</t>
+          <t>4077.1_1454_S.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>16008.9_5968_S.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>6038.2_2121_P.</t>
+          <t>10030.5_4765_C.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>553.2_224_S.</t>
+          <t>7145.5_2856_E.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>5040.0_2971_A.</t>
+          <t>12006.1_5290_X.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>6620.4_2477_P.</t>
+          <t>2185.4_792_S.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2735.8_959_S.</t>
+          <t>12342.9_3211_M.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>5451.1_1905_T.</t>
+          <t>1083.2_390_M.</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>21442.0_7959_F.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>5981.9_2551_P.</t>
+          <t>7312.2_2446_G.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>18102.7_4949_M.</t>
+          <t>3412.3_1947_C.</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>9209.1_3141_E.</t>
+          <t>14009.0_5498_A.</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>10010.0_2910_V.</t>
+          <t>5904.3_2699_P.</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>4576.3_2084_S.</t>
+          <t>10001.9_4466_P.</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>4830.1_2569_C.</t>
+          <t>5081.5_1647_G.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>7022.4_3008_L.</t>
+          <t>4731.9_1407_T.</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>10533.4_4020_F.</t>
+          <t>7502.4_3467_P.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>3023.2_962_S.</t>
+          <t>7127.8_1843_G.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>10012.3_3067_S.</t>
+          <t>21250.2_9506_P.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>22008.4_8412_F.</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>10503.6_3278_M.</t>
+          <t>7003.6_2437_P.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>3006.0_1286_M.</t>
+          <t>5005.4_2618_L.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>5007.1_1751_T.</t>
+          <t>2355.5_726_S.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>5256.5_1535_S.</t>
+          <t>1002.7_460_S.</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>15637.2_5789_G.</t>
+          <t>12022.7_5417_L.</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>960.0_1109_A.</t>
+          <t>5000.6_1856_M.</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2556.5_1160_M.</t>
+          <t>4781.2_1507_A.</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>657.7_273_S.</t>
+          <t>3059.2_956_T.</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>6036.4_2875_V.</t>
+          <t>6472.0_2501_S.</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>14019.6_6253_L.</t>
+          <t>2186.2_736_G.</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>5869.6_2613_P.</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>6610.9_1738_P.</t>
+          <t>1206.7_12400_M.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>5005.8_1527_S.</t>
+          <t>4688.1_2291_C.</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>4790.7_1897_F.</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>6016.7_2122_M.</t>
+          <t>10011.5_3070_S.</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>10348.3_2647_S.</t>
+          <t>4101.5_1485_V.</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>10003.3_3845_P.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>2064.3_708_S.</t>
+          <t>7880.9_2433_E.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>5522.8_2716_V.</t>
+          <t>8618.0_2344_P.</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>9005.3_4344_A.</t>
+          <t>3798.9_1319_S.</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>2880.9_1210_L.</t>
+          <t>5027.8_1361_P.</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>7001.2_3357_M.</t>
+          <t>5005.8_1527_S.</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>7127.8_1843_G.</t>
+          <t>5100.0_2587_A.</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>10007.4_3588_V.</t>
+          <t>5017.7_1147_M.</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>13008.2_4958_P.</t>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2557.8_1206_V.</t>
+          <t>5119.6_3153_M.</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>5144.4_2349_P.</t>
+          <t>7419.2_3469_F.</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>5049.0_2240_C.</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>2510.2_1366_V.</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>21207.4_6474_V.</t>
+          <t>10007.4_3588_V.</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>3012.4_1258_P.</t>
+          <t>5001.9_1291_V.</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>22320.3_9183_F.</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>5224.2_2340_C.</t>
+          <t>5522.8_2716_V.</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>1432.9_3942_M.</t>
+          <t>2557.8_1206_V.</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>2783.5_952_S.</t>
+          <t>773.5_238_S.</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>3412.3_1947_C.</t>
+          <t>5004.5_1548_A.</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>22008.4_8412_F.</t>
+          <t>15016.9_6221_G.</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>8218.3_2327_P.</t>
+          <t>2504.7_703_🔋.</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>8196.1_2807_T.</t>
+          <t>14119.3_5262_S.</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>20105.6_7766_F.</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>7001.2_3357_M.</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>7003.6_2437_P.</t>
+          <t>7186.5_2708_S.</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>8024.4_2933_S.</t>
+          <t>6113.5_2883_C.</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>7024.3_3266_L.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>4850.9_2239_C.</t>
+          <t>5010.0_1872_A.</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>5000.5_1919_P.</t>
+          <t>9791.4_3527_G.</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>5242.7_1657_S.</t>
+          <t>14014.7_3537_S.</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>4821.0_1857_P.</t>
+          <t>2735.8_959_S.</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>10002.4_5136_P.</t>
+          <t>10062.5_2886_M.</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>18516.8_6699_G.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>7145.5_2856_E.</t>
+          <t>3757.2_1716_A.</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>1012.0_375_E.</t>
+          <t>5382.2_2690_M.</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>2504.7_703_🔋.</t>
+          <t>5004.9_1790_A.</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>6007.4_1804_G.</t>
+          <t>5010.3_1888_G.</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>1002.7_460_S.</t>
+          <t>4017.3_1883_C.</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>10001.9_4466_P.</t>
+          <t>6833.7_2100_G.</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>15223.0_6245_P.</t>
+          <t>7985.2_2173_P.</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>5022.5_1222_P.</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>12008.4_3832_G.</t>
+          <t>8120.9_2737_G.</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>6004.0_2559_P.</t>
+          <t>6035.0_2481_P.</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>12342.9_3211_M.</t>
+          <t>10643.3_3263_S.</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>6779.9_2003_E.</t>
+          <t>6951.4_2856_S.</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>5085.1_1840_G.</t>
+          <t>4700.4_1216_V.</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>4896.8_2251_L.</t>
+          <t>10003.1_5062_V.</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>5014.5_1497_G.</t>
+          <t>4814.5_1705_🔋.</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>25020.8_7832_V.</t>
+          <t>10718.1_9873_S.</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>15186.5_3866_S.</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>5580.0_2471_A.</t>
+          <t>1380.0_562_A.</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>12524.7_3259_S.</t>
+          <t>4735.2_997_S.</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>5009.1_2246_C.</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>5724.1_3694_S.</t>
+          <t>10503.6_3278_M.</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>7992.7_2506_F.</t>
+          <t>6006.6_2009_P.</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>22002.4_8469_M.</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>8004.6_2357_G.</t>
+          <t>7025.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>4692.9_1546_P.</t>
+          <t>2004.9_754_S.</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>2011.7_731_S.</t>
+          <t>12006.1_5290_T.</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>8008.0_2930_A.</t>
+          <t>5580.0_2471_A.</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>3059.2_956_T.</t>
+          <t>4540.8_1823_A.</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>5001.9_1291_V.</t>
+          <t>21114.4_6098_P.</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>18107.4_4577_M.</t>
+          <t>5282.8_2392_C.</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>5021.7_1930_A.</t>
+          <t>2556.5_1160_M.</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>3019.8_1453_F.</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>4177.9_1557_T.</t>
+          <t>5006.8_1080_M.</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>22002.4_8469_M.</t>
+          <t>5020.6_1328_M.</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>5043.1_2254_C.</t>
+          <t>5299.8_2406_C.</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>10011.5_3070_S.</t>
+          <t>10003.3_3845_P.</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>6903.6_2566_G.</t>
+          <t>5287.4_1835_V.</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>7516.9_3203_A.</t>
+          <t>2783.5_952_S.</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>56121.5_25636_F.</t>
+          <t>419.0_180_P.</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>12002.7_4232_S.</t>
+          <t>5007.4_1601_A.</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>5770.8_2848_G.</t>
+          <t>21106.2_7925_P.</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>5235.4_1766_P.</t>
+          <t>10007.8_2668_V.</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>7114.0_2850_S.</t>
+          <t>9562.8_3145_M.</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>6600.2_1915_M.</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>5025.8_1214_P.</t>
+          <t>4768.0_1875_L.</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>14004.5_5478_M.</t>
+          <t>5072.4_1931_S.</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>5235.4_1766_P.</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>5086.0_1810_G.</t>
+          <t>5000.5_1919_P.</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>6038.2_2121_P.</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>5009.1_2246_C.</t>
+          <t>3026.1_1490_A.</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>1020.0_679_T.</t>
+          <t>6536.2_2241_P.</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>3089.9_1508_C.</t>
+          <t>8104.2_2652_M.</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>4921.0_2491_A.</t>
+          <t>5014.5_1497_G.</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>773.5_238_S.</t>
+          <t>10006.0_2772_V.</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>4864.8_1353_E.</t>
+          <t>3010.0_1289_A.</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>6011.5_2408_A.</t>
+          <t>1011.0_396_L.</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>5010.3_1888_G.</t>
+          <t>9415.9_3699_G.</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>21141.5_8155_F.</t>
+          <t>3023.2_962_S.</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>10030.5_4765_C.</t>
+          <t>3597.6_2910_E.</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>10643.3_3263_S.</t>
+          <t>5163.5_1775_V.</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>5003.2_1389_E.</t>
+          <t>10006.5_3648_X.</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>5904.3_2699_P.</t>
+          <t>4917.5_2381_T.</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>3757.2_1716_A.</t>
+          <t>5085.1_1840_G.</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>6818.2_2036_P.</t>
+          <t>15194.4_3911_S.</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>5013.9_1673_A.</t>
+          <t>13023.5_5156_L.</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>12006.1_5290_T.</t>
+          <t>5043.1_2254_C.</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>4974.4_1533_E.</t>
+          <t>5365.6_2437_C.</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>5827.8_2106_S.</t>
+          <t>1701.7_720_F.</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>4214.8_2018_A.</t>
+          <t>6518.4_2914_A.</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>6173.6_2865_M.</t>
+          <t>5301.0_2064_F.</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>6661.8_3736_P.</t>
+          <t>1432.9_3942_M.</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>5029.4_1585_P.</t>
+          <t>4214.8_2018_A.</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>8442.5_3038_G.</t>
+          <t>7012.1_3931_🔋.</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>4078.1_1810_A.</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>5010.3_3392_P.</t>
+          <t>5256.5_1535_S.</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>22320.3_9183_F.</t>
+          <t>5152.8_1800_G.</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>7569.4_2477_V.</t>
+          <t>6011.8_1873_M.</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>13023.5_5156_L.</t>
+          <t>4576.3_2084_S.</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>7230.5_2794_V.</t>
+          <t>6012.6_2984_P.</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>12006.9_5463_P.</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>7598.7_2799_S.</t>
+          <t>3005.2_1040_L.</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>10020.8_2989_M.</t>
+          <t>7090.6_3340_A.</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>5081.5_1647_G.</t>
+          <t>6006.1_2236_V.</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>5869.6_2613_P.</t>
+          <t>2060.0_802_S.</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>6035.0_2481_P.</t>
+          <t>14117.6_3844_M.</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>7874.8_2223_M.</t>
+          <t>4830.1_2569_C.</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>4540.8_1823_A.</t>
+          <t>6053.8_2077_M.</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>16397.3_4254_S.</t>
+          <t>10022.1_2875_M.</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>419.0_180_P.</t>
+          <t>8024.4_2933_S.</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>1701.7_720_F.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>5100.0_2587_A.</t>
+          <t>5021.7_1930_A.</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>5002.9_1487_P.</t>
+          <t>3735.9_1928_V.</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>15504.3_3950_M.</t>
+          <t>13008.2_4958_P.</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>5014.8_2009_A.</t>
+          <t>10001.3_4206_G.</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>5008.0_2402_P.</t>
+          <t>4921.0_2491_A.</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>5621.6_2375_P.</t>
+          <t>9756.3_2793_M.</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>6804.1_2088_P.</t>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>9756.3_2793_M.</t>
+          <t>1884.9_866_S.</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>10012.1_3139_S.</t>
+          <t>5981.9_2551_P.</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>9012.4_2700_M.</t>
+          <t>10012.1_3139_S.</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>6004.0_2559_P.</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>5011.9_1594_P.</t>
+          <t>15223.0_6245_P.</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>7090.6_3340_A.</t>
+          <t>5451.1_1905_T.</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>2000.0_724_A.</t>
+          <t>2175.4_712_S.</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>5064.2_1636_G.</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>9006.5_3085_X.</t>
+          <t>7114.0_2850_S.</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>14119.3_5262_S.</t>
+          <t>4013.7_1173_V.</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>4613.1_1806_A.</t>
+          <t>10002.4_5136_P.</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>6833.7_2100_G.</t>
+          <t>8253.0_2972_🔋.</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>1114.9_359_S.</t>
+          <t>3089.9_1508_C.</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>5010.0_1872_A.</t>
+          <t>4937.4_1783_A.</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>2186.2_736_G.</t>
+          <t>10006.9_3646_X.</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>553.2_224_S.</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>5028.5_4433_S.</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>5827.8_2106_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>6620.4_2477_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>4864.8_1353_E.</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>8008.0_2930_A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2558.7_905_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>4613.1_1806_A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>21207.4_6474_V.</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>10058.8_3483_F.</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>611.2_221_M.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_500km_2026.xlsx
+++ b/Ranking_CNB_500km_2026.xlsx
@@ -488,12 +488,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>314,0 km</t>
+          <t>322,0 km</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.107 m</t>
+          <t>3.196 m</t>
         </is>
       </c>
     </row>
@@ -522,12 +522,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>227,4 km</t>
+          <t>232,8 km</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.666 m</t>
+          <t>2.705 m</t>
         </is>
       </c>
     </row>
@@ -590,12 +590,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>189,3 km</t>
+          <t>195,3 km</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.284 m</t>
+          <t>1.363 m</t>
         </is>
       </c>
     </row>
@@ -607,12 +607,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>171,6 km</t>
+          <t>179,6 km</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.249 m</t>
+          <t>2.371 m</t>
         </is>
       </c>
     </row>
@@ -624,46 +624,46 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>162,0 km</t>
+          <t>168,1 km</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.120 m</t>
+          <t>1.131 m</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Alexsia A.</t>
+          <t>Cassia C.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>152,9 km</t>
+          <t>156,9 km</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.662 m</t>
+          <t>1.944 m</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Cassia C.</t>
+          <t>Alexsia A.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>152,7 km</t>
+          <t>152,9 km</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.901 m</t>
+          <t>1.662 m</t>
         </is>
       </c>
     </row>
@@ -675,12 +675,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>141,2 km</t>
+          <t>149,4 km</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.210 m</t>
+          <t>1.220 m</t>
         </is>
       </c>
     </row>
@@ -772,34 +772,34 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Maria E.</t>
+          <t>Izac S.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>94,6 km</t>
+          <t>101,0 km</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.170 m</t>
+          <t>1.164 m</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Izac S.</t>
+          <t>Maria E.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>92,1 km</t>
+          <t>94,6 km</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.058 m</t>
+          <t>1.170 m</t>
         </is>
       </c>
     </row>
@@ -964,12 +964,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>7,9 km</t>
+          <t>12,4 km</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>108 m</t>
+          <t>161 m</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A401"/>
+  <dimension ref="A1:A410"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1014,2030 +1014,2030 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5051.4_1993_M.</t>
+          <t>10643.3_3263_S.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5005.9_1755_X.</t>
+          <t>4150.2_2042_C.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>15637.2_5789_G.</t>
+          <t>12006.1_5290_T.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2880.9_1210_L.</t>
+          <t>5006.8_1080_M.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>5008.1_1825_M.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>6011.5_2408_A.</t>
+          <t>4735.2_997_S.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2002.2_938_P.</t>
+          <t>5040.0_2971_A.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>7598.7_2799_S.</t>
+          <t>7593.7_2701_E.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6622.5_2224_E.</t>
+          <t>5301.0_2064_F.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5011.9_1594_P.</t>
+          <t>419.0_180_P.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10348.3_2647_S.</t>
+          <t>5033.4_1976_M.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>5040.0_2299_A.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4899.2_1459_A.</t>
+          <t>5010.3_3392_P.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>611.2_221_M.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4821.0_1857_P.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5014.8_2009_A.</t>
+          <t>401.2_179_S.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>15057.9_8625_F.</t>
+          <t>5365.6_2437_C.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>8200.5_2738_M.</t>
+          <t>5382.2_2690_M.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6007.4_1804_G.</t>
+          <t>3412.3_1947_C.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5724.1_3694_S.</t>
+          <t>5002.9_1487_P.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>531.0_343_A.</t>
+          <t>5451.1_1905_T.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>8092.0_4532_P.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>4974.4_1533_E.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2000.0_724_A.</t>
+          <t>10007.8_2668_V.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>18107.4_4577_M.</t>
+          <t>5020.4_2167_C.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>17003.0_7696_P.</t>
+          <t>6007.1_2393_M.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5296.8_1844_P.</t>
+          <t>5025.8_1214_P.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>6047.4_2816_T.</t>
+          <t>7025.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3010.0_1424_A.</t>
+          <t>15057.9_8625_F.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1012.0_375_E.</t>
+          <t>6622.5_2224_E.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>6779.9_2003_E.</t>
+          <t>2510.2_1366_V.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2036.1_839_S.</t>
+          <t>26010.2_9812_F.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>8132.9_2716_S.</t>
+          <t>10020.8_2989_M.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>9639.7_4763_P.</t>
+          <t>22008.4_8412_F.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>14019.6_6253_L.</t>
+          <t>5522.8_2716_V.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5002.9_1487_P.</t>
+          <t>7015.4_2141_T.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>6610.9_1738_P.</t>
+          <t>21141.5_8155_F.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2064.3_708_S.</t>
+          <t>1083.2_390_M.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3010.0_1685_A.</t>
+          <t>5579.8_1990_E.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10003.7_2721_V.</t>
+          <t>123.0_5992_A.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>8196.1_2807_T.</t>
+          <t>6035.0_2481_P.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>6345.4_2376_S.</t>
+          <t>9012.4_2700_M.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>16520.2_4844_M.</t>
+          <t>6084.1_2156_V.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>6036.4_2875_V.</t>
+          <t>5238.0_2781_F.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>8351.7_4153_C.</t>
+          <t>3580.9_1198_S.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>5040.0_2299_A.</t>
+          <t>10016.9_3028_M.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1366.2_487_L.</t>
+          <t>6010.6_2144_A.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>10016.9_3028_M.</t>
+          <t>25020.8_7832_V.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>5086.0_1810_G.</t>
+          <t>4688.1_2291_C.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>8506.3_4050_C.</t>
+          <t>21106.2_7925_P.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>8396.0_2595_S.</t>
+          <t>9415.9_3699_G.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>5579.8_1990_E.</t>
+          <t>5144.4_2349_P.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>5010.3_3392_P.</t>
+          <t>10006.0_2772_V.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>14009.0_5498_A.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>5004.0_2103_C.</t>
+          <t>4791.5_1524_E.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>7874.8_2223_M.</t>
+          <t>21114.4_6098_P.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>5581.6_3687_P.</t>
+          <t>56121.5_25636_F.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>4791.5_1524_E.</t>
+          <t>2186.2_736_G.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>4692.9_1546_P.</t>
+          <t>5004.5_1548_A.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>4797.2_1541_G.</t>
+          <t>6012.6_2984_P.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>6016.7_2122_M.</t>
+          <t>3089.9_1508_C.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>8004.6_2357_G.</t>
+          <t>5621.6_2375_P.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>25020.8_7832_V.</t>
+          <t>14004.5_5478_M.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>6173.6_2865_M.</t>
+          <t>5904.3_2699_P.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>8367.5_4269_C.</t>
+          <t>7569.4_2477_V.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>15200.8_10718_F.</t>
+          <t>10503.6_3278_M.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>4896.8_2251_L.</t>
+          <t>10533.4_4020_F.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>5003.2_1389_E.</t>
+          <t>8200.8_2347_T.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>21141.5_8155_F.</t>
+          <t>10062.5_2886_M.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>8092.0_4532_P.</t>
+          <t>2735.8_959_S.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>4972.5_2522_S.</t>
+          <t>7001.2_3357_M.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>5224.2_2340_C.</t>
+          <t>22002.4_8469_M.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>10003.3_3845_P.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>10006.9_3646_F.</t>
+          <t>10007.8_2733_V.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>18665.3_4638_S.</t>
+          <t>5064.2_1636_G.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>4932.4_1545_E.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>4000.6_1659_S.</t>
+          <t>6951.4_2856_S.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>8187.1_2322_M.</t>
+          <t>5011.9_1594_P.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>8416.2_4091_P.</t>
+          <t>17003.0_7696_P.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>9005.3_4344_A.</t>
+          <t>3010.0_1289_A.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>5581.6_3687_P.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>5040.0_2971_A.</t>
+          <t>5580.0_2471_A.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>9012.4_2700_M.</t>
+          <t>7145.5_2856_E.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2011.7_731_S.</t>
+          <t>15200.8_10718_F.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1114.9_359_S.</t>
+          <t>4532.9_2322_L.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>123.0_5992_A.</t>
+          <t>12022.7_5417_L.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>8004.6_2357_G.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>5064.3_1832_F.</t>
+          <t>10106.6_3354_M.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>4153.2_3559_P.</t>
+          <t>6137.8_2406_L.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>10030.1_3124_M.</t>
+          <t>9756.3_2793_M.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>657.7_273_S.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>10020.8_2989_M.</t>
+          <t>5017.7_1147_M.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>8481.2_2463_🔋.</t>
+          <t>10006.9_3646_X.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>3004.6_746_V.</t>
+          <t>17012.6_5869_T.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>9639.7_4763_P.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>12545.4_3039_S.</t>
+          <t>14014.7_3537_S.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1020.0_679_T.</t>
+          <t>2783.5_952_S.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>4786.5_1898_P.</t>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>4678.8_1840_A.</t>
+          <t>10012.3_3067_S.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>5072.4_1931_S.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>18102.7_4949_M.</t>
+          <t>4613.1_1806_A.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>4891.7_1690_F.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>8218.3_2327_P.</t>
+          <t>8442.5_3038_G.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1443.0_851_A.</t>
+          <t>6103.6_2241_G.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>6779.9_2003_E.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>5025.8_1214_P.</t>
+          <t>5005.9_1755_X.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>5008.0_2402_P.</t>
+          <t>4786.5_1898_P.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>5621.6_2375_P.</t>
+          <t>21250.2_9506_P.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>16397.3_4254_S.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>7039.1_2754_S.</t>
+          <t>5085.1_1840_G.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>3006.0_1286_M.</t>
+          <t>12006.9_5463_P.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>5242.7_1657_S.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>8120.9_2737_G.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>11214.0_4224_V.</t>
+          <t>5235.4_1766_P.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>401.2_179_S.</t>
+          <t>5010.3_1888_G.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>1380.0_562_A.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>12002.7_4232_S.</t>
+          <t>6661.8_3736_P.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>5020.4_2167_C.</t>
+          <t>5827.8_2106_S.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>10007.8_2733_V.</t>
+          <t>8008.0_2930_A.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>10010.0_2910_V.</t>
+          <t>4000.6_1659_S.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>6804.1_2088_P.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>6011.8_1873_M.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>15504.3_3950_M.</t>
+          <t>2060.0_802_S.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>5029.4_1585_P.</t>
+          <t>8351.7_4153_C.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>14009.7_4401_V.</t>
+          <t>5040.0_2514_C.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>6003.3_2987_M.</t>
+          <t>3735.9_1928_V.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>7024.3_3266_L.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>5242.7_1657_S.</t>
+          <t>7576.8_2823_P.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>10012.3_3067_S.</t>
+          <t>1114.9_359_S.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>1034.3_279_M.</t>
+          <t>4101.5_1485_V.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>8442.5_3038_G.</t>
+          <t>2064.3_708_S.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1629.5_671_F.</t>
+          <t>773.5_238_S.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>5256.5_1535_S.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>5144.4_2349_P.</t>
+          <t>6006.6_2009_P.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>4850.9_2239_C.</t>
+          <t>2175.4_712_S.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>4932.4_1545_E.</t>
+          <t>5051.4_1993_M.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>5007.1_1751_T.</t>
+          <t>4790.7_1897_F.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>12524.7_3259_S.</t>
+          <t>8196.1_2807_T.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>7024.3_3266_L.</t>
+          <t>10106.6_2889_P.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>12013.5_4635_X.</t>
+          <t>4731.9_1407_T.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>56121.5_25636_F.</t>
+          <t>5029.4_1585_P.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>7090.6_3340_A.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>53755.6_36604_F.</t>
+          <t>4678.8_1840_A.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>9209.1_3141_E.</t>
+          <t>18107.4_4577_M.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>10027.3_2906_P.</t>
+          <t>7874.8_2223_M.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>7012.1_3931_🔋.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>5033.4_1976_M.</t>
+          <t>5282.8_2392_C.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>6903.6_2566_G.</t>
+          <t>5003.2_1389_E.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>18516.8_6699_G.</t>
+          <t>6047.4_2816_T.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>16397.3_4254_S.</t>
+          <t>2504.7_703_🔋.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>5009.1_2246_C.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>4028.8_1699_L.</t>
+          <t>553.2_224_S.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>4969.4_2146_P.</t>
+          <t>4781.2_1507_A.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>5422.4_1911_G.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>1027.7_364_S.</t>
+          <t>4974.4_1533_E.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>10533.4_4020_F.</t>
+          <t>5022.5_1222_P.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>7593.7_2701_E.</t>
+          <t>6903.6_2566_G.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>4177.9_1557_T.</t>
+          <t>5000.5_1919_P.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>9007.1_3080_P.</t>
+          <t>9791.4_3527_G.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>7516.9_3203_A.</t>
+          <t>6472.0_2501_S.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>7022.4_3008_L.</t>
+          <t>3059.2_956_T.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>7569.4_2477_V.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>5008.1_1825_M.</t>
+          <t>1011.0_396_L.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>9507.9_2851_M.</t>
+          <t>6804.1_2088_P.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>6661.8_3736_P.</t>
+          <t>2880.9_1210_L.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>14004.5_5478_M.</t>
+          <t>6016.7_2122_M.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>5008.2_1646_A.</t>
+          <t>2004.9_754_S.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>10277.3_4318_L.</t>
+          <t>3010.0_1424_A.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>7230.5_2794_V.</t>
+          <t>2011.7_731_S.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>7992.7_2506_F.</t>
+          <t>8506.3_4050_C.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>7420.2_4318_C.</t>
+          <t>5299.8_2406_C.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>10030.0_3041_G.</t>
+          <t>10003.7_2721_V.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>12008.4_3832_G.</t>
+          <t>5064.3_1832_F.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>5238.0_2781_F.</t>
+          <t>12008.4_3832_G.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>7576.8_2823_P.</t>
+          <t>5043.1_2254_C.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>3138.1_1120_S.</t>
+          <t>9006.5_3085_X.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>5004.0_2103_C.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>6007.1_3172_F.</t>
+          <t>5010.0_1872_A.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>5981.9_2551_P.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>4788.2_1476_P.</t>
+          <t>2036.1_839_S.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2047.9_924_L.</t>
+          <t>5119.6_3153_M.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>6818.2_2036_P.</t>
+          <t>4788.2_1476_P.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>26010.2_9812_F.</t>
+          <t>8024.4_2933_S.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>3958.9_1777_P.</t>
+          <t>5086.0_1810_G.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>3012.4_1258_P.</t>
+          <t>1206.7_12400_M.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>7006.7_5717_S.</t>
+          <t>5001.9_1291_V.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>5770.8_2848_G.</t>
+          <t>7230.5_2794_V.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>10031.8_2663_P.</t>
+          <t>13008.2_4958_P.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>37036.6_17889_F.</t>
+          <t>9029.6_4595_P.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>10008.1_2966_M.</t>
+          <t>3138.1_1120_S.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>9006.5_3085_X.</t>
+          <t>5224.2_2340_C.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>10106.6_2889_P.</t>
+          <t>5049.0_2240_C.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>6010.6_2144_A.</t>
+          <t>21207.4_6474_V.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>791.5_266_G.</t>
+          <t>2002.2_938_P.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>21124.1_8011_F.</t>
+          <t>7516.9_3203_A.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>5013.9_1673_A.</t>
+          <t>37036.6_17889_F.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>9555.5_5689_S.</t>
+          <t>208.3_85_P.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>5000.2_1932_E.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>960.0_1109_A.</t>
+          <t>4850.9_2239_C.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>9029.6_4595_P.</t>
+          <t>4017.3_1883_C.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>5040.0_2514_C.</t>
+          <t>7419.2_3469_F.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>6084.1_2156_V.</t>
+          <t>2185.4_792_S.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>6007.1_2393_M.</t>
+          <t>3006.0_1286_M.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>5004.1_1610_M.</t>
+          <t>10002.4_5136_P.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>6007.1_3172_F.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>16008.9_5968_S.</t>
+          <t>9562.8_3145_M.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>10030.5_4765_C.</t>
+          <t>13023.5_5156_L.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>7145.5_2856_E.</t>
+          <t>6046.5_3239_S.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>12006.1_5290_X.</t>
+          <t>4077.1_1454_S.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2185.4_792_S.</t>
+          <t>14119.3_5262_S.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>12342.9_3211_M.</t>
+          <t>2051.8_860_S.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>1083.2_390_M.</t>
+          <t>2556.5_1160_M.</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>6006.1_2236_V.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>7312.2_2446_G.</t>
+          <t>8013.1_2082_P.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>3412.3_1947_C.</t>
+          <t>4969.4_2146_P.</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>14009.0_5498_A.</t>
+          <t>8481.2_2463_🔋.</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>5904.3_2699_P.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>10001.9_4466_P.</t>
+          <t>15186.5_3866_S.</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>5081.5_1647_G.</t>
+          <t>7186.5_2708_S.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>11214.0_4224_V.</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>7502.4_3467_P.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>7127.8_1843_G.</t>
+          <t>7022.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>21250.2_9506_P.</t>
+          <t>6818.2_2036_P.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>22008.4_8412_F.</t>
+          <t>791.5_266_G.</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>7003.6_2437_P.</t>
+          <t>10006.9_3646_F.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>5005.4_2618_L.</t>
+          <t>5027.8_1361_P.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2355.5_726_S.</t>
+          <t>5007.4_1601_A.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>1002.7_460_S.</t>
+          <t>10006.5_3648_X.</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>12022.7_5417_L.</t>
+          <t>5008.0_2402_P.</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>5000.6_1856_M.</t>
+          <t>531.0_343_A.</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>4781.2_1507_A.</t>
+          <t>5005.8_1527_S.</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>3059.2_956_T.</t>
+          <t>5014.5_1497_G.</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>1027.7_364_S.</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2186.2_736_G.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>5869.6_2613_P.</t>
+          <t>8187.1_2322_M.</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>1206.7_12400_M.</t>
+          <t>2558.7_905_S.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>4688.1_2291_C.</t>
+          <t>9507.9_2851_M.</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>4790.7_1897_F.</t>
+          <t>3026.1_1490_A.</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>10011.5_3070_S.</t>
+          <t>6011.5_2408_A.</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>4101.5_1485_V.</t>
+          <t>3958.9_1777_P.</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>5004.1_1610_M.</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>7880.9_2433_E.</t>
+          <t>10012.1_3139_S.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>8618.0_2344_P.</t>
+          <t>15637.2_5789_G.</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>3798.9_1319_S.</t>
+          <t>14117.6_3844_M.</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>5027.8_1361_P.</t>
+          <t>10058.8_3483_F.</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>5005.8_1527_S.</t>
+          <t>10001.3_4206_G.</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>5100.0_2587_A.</t>
+          <t>2047.9_924_L.</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>5017.7_1147_M.</t>
+          <t>53755.6_36604_F.</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>960.0_1109_A.</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>8200.5_2738_M.</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>7419.2_3469_F.</t>
+          <t>4153.2_3559_P.</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>5049.0_2240_C.</t>
+          <t>5004.9_1790_A.</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>2510.2_1366_V.</t>
+          <t>5021.7_1930_A.</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>10007.4_3588_V.</t>
+          <t>18102.7_4949_M.</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>5001.9_1291_V.</t>
+          <t>3004.6_746_V.</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>22320.3_9183_F.</t>
+          <t>4078.1_1810_A.</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>5522.8_2716_V.</t>
+          <t>1443.0_851_A.</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>2557.8_1206_V.</t>
+          <t>6036.4_2875_V.</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>773.5_238_S.</t>
+          <t>4896.8_2251_L.</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>5004.5_1548_A.</t>
+          <t>4797.2_1541_G.</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>15016.9_6221_G.</t>
+          <t>8132.9_2716_S.</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>2504.7_703_🔋.</t>
+          <t>8218.3_2327_P.</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>14119.3_5262_S.</t>
+          <t>15504.3_3950_M.</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>20105.6_7766_F.</t>
+          <t>1012.0_375_E.</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>7001.2_3357_M.</t>
+          <t>3023.2_962_S.</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>7186.5_2708_S.</t>
+          <t>4028.8_1699_L.</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>6113.5_2883_C.</t>
+          <t>5000.2_1932_E.</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>5770.8_2848_G.</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>5010.0_1872_A.</t>
+          <t>5163.5_1775_V.</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>9791.4_3527_G.</t>
+          <t>5081.5_1647_G.</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>14014.7_3537_S.</t>
+          <t>16520.2_4844_M.</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>2735.8_959_S.</t>
+          <t>5013.9_1673_A.</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>5296.8_1844_P.</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>10718.1_9873_S.</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>3757.2_1716_A.</t>
+          <t>9007.1_3080_P.</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>5382.2_2690_M.</t>
+          <t>12545.4_3039_S.</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>5004.9_1790_A.</t>
+          <t>10031.8_2663_P.</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>5010.3_1888_G.</t>
+          <t>10174.3_3680_S.</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>4017.3_1883_C.</t>
+          <t>2355.5_726_S.</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>6833.7_2100_G.</t>
+          <t>4864.8_1353_E.</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>7985.2_2173_P.</t>
+          <t>22320.3_9183_F.</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>5022.5_1222_P.</t>
+          <t>10022.1_2875_M.</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>21124.1_8011_F.</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>6035.0_2481_P.</t>
+          <t>20105.6_7766_F.</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>10643.3_3263_S.</t>
+          <t>6003.3_2987_M.</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>6951.4_2856_S.</t>
+          <t>10001.9_4466_P.</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>4700.4_1216_V.</t>
+          <t>3597.6_2910_E.</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>10003.1_5062_V.</t>
+          <t>1020.0_679_T.</t>
         </is>
       </c>
     </row>
@@ -3051,763 +3051,826 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>10718.1_9873_S.</t>
+          <t>5008.2_1646_A.</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>15186.5_3866_S.</t>
+          <t>6113.5_2883_C.</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>1380.0_562_A.</t>
+          <t>12342.9_3211_M.</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>4735.2_997_S.</t>
+          <t>3757.2_1716_A.</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>5009.1_2246_C.</t>
+          <t>5014.8_2009_A.</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>10503.6_3278_M.</t>
+          <t>5869.6_2613_P.</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>6006.6_2009_P.</t>
+          <t>12006.1_5290_X.</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>22002.4_8469_M.</t>
+          <t>3012.4_1258_P.</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>7025.4_3008_L.</t>
+          <t>7114.0_2850_S.</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>2004.9_754_S.</t>
+          <t>6012.6_2984_F.</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>12006.1_5290_T.</t>
+          <t>4821.0_1857_P.</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>5580.0_2471_A.</t>
+          <t>7502.4_3467_P.</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>4540.8_1823_A.</t>
+          <t>10011.5_3070_S.</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>21114.4_6098_P.</t>
+          <t>6833.7_2100_G.</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>5282.8_2392_C.</t>
+          <t>1034.3_279_M.</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>2556.5_1160_M.</t>
+          <t>6173.6_2865_M.</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>8104.2_2652_M.</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>5006.8_1080_M.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>5020.6_1328_M.</t>
+          <t>12524.7_3259_S.</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>5299.8_2406_C.</t>
+          <t>3005.2_1040_L.</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>10003.3_3845_P.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>5287.4_1835_V.</t>
+          <t>8618.0_2344_P.</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>2783.5_952_S.</t>
+          <t>10030.0_3041_G.</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>419.0_180_P.</t>
+          <t>4700.4_1216_V.</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>5007.4_1601_A.</t>
+          <t>15016.9_6221_G.</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>21106.2_7925_P.</t>
+          <t>4921.0_2491_A.</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>10007.8_2668_V.</t>
+          <t>10030.5_4765_C.</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>8253.0_2972_🔋.</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>6600.2_1915_M.</t>
+          <t>3614.8_970_🔋.</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>3010.0_1685_A.</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>5072.4_1931_S.</t>
+          <t>18665.3_4638_S.</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>5235.4_1766_P.</t>
+          <t>7039.1_2754_S.</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>5000.5_1919_P.</t>
+          <t>2305.1_940_S.</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>6038.2_2121_P.</t>
+          <t>9013.7_2337_M.</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>3026.1_1490_A.</t>
+          <t>5005.4_2618_L.</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>6536.2_2241_P.</t>
+          <t>3019.8_1453_F.</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>6028.3_2419_L.</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>5014.5_1497_G.</t>
+          <t>6610.9_1738_P.</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>10006.0_2772_V.</t>
+          <t>5100.0_2587_A.</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>3010.0_1289_A.</t>
+          <t>8899.2_2910_S.</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>9415.9_3699_G.</t>
+          <t>6038.2_2121_P.</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>3023.2_962_S.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>3597.6_2910_E.</t>
+          <t>6345.4_2376_S.</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>5163.5_1775_V.</t>
+          <t>6053.8_2077_M.</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>10006.5_3648_X.</t>
+          <t>10348.3_2647_S.</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>4917.5_2381_T.</t>
+          <t>12002.7_4232_S.</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>5085.1_1840_G.</t>
+          <t>6007.4_1804_G.</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>15194.4_3911_S.</t>
+          <t>10027.3_2906_P.</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>13023.5_5156_L.</t>
+          <t>14019.6_6253_L.</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>5043.1_2254_C.</t>
+          <t>4214.8_2018_A.</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>5365.6_2437_C.</t>
+          <t>3798.9_1319_S.</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>1701.7_720_F.</t>
+          <t>8396.0_2595_S.</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>6518.4_2914_A.</t>
+          <t>8006.7_2244_V.</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>5301.0_2064_F.</t>
+          <t>7420.2_4318_C.</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>1432.9_3942_M.</t>
+          <t>4576.3_2084_S.</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>4214.8_2018_A.</t>
+          <t>10030.1_3124_M.</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>7012.1_3931_🔋.</t>
+          <t>10003.1_5062_V.</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>4078.1_1810_A.</t>
+          <t>1884.9_866_S.</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>5256.5_1535_S.</t>
+          <t>4899.2_1459_A.</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>5152.8_1800_G.</t>
+          <t>10010.0_2910_V.</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>6011.8_1873_M.</t>
+          <t>6600.2_1915_M.</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>4576.3_2084_S.</t>
+          <t>4972.5_2522_S.</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>6012.6_2984_P.</t>
+          <t>18516.8_6699_G.</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>4763.8_1720_P.</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>7992.7_2506_F.</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>7090.6_3340_A.</t>
+          <t>7880.9_2433_E.</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>6006.1_2236_V.</t>
+          <t>12326.4_4833_S.</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>2060.0_802_S.</t>
+          <t>4177.9_1557_T.</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>4830.1_2569_C.</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>14117.6_3844_M.</t>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>4830.1_2569_C.</t>
+          <t>5028.5_4433_S.</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>6053.8_2077_M.</t>
+          <t>7006.7_5717_S.</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>10022.1_2875_M.</t>
+          <t>8416.2_4091_P.</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>8024.4_2933_S.</t>
+          <t>7003.6_2437_P.</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>12521.4_4814_M.</t>
+          <t>4540.8_1823_A.</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>5021.7_1930_A.</t>
+          <t>10007.4_3588_V.</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>3735.9_1928_V.</t>
+          <t>15194.4_3911_S.</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>13008.2_4958_P.</t>
+          <t>9005.3_4344_A.</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>10001.3_4206_G.</t>
+          <t>2557.8_1206_V.</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>4921.0_2491_A.</t>
+          <t>14009.7_4401_V.</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>9756.3_2793_M.</t>
+          <t>7127.8_1843_G.</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>6518.4_2914_A.</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>5981.9_2551_P.</t>
+          <t>10277.3_4318_L.</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>10012.1_3139_S.</t>
+          <t>21442.0_7959_F.</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>6004.0_2559_P.</t>
+          <t>6536.2_2241_P.</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>15223.0_6245_P.</t>
+          <t>4937.4_1783_A.</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>5451.1_1905_T.</t>
+          <t>4768.0_1875_L.</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>4705.5_1241_G.</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>5064.2_1636_G.</t>
+          <t>7985.2_2173_P.</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>7114.0_2850_S.</t>
+          <t>4692.9_1546_P.</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>4013.7_1173_V.</t>
+          <t>5014.3_1731_F.</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>10002.4_5136_P.</t>
+          <t>1432.9_3942_M.</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>1366.2_487_L.</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>3089.9_1508_C.</t>
+          <t>9555.5_5689_S.</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>4937.4_1783_A.</t>
+          <t>7598.7_2799_S.</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>10006.9_3646_X.</t>
+          <t>12013.5_4635_X.</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>553.2_224_S.</t>
+          <t>1701.7_720_F.</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>5028.5_4433_S.</t>
+          <t>2000.0_724_A.</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>5827.8_2106_S.</t>
+          <t>4917.5_2381_T.</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>6620.4_2477_P.</t>
+          <t>4013.7_1173_V.</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>4864.8_1353_E.</t>
+          <t>16008.9_5968_S.</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>8008.0_2930_A.</t>
+          <t>7312.2_2446_G.</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>2558.7_905_S.</t>
+          <t>5020.6_1328_M.</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>4613.1_1806_A.</t>
+          <t>15223.0_6245_P.</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>21207.4_6474_V.</t>
+          <t>5724.1_3694_S.</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>5287.4_1835_V.</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>611.2_221_M.</t>
+          <t>1002.7_460_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>6004.0_2559_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>5152.8_1800_G.</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>5000.6_1856_M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>9209.1_3141_E.</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>6620.4_2477_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>657.7_273_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>8367.5_4269_C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>5007.1_1751_T.</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>1629.5_671_F.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_500km_2026.xlsx
+++ b/Ranking_CNB_500km_2026.xlsx
@@ -505,12 +505,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>270,1 km</t>
+          <t>275,9 km</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.219 m</t>
+          <t>2.343 m</t>
         </is>
       </c>
     </row>
@@ -522,12 +522,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>232,8 km</t>
+          <t>240,8 km</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.705 m</t>
+          <t>2.814 m</t>
         </is>
       </c>
     </row>
@@ -539,12 +539,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>224,2 km</t>
+          <t>235,2 km</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.093 m</t>
+          <t>2.150 m</t>
         </is>
       </c>
     </row>
@@ -573,12 +573,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>204,2 km</t>
+          <t>211,8 km</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.304 m</t>
+          <t>2.380 m</t>
         </is>
       </c>
     </row>
@@ -806,34 +806,34 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Jhonny E.</t>
+          <t>Pierre P.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>73,1 km</t>
+          <t>76,5 km</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>728 m</t>
+          <t>829 m</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Pierre P.</t>
+          <t>Jhonny E.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>71,8 km</t>
+          <t>73,1 km</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>782 m</t>
+          <t>728 m</t>
         </is>
       </c>
     </row>
@@ -874,34 +874,34 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Eduardo T.</t>
+          <t>Filipe M.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>33,7 km</t>
+          <t>35,8 km</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>376 m</t>
+          <t>500 m</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Filipe M.</t>
+          <t>Eduardo T.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>33,2 km</t>
+          <t>33,7 km</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>464 m</t>
+          <t>376 m</t>
         </is>
       </c>
     </row>
@@ -913,12 +913,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>30,6 km</t>
+          <t>33,2 km</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>430 m</t>
+          <t>466 m</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A410"/>
+  <dimension ref="A1:A418"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1014,2863 +1014,2919 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10643.3_3263_S.</t>
+          <t>5904.3_2699_P.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4150.2_2042_C.</t>
+          <t>5002.9_1487_P.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>12006.1_5290_T.</t>
+          <t>8104.2_2652_M.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5006.8_1080_M.</t>
+          <t>8200.8_2347_T.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5008.1_1825_M.</t>
+          <t>10174.3_3680_S.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4735.2_997_S.</t>
+          <t>10020.8_2989_M.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5040.0_2971_A.</t>
+          <t>2051.8_860_S.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>7593.7_2701_E.</t>
+          <t>7090.6_3340_A.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5301.0_2064_F.</t>
+          <t>9791.4_3527_G.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>419.0_180_P.</t>
+          <t>14119.3_5262_S.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5033.4_1976_M.</t>
+          <t>4688.1_2291_C.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5040.0_2299_A.</t>
+          <t>6113.5_2883_C.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5010.3_3392_P.</t>
+          <t>12326.4_4833_S.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>611.2_221_M.</t>
+          <t>9006.5_3085_X.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>12521.4_4814_M.</t>
+          <t>10002.4_5136_P.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>401.2_179_S.</t>
+          <t>4972.5_2522_S.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5365.6_2437_C.</t>
+          <t>7419.2_3469_F.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5382.2_2690_M.</t>
+          <t>5005.4_2618_L.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3412.3_1947_C.</t>
+          <t>6779.9_2003_E.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5002.9_1487_P.</t>
+          <t>5008.0_2402_P.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5451.1_1905_T.</t>
+          <t>5011.9_1594_P.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>8092.0_4532_P.</t>
+          <t>6472.0_2501_S.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>123.0_5992_A.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10007.8_2668_V.</t>
+          <t>553.2_224_S.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5020.4_2167_C.</t>
+          <t>5238.0_2781_F.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>6007.1_2393_M.</t>
+          <t>10030.0_3041_G.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5025.8_1214_P.</t>
+          <t>9209.1_3141_E.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>7025.4_3008_L.</t>
+          <t>5287.4_1835_V.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>15057.9_8625_F.</t>
+          <t>14014.7_3537_S.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>6622.5_2224_E.</t>
+          <t>21106.2_7925_P.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2510.2_1366_V.</t>
+          <t>7025.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>26010.2_9812_F.</t>
+          <t>5299.8_2406_C.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10020.8_2989_M.</t>
+          <t>4791.5_1524_E.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>22008.4_8412_F.</t>
+          <t>17003.0_7696_P.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5522.8_2716_V.</t>
+          <t>8618.0_2344_P.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>6028.3_2419_L.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>21141.5_8155_F.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1083.2_390_M.</t>
+          <t>5008.2_1646_A.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>5579.8_1990_E.</t>
+          <t>9555.5_5689_S.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>123.0_5992_A.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>6035.0_2481_P.</t>
+          <t>5022.5_1222_P.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>9012.4_2700_M.</t>
+          <t>4830.1_2569_C.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>6084.1_2156_V.</t>
+          <t>5007.4_1601_A.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>5238.0_2781_F.</t>
+          <t>3026.1_1490_A.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>10030.1_3124_M.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>10016.9_3028_M.</t>
+          <t>5085.1_1840_G.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>6010.6_2144_A.</t>
+          <t>4814.5_1705_🔋.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>25020.8_7832_V.</t>
+          <t>531.0_343_A.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>4688.1_2291_C.</t>
+          <t>12013.5_4635_X.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>21106.2_7925_P.</t>
+          <t>5224.2_2340_C.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>9415.9_3699_G.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>5144.4_2349_P.</t>
+          <t>4017.3_1883_C.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>10006.0_2772_V.</t>
+          <t>4540.8_1823_A.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>14009.0_5498_A.</t>
+          <t>22320.3_9183_F.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>4791.5_1524_E.</t>
+          <t>14004.5_5478_M.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>21114.4_6098_P.</t>
+          <t>5010.3_1888_G.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>56121.5_25636_F.</t>
+          <t>2000.0_724_A.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2186.2_736_G.</t>
+          <t>56121.5_25636_F.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>5004.5_1548_A.</t>
+          <t>5004.1_1610_M.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>6012.6_2984_P.</t>
+          <t>7022.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>3089.9_1508_C.</t>
+          <t>5004.0_2103_C.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>5621.6_2375_P.</t>
+          <t>4692.9_1546_P.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>14004.5_5478_M.</t>
+          <t>6012.6_2984_P.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>5904.3_2699_P.</t>
+          <t>14009.0_5498_A.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>7569.4_2477_V.</t>
+          <t>10001.3_4206_G.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>10503.6_3278_M.</t>
+          <t>6600.2_1915_M.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>10533.4_4020_F.</t>
+          <t>4214.8_2018_A.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>8200.8_2347_T.</t>
+          <t>5040.0_2299_A.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>5869.6_2613_P.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2735.8_959_S.</t>
+          <t>5043.1_2254_C.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>7001.2_3357_M.</t>
+          <t>15057.9_8625_F.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>22002.4_8469_M.</t>
+          <t>5296.8_1844_P.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>10003.3_3845_P.</t>
+          <t>3006.0_1286_M.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>10007.8_2733_V.</t>
+          <t>4705.5_1241_G.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>5064.2_1636_G.</t>
+          <t>3005.2_1040_L.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>4932.4_1545_E.</t>
+          <t>14009.7_4401_V.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>6951.4_2856_S.</t>
+          <t>4937.4_1783_A.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>5011.9_1594_P.</t>
+          <t>12022.7_5417_L.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>17003.0_7696_P.</t>
+          <t>6004.0_2559_P.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>3010.0_1289_A.</t>
+          <t>4763.8_1720_P.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>5581.6_3687_P.</t>
+          <t>611.2_221_M.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>5580.0_2471_A.</t>
+          <t>8218.3_2327_P.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>7145.5_2856_E.</t>
+          <t>12545.4_3039_S.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>15200.8_10718_F.</t>
+          <t>6833.7_2100_G.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>4532.9_2322_L.</t>
+          <t>3580.9_1198_S.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>12022.7_5417_L.</t>
+          <t>7502.4_3467_P.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>8004.6_2357_G.</t>
+          <t>7230.5_2794_V.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>5008.1_1825_M.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>657.7_273_S.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>10012.1_3139_S.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>9756.3_2793_M.</t>
+          <t>3012.4_1258_P.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>1011.0_396_L.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>5017.7_1147_M.</t>
+          <t>10003.3_3845_P.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>10006.9_3646_X.</t>
+          <t>6036.4_2875_V.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>7992.7_2506_F.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>9639.7_4763_P.</t>
+          <t>15637.2_5789_G.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>14014.7_3537_S.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2783.5_952_S.</t>
+          <t>2002.2_938_P.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>12002.7_4232_S.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>10012.3_3067_S.</t>
+          <t>7593.7_2701_E.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>1629.5_671_F.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>5072.4_1931_S.</t>
+          <t>5033.4_1976_M.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>4613.1_1806_A.</t>
+          <t>2185.4_792_S.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>6345.4_2376_S.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>8442.5_3038_G.</t>
+          <t>1020.0_679_T.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>6103.6_2241_G.</t>
+          <t>10643.3_3263_S.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>6779.9_2003_E.</t>
+          <t>5020.6_1328_M.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>5005.9_1755_X.</t>
+          <t>4101.5_1485_V.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>4786.5_1898_P.</t>
+          <t>53755.6_36604_F.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>21250.2_9506_P.</t>
+          <t>1083.2_390_M.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>16397.3_4254_S.</t>
+          <t>3798.9_1319_S.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>5085.1_1840_G.</t>
+          <t>7516.9_3203_A.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>9562.8_3145_M.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>5242.7_1657_S.</t>
+          <t>10007.4_3588_V.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>5163.5_1775_V.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>5235.4_1766_P.</t>
+          <t>12524.7_3259_S.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>5010.3_1888_G.</t>
+          <t>4013.7_1173_V.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1380.0_562_A.</t>
+          <t>21442.0_7959_F.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>6661.8_3736_P.</t>
+          <t>22008.4_8412_F.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>5827.8_2106_S.</t>
+          <t>10011.5_3070_S.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>8008.0_2930_A.</t>
+          <t>4613.1_1806_A.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>4000.6_1659_S.</t>
+          <t>6536.2_2241_P.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>3597.6_2910_E.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>6011.8_1873_M.</t>
+          <t>18516.8_6699_G.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2060.0_802_S.</t>
+          <t>5365.6_2437_C.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>8351.7_4153_C.</t>
+          <t>5119.6_3153_M.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>5040.0_2514_C.</t>
+          <t>2036.1_839_S.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>3735.9_1928_V.</t>
+          <t>5028.5_4433_S.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>7024.3_3266_L.</t>
+          <t>5422.4_1911_G.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>7576.8_2823_P.</t>
+          <t>15016.9_6221_G.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>1114.9_359_S.</t>
+          <t>2783.5_952_S.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>4101.5_1485_V.</t>
+          <t>6103.6_2241_G.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2064.3_708_S.</t>
+          <t>6016.7_2122_M.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>773.5_238_S.</t>
+          <t>6012.6_2984_F.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>5256.5_1535_S.</t>
+          <t>10001.9_4466_P.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>6006.6_2009_P.</t>
+          <t>5064.2_1636_G.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>6003.3_2987_M.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>5051.4_1993_M.</t>
+          <t>5005.9_1755_X.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>4790.7_1897_F.</t>
+          <t>4078.1_1810_A.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>8196.1_2807_T.</t>
+          <t>15186.5_3866_S.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>10106.6_2889_P.</t>
+          <t>8004.6_2357_G.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>4969.4_2146_P.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>5029.4_1585_P.</t>
+          <t>10106.6_2889_P.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>7090.6_3340_A.</t>
+          <t>3089.9_1508_C.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>4678.8_1840_A.</t>
+          <t>5000.5_1919_P.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>18107.4_4577_M.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>7874.8_2223_M.</t>
+          <t>5064.3_1832_F.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>7012.1_3931_🔋.</t>
+          <t>7145.5_2856_E.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>5282.8_2392_C.</t>
+          <t>6137.8_2406_L.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>5003.2_1389_E.</t>
+          <t>4864.8_1353_E.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>6047.4_2816_T.</t>
+          <t>7015.4_2141_T.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2504.7_703_🔋.</t>
+          <t>10106.6_3354_M.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>5009.1_2246_C.</t>
+          <t>10348.3_2647_S.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>553.2_224_S.</t>
+          <t>6011.8_1873_M.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>4781.2_1507_A.</t>
+          <t>7024.3_3266_L.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>5422.4_1911_G.</t>
+          <t>9639.7_4763_P.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>4974.4_1533_E.</t>
+          <t>1884.9_866_S.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>5022.5_1222_P.</t>
+          <t>3412.3_1947_C.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>6903.6_2566_G.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>5000.5_1919_P.</t>
+          <t>3023.2_962_S.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>9791.4_3527_G.</t>
+          <t>15223.0_6245_P.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>14117.6_3844_M.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>3059.2_956_T.</t>
+          <t>10027.3_2906_P.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>5051.4_1993_M.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>6804.1_2088_P.</t>
+          <t>5579.8_1990_E.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2880.9_1210_L.</t>
+          <t>2175.4_712_S.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>6016.7_2122_M.</t>
+          <t>3010.0_1685_A.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2004.9_754_S.</t>
+          <t>3735.9_1928_V.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>3010.0_1424_A.</t>
+          <t>6038.2_2121_P.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2011.7_731_S.</t>
+          <t>5021.7_1930_A.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>8506.3_4050_C.</t>
+          <t>2004.9_754_S.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>5299.8_2406_C.</t>
+          <t>10718.1_9873_S.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>10003.7_2721_V.</t>
+          <t>10503.6_3278_M.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>5064.3_1832_F.</t>
+          <t>7569.4_2477_V.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>12008.4_3832_G.</t>
+          <t>8024.4_2933_S.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>5043.1_2254_C.</t>
+          <t>9507.9_2851_M.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>9006.5_3085_X.</t>
+          <t>5301.0_2064_F.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>5004.0_2103_C.</t>
+          <t>14019.6_6253_L.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>5010.0_1872_A.</t>
+          <t>5013.9_1673_A.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>5981.9_2551_P.</t>
+          <t>7598.7_2799_S.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2036.1_839_S.</t>
+          <t>3958.9_1777_P.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>4891.7_1690_F.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>4788.2_1476_P.</t>
+          <t>3004.6_746_V.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>8024.4_2933_S.</t>
+          <t>5000.2_1932_E.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>5086.0_1810_G.</t>
+          <t>2880.9_1210_L.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>1206.7_12400_M.</t>
+          <t>21141.5_8155_F.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>5001.9_1291_V.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>7230.5_2794_V.</t>
+          <t>6951.4_2856_S.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>13008.2_4958_P.</t>
+          <t>18665.3_4638_S.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>9029.6_4595_P.</t>
+          <t>4028.8_1699_L.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>3138.1_1120_S.</t>
+          <t>208.3_85_P.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>5224.2_2340_C.</t>
+          <t>6006.6_2009_P.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>5049.0_2240_C.</t>
+          <t>5004.5_1548_A.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>21207.4_6474_V.</t>
+          <t>791.5_266_G.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2002.2_938_P.</t>
+          <t>2011.7_731_S.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>7516.9_3203_A.</t>
+          <t>7604.2_3303_P.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>37036.6_17889_F.</t>
+          <t>5029.4_1585_P.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>5724.1_3694_S.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>4850.9_2239_C.</t>
+          <t>5027.8_1361_P.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>4017.3_1883_C.</t>
+          <t>6084.1_2156_V.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>7419.2_3469_F.</t>
+          <t>5017.7_1147_M.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2185.4_792_S.</t>
+          <t>10030.5_4765_C.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>3006.0_1286_M.</t>
+          <t>2558.7_905_S.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>10002.4_5136_P.</t>
+          <t>1027.7_364_S.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>6007.1_3172_F.</t>
+          <t>6053.8_2077_M.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>7003.6_2437_P.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>13023.5_5156_L.</t>
+          <t>5256.5_1535_S.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>4678.8_1840_A.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>4177.9_1557_T.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>14119.3_5262_S.</t>
+          <t>10007.8_2733_V.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>10003.1_5062_V.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2556.5_1160_M.</t>
+          <t>5621.6_2375_P.</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>6006.1_2236_V.</t>
+          <t>2556.5_1160_M.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>8013.1_2082_P.</t>
+          <t>7874.8_2223_M.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>4969.4_2146_P.</t>
+          <t>7006.7_5717_S.</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>8481.2_2463_🔋.</t>
+          <t>10006.9_3646_X.</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>6518.4_2914_A.</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>15186.5_3866_S.</t>
+          <t>5040.0_2971_A.</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>7186.5_2708_S.</t>
+          <t>13023.5_5156_L.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>11214.0_4224_V.</t>
+          <t>5020.4_2167_C.</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>6804.1_2088_P.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>7022.4_3008_L.</t>
+          <t>6010.6_2144_A.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>6818.2_2036_P.</t>
+          <t>10031.8_2663_P.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>791.5_266_G.</t>
+          <t>6610.9_1738_P.</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>10006.9_3646_F.</t>
+          <t>2355.5_726_S.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>5027.8_1361_P.</t>
+          <t>8367.5_4269_C.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>5007.4_1601_A.</t>
+          <t>15200.8_10718_F.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>10006.5_3648_X.</t>
+          <t>4781.2_1507_A.</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>5008.0_2402_P.</t>
+          <t>5770.8_2848_G.</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>531.0_343_A.</t>
+          <t>8092.0_4532_P.</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>5005.8_1527_S.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>5014.5_1497_G.</t>
+          <t>5003.2_1389_E.</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>1027.7_364_S.</t>
+          <t>4797.2_1541_G.</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>12006.9_5463_P.</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>8187.1_2322_M.</t>
+          <t>4735.2_997_S.</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>2558.7_905_S.</t>
+          <t>773.5_238_S.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>9507.9_2851_M.</t>
+          <t>1206.7_12400_M.</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>3026.1_1490_A.</t>
+          <t>6007.4_1804_G.</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>6011.5_2408_A.</t>
+          <t>8396.0_2595_S.</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>3958.9_1777_P.</t>
+          <t>4788.2_1476_P.</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>5004.1_1610_M.</t>
+          <t>5981.9_2551_P.</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>10012.1_3139_S.</t>
+          <t>10062.5_2886_M.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>15637.2_5789_G.</t>
+          <t>12006.1_5290_T.</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>14117.6_3844_M.</t>
+          <t>5007.1_1751_T.</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>4576.3_2084_S.</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>10001.3_4206_G.</t>
+          <t>12342.9_3211_M.</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2047.9_924_L.</t>
+          <t>5000.6_1856_M.</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>53755.6_36604_F.</t>
+          <t>6011.5_2408_A.</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>960.0_1109_A.</t>
+          <t>2504.7_703_🔋.</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>8200.5_2738_M.</t>
+          <t>3138.1_1120_S.</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>4153.2_3559_P.</t>
+          <t>2305.1_940_S.</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>5004.9_1790_A.</t>
+          <t>15504.3_3950_M.</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>5021.7_1930_A.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>18102.7_4949_M.</t>
+          <t>11005.3_5159_P.</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>3004.6_746_V.</t>
+          <t>10006.0_2772_V.</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>4078.1_1810_A.</t>
+          <t>5014.5_1497_G.</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>1443.0_851_A.</t>
+          <t>16520.2_4844_M.</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>6036.4_2875_V.</t>
+          <t>12006.1_5290_X.</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>4896.8_2251_L.</t>
+          <t>10007.8_2668_V.</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>4797.2_1541_G.</t>
+          <t>3019.8_1453_F.</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>8132.9_2716_S.</t>
+          <t>4932.4_1545_E.</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>8218.3_2327_P.</t>
+          <t>1152.4_938_S.</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>15504.3_3950_M.</t>
+          <t>5010.0_1872_A.</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>1012.0_375_E.</t>
+          <t>5009.1_2246_C.</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>3023.2_962_S.</t>
+          <t>4619.4_1440_S.</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>4028.8_1699_L.</t>
+          <t>9756.3_2793_M.</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>5000.2_1932_E.</t>
+          <t>4917.5_2381_T.</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>5770.8_2848_G.</t>
+          <t>4850.9_2239_C.</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>5163.5_1775_V.</t>
+          <t>4729.8_2058_P.</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>5081.5_1647_G.</t>
+          <t>5144.4_2349_P.</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>16520.2_4844_M.</t>
+          <t>9415.9_3699_G.</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>5013.9_1673_A.</t>
+          <t>7127.8_1843_G.</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>5296.8_1844_P.</t>
+          <t>5100.0_2587_A.</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>10718.1_9873_S.</t>
+          <t>4000.6_1659_S.</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>9007.1_3080_P.</t>
+          <t>5580.0_2471_A.</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>12545.4_3039_S.</t>
+          <t>9012.4_2700_M.</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>10031.8_2663_P.</t>
+          <t>3757.2_1716_A.</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>7880.9_2433_E.</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>2355.5_726_S.</t>
+          <t>2060.0_802_S.</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>4864.8_1353_E.</t>
+          <t>3614.8_970_🔋.</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>22320.3_9183_F.</t>
+          <t>7012.1_3931_🔋.</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>10022.1_2875_M.</t>
+          <t>6903.6_2566_G.</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>21124.1_8011_F.</t>
+          <t>1380.0_562_A.</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>20105.6_7766_F.</t>
+          <t>7420.2_4318_C.</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>6003.3_2987_M.</t>
+          <t>6622.5_2224_E.</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>10001.9_4466_P.</t>
+          <t>8416.2_4091_P.</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>3597.6_2910_E.</t>
+          <t>3010.0_1289_A.</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>1020.0_679_T.</t>
+          <t>5049.0_2240_C.</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>5008.2_1646_A.</t>
+          <t>9013.7_2337_M.</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>6113.5_2883_C.</t>
+          <t>8481.2_2463_🔋.</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>12342.9_3211_M.</t>
+          <t>6007.1_2393_M.</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>3757.2_1716_A.</t>
+          <t>13008.2_4958_P.</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>5014.8_2009_A.</t>
+          <t>7039.1_2754_S.</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>5869.6_2613_P.</t>
+          <t>8047.1_2948_G.</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>12006.1_5290_X.</t>
+          <t>10006.9_3646_F.</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>3012.4_1258_P.</t>
+          <t>7576.8_2823_P.</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>7114.0_2850_S.</t>
+          <t>5086.0_1810_G.</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>5827.8_2106_S.</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>4821.0_1857_P.</t>
+          <t>10058.8_3483_F.</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>7502.4_3467_P.</t>
+          <t>12008.4_3832_G.</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>10011.5_3070_S.</t>
+          <t>11214.0_4224_V.</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>6833.7_2100_G.</t>
+          <t>8351.7_4153_C.</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>1034.3_279_M.</t>
+          <t>4790.7_1897_F.</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>6173.6_2865_M.</t>
+          <t>5382.2_2690_M.</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>5152.8_1800_G.</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>10008.1_2966_M.</t>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>12524.7_3259_S.</t>
+          <t>2064.3_708_S.</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>4896.8_2251_L.</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>6173.6_2865_M.</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>8618.0_2344_P.</t>
+          <t>5014.3_1731_F.</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>10030.0_3041_G.</t>
+          <t>1366.2_487_L.</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>4700.4_1216_V.</t>
+          <t>8506.3_4050_C.</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>15016.9_6221_G.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>4921.0_2491_A.</t>
+          <t>2557.8_1206_V.</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>10030.5_4765_C.</t>
+          <t>10277.3_4318_L.</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>4899.2_1459_A.</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>1701.7_720_F.</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>3010.0_1685_A.</t>
+          <t>4974.4_1533_E.</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>18665.3_4638_S.</t>
+          <t>5001.9_1291_V.</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>7039.1_2754_S.</t>
+          <t>2510.2_1366_V.</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>21114.4_6098_P.</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>960.0_1109_A.</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>5005.4_2618_L.</t>
+          <t>5081.5_1647_G.</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>8899.2_2910_S.</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>6028.3_2419_L.</t>
+          <t>8253.0_2972_🔋.</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>6610.9_1738_P.</t>
+          <t>6006.1_2236_V.</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>5100.0_2587_A.</t>
+          <t>8006.7_2244_V.</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>8899.2_2910_S.</t>
+          <t>17012.6_5869_T.</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>16397.3_4254_S.</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>6038.2_2121_P.</t>
+          <t>8196.1_2807_T.</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>21207.4_6474_V.</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>6345.4_2376_S.</t>
+          <t>20105.6_7766_F.</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>6053.8_2077_M.</t>
+          <t>5282.8_2392_C.</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>10348.3_2647_S.</t>
+          <t>6035.0_2481_P.</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>12002.7_4232_S.</t>
+          <t>4153.2_3559_P.</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>6007.4_1804_G.</t>
+          <t>419.0_180_P.</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>10027.3_2906_P.</t>
+          <t>6620.4_2477_P.</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>14019.6_6253_L.</t>
+          <t>22002.4_8469_M.</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>4214.8_2018_A.</t>
+          <t>2186.2_736_G.</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>3798.9_1319_S.</t>
+          <t>10022.1_2875_M.</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>8396.0_2595_S.</t>
+          <t>1002.7_460_S.</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>8006.7_2244_V.</t>
+          <t>3059.2_956_T.</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>7420.2_4318_C.</t>
+          <t>37036.6_17889_F.</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>4576.3_2084_S.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>10030.1_3124_M.</t>
+          <t>7001.2_3357_M.</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>10003.1_5062_V.</t>
+          <t>4077.1_1454_S.</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>4921.0_2491_A.</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>4899.2_1459_A.</t>
+          <t>8442.5_3038_G.</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>10010.0_2910_V.</t>
+          <t>5005.8_1527_S.</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>6600.2_1915_M.</t>
+          <t>1432.9_3942_M.</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>4972.5_2522_S.</t>
+          <t>1034.3_279_M.</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>18516.8_6699_G.</t>
+          <t>18102.7_4949_M.</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>6007.1_3172_F.</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>7992.7_2506_F.</t>
+          <t>2047.9_924_L.</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>7880.9_2433_E.</t>
+          <t>7186.5_2708_S.</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>6047.4_2816_T.</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>4177.9_1557_T.</t>
+          <t>2629.2_1249_M.</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>4830.1_2569_C.</t>
+          <t>8120.9_2737_G.</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>16008.9_5968_S.</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>5028.5_4433_S.</t>
+          <t>4786.5_1898_P.</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>7006.7_5717_S.</t>
+          <t>8132.9_2716_S.</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>8416.2_4091_P.</t>
+          <t>6046.5_3239_S.</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>7003.6_2437_P.</t>
+          <t>8200.5_2738_M.</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>4540.8_1823_A.</t>
+          <t>5025.8_1214_P.</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>10007.4_3588_V.</t>
+          <t>5242.7_1657_S.</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>15194.4_3911_S.</t>
+          <t>5235.4_1766_P.</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>9005.3_4344_A.</t>
+          <t>9007.1_3080_P.</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>2557.8_1206_V.</t>
+          <t>8187.1_2322_M.</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>14009.7_4401_V.</t>
+          <t>1114.9_359_S.</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>7127.8_1843_G.</t>
+          <t>6818.2_2036_P.</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>6518.4_2914_A.</t>
+          <t>5522.8_2716_V.</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>18107.4_4577_M.</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>10277.3_4318_L.</t>
+          <t>5451.1_1905_T.</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>5010.3_3392_P.</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>6536.2_2241_P.</t>
+          <t>5040.0_2514_C.</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>4937.4_1783_A.</t>
+          <t>9005.3_4344_A.</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>5581.6_3687_P.</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>5072.4_1931_S.</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>7985.2_2173_P.</t>
+          <t>26010.2_9812_F.</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>4692.9_1546_P.</t>
+          <t>5006.8_1080_M.</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>5014.8_2009_A.</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>1432.9_3942_M.</t>
+          <t>2735.8_959_S.</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>1366.2_487_L.</t>
+          <t>4150.2_2042_C.</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>9555.5_5689_S.</t>
+          <t>4821.0_1857_P.</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>7598.7_2799_S.</t>
+          <t>15194.4_3911_S.</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>12013.5_4635_X.</t>
+          <t>10016.9_3028_M.</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>1701.7_720_F.</t>
+          <t>3010.0_1424_A.</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>2000.0_724_A.</t>
+          <t>4532.9_2322_L.</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>4917.5_2381_T.</t>
+          <t>10006.5_3648_X.</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>4013.7_1173_V.</t>
+          <t>21124.1_8011_F.</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>16008.9_5968_S.</t>
+          <t>10010.0_2910_V.</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>7312.2_2446_G.</t>
+          <t>10012.3_3067_S.</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>5020.6_1328_M.</t>
+          <t>401.2_179_S.</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>15223.0_6245_P.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>5724.1_3694_S.</t>
+          <t>25020.8_7832_V.</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>5287.4_1835_V.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>1002.7_460_S.</t>
+          <t>7985.2_2173_P.</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>6004.0_2559_P.</t>
+          <t>8013.1_2082_P.</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>5152.8_1800_G.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>5000.6_1856_M.</t>
+          <t>10533.4_4020_F.</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>9209.1_3141_E.</t>
+          <t>6661.8_3736_P.</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>6620.4_2477_P.</t>
+          <t>8008.0_2930_A.</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>657.7_273_S.</t>
+          <t>21250.2_9506_P.</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>8367.5_4269_C.</t>
+          <t>4731.9_1407_T.</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>5007.1_1751_T.</t>
+          <t>1012.0_375_E.</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>1629.5_671_F.</t>
+          <t>7312.2_2446_G.</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>7114.0_2850_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>2629.2_1249_V.</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>5004.9_1790_A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>4768.0_1875_L.</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>10003.7_2721_V.</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>9029.6_4595_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>1443.0_851_A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>4700.4_1216_V.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_500km_2026.xlsx
+++ b/Ranking_CNB_500km_2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,12 +471,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>505,5 km</t>
+          <t>514,5 km</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>6.716 m</t>
+          <t>6.826 m</t>
         </is>
       </c>
     </row>
@@ -522,12 +522,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>240,8 km</t>
+          <t>254,7 km</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.814 m</t>
+          <t>2.991 m</t>
         </is>
       </c>
     </row>
@@ -556,12 +556,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>214,8 km</t>
+          <t>223,5 km</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.722 m</t>
+          <t>2.833 m</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>195,3 km</t>
+          <t>197,2 km</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -636,34 +636,34 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cassia C.</t>
+          <t>Alexsia A.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>156,9 km</t>
+          <t>158,9 km</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.944 m</t>
+          <t>1.716 m</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Alexsia A.</t>
+          <t>Cassia C.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>152,9 km</t>
+          <t>156,9 km</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.662 m</t>
+          <t>1.944 m</t>
         </is>
       </c>
     </row>
@@ -687,51 +687,51 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Duda X.</t>
+          <t>Edivânia M.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>136,6 km</t>
+          <t>137,0 km</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.627 m</t>
+          <t>1.486 m</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Naiane C.</t>
+          <t>Duda X.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>132,0 km</t>
+          <t>136,6 km</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.234 m</t>
+          <t>1.627 m</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Edivânia M.</t>
+          <t>Naiane C.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>131,0 km</t>
+          <t>132,0 km</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.432 m</t>
+          <t>1.234 m</t>
         </is>
       </c>
     </row>
@@ -760,12 +760,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>106,3 km</t>
+          <t>111,3 km</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>836 m</t>
+          <t>866 m</t>
         </is>
       </c>
     </row>
@@ -777,12 +777,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>101,0 km</t>
+          <t>111,0 km</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.164 m</t>
+          <t>1.275 m</t>
         </is>
       </c>
     </row>
@@ -823,168 +823,185 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Jhonny E.</t>
+          <t>Denis G.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>73,1 km</t>
+          <t>73,6 km</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>728 m</t>
+          <t>608 m</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Eduarda A.</t>
+          <t>Jhonny E.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>65,7 km</t>
+          <t>73,1 km</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>610 m</t>
+          <t>728 m</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Renato C.</t>
+          <t>Eduarda A.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>36,2 km</t>
+          <t>65,7 km</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>440 m</t>
+          <t>610 m</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Filipe M.</t>
+          <t>Renato C.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>35,8 km</t>
+          <t>36,2 km</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>500 m</t>
+          <t>440 m</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Eduardo T.</t>
+          <t>Filipe M.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>33,7 km</t>
+          <t>35,8 km</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>376 m</t>
+          <t>500 m</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Thaisa V.</t>
+          <t>Eduardo T.</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>33,2 km</t>
+          <t>33,7 km</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>466 m</t>
+          <t>376 m</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>José E.</t>
+          <t>Thaisa V.</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>27,2 km</t>
+          <t>33,2 km</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>287 m</t>
+          <t>466 m</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Karine F.</t>
+          <t>José E.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>25,1 km</t>
+          <t>27,2 km</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>294 m</t>
+          <t>287 m</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Mariana L.</t>
+          <t>Karine F.</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>12,4 km</t>
+          <t>25,1 km</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>161 m</t>
+          <t>294 m</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>Mariana L.</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>12,4 km</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>161 m</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>Marta L.</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>0,0 km</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>0 m</t>
         </is>
@@ -1001,7 +1018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A418"/>
+  <dimension ref="A1:A435"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1014,2919 +1031,3038 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5904.3_2699_P.</t>
+          <t>10106.6_2889_P.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5002.9_1487_P.</t>
+          <t>8978.9_3078_G.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>6016.7_2122_M.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>8200.8_2347_T.</t>
+          <t>1629.5_671_F.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>5282.8_2392_C.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10020.8_2989_M.</t>
+          <t>7127.8_1843_G.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>14014.7_3537_S.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>7090.6_3340_A.</t>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>9791.4_3527_G.</t>
+          <t>21114.4_6098_P.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>14119.3_5262_S.</t>
+          <t>5004.1_1610_M.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4688.1_2291_C.</t>
+          <t>5004.5_1548_A.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6113.5_2883_C.</t>
+          <t>7186.5_2708_S.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>5043.1_2254_C.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>9006.5_3085_X.</t>
+          <t>5580.0_2471_A.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10002.4_5136_P.</t>
+          <t>6006.1_2236_V.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>4972.5_2522_S.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>7419.2_3469_F.</t>
+          <t>4077.1_1454_S.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5005.4_2618_L.</t>
+          <t>5724.1_3694_S.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6779.9_2003_E.</t>
+          <t>22002.4_8469_M.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5008.0_2402_P.</t>
+          <t>2036.1_839_S.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5011.9_1594_P.</t>
+          <t>10016.9_3028_M.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>6903.6_2566_G.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>123.0_5992_A.</t>
+          <t>10025.6_4018_G.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>553.2_224_S.</t>
+          <t>15057.9_8625_F.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5238.0_2781_F.</t>
+          <t>7516.9_3203_A.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10030.0_3041_G.</t>
+          <t>123.0_5992_A.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>9209.1_3141_E.</t>
+          <t>2355.5_726_S.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5287.4_1835_V.</t>
+          <t>5020.4_2167_C.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>14014.7_3537_S.</t>
+          <t>2305.1_940_S.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>21106.2_7925_P.</t>
+          <t>12342.9_3211_M.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>7025.4_3008_L.</t>
+          <t>531.0_343_A.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5299.8_2406_C.</t>
+          <t>7569.4_2477_V.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>4791.5_1524_E.</t>
+          <t>5287.4_1835_V.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>17003.0_7696_P.</t>
+          <t>7992.7_2506_F.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>8618.0_2344_P.</t>
+          <t>4891.7_1690_F.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>6028.3_2419_L.</t>
+          <t>6038.2_2121_P.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>4788.2_1476_P.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>5008.2_1646_A.</t>
+          <t>2000.0_724_A.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>9555.5_5689_S.</t>
+          <t>10006.9_3646_X.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>4896.8_2251_L.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>5022.5_1222_P.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>4830.1_2569_C.</t>
+          <t>9013.7_2337_M.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>5007.4_1601_A.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3026.1_1490_A.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>10030.1_3124_M.</t>
+          <t>7230.5_2794_V.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>5085.1_1840_G.</t>
+          <t>5010.3_1888_G.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>6779.9_2003_E.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>531.0_343_A.</t>
+          <t>4000.6_1659_S.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>12013.5_4635_X.</t>
+          <t>3757.2_1716_A.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>5224.2_2340_C.</t>
+          <t>9006.5_3085_X.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>6012.6_2984_P.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>4017.3_1883_C.</t>
+          <t>10001.9_4466_P.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>4540.8_1823_A.</t>
+          <t>5085.1_1840_G.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>22320.3_9183_F.</t>
+          <t>5081.5_1647_G.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>14004.5_5478_M.</t>
+          <t>3010.0_1289_A.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>5010.3_1888_G.</t>
+          <t>10643.3_3263_S.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2000.0_724_A.</t>
+          <t>4797.2_1541_G.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>56121.5_25636_F.</t>
+          <t>4214.8_2018_A.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>5004.1_1610_M.</t>
+          <t>5256.5_1535_S.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>7022.4_3008_L.</t>
+          <t>10011.5_3070_S.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>5004.0_2103_C.</t>
+          <t>21106.2_7925_P.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>4692.9_1546_P.</t>
+          <t>10106.6_3354_M.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>6012.6_2984_P.</t>
+          <t>9756.3_2793_M.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>14009.0_5498_A.</t>
+          <t>3059.2_956_T.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>10001.3_4206_G.</t>
+          <t>7420.2_4318_C.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>6600.2_1915_M.</t>
+          <t>8367.5_4269_C.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>4214.8_2018_A.</t>
+          <t>7312.2_2446_G.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>5040.0_2299_A.</t>
+          <t>6012.3_2200_M.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>5869.6_2613_P.</t>
+          <t>5522.8_2716_V.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>5043.1_2254_C.</t>
+          <t>6536.2_2241_P.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>15057.9_8625_F.</t>
+          <t>14117.6_3844_M.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>5296.8_1844_P.</t>
+          <t>6600.2_1915_M.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>3006.0_1286_M.</t>
+          <t>1701.7_720_F.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>21442.0_7959_F.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>4966.0_1709_G.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>14009.7_4401_V.</t>
+          <t>4932.4_1545_E.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>4937.4_1783_A.</t>
+          <t>15016.9_6221_G.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>12022.7_5417_L.</t>
+          <t>5006.8_1080_M.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>6004.0_2559_P.</t>
+          <t>3614.8_970_🔋.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>5869.6_2613_P.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>611.2_221_M.</t>
+          <t>5004.9_1790_A.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>8218.3_2327_P.</t>
+          <t>25020.8_7832_V.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>12545.4_3039_S.</t>
+          <t>3958.9_1777_P.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>6833.7_2100_G.</t>
+          <t>2175.4_712_S.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>9555.5_5689_S.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>7502.4_3467_P.</t>
+          <t>6012.6_2984_F.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>7230.5_2794_V.</t>
+          <t>4177.9_1557_T.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>5008.1_1825_M.</t>
+          <t>5163.5_1775_V.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>657.7_273_S.</t>
+          <t>6011.8_1873_M.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>10012.1_3139_S.</t>
+          <t>5126.8_1941_G.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>3012.4_1258_P.</t>
+          <t>10030.0_3041_G.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>16397.3_4254_S.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>10003.3_3845_P.</t>
+          <t>5008.0_2402_P.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>6036.4_2875_V.</t>
+          <t>5581.6_3687_P.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>7992.7_2506_F.</t>
+          <t>5451.1_1905_T.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>15637.2_5789_G.</t>
+          <t>12006.1_5290_X.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>6007.1_2393_M.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2002.2_938_P.</t>
+          <t>2051.8_860_S.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>12002.7_4232_S.</t>
+          <t>4937.4_1783_A.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>7593.7_2701_E.</t>
+          <t>2735.8_959_S.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1629.5_671_F.</t>
+          <t>4921.0_2491_A.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>5033.4_1976_M.</t>
+          <t>10007.4_3588_V.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2185.4_792_S.</t>
+          <t>9209.1_3141_E.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>6345.4_2376_S.</t>
+          <t>10007.8_2668_V.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1020.0_679_T.</t>
+          <t>6084.1_2156_V.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>10643.3_3263_S.</t>
+          <t>1206.7_12400_M.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>5020.6_1328_M.</t>
+          <t>10002.4_5136_P.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>4101.5_1485_V.</t>
+          <t>419.0_180_P.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>53755.6_36604_F.</t>
+          <t>10001.3_4206_G.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1083.2_390_M.</t>
+          <t>7001.2_3357_M.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>3798.9_1319_S.</t>
+          <t>4576.3_2084_S.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>7516.9_3203_A.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>4101.5_1485_V.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>10007.4_3588_V.</t>
+          <t>7006.7_5717_S.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>5163.5_1775_V.</t>
+          <t>4619.4_1440_S.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>12524.7_3259_S.</t>
+          <t>773.5_238_S.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>4013.7_1173_V.</t>
+          <t>10006.0_2772_V.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>1884.9_866_S.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>22008.4_8412_F.</t>
+          <t>10003.3_3845_P.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>10011.5_3070_S.</t>
+          <t>8196.1_2807_T.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>4613.1_1806_A.</t>
+          <t>12326.4_4833_S.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>6536.2_2241_P.</t>
+          <t>17012.6_5869_T.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>3597.6_2910_E.</t>
+          <t>14009.0_5498_A.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>18516.8_6699_G.</t>
+          <t>18107.4_4577_M.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>5365.6_2437_C.</t>
+          <t>6951.4_2856_S.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>7114.0_2850_S.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2036.1_839_S.</t>
+          <t>10062.5_2886_M.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>5028.5_4433_S.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>5422.4_1911_G.</t>
+          <t>6047.4_2816_T.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>15016.9_6221_G.</t>
+          <t>5000.2_1932_E.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2783.5_952_S.</t>
+          <t>4705.5_1241_G.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>6103.6_2241_G.</t>
+          <t>5017.7_1147_M.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>6016.7_2122_M.</t>
+          <t>12545.4_3039_S.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>5238.0_2781_F.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>10001.9_4466_P.</t>
+          <t>8008.0_2930_A.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>5064.2_1636_G.</t>
+          <t>2011.7_731_S.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>6003.3_2987_M.</t>
+          <t>8013.1_2082_P.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>5005.9_1755_X.</t>
+          <t>10003.8_3195_S.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>4078.1_1810_A.</t>
+          <t>9020.0_2605_M.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>15186.5_3866_S.</t>
+          <t>2002.2_938_P.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>8004.6_2357_G.</t>
+          <t>1380.0_562_A.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>4969.4_2146_P.</t>
+          <t>1432.9_3942_M.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>10106.6_2889_P.</t>
+          <t>9029.6_4595_P.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>3089.9_1508_C.</t>
+          <t>10005.2_3808_G.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>5000.5_1919_P.</t>
+          <t>5382.2_2690_M.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>4791.5_1524_E.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>5064.3_1832_F.</t>
+          <t>611.2_221_M.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>7145.5_2856_E.</t>
+          <t>5422.4_1911_G.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>56121.5_25636_F.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>4864.8_1353_E.</t>
+          <t>2557.8_1206_V.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>10030.5_4765_C.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>8416.2_4091_P.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>10348.3_2647_S.</t>
+          <t>4532.9_2322_L.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>6011.8_1873_M.</t>
+          <t>2558.7_905_S.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>7024.3_3266_L.</t>
+          <t>5051.4_1993_M.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>9639.7_4763_P.</t>
+          <t>9005.3_4344_A.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>4830.1_2569_C.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>3412.3_1947_C.</t>
+          <t>15200.8_10718_F.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>7598.7_2799_S.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>3023.2_962_S.</t>
+          <t>7576.8_2823_P.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>15223.0_6245_P.</t>
+          <t>4864.8_1353_E.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>14117.6_3844_M.</t>
+          <t>5011.9_1594_P.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>10027.3_2906_P.</t>
+          <t>6518.4_2914_A.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>5051.4_1993_M.</t>
+          <t>12022.7_5417_L.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>13344.7_5916_G.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>5579.8_1990_E.</t>
+          <t>5008.1_1825_M.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>8120.9_2737_G.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>3010.0_1685_A.</t>
+          <t>5020.6_1328_M.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>3735.9_1928_V.</t>
+          <t>3029.5_1536_G.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>6038.2_2121_P.</t>
+          <t>5224.2_2340_C.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>5021.7_1930_A.</t>
+          <t>5621.6_2375_P.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2004.9_754_S.</t>
+          <t>3735.9_1928_V.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>10718.1_9873_S.</t>
+          <t>1027.7_364_S.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>10503.6_3278_M.</t>
+          <t>5014.3_1731_F.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>7569.4_2477_V.</t>
+          <t>1152.4_938_S.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>8024.4_2933_S.</t>
+          <t>11214.0_4224_V.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>9507.9_2851_M.</t>
+          <t>15637.2_5789_G.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>5301.0_2064_F.</t>
+          <t>5027.8_1361_P.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>14019.6_6253_L.</t>
+          <t>20105.6_7766_F.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>5013.9_1673_A.</t>
+          <t>9562.8_3145_M.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>7598.7_2799_S.</t>
+          <t>3010.0_1685_A.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>3958.9_1777_P.</t>
+          <t>4017.3_1883_C.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>6046.5_3239_S.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>3004.6_746_V.</t>
+          <t>6035.0_2481_P.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>5000.2_1932_E.</t>
+          <t>5005.9_1755_X.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2880.9_1210_L.</t>
+          <t>18516.8_6699_G.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>21141.5_8155_F.</t>
+          <t>5579.8_1990_E.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>6053.8_2077_M.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>6951.4_2856_S.</t>
+          <t>6003.3_2987_M.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>18665.3_4638_S.</t>
+          <t>6007.4_1804_G.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>4028.8_1699_L.</t>
+          <t>4078.1_1810_A.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>6610.9_1738_P.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>6006.6_2009_P.</t>
+          <t>3026.1_1490_A.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>5004.5_1548_A.</t>
+          <t>4768.0_1875_L.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>791.5_266_G.</t>
+          <t>3023.2_962_S.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2011.7_731_S.</t>
+          <t>8899.2_2910_S.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>7604.2_3303_P.</t>
+          <t>2629.2_1249_M.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>5029.4_1585_P.</t>
+          <t>4821.0_1857_P.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>5724.1_3694_S.</t>
+          <t>4790.7_1897_F.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>8218.3_2327_P.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>5027.8_1361_P.</t>
+          <t>15504.3_3950_M.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>6084.1_2156_V.</t>
+          <t>8396.0_2595_S.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>5017.7_1147_M.</t>
+          <t>553.2_224_S.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>10030.5_4765_C.</t>
+          <t>2185.4_792_S.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2558.7_905_S.</t>
+          <t>14009.7_4401_V.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>1027.7_364_S.</t>
+          <t>5000.6_1856_M.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>6053.8_2077_M.</t>
+          <t>1114.9_359_S.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>7003.6_2437_P.</t>
+          <t>8200.5_2738_M.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>5256.5_1535_S.</t>
+          <t>7039.1_2754_S.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>4678.8_1840_A.</t>
+          <t>2047.9_924_L.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>4177.9_1557_T.</t>
+          <t>12006.9_5463_P.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>10007.8_2733_V.</t>
+          <t>3006.0_1286_M.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>10003.1_5062_V.</t>
+          <t>6007.1_3172_F.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>5621.6_2375_P.</t>
+          <t>5005.4_2618_L.</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2556.5_1160_M.</t>
+          <t>5301.0_2064_F.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>7874.8_2223_M.</t>
+          <t>6028.3_2419_L.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>7006.7_5717_S.</t>
+          <t>5009.1_2246_C.</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>10006.9_3646_X.</t>
+          <t>4692.9_1546_P.</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>6518.4_2914_A.</t>
+          <t>4729.8_2058_P.</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>5040.0_2971_A.</t>
+          <t>10058.8_3483_F.</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>13023.5_5156_L.</t>
+          <t>13008.2_4958_P.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>5020.4_2167_C.</t>
+          <t>7985.2_2173_P.</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>6804.1_2088_P.</t>
+          <t>5040.0_2514_C.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>6010.6_2144_A.</t>
+          <t>8200.8_2347_T.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>10031.8_2663_P.</t>
+          <t>6818.2_2036_P.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>6610.9_1738_P.</t>
+          <t>4899.2_1459_A.</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2355.5_726_S.</t>
+          <t>4700.4_1216_V.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>8367.5_4269_C.</t>
+          <t>5022.0_1862_A.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>15200.8_10718_F.</t>
+          <t>5299.8_2406_C.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>4781.2_1507_A.</t>
+          <t>7604.2_3303_P.</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>5770.8_2848_G.</t>
+          <t>10030.1_3124_M.</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>8092.0_4532_P.</t>
+          <t>7022.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>10031.8_2663_P.</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>5003.2_1389_E.</t>
+          <t>6472.0_2501_S.</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>4797.2_1541_G.</t>
+          <t>7012.1_3931_🔋.</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>5981.9_2551_P.</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>4735.2_997_S.</t>
+          <t>13023.5_5156_L.</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>773.5_238_S.</t>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>1206.7_12400_M.</t>
+          <t>6173.6_2865_M.</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>6007.4_1804_G.</t>
+          <t>7015.4_2141_T.</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>8396.0_2595_S.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>4788.2_1476_P.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>5981.9_2551_P.</t>
+          <t>16008.9_5968_S.</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>22320.3_9183_F.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>12006.1_5290_T.</t>
+          <t>3012.4_1258_P.</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>5007.1_1751_T.</t>
+          <t>1002.7_460_S.</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>4576.3_2084_S.</t>
+          <t>1012.0_375_E.</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>12342.9_3211_M.</t>
+          <t>10027.3_2906_P.</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>5000.6_1856_M.</t>
+          <t>6103.6_2241_G.</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>6011.5_2408_A.</t>
+          <t>4969.4_2146_P.</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>2504.7_703_🔋.</t>
+          <t>4028.8_1699_L.</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>3138.1_1120_S.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>6661.8_3736_P.</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>15504.3_3950_M.</t>
+          <t>5001.9_1291_V.</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>5002.9_1487_P.</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>11005.3_5159_P.</t>
+          <t>9012.4_2700_M.</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>10006.0_2772_V.</t>
+          <t>8442.5_3038_G.</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>5014.5_1497_G.</t>
+          <t>7502.4_3467_P.</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>16520.2_4844_M.</t>
+          <t>5010.3_3392_P.</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>12006.1_5290_X.</t>
+          <t>4013.7_1173_V.</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>10007.8_2668_V.</t>
+          <t>6113.5_2883_C.</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>14019.6_6253_L.</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>4932.4_1545_E.</t>
+          <t>18665.3_4638_S.</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>1152.4_938_S.</t>
+          <t>5119.6_3153_M.</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>5010.0_1872_A.</t>
+          <t>2186.2_736_G.</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>5009.1_2246_C.</t>
+          <t>10718.1_9873_S.</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>4619.4_1440_S.</t>
+          <t>5152.8_1800_G.</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>9756.3_2793_M.</t>
+          <t>5072.4_1931_S.</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>4917.5_2381_T.</t>
+          <t>5004.0_2103_C.</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>4850.9_2239_C.</t>
+          <t>3019.8_1453_F.</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>4729.8_2058_P.</t>
+          <t>1020.0_679_T.</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>5144.4_2349_P.</t>
+          <t>10020.8_2989_M.</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>9415.9_3699_G.</t>
+          <t>5021.7_1930_A.</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>7127.8_1843_G.</t>
+          <t>5040.0_2971_A.</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>5100.0_2587_A.</t>
+          <t>7090.6_3340_A.</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>4000.6_1659_S.</t>
+          <t>7593.7_2701_E.</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>5580.0_2471_A.</t>
+          <t>4974.4_1533_E.</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>9012.4_2700_M.</t>
+          <t>791.5_266_G.</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>3757.2_1716_A.</t>
+          <t>9507.9_2851_M.</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>7880.9_2433_E.</t>
+          <t>2556.5_1160_M.</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>2060.0_802_S.</t>
+          <t>960.0_1109_A.</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>6622.5_2224_E.</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>7012.1_3931_🔋.</t>
+          <t>3010.0_1424_A.</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>6903.6_2566_G.</t>
+          <t>10277.3_4318_L.</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>1380.0_562_A.</t>
+          <t>5022.5_1222_P.</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>7420.2_4318_C.</t>
+          <t>5014.5_1497_G.</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>6622.5_2224_E.</t>
+          <t>6345.4_2376_S.</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>8416.2_4091_P.</t>
+          <t>5365.6_2437_C.</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>3010.0_1289_A.</t>
+          <t>10503.6_3278_M.</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>5049.0_2240_C.</t>
+          <t>10022.1_2875_M.</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>10008.1_2966_M.</t>
+          <t>9791.4_3527_G.</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>5242.7_1657_S.</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>8481.2_2463_🔋.</t>
+          <t>1366.2_487_L.</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>6007.1_2393_M.</t>
+          <t>5235.4_1766_P.</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>13008.2_4958_P.</t>
+          <t>4972.5_2522_S.</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>7039.1_2754_S.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>8047.1_2948_G.</t>
+          <t>5000.5_1919_P.</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>10006.9_3646_F.</t>
+          <t>12013.5_4635_X.</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>7576.8_2823_P.</t>
+          <t>5033.4_1976_M.</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>5086.0_1810_G.</t>
+          <t>3597.6_2910_E.</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>5827.8_2106_S.</t>
+          <t>8092.0_4532_P.</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>11005.3_5159_P.</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>12008.4_3832_G.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>11214.0_4224_V.</t>
+          <t>10006.5_3648_X.</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>8351.7_4153_C.</t>
+          <t>4678.8_1840_A.</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>4790.7_1897_F.</t>
+          <t>1011.0_396_L.</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>5382.2_2690_M.</t>
+          <t>4613.1_1806_A.</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>5152.8_1800_G.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>657.7_273_S.</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>2064.3_708_S.</t>
+          <t>3004.6_746_V.</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>4896.8_2251_L.</t>
+          <t>2064.3_708_S.</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>6173.6_2865_M.</t>
+          <t>3798.9_1319_S.</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>5086.0_1810_G.</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>1366.2_487_L.</t>
+          <t>5904.3_2699_P.</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>8506.3_4050_C.</t>
+          <t>5770.8_2848_G.</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>5040.0_2299_A.</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>2557.8_1206_V.</t>
+          <t>5007.1_1751_T.</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>10277.3_4318_L.</t>
+          <t>10533.4_4020_F.</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>4899.2_1459_A.</t>
+          <t>1443.0_851_A.</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>1701.7_720_F.</t>
+          <t>8104.2_2652_M.</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>4974.4_1533_E.</t>
+          <t>21141.5_8155_F.</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>5001.9_1291_V.</t>
+          <t>8024.4_2933_S.</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>2510.2_1366_V.</t>
+          <t>12008.4_3832_G.</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>21114.4_6098_P.</t>
+          <t>2880.9_1210_L.</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>960.0_1109_A.</t>
+          <t>4540.8_1823_A.</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>5081.5_1647_G.</t>
+          <t>7083.1_2912_G.</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>8899.2_2910_S.</t>
+          <t>8004.6_2357_G.</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>6036.4_2875_V.</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>6006.1_2236_V.</t>
+          <t>8006.7_2244_V.</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>8006.7_2244_V.</t>
+          <t>4150.2_2042_C.</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>3580.9_1198_S.</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>16397.3_4254_S.</t>
+          <t>6011.5_2408_A.</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>8196.1_2807_T.</t>
+          <t>9415.9_3699_G.</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>21207.4_6474_V.</t>
+          <t>5827.8_2106_S.</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>20105.6_7766_F.</t>
+          <t>4917.5_2381_T.</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>5282.8_2392_C.</t>
+          <t>7025.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>6035.0_2481_P.</t>
+          <t>10013.4_3721_G.</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>4153.2_3559_P.</t>
+          <t>21207.4_6474_V.</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>419.0_180_P.</t>
+          <t>10003.7_2721_V.</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>6620.4_2477_P.</t>
+          <t>3089.9_1508_C.</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>22002.4_8469_M.</t>
+          <t>1885.0_952_L.</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>2186.2_736_G.</t>
+          <t>401.2_179_S.</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>10022.1_2875_M.</t>
+          <t>8132.9_2716_S.</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>1002.7_460_S.</t>
+          <t>6005.3_2226_A.</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>3059.2_956_T.</t>
+          <t>12002.7_4232_S.</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>37036.6_17889_F.</t>
+          <t>4781.2_1507_A.</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>4786.5_1898_P.</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>7001.2_3357_M.</t>
+          <t>6004.0_2559_P.</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>1083.2_390_M.</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>4921.0_2491_A.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>8442.5_3038_G.</t>
+          <t>53755.6_36604_F.</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>5005.8_1527_S.</t>
+          <t>4153.2_3559_P.</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>1432.9_3942_M.</t>
+          <t>2783.5_952_S.</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>1034.3_279_M.</t>
+          <t>10348.3_2647_S.</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>18102.7_4949_M.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>6007.1_3172_F.</t>
+          <t>5100.0_2587_A.</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>2047.9_924_L.</t>
+          <t>5049.0_2240_C.</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>7186.5_2708_S.</t>
+          <t>8187.1_2322_M.</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>6047.4_2816_T.</t>
+          <t>7874.8_2223_M.</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>2629.2_1249_M.</t>
+          <t>18102.7_4949_M.</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>8506.3_4050_C.</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>16008.9_5968_S.</t>
+          <t>2060.0_802_S.</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>4786.5_1898_P.</t>
+          <t>5029.4_1585_P.</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>8132.9_2716_S.</t>
+          <t>10007.8_2733_V.</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>9639.7_4763_P.</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>8200.5_2738_M.</t>
+          <t>6010.6_2144_A.</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>5025.8_1214_P.</t>
+          <t>8047.1_2948_G.</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>5242.7_1657_S.</t>
+          <t>5064.2_1636_G.</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>5235.4_1766_P.</t>
+          <t>5025.8_1214_P.</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>9007.1_3080_P.</t>
+          <t>6620.4_2477_P.</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>8187.1_2322_M.</t>
+          <t>10006.9_3646_F.</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>1114.9_359_S.</t>
+          <t>7003.6_2437_P.</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>6818.2_2036_P.</t>
+          <t>21250.2_9506_P.</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>5522.8_2716_V.</t>
+          <t>1034.3_279_M.</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>18107.4_4577_M.</t>
+          <t>3005.2_1040_L.</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>5451.1_1905_T.</t>
+          <t>8724.4_2500_M.</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>5010.3_3392_P.</t>
+          <t>37036.6_17889_F.</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>5040.0_2514_C.</t>
+          <t>10012.3_3067_S.</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>9005.3_4344_A.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>5581.6_3687_P.</t>
+          <t>5296.8_1844_P.</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>5072.4_1931_S.</t>
+          <t>14119.3_5262_S.</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>26010.2_9812_F.</t>
+          <t>15010.8_6619_G.</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>5006.8_1080_M.</t>
+          <t>15186.5_3866_S.</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>5014.8_2009_A.</t>
+          <t>7880.9_2433_E.</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>2735.8_959_S.</t>
+          <t>21124.1_8011_F.</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>4150.2_2042_C.</t>
+          <t>5028.5_4433_S.</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>4821.0_1857_P.</t>
+          <t>5005.8_1527_S.</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>15194.4_3911_S.</t>
+          <t>5013.9_1673_A.</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>10016.9_3028_M.</t>
+          <t>6804.1_2088_P.</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>3010.0_1424_A.</t>
+          <t>2504.7_703_🔋.</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>4532.9_2322_L.</t>
+          <t>26010.2_9812_F.</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>10006.5_3648_X.</t>
+          <t>4688.1_2291_C.</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>21124.1_8011_F.</t>
+          <t>4763.8_1720_P.</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>10010.0_2910_V.</t>
+          <t>4735.2_997_S.</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>10012.3_3067_S.</t>
+          <t>8618.0_2344_P.</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>401.2_179_S.</t>
+          <t>12524.7_3259_S.</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>12521.4_4814_M.</t>
+          <t>8253.0_2972_🔋.</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>25020.8_7832_V.</t>
+          <t>5014.8_2009_A.</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>5010.0_1872_A.</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>7985.2_2173_P.</t>
+          <t>5007.4_1601_A.</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>8013.1_2082_P.</t>
+          <t>4814.5_1705_🔋.</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>4850.9_2239_C.</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>10533.4_4020_F.</t>
+          <t>6006.6_2009_P.</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>6661.8_3736_P.</t>
+          <t>3412.3_1947_C.</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>8008.0_2930_A.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>21250.2_9506_P.</t>
+          <t>2629.2_1249_V.</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>7145.5_2856_E.</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>1012.0_375_E.</t>
+          <t>17003.0_7696_P.</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>7312.2_2446_G.</t>
+          <t>5003.2_1389_E.</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>7114.0_2850_S.</t>
+          <t>10003.1_5062_V.</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>2629.2_1249_V.</t>
+          <t>8351.7_4153_C.</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>5004.9_1790_A.</t>
+          <t>5064.3_1832_F.</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>10012.1_3139_S.</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>10003.7_2721_V.</t>
+          <t>2004.9_754_S.</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>9029.6_4595_P.</t>
+          <t>8481.2_2463_🔋.</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>1443.0_851_A.</t>
+          <t>2510.2_1366_V.</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>4700.4_1216_V.</t>
+          <t>4731.9_1407_T.</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>7024.3_3266_L.</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>22008.4_8412_F.</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>5144.4_2349_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>16520.2_4844_M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>6137.8_2406_L.</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>6833.7_2100_G.</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>5008.2_1646_A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>15194.4_3911_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>10010.0_2910_V.</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>10174.3_3680_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>7419.2_3469_F.</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>14004.5_5478_M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>208.3_85_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>15223.0_6245_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>12006.1_5290_T.</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>3138.1_1120_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>9007.1_3080_P.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_500km_2026.xlsx
+++ b/Ranking_CNB_500km_2026.xlsx
@@ -488,12 +488,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>322,0 km</t>
+          <t>332,0 km</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.196 m</t>
+          <t>3.285 m</t>
         </is>
       </c>
     </row>
@@ -505,12 +505,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>275,9 km</t>
+          <t>288,9 km</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.343 m</t>
+          <t>2.378 m</t>
         </is>
       </c>
     </row>
@@ -522,12 +522,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>254,7 km</t>
+          <t>259,8 km</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.991 m</t>
+          <t>3.062 m</t>
         </is>
       </c>
     </row>
@@ -539,12 +539,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>235,2 km</t>
+          <t>242,2 km</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.150 m</t>
+          <t>2.219 m</t>
         </is>
       </c>
     </row>
@@ -573,12 +573,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>211,8 km</t>
+          <t>218,0 km</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.380 m</t>
+          <t>2.417 m</t>
         </is>
       </c>
     </row>
@@ -590,12 +590,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>197,2 km</t>
+          <t>200,8 km</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.363 m</t>
+          <t>1.370 m</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>168,1 km</t>
+          <t>175,3 km</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -687,7 +687,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Edivânia M.</t>
+          <t>Naiane C.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -697,41 +697,41 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.486 m</t>
+          <t>1.285 m</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Duda X.</t>
+          <t>Edivânia M.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>136,6 km</t>
+          <t>137,0 km</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.627 m</t>
+          <t>1.486 m</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Naiane C.</t>
+          <t>Duda X.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>132,0 km</t>
+          <t>136,6 km</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.234 m</t>
+          <t>1.627 m</t>
         </is>
       </c>
     </row>
@@ -806,34 +806,34 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Pierre P.</t>
+          <t>Denis G.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>76,5 km</t>
+          <t>83,6 km</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>829 m</t>
+          <t>690 m</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Denis G.</t>
+          <t>Pierre P.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>73,6 km</t>
+          <t>76,5 km</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>608 m</t>
+          <t>829 m</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A435"/>
+  <dimension ref="A1:A448"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1031,826 +1031,826 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10106.6_2889_P.</t>
+          <t>6004.0_2559_P.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>8978.9_3078_G.</t>
+          <t>5051.4_1993_M.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>6016.7_2122_M.</t>
+          <t>4937.4_1783_A.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1629.5_671_F.</t>
+          <t>9415.9_3699_G.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5282.8_2392_C.</t>
+          <t>4830.1_2569_C.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>7127.8_1843_G.</t>
+          <t>791.5_266_G.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>14014.7_3537_S.</t>
+          <t>10027.3_2906_P.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>5040.0_2514_C.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>21114.4_6098_P.</t>
+          <t>7145.5_2856_E.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5004.1_1610_M.</t>
+          <t>20105.6_7766_F.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5004.5_1548_A.</t>
+          <t>4786.5_1898_P.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>7186.5_2708_S.</t>
+          <t>3412.3_1947_C.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5043.1_2254_C.</t>
+          <t>8367.5_4269_C.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5580.0_2471_A.</t>
+          <t>1629.5_671_F.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>6006.1_2236_V.</t>
+          <t>5010.3_1888_G.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>6620.4_2477_P.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>5005.9_1755_X.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5724.1_3694_S.</t>
+          <t>7230.5_2794_V.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>22002.4_8469_M.</t>
+          <t>8200.8_2347_T.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2036.1_839_S.</t>
+          <t>5287.4_1835_V.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10016.9_3028_M.</t>
+          <t>14019.6_6253_L.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>6903.6_2566_G.</t>
+          <t>3012.4_1258_P.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10025.6_4018_G.</t>
+          <t>5299.8_2406_C.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>15057.9_8625_F.</t>
+          <t>1012.0_375_E.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>7516.9_3203_A.</t>
+          <t>8047.1_2948_G.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>123.0_5992_A.</t>
+          <t>9012.4_2700_M.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2355.5_726_S.</t>
+          <t>10503.6_3278_M.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5020.4_2167_C.</t>
+          <t>9007.1_3080_P.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>10030.1_3124_M.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>12342.9_3211_M.</t>
+          <t>21442.0_7959_F.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>531.0_343_A.</t>
+          <t>401.2_179_S.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>7569.4_2477_V.</t>
+          <t>7516.9_3203_A.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5287.4_1835_V.</t>
+          <t>5027.8_1361_P.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>7992.7_2506_F.</t>
+          <t>12006.1_5290_X.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>6038.2_2121_P.</t>
+          <t>8008.0_2930_A.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>4788.2_1476_P.</t>
+          <t>6622.5_2224_E.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2000.0_724_A.</t>
+          <t>2185.4_792_S.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10006.9_3646_X.</t>
+          <t>2175.4_712_S.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>4896.8_2251_L.</t>
+          <t>5422.4_1911_G.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>12326.4_4833_S.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>4891.7_1690_F.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>14009.0_5498_A.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>1884.9_866_S.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>7230.5_2794_V.</t>
+          <t>7022.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>5010.3_1888_G.</t>
+          <t>5904.3_2699_P.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>6779.9_2003_E.</t>
+          <t>5451.1_1905_T.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>4000.6_1659_S.</t>
+          <t>2629.2_1249_V.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3757.2_1716_A.</t>
+          <t>5008.2_1646_A.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>9006.5_3085_X.</t>
+          <t>5049.0_2240_C.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>6012.6_2984_P.</t>
+          <t>1467.9_482_S.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>10001.9_4466_P.</t>
+          <t>10007.4_3588_V.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>5085.1_1840_G.</t>
+          <t>17012.6_5869_T.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>5081.5_1647_G.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>3010.0_1289_A.</t>
+          <t>2504.7_703_🔋.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>10643.3_3263_S.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>4797.2_1541_G.</t>
+          <t>5014.5_1497_G.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>4214.8_2018_A.</t>
+          <t>8132.9_2716_S.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>5256.5_1535_S.</t>
+          <t>5296.8_1844_P.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>10011.5_3070_S.</t>
+          <t>7419.2_3469_F.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>21106.2_7925_P.</t>
+          <t>4899.2_1459_A.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>123.0_5992_A.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>9756.3_2793_M.</t>
+          <t>6028.3_2419_L.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>3059.2_956_T.</t>
+          <t>3958.9_1777_P.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>7420.2_4318_C.</t>
+          <t>5014.8_2009_A.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>8367.5_4269_C.</t>
+          <t>8416.2_4091_P.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>7312.2_2446_G.</t>
+          <t>3798.9_1319_S.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>6012.3_2200_M.</t>
+          <t>10005.2_3808_G.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>5522.8_2716_V.</t>
+          <t>3006.0_1286_M.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>6536.2_2241_P.</t>
+          <t>5004.1_1610_M.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>14117.6_3844_M.</t>
+          <t>8253.0_2972_🔋.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>6600.2_1915_M.</t>
+          <t>4017.3_1883_C.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1701.7_720_F.</t>
+          <t>9006.5_3085_X.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>8120.9_2737_G.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>4966.0_1709_G.</t>
+          <t>15223.0_6245_P.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>4932.4_1545_E.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>15016.9_6221_G.</t>
+          <t>8481.2_2463_🔋.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>5006.8_1080_M.</t>
+          <t>6833.7_2100_G.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>15194.4_3911_S.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>5869.6_2613_P.</t>
+          <t>10002.4_5136_P.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>5004.9_1790_A.</t>
+          <t>16008.9_5968_S.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>25020.8_7832_V.</t>
+          <t>22008.4_8412_F.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>3958.9_1777_P.</t>
+          <t>8092.0_4532_P.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>4678.8_1840_A.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>9555.5_5689_S.</t>
+          <t>7025.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>4821.0_1857_P.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>4177.9_1557_T.</t>
+          <t>17003.0_7696_P.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>5163.5_1775_V.</t>
+          <t>11214.0_4224_V.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>6011.8_1873_M.</t>
+          <t>2629.2_1249_M.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>5126.8_1941_G.</t>
+          <t>4921.0_2491_A.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>10030.0_3041_G.</t>
+          <t>5021.7_1930_A.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>16397.3_4254_S.</t>
+          <t>5014.3_1731_F.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>5008.0_2402_P.</t>
+          <t>3010.0_1424_A.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>5581.6_3687_P.</t>
+          <t>6518.4_2914_A.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>5451.1_1905_T.</t>
+          <t>8218.3_2327_P.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>12006.1_5290_X.</t>
+          <t>7012.1_3931_🔋.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>6007.1_2393_M.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>9507.9_2851_M.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>4937.4_1783_A.</t>
+          <t>4540.8_1823_A.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2735.8_959_S.</t>
+          <t>7992.7_2506_F.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>4921.0_2491_A.</t>
+          <t>5188.5_1799_S.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>10007.4_3588_V.</t>
+          <t>5043.1_2254_C.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>9209.1_3141_E.</t>
+          <t>2064.3_708_S.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>10007.8_2668_V.</t>
+          <t>37036.6_17889_F.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>6084.1_2156_V.</t>
+          <t>5017.7_1147_M.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1206.7_12400_M.</t>
+          <t>6007.1_2393_M.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>10002.4_5136_P.</t>
+          <t>15186.5_3866_S.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>419.0_180_P.</t>
+          <t>8506.3_4050_C.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>10001.3_4206_G.</t>
+          <t>21250.2_9506_P.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>7001.2_3357_M.</t>
+          <t>26010.2_9812_F.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>4576.3_2084_S.</t>
+          <t>5144.4_2349_P.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>7127.8_1843_G.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>4101.5_1485_V.</t>
+          <t>10348.3_2647_S.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>7006.7_5717_S.</t>
+          <t>6003.3_2987_M.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>4619.4_1440_S.</t>
+          <t>5007.1_1751_T.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>773.5_238_S.</t>
+          <t>4791.5_1524_E.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>10006.0_2772_V.</t>
+          <t>9555.5_5689_S.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>7598.7_2799_S.</t>
         </is>
       </c>
     </row>
@@ -1864,469 +1864,469 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>8196.1_2807_T.</t>
+          <t>7243.5_2118_G.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>3010.0_1685_A.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>5235.4_1766_P.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>14009.0_5498_A.</t>
+          <t>12013.5_4635_X.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>18107.4_4577_M.</t>
+          <t>1114.9_359_S.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>6951.4_2856_S.</t>
+          <t>18102.7_4949_M.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>7114.0_2850_S.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>4972.5_2522_S.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>2556.5_1160_M.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>6047.4_2816_T.</t>
+          <t>1002.7_460_S.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>5000.2_1932_E.</t>
+          <t>4788.2_1476_P.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>8724.4_2500_M.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>5017.7_1147_M.</t>
+          <t>5001.9_1291_V.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>12545.4_3039_S.</t>
+          <t>3029.5_1536_G.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>5238.0_2781_F.</t>
+          <t>9562.8_3145_M.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>8008.0_2930_A.</t>
+          <t>10021.0_4009_G.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2011.7_731_S.</t>
+          <t>6012.3_2200_M.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>8013.1_2082_P.</t>
+          <t>2557.8_1206_V.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>10003.8_3195_S.</t>
+          <t>4729.8_2058_P.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>9020.0_2605_M.</t>
+          <t>8442.5_3038_G.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2002.2_938_P.</t>
+          <t>5064.3_1832_F.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>1380.0_562_A.</t>
+          <t>5033.4_1976_M.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1432.9_3942_M.</t>
+          <t>5010.0_1872_A.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>9029.6_4595_P.</t>
+          <t>4619.4_1440_S.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>10005.2_3808_G.</t>
+          <t>14004.5_5478_M.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>5382.2_2690_M.</t>
+          <t>10006.0_2772_V.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>4791.5_1524_E.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>611.2_221_M.</t>
+          <t>6241.6_2497_P.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>5422.4_1911_G.</t>
+          <t>12545.4_3039_S.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>56121.5_25636_F.</t>
+          <t>3059.2_956_T.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2557.8_1206_V.</t>
+          <t>4078.1_1810_A.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>10030.5_4765_C.</t>
+          <t>16520.2_4844_M.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>8416.2_4091_P.</t>
+          <t>10003.8_3195_S.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>4532.9_2322_L.</t>
+          <t>9013.7_2337_M.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2558.7_905_S.</t>
+          <t>553.2_224_S.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>5051.4_1993_M.</t>
+          <t>6113.5_2883_C.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>9005.3_4344_A.</t>
+          <t>3004.6_746_V.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>4830.1_2569_C.</t>
+          <t>10643.3_3263_S.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>15200.8_10718_F.</t>
+          <t>6006.6_2009_P.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>7598.7_2799_S.</t>
+          <t>18516.8_6699_G.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>7576.8_2823_P.</t>
+          <t>5010.3_3392_P.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>4864.8_1353_E.</t>
+          <t>4077.1_1454_S.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>5011.9_1594_P.</t>
+          <t>1152.4_938_S.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>6518.4_2914_A.</t>
+          <t>6818.2_2036_P.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>12022.7_5417_L.</t>
+          <t>4028.8_1699_L.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>13344.7_5916_G.</t>
+          <t>13023.5_5156_L.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>5008.1_1825_M.</t>
+          <t>7604.2_3303_P.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>6345.4_2376_S.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>5020.6_1328_M.</t>
+          <t>15637.2_5789_G.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>3029.5_1536_G.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>5224.2_2340_C.</t>
+          <t>8351.7_4153_C.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>5621.6_2375_P.</t>
+          <t>10533.4_4020_F.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>3735.9_1928_V.</t>
+          <t>5003.2_1389_E.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>1027.7_364_S.</t>
+          <t>2735.8_959_S.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>3005.2_1040_L.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1152.4_938_S.</t>
+          <t>2761.5_1068_S.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>11214.0_4224_V.</t>
+          <t>15010.8_6619_G.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>15637.2_5789_G.</t>
+          <t>4532.9_2322_L.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>5027.8_1361_P.</t>
+          <t>8618.0_2344_P.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>20105.6_7766_F.</t>
+          <t>7985.2_2173_P.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>7012.2_4093_P.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>3010.0_1685_A.</t>
+          <t>12006.1_5290_T.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>4017.3_1883_C.</t>
+          <t>15200.8_10718_F.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>6103.6_2241_G.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>6035.0_2481_P.</t>
+          <t>2783.5_952_S.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>5005.9_1755_X.</t>
+          <t>3580.9_1198_S.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>18516.8_6699_G.</t>
+          <t>5086.0_1810_G.</t>
         </is>
       </c>
     </row>
@@ -2340,1729 +2340,1820 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>6053.8_2077_M.</t>
+          <t>25020.8_7832_V.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>6003.3_2987_M.</t>
+          <t>8004.6_2357_G.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>6007.4_1804_G.</t>
+          <t>5004.5_1548_A.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>4078.1_1810_A.</t>
+          <t>5020.6_1328_M.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>6610.9_1738_P.</t>
+          <t>8899.2_2910_S.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>3026.1_1490_A.</t>
+          <t>13008.2_4958_P.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>10003.1_5062_V.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>3023.2_962_S.</t>
+          <t>14014.7_3537_S.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>8899.2_2910_S.</t>
+          <t>2558.7_905_S.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2629.2_1249_M.</t>
+          <t>16397.3_4254_S.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>4821.0_1857_P.</t>
+          <t>56121.5_25636_F.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>4790.7_1897_F.</t>
+          <t>6046.5_3239_S.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>8218.3_2327_P.</t>
+          <t>6472.0_2501_S.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>15504.3_3950_M.</t>
+          <t>5005.4_2618_L.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>8396.0_2595_S.</t>
+          <t>7001.2_3357_M.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>553.2_224_S.</t>
+          <t>7003.6_2437_P.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2185.4_792_S.</t>
+          <t>5522.8_2716_V.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>14009.7_4401_V.</t>
+          <t>1443.0_851_A.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>5000.6_1856_M.</t>
+          <t>10718.1_9873_S.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>1114.9_359_S.</t>
+          <t>4153.2_3559_P.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>8200.5_2738_M.</t>
+          <t>1027.7_364_S.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>7039.1_2754_S.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2047.9_924_L.</t>
+          <t>9791.4_3527_G.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>2002.2_938_P.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>3006.0_1286_M.</t>
+          <t>1011.0_396_L.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>6007.1_3172_F.</t>
+          <t>8013.1_2082_P.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>5005.4_2618_L.</t>
+          <t>7006.7_5717_S.</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>5301.0_2064_F.</t>
+          <t>10012.1_3139_S.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>6028.3_2419_L.</t>
+          <t>1885.0_952_L.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>5009.1_2246_C.</t>
+          <t>4613.1_1806_A.</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>4692.9_1546_P.</t>
+          <t>9005.3_4344_A.</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>4729.8_2058_P.</t>
+          <t>4790.7_1897_F.</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>12342.9_3211_M.</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>13008.2_4958_P.</t>
+          <t>4896.8_2251_L.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>7985.2_2173_P.</t>
+          <t>10016.9_3028_M.</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>5040.0_2514_C.</t>
+          <t>5064.2_1636_G.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>8200.8_2347_T.</t>
+          <t>5100.0_2587_A.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>6818.2_2036_P.</t>
+          <t>7114.0_2850_S.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>4899.2_1459_A.</t>
+          <t>10277.3_4318_L.</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>4700.4_1216_V.</t>
+          <t>4731.9_1407_T.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>5022.0_1862_A.</t>
+          <t>5007.4_1601_A.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>5299.8_2406_C.</t>
+          <t>2051.8_860_S.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>7604.2_3303_P.</t>
+          <t>21124.1_8011_F.</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>10030.1_3124_M.</t>
+          <t>7090.6_3340_A.</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>7022.4_3008_L.</t>
+          <t>3551.6_1303_S.</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>10031.8_2663_P.</t>
+          <t>12008.4_3832_G.</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>5580.0_2471_A.</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>7012.1_3931_🔋.</t>
+          <t>10007.8_2733_V.</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>5981.9_2551_P.</t>
+          <t>5119.6_3153_M.</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>13023.5_5156_L.</t>
+          <t>10011.5_3070_S.</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>9756.3_2793_M.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>6173.6_2865_M.</t>
+          <t>6035.0_2481_P.</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>6661.8_3736_P.</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>2036.1_839_S.</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>21207.4_6474_V.</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>16008.9_5968_S.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>22320.3_9183_F.</t>
+          <t>6006.1_2236_V.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>3012.4_1258_P.</t>
+          <t>7576.8_2823_P.</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>1002.7_460_S.</t>
+          <t>6804.1_2088_P.</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>1012.0_375_E.</t>
+          <t>10006.9_3646_X.</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>10027.3_2906_P.</t>
+          <t>1380.0_562_A.</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>6103.6_2241_G.</t>
+          <t>8006.7_2244_V.</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>4969.4_2146_P.</t>
+          <t>5020.4_2167_C.</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>4028.8_1699_L.</t>
+          <t>15057.9_8625_F.</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>600.2_261_L.</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>6661.8_3736_P.</t>
+          <t>4932.4_1545_E.</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>5001.9_1291_V.</t>
+          <t>12022.7_5417_L.</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>5002.9_1487_P.</t>
+          <t>2047.9_924_L.</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>9012.4_2700_M.</t>
+          <t>8978.9_3078_G.</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>8442.5_3038_G.</t>
+          <t>531.0_343_A.</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>7502.4_3467_P.</t>
+          <t>6010.6_2144_A.</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>5010.3_3392_P.</t>
+          <t>611.2_221_M.</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>4013.7_1173_V.</t>
+          <t>8104.2_2652_M.</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>6113.5_2883_C.</t>
+          <t>5036.1_2201_C.</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>14019.6_6253_L.</t>
+          <t>960.0_1109_A.</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>18665.3_4638_S.</t>
+          <t>7015.4_2141_T.</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>11005.3_5159_P.</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>2186.2_736_G.</t>
+          <t>10005.5_2697_V.</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>10718.1_9873_S.</t>
+          <t>3089.9_1508_C.</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>5152.8_1800_G.</t>
+          <t>5000.5_1919_P.</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>5072.4_1931_S.</t>
+          <t>9209.1_3141_E.</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>5004.0_2103_C.</t>
+          <t>10030.5_4765_C.</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>1020.0_679_T.</t>
+          <t>5004.0_2103_C.</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>10020.8_2989_M.</t>
+          <t>7420.2_4318_C.</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>5021.7_1930_A.</t>
+          <t>9029.6_4595_P.</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>5040.0_2971_A.</t>
+          <t>6610.9_1738_P.</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>7090.6_3340_A.</t>
+          <t>8396.0_2595_S.</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>7593.7_2701_E.</t>
+          <t>2011.7_731_S.</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>4974.4_1533_E.</t>
+          <t>12524.7_3259_S.</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>791.5_266_G.</t>
+          <t>6173.6_2865_M.</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>9507.9_2851_M.</t>
+          <t>3039.1_1013_L.</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>2556.5_1160_M.</t>
+          <t>22320.3_9183_F.</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>960.0_1109_A.</t>
+          <t>6012.6_2984_P.</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>6622.5_2224_E.</t>
+          <t>2004.9_754_S.</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>3010.0_1424_A.</t>
+          <t>2355.5_726_S.</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>10277.3_4318_L.</t>
+          <t>6903.6_2566_G.</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>5022.5_1222_P.</t>
+          <t>10030.0_3041_G.</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>5014.5_1497_G.</t>
+          <t>3597.6_2910_E.</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>6345.4_2376_S.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>5365.6_2437_C.</t>
+          <t>5028.5_4433_S.</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>10503.6_3278_M.</t>
+          <t>6007.1_3172_F.</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>10022.1_2875_M.</t>
+          <t>18107.4_4577_M.</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>9791.4_3527_G.</t>
+          <t>5282.8_2392_C.</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>5242.7_1657_S.</t>
+          <t>8024.4_2933_S.</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>1366.2_487_L.</t>
+          <t>5827.8_2106_S.</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>5235.4_1766_P.</t>
+          <t>8187.1_2322_M.</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>4972.5_2522_S.</t>
+          <t>4735.2_997_S.</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>10008.1_2966_M.</t>
+          <t>3138.1_1120_S.</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>5000.5_1919_P.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>12013.5_4635_X.</t>
+          <t>3735.9_1928_V.</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>5033.4_1976_M.</t>
+          <t>5163.5_1775_V.</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>3597.6_2910_E.</t>
+          <t>2060.0_802_S.</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>8092.0_4532_P.</t>
+          <t>14119.3_5262_S.</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>11005.3_5159_P.</t>
+          <t>10006.9_3646_F.</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>3010.0_1289_A.</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>10006.5_3648_X.</t>
+          <t>10001.9_4466_P.</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>4678.8_1840_A.</t>
+          <t>5621.6_2375_P.</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>1020.0_679_T.</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>4613.1_1806_A.</t>
+          <t>2000.0_724_A.</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>6600.2_1915_M.</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>657.7_273_S.</t>
+          <t>5022.0_1862_A.</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>3004.6_746_V.</t>
+          <t>6779.9_2003_E.</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>2064.3_708_S.</t>
+          <t>4101.5_1485_V.</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>3798.9_1319_S.</t>
+          <t>5011.9_1594_P.</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>5086.0_1810_G.</t>
+          <t>5000.2_1932_E.</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>5904.3_2699_P.</t>
+          <t>21106.2_7925_P.</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>5770.8_2848_G.</t>
+          <t>5029.4_1585_P.</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>5040.0_2299_A.</t>
+          <t>7039.1_2754_S.</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>5007.1_1751_T.</t>
+          <t>21141.5_8155_F.</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>10533.4_4020_F.</t>
+          <t>6951.4_2856_S.</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>1443.0_851_A.</t>
+          <t>3019.8_1453_F.</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>4969.4_2146_P.</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>21141.5_8155_F.</t>
+          <t>7312.2_2446_G.</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>8024.4_2933_S.</t>
+          <t>12006.9_5463_P.</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>12008.4_3832_G.</t>
+          <t>10006.5_3648_X.</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>2880.9_1210_L.</t>
+          <t>4688.1_2291_C.</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>4540.8_1823_A.</t>
+          <t>5256.5_1535_S.</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>7083.1_2912_G.</t>
+          <t>15016.9_6221_G.</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>8004.6_2357_G.</t>
+          <t>22002.4_8469_M.</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>6036.4_2875_V.</t>
+          <t>4692.9_1546_P.</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>8006.7_2244_V.</t>
+          <t>9020.0_2605_M.</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>4150.2_2042_C.</t>
+          <t>657.7_273_S.</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>6005.3_2226_A.</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>6011.5_2408_A.</t>
+          <t>7880.9_2433_E.</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>9415.9_3699_G.</t>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>5827.8_2106_S.</t>
+          <t>1034.3_279_M.</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>4917.5_2381_T.</t>
+          <t>773.5_238_S.</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>7025.4_3008_L.</t>
+          <t>5013.9_1673_A.</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>10013.4_3721_G.</t>
+          <t>5869.6_2613_P.</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>21207.4_6474_V.</t>
+          <t>5002.9_1487_P.</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>10003.7_2721_V.</t>
+          <t>6036.4_2875_V.</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>3089.9_1508_C.</t>
+          <t>12002.7_4232_S.</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>1885.0_952_L.</t>
+          <t>6137.8_2406_L.</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>401.2_179_S.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>8132.9_2716_S.</t>
+          <t>5022.5_1222_P.</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>6005.3_2226_A.</t>
+          <t>10174.3_3680_S.</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>12002.7_4232_S.</t>
+          <t>6011.5_2408_A.</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>4781.2_1507_A.</t>
+          <t>5072.4_1931_S.</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>4786.5_1898_P.</t>
+          <t>4850.9_2239_C.</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>6004.0_2559_P.</t>
+          <t>8196.1_2807_T.</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>1083.2_390_M.</t>
+          <t>3023.2_962_S.</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>12521.4_4814_M.</t>
+          <t>7874.8_2223_M.</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>53755.6_36604_F.</t>
+          <t>5981.9_2551_P.</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>4153.2_3559_P.</t>
+          <t>4013.7_1173_V.</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>2783.5_952_S.</t>
+          <t>5724.1_3694_S.</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>10348.3_2647_S.</t>
+          <t>10020.8_2989_M.</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>10022.1_2875_M.</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>5100.0_2587_A.</t>
+          <t>1083.2_390_M.</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>5049.0_2240_C.</t>
+          <t>6012.6_2984_F.</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>8187.1_2322_M.</t>
+          <t>3757.2_1716_A.</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>7874.8_2223_M.</t>
+          <t>3614.8_970_🔋.</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>18102.7_4949_M.</t>
+          <t>10062.5_2886_M.</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>8506.3_4050_C.</t>
+          <t>14117.6_3844_M.</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>2060.0_802_S.</t>
+          <t>5025.8_1214_P.</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>5029.4_1585_P.</t>
+          <t>10025.6_4018_G.</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>10007.8_2733_V.</t>
+          <t>10003.7_2721_V.</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>9639.7_4763_P.</t>
+          <t>5040.0_2299_A.</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>6010.6_2144_A.</t>
+          <t>53755.6_36604_F.</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>8047.1_2948_G.</t>
+          <t>5085.1_1840_G.</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>5064.2_1636_G.</t>
+          <t>5382.2_2690_M.</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>5025.8_1214_P.</t>
+          <t>5139.2_2082_G.</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>6620.4_2477_P.</t>
+          <t>7502.4_3467_P.</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>10006.9_3646_F.</t>
+          <t>7569.4_2477_V.</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>7003.6_2437_P.</t>
+          <t>2510.2_1366_V.</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>21250.2_9506_P.</t>
+          <t>6016.7_2122_M.</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>1034.3_279_M.</t>
+          <t>9639.7_4763_P.</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>1206.7_12400_M.</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>8724.4_2500_M.</t>
+          <t>6011.8_1873_M.</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>37036.6_17889_F.</t>
+          <t>5040.0_2971_A.</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>10012.3_3067_S.</t>
+          <t>7024.3_3266_L.</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>21114.4_6098_P.</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>5296.8_1844_P.</t>
+          <t>4763.8_1720_P.</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>14119.3_5262_S.</t>
+          <t>1701.7_720_F.</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>15010.8_6619_G.</t>
+          <t>8200.5_2738_M.</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>15186.5_3866_S.</t>
+          <t>2880.9_1210_L.</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>7880.9_2433_E.</t>
+          <t>10106.6_2889_P.</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>21124.1_8011_F.</t>
+          <t>2186.2_736_G.</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>5028.5_4433_S.</t>
+          <t>4797.2_1541_G.</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>5005.8_1527_S.</t>
+          <t>10010.0_2910_V.</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>5013.9_1673_A.</t>
+          <t>6007.4_1804_G.</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>6804.1_2088_P.</t>
+          <t>5242.7_1657_S.</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>2504.7_703_🔋.</t>
+          <t>6047.4_2816_T.</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>26010.2_9812_F.</t>
+          <t>5000.6_1856_M.</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>4688.1_2291_C.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>15504.3_3950_M.</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>4735.2_997_S.</t>
+          <t>5581.6_3687_P.</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>8618.0_2344_P.</t>
+          <t>4177.9_1557_T.</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>12524.7_3259_S.</t>
+          <t>4000.6_1659_S.</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>4705.5_1241_G.</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>5014.8_2009_A.</t>
+          <t>10012.3_3067_S.</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>5010.0_1872_A.</t>
+          <t>10007.8_2668_V.</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>5007.4_1601_A.</t>
+          <t>4966.0_1709_G.</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>1432.9_3942_M.</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>4850.9_2239_C.</t>
+          <t>4974.4_1533_E.</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>6006.6_2009_P.</t>
+          <t>7083.1_2912_G.</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>3412.3_1947_C.</t>
+          <t>10031.8_2663_P.</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>6084.1_2156_V.</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>2629.2_1249_V.</t>
+          <t>5126.8_1941_G.</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>7145.5_2856_E.</t>
+          <t>6038.2_2121_P.</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>17003.0_7696_P.</t>
+          <t>1366.2_487_L.</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>5003.2_1389_E.</t>
+          <t>4768.0_1875_L.</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>10003.1_5062_V.</t>
+          <t>4864.8_1353_E.</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>8351.7_4153_C.</t>
+          <t>208.3_85_P.</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>5064.3_1832_F.</t>
+          <t>5005.8_1527_S.</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>10012.1_3139_S.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>2004.9_754_S.</t>
+          <t>4917.5_2381_T.</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>8481.2_2463_🔋.</t>
+          <t>5770.8_2848_G.</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>2510.2_1366_V.</t>
+          <t>5009.1_2246_C.</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>5006.8_1080_M.</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>7024.3_3266_L.</t>
+          <t>4700.4_1216_V.</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>22008.4_8412_F.</t>
+          <t>4150.2_2042_C.</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>5144.4_2349_P.</t>
+          <t>2305.1_940_S.</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>16520.2_4844_M.</t>
+          <t>419.0_180_P.</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>6053.8_2077_M.</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>6833.7_2100_G.</t>
+          <t>5238.0_2781_F.</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>5008.2_1646_A.</t>
+          <t>4814.5_1705_🔋.</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>15194.4_3911_S.</t>
+          <t>18665.3_4638_S.</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>10010.0_2910_V.</t>
+          <t>7186.5_2708_S.</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>10106.6_3354_M.</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>7419.2_3469_F.</t>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>14004.5_5478_M.</t>
+          <t>5081.5_1647_G.</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>4781.2_1507_A.</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>15223.0_6245_P.</t>
+          <t>5152.8_1800_G.</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>12006.1_5290_T.</t>
+          <t>5301.0_2064_F.</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>3138.1_1120_S.</t>
+          <t>14009.7_4401_V.</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>9007.1_3080_P.</t>
+          <t>7593.7_2701_E.</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>5008.0_2402_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>10058.8_3483_F.</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>5365.6_2437_C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>4576.3_2084_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>13344.7_5916_G.</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>4214.8_2018_A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>10013.4_3721_G.</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>5004.9_1790_A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>5224.2_2340_C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>6536.2_2241_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>3026.1_1490_A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>5008.1_1825_M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>10001.3_4206_G.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_500km_2026.xlsx
+++ b/Ranking_CNB_500km_2026.xlsx
@@ -743,12 +743,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>124,1 km</t>
+          <t>135,6 km</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.219 m</t>
+          <t>1.318 m</t>
         </is>
       </c>
     </row>
@@ -760,12 +760,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>111,3 km</t>
+          <t>121,3 km</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>866 m</t>
+          <t>966 m</t>
         </is>
       </c>
     </row>
@@ -874,51 +874,51 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Renato C.</t>
+          <t>Eduardo T.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>36,2 km</t>
+          <t>39,1 km</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>440 m</t>
+          <t>425 m</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Filipe M.</t>
+          <t>Renato C.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>35,8 km</t>
+          <t>36,2 km</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>500 m</t>
+          <t>440 m</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Eduardo T.</t>
+          <t>Filipe M.</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>33,7 km</t>
+          <t>35,8 km</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>376 m</t>
+          <t>500 m</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A448"/>
+  <dimension ref="A1:A451"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1031,553 +1031,553 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>6004.0_2559_P.</t>
+          <t>9756.3_2793_M.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5051.4_1993_M.</t>
+          <t>1114.9_359_S.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4937.4_1783_A.</t>
+          <t>6103.6_2241_G.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>9415.9_3699_G.</t>
+          <t>7025.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4830.1_2569_C.</t>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>791.5_266_G.</t>
+          <t>3597.6_2910_E.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10027.3_2906_P.</t>
+          <t>8187.1_2322_M.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5040.0_2514_C.</t>
+          <t>401.2_179_S.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>7145.5_2856_E.</t>
+          <t>10062.5_2886_M.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20105.6_7766_F.</t>
+          <t>5036.1_2201_C.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4786.5_1898_P.</t>
+          <t>4969.4_2146_P.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3412.3_1947_C.</t>
+          <t>8442.5_3038_G.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>8367.5_4269_C.</t>
+          <t>7006.7_5717_S.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1629.5_671_F.</t>
+          <t>5152.8_1800_G.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5010.3_1888_G.</t>
+          <t>3958.9_1777_P.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>6620.4_2477_P.</t>
+          <t>9415.9_3699_G.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5005.9_1755_X.</t>
+          <t>10718.1_9873_S.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>7230.5_2794_V.</t>
+          <t>22008.4_8412_F.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>8200.8_2347_T.</t>
+          <t>6833.7_2100_G.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5287.4_1835_V.</t>
+          <t>5014.5_1497_G.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>14019.6_6253_L.</t>
+          <t>3004.6_746_V.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3012.4_1258_P.</t>
+          <t>12342.9_3211_M.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5299.8_2406_C.</t>
+          <t>4788.2_1476_P.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1012.0_375_E.</t>
+          <t>5100.0_2587_A.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>8047.1_2948_G.</t>
+          <t>6903.6_2566_G.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>9012.4_2700_M.</t>
+          <t>5522.8_2716_V.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10503.6_3278_M.</t>
+          <t>4688.1_2291_C.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>9007.1_3080_P.</t>
+          <t>1885.0_952_L.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10030.1_3124_M.</t>
+          <t>11214.0_4224_V.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>6053.8_2077_M.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>401.2_179_S.</t>
+          <t>6028.3_2419_L.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>7516.9_3203_A.</t>
+          <t>22320.3_9183_F.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5027.8_1361_P.</t>
+          <t>10006.9_3646_F.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>12006.1_5290_X.</t>
+          <t>6038.2_2121_P.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>5365.6_2437_C.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>8008.0_2930_A.</t>
+          <t>5004.9_1790_A.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>6622.5_2224_E.</t>
+          <t>5081.5_1647_G.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2185.4_792_S.</t>
+          <t>5014.8_2009_A.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>14117.6_3844_M.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5422.4_1911_G.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>5579.8_1990_E.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>5382.2_2690_M.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>14009.0_5498_A.</t>
+          <t>3019.8_1453_F.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>9005.3_4344_A.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>7022.4_3008_L.</t>
+          <t>10010.0_2910_V.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>5904.3_2699_P.</t>
+          <t>611.2_221_M.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>5451.1_1905_T.</t>
+          <t>25020.8_7832_V.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2629.2_1249_V.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>5008.2_1646_A.</t>
+          <t>1012.0_375_E.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>5049.0_2240_C.</t>
+          <t>2629.2_1249_M.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1467.9_482_S.</t>
+          <t>10277.3_4318_L.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>10007.4_3588_V.</t>
+          <t>1011.0_396_L.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>5235.4_1766_P.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>5029.4_1585_P.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2504.7_703_🔋.</t>
+          <t>6007.4_1804_G.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>1027.7_364_S.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>5014.5_1497_G.</t>
+          <t>10023.3_4468_A.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>8132.9_2716_S.</t>
+          <t>14004.5_5478_M.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>5296.8_1844_P.</t>
+          <t>5422.4_1911_G.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>7419.2_3469_F.</t>
+          <t>8481.2_2463_🔋.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>4899.2_1459_A.</t>
+          <t>7985.2_2173_P.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>123.0_5992_A.</t>
+          <t>5005.9_1755_X.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>6028.3_2419_L.</t>
+          <t>10007.8_2733_V.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>3958.9_1777_P.</t>
+          <t>5004.5_1548_A.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>5014.8_2009_A.</t>
+          <t>6046.5_3239_S.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>8416.2_4091_P.</t>
+          <t>9013.7_2337_M.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>3798.9_1319_S.</t>
+          <t>7230.5_2794_V.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>10005.2_3808_G.</t>
+          <t>4576.3_2084_S.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>3006.0_1286_M.</t>
+          <t>6007.1_3172_F.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>5004.1_1610_M.</t>
+          <t>5085.1_1840_G.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>4017.3_1883_C.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>4017.3_1883_C.</t>
+          <t>5043.1_2254_C.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>9006.5_3085_X.</t>
+          <t>3005.2_1040_L.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>2002.2_938_P.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>15223.0_6245_P.</t>
+          <t>4678.8_1840_A.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>10008.1_2966_M.</t>
+          <t>6012.6_2984_P.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>8481.2_2463_🔋.</t>
+          <t>9639.7_4763_P.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>6833.7_2100_G.</t>
+          <t>7114.0_2850_S.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>15194.4_3911_S.</t>
+          <t>6610.9_1738_P.</t>
         </is>
       </c>
     </row>
@@ -1591,1736 +1591,1736 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>16008.9_5968_S.</t>
+          <t>21141.5_8155_F.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>22008.4_8412_F.</t>
+          <t>657.7_273_S.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>8092.0_4532_P.</t>
+          <t>6241.6_2497_P.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>4678.8_1840_A.</t>
+          <t>4899.2_1459_A.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>7025.4_3008_L.</t>
+          <t>14119.3_5262_S.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>4821.0_1857_P.</t>
+          <t>5025.8_1214_P.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>17003.0_7696_P.</t>
+          <t>3580.9_1198_S.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>11214.0_4224_V.</t>
+          <t>4830.1_2569_C.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2629.2_1249_M.</t>
+          <t>9562.8_3145_M.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>4921.0_2491_A.</t>
+          <t>8416.2_4091_P.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>5021.7_1930_A.</t>
+          <t>12022.7_5417_L.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>15010.8_6619_G.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>3010.0_1424_A.</t>
+          <t>1432.9_3942_M.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>6518.4_2914_A.</t>
+          <t>5020.4_2167_C.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>8218.3_2327_P.</t>
+          <t>11527.8_4172_V.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>7012.1_3931_🔋.</t>
+          <t>4731.9_1407_T.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>11005.3_5159_P.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>9507.9_2851_M.</t>
+          <t>5301.0_2064_F.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>4540.8_1823_A.</t>
+          <t>6003.3_2987_M.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>7992.7_2506_F.</t>
+          <t>960.0_1109_A.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>5188.5_1799_S.</t>
+          <t>8132.9_2716_S.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>5043.1_2254_C.</t>
+          <t>8218.3_2327_P.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2064.3_708_S.</t>
+          <t>6113.5_2883_C.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>37036.6_17889_F.</t>
+          <t>1366.2_487_L.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>5017.7_1147_M.</t>
+          <t>7419.2_3469_F.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>6007.1_2393_M.</t>
+          <t>7420.2_4318_C.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>15186.5_3866_S.</t>
+          <t>2504.7_703_🔋.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>8506.3_4050_C.</t>
+          <t>5010.0_1872_A.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>21250.2_9506_P.</t>
+          <t>5013.9_1673_A.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>26010.2_9812_F.</t>
+          <t>4078.1_1810_A.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>5144.4_2349_P.</t>
+          <t>1629.5_671_F.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>7127.8_1843_G.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>10348.3_2647_S.</t>
+          <t>6622.5_2224_E.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>6003.3_2987_M.</t>
+          <t>10001.9_4466_P.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>5007.1_1751_T.</t>
+          <t>4917.5_2381_T.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>4791.5_1524_E.</t>
+          <t>7874.8_2223_M.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>9555.5_5689_S.</t>
+          <t>5000.6_1856_M.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>7598.7_2799_S.</t>
+          <t>10533.4_4020_F.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>10003.3_3845_P.</t>
+          <t>7083.1_2912_G.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>7243.5_2118_G.</t>
+          <t>4000.6_1659_S.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>3010.0_1685_A.</t>
+          <t>7012.1_3931_🔋.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>5235.4_1766_P.</t>
+          <t>6661.8_3736_P.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>12013.5_4635_X.</t>
+          <t>5581.6_3687_P.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1114.9_359_S.</t>
+          <t>553.2_224_S.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>18102.7_4949_M.</t>
+          <t>10643.3_3263_S.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>3735.9_1928_V.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>4972.5_2522_S.</t>
+          <t>5051.4_1993_M.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2556.5_1160_M.</t>
+          <t>10020.8_2989_M.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1002.7_460_S.</t>
+          <t>15223.0_6245_P.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>4788.2_1476_P.</t>
+          <t>5242.7_1657_S.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>8724.4_2500_M.</t>
+          <t>10003.3_3845_P.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>5001.9_1291_V.</t>
+          <t>5002.9_1487_P.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>3029.5_1536_G.</t>
+          <t>4177.9_1557_T.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>6011.8_1873_M.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>10021.0_4009_G.</t>
+          <t>1380.0_562_A.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>6012.3_2200_M.</t>
+          <t>14014.7_3537_S.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2557.8_1206_V.</t>
+          <t>9209.1_3141_E.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>4729.8_2058_P.</t>
+          <t>10503.6_3278_M.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>8442.5_3038_G.</t>
+          <t>2629.2_1249_V.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>5064.3_1832_F.</t>
+          <t>2735.8_959_S.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>5033.4_1976_M.</t>
+          <t>5580.0_2471_A.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>5010.0_1872_A.</t>
+          <t>5021.7_1930_A.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>4619.4_1440_S.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>14004.5_5478_M.</t>
+          <t>18516.8_6699_G.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>10006.0_2772_V.</t>
+          <t>3006.0_1286_M.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>8092.0_4532_P.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>6241.6_2497_P.</t>
+          <t>10106.6_3354_M.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>12545.4_3039_S.</t>
+          <t>1884.9_866_S.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>3059.2_956_T.</t>
+          <t>7312.2_2446_G.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>4078.1_1810_A.</t>
+          <t>5869.6_2613_P.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>16520.2_4844_M.</t>
+          <t>53755.6_36604_F.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>10003.8_3195_S.</t>
+          <t>7880.9_2433_E.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>773.5_238_S.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>553.2_224_S.</t>
+          <t>5296.8_1844_P.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>6113.5_2883_C.</t>
+          <t>3614.8_970_🔋.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>3004.6_746_V.</t>
+          <t>2510.2_1366_V.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>10643.3_3263_S.</t>
+          <t>6012.3_2200_M.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>6006.6_2009_P.</t>
+          <t>5770.8_2848_G.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>18516.8_6699_G.</t>
+          <t>21207.4_6474_V.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>5010.3_3392_P.</t>
+          <t>1083.2_390_M.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>4937.4_1783_A.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>1152.4_938_S.</t>
+          <t>2047.9_924_L.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>6818.2_2036_P.</t>
+          <t>5287.4_1835_V.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>4028.8_1699_L.</t>
+          <t>2004.9_754_S.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>13023.5_5156_L.</t>
+          <t>10003.1_5062_V.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>7604.2_3303_P.</t>
+          <t>2556.5_1160_M.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>6345.4_2376_S.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>15637.2_5789_G.</t>
+          <t>7604.2_3303_P.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>6016.7_2122_M.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>8351.7_4153_C.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>10533.4_4020_F.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>5003.2_1389_E.</t>
+          <t>8200.5_2738_M.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2735.8_959_S.</t>
+          <t>6173.6_2865_M.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>5033.4_1976_M.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2761.5_1068_S.</t>
+          <t>4729.8_2058_P.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>15010.8_6619_G.</t>
+          <t>5904.3_2699_P.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>4532.9_2322_L.</t>
+          <t>5040.0_2971_A.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>8618.0_2344_P.</t>
+          <t>6951.4_2856_S.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>7985.2_2173_P.</t>
+          <t>5238.0_2781_F.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>7012.2_4093_P.</t>
+          <t>5049.0_2240_C.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>12006.1_5290_T.</t>
+          <t>7992.7_2506_F.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>15200.8_10718_F.</t>
+          <t>10003.8_3195_S.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>6103.6_2241_G.</t>
+          <t>1467.9_482_S.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2783.5_952_S.</t>
+          <t>6047.4_2816_T.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>21250.2_9506_P.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>5086.0_1810_G.</t>
+          <t>3412.3_1947_C.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>5579.8_1990_E.</t>
+          <t>3059.2_956_T.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>25020.8_7832_V.</t>
+          <t>5005.4_2618_L.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>8004.6_2357_G.</t>
+          <t>56121.5_25636_F.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>5004.5_1548_A.</t>
+          <t>15200.8_10718_F.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>5020.6_1328_M.</t>
+          <t>12545.4_3039_S.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>8899.2_2910_S.</t>
+          <t>10012.3_3067_S.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>13008.2_4958_P.</t>
+          <t>7022.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>10003.1_5062_V.</t>
+          <t>8024.4_2933_S.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>14014.7_3537_S.</t>
+          <t>5086.0_1810_G.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2558.7_905_S.</t>
+          <t>3039.1_1013_L.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>16397.3_4254_S.</t>
+          <t>7039.1_2754_S.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>56121.5_25636_F.</t>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>2558.7_905_S.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>2557.8_1206_V.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>5005.4_2618_L.</t>
+          <t>5064.3_1832_F.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>7001.2_3357_M.</t>
+          <t>10006.9_3646_X.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>7003.6_2437_P.</t>
+          <t>2880.9_1210_L.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>5522.8_2716_V.</t>
+          <t>4700.4_1216_V.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>1443.0_851_A.</t>
+          <t>4790.7_1897_F.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>10718.1_9873_S.</t>
+          <t>9555.5_5689_S.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>4153.2_3559_P.</t>
+          <t>1152.4_938_S.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>1027.7_364_S.</t>
+          <t>1034.3_279_M.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>4786.5_1898_P.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>9791.4_3527_G.</t>
+          <t>12002.7_4232_S.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2002.2_938_P.</t>
+          <t>4735.2_997_S.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>5017.7_1147_M.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>8013.1_2082_P.</t>
+          <t>6620.4_2477_P.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>7006.7_5717_S.</t>
+          <t>4864.8_1353_E.</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>10012.1_3139_S.</t>
+          <t>10348.3_2647_S.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>1885.0_952_L.</t>
+          <t>12006.1_5290_T.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>4613.1_1806_A.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>9005.3_4344_A.</t>
+          <t>10005.5_2697_V.</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>4790.7_1897_F.</t>
+          <t>14009.7_4401_V.</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>12342.9_3211_M.</t>
+          <t>1206.7_12400_M.</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>4896.8_2251_L.</t>
+          <t>10016.9_3028_M.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>10016.9_3028_M.</t>
+          <t>21106.2_7925_P.</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>5064.2_1636_G.</t>
+          <t>6818.2_2036_P.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>5100.0_2587_A.</t>
+          <t>6011.5_2408_A.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>7114.0_2850_S.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>10277.3_4318_L.</t>
+          <t>6518.4_2914_A.</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>22002.4_8469_M.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>5007.4_1601_A.</t>
+          <t>4781.2_1507_A.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>5003.2_1389_E.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>21124.1_8011_F.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>7090.6_3340_A.</t>
+          <t>8978.9_3078_G.</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>3551.6_1303_S.</t>
+          <t>13344.7_5916_G.</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>12008.4_3832_G.</t>
+          <t>10013.4_3721_G.</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>5580.0_2471_A.</t>
+          <t>4791.5_1524_E.</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>10007.8_2733_V.</t>
+          <t>7127.8_1843_G.</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>5007.4_1601_A.</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>10011.5_3070_S.</t>
+          <t>5072.4_1931_S.</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>9756.3_2793_M.</t>
+          <t>5724.1_3694_S.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>6035.0_2481_P.</t>
+          <t>8899.2_2910_S.</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>6661.8_3736_P.</t>
+          <t>5008.2_1646_A.</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2036.1_839_S.</t>
+          <t>4028.8_1699_L.</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>21207.4_6474_V.</t>
+          <t>4891.7_1690_F.</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>7516.9_3203_A.</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>6006.1_2236_V.</t>
+          <t>4532.9_2322_L.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>7576.8_2823_P.</t>
+          <t>6035.0_2481_P.</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>6804.1_2088_P.</t>
+          <t>5004.1_1610_M.</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>10006.9_3646_X.</t>
+          <t>208.3_85_P.</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>1380.0_562_A.</t>
+          <t>5020.6_1328_M.</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>8006.7_2244_V.</t>
+          <t>5011.9_1594_P.</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>5020.4_2167_C.</t>
+          <t>5022.5_1222_P.</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>15057.9_8625_F.</t>
+          <t>4768.0_1875_L.</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>600.2_261_L.</t>
+          <t>5451.1_1905_T.</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>4932.4_1545_E.</t>
+          <t>2175.4_712_S.</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>12022.7_5417_L.</t>
+          <t>10030.0_3041_G.</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>2047.9_924_L.</t>
+          <t>5007.1_1751_T.</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>8978.9_3078_G.</t>
+          <t>6012.6_2984_F.</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>531.0_343_A.</t>
+          <t>791.5_266_G.</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>6010.6_2144_A.</t>
+          <t>123.0_5992_A.</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>611.2_221_M.</t>
+          <t>6006.1_2236_V.</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>20105.6_7766_F.</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>5036.1_2201_C.</t>
+          <t>5014.3_1731_F.</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>960.0_1109_A.</t>
+          <t>15057.9_8625_F.</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>8200.8_2347_T.</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>11005.3_5159_P.</t>
+          <t>5144.4_2349_P.</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>10005.5_2697_V.</t>
+          <t>15637.2_5789_G.</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>3089.9_1508_C.</t>
+          <t>3023.2_962_S.</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>5000.5_1919_P.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>9209.1_3141_E.</t>
+          <t>5119.6_3153_M.</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>10030.5_4765_C.</t>
+          <t>6137.8_2406_L.</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>7186.5_2708_S.</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>5004.0_2103_C.</t>
+          <t>5139.2_2082_G.</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>7420.2_4318_C.</t>
+          <t>4763.8_1720_P.</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>9029.6_4595_P.</t>
+          <t>8618.0_2344_P.</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>6610.9_1738_P.</t>
+          <t>531.0_343_A.</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>8396.0_2595_S.</t>
+          <t>7243.5_2118_G.</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>2011.7_731_S.</t>
+          <t>8008.0_2930_A.</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>12524.7_3259_S.</t>
+          <t>5224.2_2340_C.</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>6173.6_2865_M.</t>
+          <t>4153.2_3559_P.</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>3039.1_1013_L.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>22320.3_9183_F.</t>
+          <t>5356.1_1825_T.</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>6012.6_2984_P.</t>
+          <t>4613.1_1806_A.</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>2004.9_754_S.</t>
+          <t>18107.4_4577_M.</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>2355.5_726_S.</t>
+          <t>7576.8_2823_P.</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>6903.6_2566_G.</t>
+          <t>37036.6_17889_F.</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>10030.0_3041_G.</t>
+          <t>8120.9_2737_G.</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>3597.6_2910_E.</t>
+          <t>2051.8_860_S.</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>10007.4_3588_V.</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>5028.5_4433_S.</t>
+          <t>5006.8_1080_M.</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>6007.1_3172_F.</t>
+          <t>5299.8_2406_C.</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>18107.4_4577_M.</t>
+          <t>1002.7_460_S.</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>5282.8_2392_C.</t>
+          <t>5022.0_1862_A.</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>8024.4_2933_S.</t>
+          <t>2000.0_724_A.</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>5827.8_2106_S.</t>
+          <t>4692.9_1546_P.</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>8187.1_2322_M.</t>
+          <t>26010.2_9812_F.</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>4735.2_997_S.</t>
+          <t>12006.1_5290_X.</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>3138.1_1120_S.</t>
+          <t>10106.6_2889_P.</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>12521.4_4814_M.</t>
+          <t>5981.9_2551_P.</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>3735.9_1928_V.</t>
+          <t>9029.6_4595_P.</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>5163.5_1775_V.</t>
+          <t>4077.1_1454_S.</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>2060.0_802_S.</t>
+          <t>10031.8_2663_P.</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>14119.3_5262_S.</t>
+          <t>5282.8_2392_C.</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>10006.9_3646_F.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>3010.0_1289_A.</t>
+          <t>12008.4_3832_G.</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>10001.9_4466_P.</t>
+          <t>8367.5_4269_C.</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>5621.6_2375_P.</t>
+          <t>4932.4_1545_E.</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>1020.0_679_T.</t>
+          <t>10027.3_2906_P.</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>2000.0_724_A.</t>
+          <t>8013.1_2082_P.</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>6600.2_1915_M.</t>
+          <t>15504.3_3950_M.</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>5022.0_1862_A.</t>
+          <t>7012.2_4093_P.</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>6779.9_2003_E.</t>
+          <t>9507.9_2851_M.</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>4101.5_1485_V.</t>
+          <t>6804.1_2088_P.</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>5011.9_1594_P.</t>
+          <t>5163.5_1775_V.</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>5000.2_1932_E.</t>
+          <t>2355.5_726_S.</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>21106.2_7925_P.</t>
+          <t>14019.6_6253_L.</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>5029.4_1585_P.</t>
+          <t>16008.9_5968_S.</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>7039.1_2754_S.</t>
+          <t>6345.4_2376_S.</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>21141.5_8155_F.</t>
+          <t>21442.0_7959_F.</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>6951.4_2856_S.</t>
+          <t>5000.2_1932_E.</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>5256.5_1535_S.</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>4969.4_2146_P.</t>
+          <t>6005.3_2226_A.</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>7312.2_2446_G.</t>
+          <t>3010.0_1424_A.</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>9791.4_3527_G.</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>10006.5_3648_X.</t>
+          <t>5010.3_1888_G.</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>4688.1_2291_C.</t>
+          <t>9012.4_2700_M.</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>5256.5_1535_S.</t>
+          <t>7569.4_2477_V.</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>15016.9_6221_G.</t>
+          <t>5009.1_2246_C.</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>22002.4_8469_M.</t>
+          <t>16397.3_4254_S.</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>4692.9_1546_P.</t>
+          <t>7015.4_2141_T.</t>
         </is>
       </c>
     </row>
@@ -3334,826 +3334,847 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>657.7_273_S.</t>
+          <t>5010.3_3392_P.</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>6005.3_2226_A.</t>
+          <t>8351.7_4153_C.</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>7880.9_2433_E.</t>
+          <t>4821.0_1857_P.</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>7090.6_3340_A.</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>1034.3_279_M.</t>
+          <t>9007.1_3080_P.</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>773.5_238_S.</t>
+          <t>2783.5_952_S.</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>5013.9_1673_A.</t>
+          <t>8724.4_2500_M.</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>5869.6_2613_P.</t>
+          <t>13023.5_5156_L.</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>5002.9_1487_P.</t>
+          <t>8196.1_2807_T.</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>6036.4_2875_V.</t>
+          <t>600.2_261_L.</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>12002.7_4232_S.</t>
+          <t>6010.6_2144_A.</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>10007.8_2668_V.</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>5022.5_1222_P.</t>
+          <t>8006.7_2244_V.</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>5827.8_2106_S.</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>6011.5_2408_A.</t>
+          <t>7001.2_3357_M.</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>5072.4_1931_S.</t>
+          <t>12326.4_4833_S.</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>4850.9_2239_C.</t>
+          <t>14009.0_5498_A.</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>8196.1_2807_T.</t>
+          <t>10006.5_3648_X.</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>3023.2_962_S.</t>
+          <t>10012.1_3139_S.</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>7874.8_2223_M.</t>
+          <t>10022.1_2875_M.</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>5981.9_2551_P.</t>
+          <t>21124.1_8011_F.</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>4013.7_1173_V.</t>
+          <t>4214.8_2018_A.</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>5724.1_3694_S.</t>
+          <t>2185.4_792_S.</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>10020.8_2989_M.</t>
+          <t>3551.6_1303_S.</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>10022.1_2875_M.</t>
+          <t>10174.3_3680_S.</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>1083.2_390_M.</t>
+          <t>8253.0_2972_🔋.</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>12013.5_4635_X.</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>3757.2_1716_A.</t>
+          <t>2036.1_839_S.</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>419.0_180_P.</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>9006.5_3085_X.</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>14117.6_3844_M.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>5025.8_1214_P.</t>
+          <t>3757.2_1716_A.</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>10025.6_4018_G.</t>
+          <t>3138.1_1120_S.</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>10003.7_2721_V.</t>
+          <t>4150.2_2042_C.</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>5040.0_2299_A.</t>
+          <t>5005.8_1527_S.</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>53755.6_36604_F.</t>
+          <t>4705.5_1241_G.</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>5085.1_1840_G.</t>
+          <t>1020.0_679_T.</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>5382.2_2690_M.</t>
+          <t>16520.2_4844_M.</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>5139.2_2082_G.</t>
+          <t>4850.9_2239_C.</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>7502.4_3467_P.</t>
+          <t>10003.7_2721_V.</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>7569.4_2477_V.</t>
+          <t>6779.9_2003_E.</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>2510.2_1366_V.</t>
+          <t>5188.5_1799_S.</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>6016.7_2122_M.</t>
+          <t>5064.2_1636_G.</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>9639.7_4763_P.</t>
+          <t>2186.2_736_G.</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>1206.7_12400_M.</t>
+          <t>5028.5_4433_S.</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>6011.8_1873_M.</t>
+          <t>6084.1_2156_V.</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>5040.0_2971_A.</t>
+          <t>10030.5_4765_C.</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>7024.3_3266_L.</t>
+          <t>5621.6_2375_P.</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>21114.4_6098_P.</t>
+          <t>8047.1_2948_G.</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>8506.3_4050_C.</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>1701.7_720_F.</t>
+          <t>4101.5_1485_V.</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>8200.5_2738_M.</t>
+          <t>1443.0_851_A.</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>2880.9_1210_L.</t>
+          <t>17012.6_5869_T.</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>10106.6_2889_P.</t>
+          <t>5040.0_2514_C.</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>2186.2_736_G.</t>
+          <t>10006.0_2772_V.</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>4797.2_1541_G.</t>
+          <t>6600.2_1915_M.</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>10010.0_2910_V.</t>
+          <t>4974.4_1533_E.</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>6007.4_1804_G.</t>
+          <t>15186.5_3866_S.</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>5242.7_1657_S.</t>
+          <t>3010.0_1685_A.</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>6047.4_2816_T.</t>
+          <t>6036.4_2875_V.</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>5000.6_1856_M.</t>
+          <t>18102.7_4949_M.</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>10005.2_3808_G.</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>15504.3_3950_M.</t>
+          <t>5001.9_1291_V.</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>5581.6_3687_P.</t>
+          <t>8004.6_2357_G.</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>4177.9_1557_T.</t>
+          <t>8396.0_2595_S.</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>4000.6_1659_S.</t>
+          <t>10025.6_4018_G.</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>21114.4_6098_P.</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>10012.3_3067_S.</t>
+          <t>10058.8_3483_F.</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>10007.8_2668_V.</t>
+          <t>7024.3_3266_L.</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>4966.0_1709_G.</t>
+          <t>4619.4_1440_S.</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>1432.9_3942_M.</t>
+          <t>4966.0_1709_G.</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>4974.4_1533_E.</t>
+          <t>7598.7_2799_S.</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>7083.1_2912_G.</t>
+          <t>13008.2_4958_P.</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>10031.8_2663_P.</t>
+          <t>5126.8_1941_G.</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>6084.1_2156_V.</t>
+          <t>2011.7_731_S.</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>5126.8_1941_G.</t>
+          <t>4972.5_2522_S.</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>6038.2_2121_P.</t>
+          <t>4540.8_1823_A.</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>1366.2_487_L.</t>
+          <t>5040.0_2299_A.</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>4921.0_2491_A.</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>4864.8_1353_E.</t>
+          <t>3029.5_1536_G.</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>3010.0_1289_A.</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>5005.8_1527_S.</t>
+          <t>6472.0_2501_S.</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>4917.5_2381_T.</t>
+          <t>7502.4_3467_P.</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>5770.8_2848_G.</t>
+          <t>2060.0_802_S.</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>5009.1_2246_C.</t>
+          <t>10021.0_4009_G.</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>5006.8_1080_M.</t>
+          <t>15016.9_6221_G.</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>4700.4_1216_V.</t>
+          <t>5027.8_1361_P.</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>4150.2_2042_C.</t>
+          <t>7593.7_2701_E.</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>6006.6_2009_P.</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>419.0_180_P.</t>
+          <t>7003.6_2437_P.</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>6053.8_2077_M.</t>
+          <t>18665.3_4638_S.</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>5238.0_2781_F.</t>
+          <t>6004.0_2559_P.</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>3026.1_1490_A.</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>18665.3_4638_S.</t>
+          <t>8104.2_2652_M.</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>7186.5_2708_S.</t>
+          <t>2305.1_940_S.</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>17003.0_7696_P.</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>10001.3_4206_G.</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>5081.5_1647_G.</t>
+          <t>3012.4_1258_P.</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>4781.2_1507_A.</t>
+          <t>2064.3_708_S.</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>5152.8_1800_G.</t>
+          <t>15194.4_3911_S.</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>5301.0_2064_F.</t>
+          <t>6007.1_2393_M.</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>14009.7_4401_V.</t>
+          <t>2761.5_1068_S.</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>7593.7_2701_E.</t>
+          <t>5004.0_2103_C.</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>5008.0_2402_P.</t>
+          <t>4896.8_2251_L.</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>12524.7_3259_S.</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>5365.6_2437_C.</t>
+          <t>12006.9_5463_P.</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>4576.3_2084_S.</t>
+          <t>5008.0_2402_P.</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>13344.7_5916_G.</t>
+          <t>4013.7_1173_V.</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>4214.8_2018_A.</t>
+          <t>5008.1_1825_M.</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>10013.4_3721_G.</t>
+          <t>10030.1_3124_M.</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>5004.9_1790_A.</t>
+          <t>4797.2_1541_G.</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>5224.2_2340_C.</t>
+          <t>4814.5_1705_🔋.</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>6536.2_2241_P.</t>
+          <t>1701.7_720_F.</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>3026.1_1490_A.</t>
+          <t>5000.5_1919_P.</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>5008.1_1825_M.</t>
+          <t>6536.2_2241_P.</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>10001.3_4206_G.</t>
+          <t>10011.5_3070_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>7145.5_2856_E.</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>3089.9_1508_C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>3798.9_1319_S.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_500km_2026.xlsx
+++ b/Ranking_CNB_500km_2026.xlsx
@@ -454,12 +454,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>664,9 km</t>
+          <t>674,9 km</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>10.327 m</t>
+          <t>10.347 m</t>
         </is>
       </c>
     </row>
@@ -471,12 +471,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>514,5 km</t>
+          <t>525,5 km</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>6.826 m</t>
+          <t>6.976 m</t>
         </is>
       </c>
     </row>
@@ -488,12 +488,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>332,0 km</t>
+          <t>342,0 km</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.285 m</t>
+          <t>3.382 m</t>
         </is>
       </c>
     </row>
@@ -505,12 +505,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>288,9 km</t>
+          <t>306,1 km</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.378 m</t>
+          <t>2.535 m</t>
         </is>
       </c>
     </row>
@@ -539,12 +539,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>242,2 km</t>
+          <t>255,2 km</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.219 m</t>
+          <t>2.349 m</t>
         </is>
       </c>
     </row>
@@ -590,46 +590,46 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>200,8 km</t>
+          <t>215,8 km</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.370 m</t>
+          <t>1.497 m</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Jandson P.</t>
+          <t>Gleydson G.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>179,6 km</t>
+          <t>190,3 km</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.371 m</t>
+          <t>1.239 m</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Gleydson G.</t>
+          <t>Jandson P.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>175,3 km</t>
+          <t>183,9 km</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.131 m</t>
+          <t>2.435 m</t>
         </is>
       </c>
     </row>
@@ -641,12 +641,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>158,9 km</t>
+          <t>163,9 km</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.716 m</t>
+          <t>1.786 m</t>
         </is>
       </c>
     </row>
@@ -658,12 +658,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>156,9 km</t>
+          <t>162,1 km</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.944 m</t>
+          <t>1.961 m</t>
         </is>
       </c>
     </row>
@@ -675,63 +675,63 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>149,4 km</t>
+          <t>159,5 km</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.220 m</t>
+          <t>1.240 m</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Naiane C.</t>
+          <t>Duda X.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>137,0 km</t>
+          <t>146,7 km</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.285 m</t>
+          <t>1.647 m</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Edivânia M.</t>
+          <t>Naiane C.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>137,0 km</t>
+          <t>142,1 km</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.486 m</t>
+          <t>1.363 m</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Duda X.</t>
+          <t>Edivânia M.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>136,6 km</t>
+          <t>142,0 km</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.627 m</t>
+          <t>1.557 m</t>
         </is>
       </c>
     </row>
@@ -777,12 +777,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>111,0 km</t>
+          <t>116,1 km</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.275 m</t>
+          <t>1.346 m</t>
         </is>
       </c>
     </row>
@@ -794,12 +794,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>94,6 km</t>
+          <t>102,0 km</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.170 m</t>
+          <t>1.253 m</t>
         </is>
       </c>
     </row>
@@ -811,12 +811,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>83,6 km</t>
+          <t>93,8 km</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>690 m</t>
+          <t>710 m</t>
         </is>
       </c>
     </row>
@@ -828,12 +828,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>76,5 km</t>
+          <t>81,5 km</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>829 m</t>
+          <t>846 m</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>73,1 km</t>
+          <t>78,2 km</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>728 m</t>
+          <t>799 m</t>
         </is>
       </c>
     </row>
@@ -879,63 +879,63 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>39,1 km</t>
+          <t>44,1 km</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>425 m</t>
+          <t>496 m</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Renato C.</t>
+          <t>Filipe M.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>36,2 km</t>
+          <t>40,7 km</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>440 m</t>
+          <t>571 m</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Filipe M.</t>
+          <t>Thaisa V.</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>35,8 km</t>
+          <t>38,1 km</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>500 m</t>
+          <t>537 m</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Thaisa V.</t>
+          <t>Renato C.</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>33,2 km</t>
+          <t>36,2 km</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>466 m</t>
+          <t>440 m</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A451"/>
+  <dimension ref="A1:A475"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1031,280 +1031,280 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>9756.3_2793_M.</t>
+          <t>6084.1_2156_V.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1114.9_359_S.</t>
+          <t>10006.9_3646_F.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>6103.6_2241_G.</t>
+          <t>6536.2_2241_P.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>7025.4_3008_L.</t>
+          <t>14119.3_5262_S.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>3138.1_1120_S.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3597.6_2910_E.</t>
+          <t>10005.5_2697_V.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>8187.1_2322_M.</t>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>401.2_179_S.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>7003.6_2437_P.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5036.1_2201_C.</t>
+          <t>5301.0_2064_F.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4969.4_2146_P.</t>
+          <t>6035.0_2481_P.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>8442.5_3038_G.</t>
+          <t>5040.0_2971_A.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>7006.7_5717_S.</t>
+          <t>3006.0_1286_M.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5152.8_1800_G.</t>
+          <t>6038.2_2121_P.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3958.9_1777_P.</t>
+          <t>7593.7_2701_E.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>9415.9_3699_G.</t>
+          <t>9209.1_3141_E.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10718.1_9873_S.</t>
+          <t>10011.5_3070_S.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>22008.4_8412_F.</t>
+          <t>5004.4_1614_A.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6833.7_2100_G.</t>
+          <t>13008.2_4958_P.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5014.5_1497_G.</t>
+          <t>4017.3_1883_C.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3004.6_746_V.</t>
+          <t>18102.7_4949_M.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>12342.9_3211_M.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>4788.2_1476_P.</t>
+          <t>6804.1_2088_P.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5100.0_2587_A.</t>
+          <t>6833.7_2100_G.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>6903.6_2566_G.</t>
+          <t>4891.7_1690_F.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5522.8_2716_V.</t>
+          <t>4153.2_3559_P.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>4688.1_2291_C.</t>
+          <t>5356.1_1825_T.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1885.0_952_L.</t>
+          <t>1002.7_460_S.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>11214.0_4224_V.</t>
+          <t>7186.5_2708_S.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>6053.8_2077_M.</t>
+          <t>6012.6_2984_F.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>6028.3_2419_L.</t>
+          <t>5085.1_1840_G.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>22320.3_9183_F.</t>
+          <t>16008.9_5968_S.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10006.9_3646_F.</t>
+          <t>6011.5_2408_A.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>6038.2_2121_P.</t>
+          <t>6011.8_1873_M.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5365.6_2437_C.</t>
+          <t>6620.4_2477_P.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5004.9_1790_A.</t>
+          <t>16520.2_4844_M.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5081.5_1647_G.</t>
+          <t>9756.3_2793_M.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>5014.8_2009_A.</t>
+          <t>4937.4_1783_A.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>14117.6_3844_M.</t>
+          <t>3004.6_746_V.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>4821.0_1857_P.</t>
         </is>
       </c>
     </row>
@@ -1318,1897 +1318,1897 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>5382.2_2690_M.</t>
+          <t>14009.7_4401_V.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>7024.3_3266_L.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>9005.3_4344_A.</t>
+          <t>3580.9_1198_S.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>10010.0_2910_V.</t>
+          <t>18107.4_4577_M.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>611.2_221_M.</t>
+          <t>5365.6_2437_C.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>25020.8_7832_V.</t>
+          <t>12006.1_5290_T.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>6012.6_2984_P.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1012.0_375_E.</t>
+          <t>53755.6_36604_F.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2629.2_1249_M.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>10277.3_4318_L.</t>
+          <t>5025.8_1214_P.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>4886.1_2212_M.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>5235.4_1766_P.</t>
+          <t>123.0_5992_A.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>5029.4_1585_P.</t>
+          <t>4864.8_1353_E.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>6007.4_1804_G.</t>
+          <t>5040.0_2514_C.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1027.7_364_S.</t>
+          <t>2629.2_1249_V.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>10023.3_4468_A.</t>
+          <t>2186.2_736_G.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>14004.5_5478_M.</t>
+          <t>10006.5_3648_X.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>5422.4_1911_G.</t>
+          <t>5010.3_3392_P.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>8481.2_2463_🔋.</t>
+          <t>4791.5_1524_E.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>7985.2_2173_P.</t>
+          <t>5163.5_1775_V.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>5005.9_1755_X.</t>
+          <t>5004.9_1790_A.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>10007.8_2733_V.</t>
+          <t>6016.7_2122_M.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>5004.5_1548_A.</t>
+          <t>5139.2_2082_G.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>6053.8_2077_M.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>1018.4_335_M.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>7230.5_2794_V.</t>
+          <t>4000.6_1659_S.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>4576.3_2084_S.</t>
+          <t>21442.0_7959_F.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>6007.1_3172_F.</t>
+          <t>3010.0_1289_A.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>5085.1_1840_G.</t>
+          <t>5086.0_1810_G.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>4017.3_1883_C.</t>
+          <t>12326.4_4833_S.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>5043.1_2254_C.</t>
+          <t>8024.4_2933_S.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>419.0_180_P.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2002.2_938_P.</t>
+          <t>5027.8_1361_P.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>4678.8_1840_A.</t>
+          <t>6137.8_2406_L.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>6012.6_2984_P.</t>
+          <t>6007.4_1804_G.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>9639.7_4763_P.</t>
+          <t>4790.7_1897_F.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>7114.0_2850_S.</t>
+          <t>14004.5_5478_M.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>6610.9_1738_P.</t>
+          <t>8253.0_2972_🔋.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10002.4_5136_P.</t>
+          <t>6003.3_2987_M.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>21141.5_8155_F.</t>
+          <t>9791.4_3527_G.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>657.7_273_S.</t>
+          <t>3735.9_1928_V.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>6241.6_2497_P.</t>
+          <t>1034.3_279_M.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>4899.2_1459_A.</t>
+          <t>21106.2_7925_P.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>14119.3_5262_S.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>5025.8_1214_P.</t>
+          <t>7012.2_4093_P.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>13023.5_5156_L.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>4830.1_2569_C.</t>
+          <t>8006.7_2244_V.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>3010.0_1424_A.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>8416.2_4091_P.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>12022.7_5417_L.</t>
+          <t>14009.0_5498_A.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>15010.8_6619_G.</t>
+          <t>3039.1_1013_L.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1432.9_3942_M.</t>
+          <t>5022.5_1222_P.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>5020.4_2167_C.</t>
+          <t>1380.0_562_A.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>11527.8_4172_V.</t>
+          <t>10503.6_3278_M.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>22008.4_8412_F.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>11005.3_5159_P.</t>
+          <t>3012.4_1258_P.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>5301.0_2064_F.</t>
+          <t>7039.1_2754_S.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>6003.3_2987_M.</t>
+          <t>4896.8_2251_L.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>960.0_1109_A.</t>
+          <t>1152.4_938_S.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>8132.9_2716_S.</t>
+          <t>5382.2_2690_M.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>8218.3_2327_P.</t>
+          <t>3089.9_1508_C.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>6113.5_2883_C.</t>
+          <t>22320.3_9183_F.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1366.2_487_L.</t>
+          <t>10058.8_3483_F.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>7419.2_3469_F.</t>
+          <t>7114.0_2850_S.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>7420.2_4318_C.</t>
+          <t>8187.1_2322_M.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2504.7_703_🔋.</t>
+          <t>6006.1_2236_V.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>5010.0_1872_A.</t>
+          <t>6345.4_2376_S.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>5013.9_1673_A.</t>
+          <t>9007.1_3080_P.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>4078.1_1810_A.</t>
+          <t>3614.8_970_🔋.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1629.5_671_F.</t>
+          <t>3412.3_1947_C.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>4177.9_1557_T.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>6622.5_2224_E.</t>
+          <t>14014.7_3537_S.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>10001.9_4466_P.</t>
+          <t>4921.0_2491_A.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>4917.5_2381_T.</t>
+          <t>7145.5_2856_E.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>7874.8_2223_M.</t>
+          <t>7576.8_2823_P.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>5000.6_1856_M.</t>
+          <t>11527.8_4172_V.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>10533.4_4020_F.</t>
+          <t>9029.6_4595_P.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>7083.1_2912_G.</t>
+          <t>15504.3_3950_M.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>4000.6_1659_S.</t>
+          <t>9507.9_2851_M.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>7012.1_3931_🔋.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>6661.8_3736_P.</t>
+          <t>5224.2_2340_C.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>5581.6_3687_P.</t>
+          <t>6173.6_2865_M.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>553.2_224_S.</t>
+          <t>4150.2_2042_C.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>10643.3_3263_S.</t>
+          <t>5040.0_2299_A.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>3735.9_1928_V.</t>
+          <t>20105.6_7766_F.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>5051.4_1993_M.</t>
+          <t>8396.0_2595_S.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>10020.8_2989_M.</t>
+          <t>10025.5_3684_F.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>15223.0_6245_P.</t>
+          <t>2629.2_1249_M.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>5242.7_1657_S.</t>
+          <t>5621.6_2375_P.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>10003.3_3845_P.</t>
+          <t>10007.4_3588_V.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>5002.9_1487_P.</t>
+          <t>6951.4_2856_S.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>4177.9_1557_T.</t>
+          <t>10007.8_2733_V.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>6011.8_1873_M.</t>
+          <t>10010.0_2910_V.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1380.0_562_A.</t>
+          <t>17012.6_5869_T.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>14014.7_3537_S.</t>
+          <t>5004.8_1628_M.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>9209.1_3141_E.</t>
+          <t>10106.6_3354_M.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>10503.6_3278_M.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2629.2_1249_V.</t>
+          <t>6903.6_2566_G.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2735.8_959_S.</t>
+          <t>9020.0_2605_M.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>5580.0_2471_A.</t>
+          <t>4966.0_1709_G.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>5021.7_1930_A.</t>
+          <t>4101.5_1485_V.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>531.0_343_A.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>18516.8_6699_G.</t>
+          <t>8047.1_2948_G.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>3006.0_1286_M.</t>
+          <t>15057.9_8625_F.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>8092.0_4532_P.</t>
+          <t>3798.9_1319_S.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>7090.6_3340_A.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>5004.1_1610_M.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>7312.2_2446_G.</t>
+          <t>5158.6_2220_C.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>5869.6_2613_P.</t>
+          <t>4692.9_1546_P.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>53755.6_36604_F.</t>
+          <t>5152.8_1800_G.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>7880.9_2433_E.</t>
+          <t>6028.3_2419_L.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>773.5_238_S.</t>
+          <t>5081.5_1647_G.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>5296.8_1844_P.</t>
+          <t>6472.0_2501_S.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>1027.7_364_S.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2510.2_1366_V.</t>
+          <t>37036.6_17889_F.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>6012.3_2200_M.</t>
+          <t>5004.5_1548_A.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>5770.8_2848_G.</t>
+          <t>5000.5_1919_P.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>21207.4_6474_V.</t>
+          <t>7874.8_2223_M.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>1083.2_390_M.</t>
+          <t>8899.2_2910_S.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>4937.4_1783_A.</t>
+          <t>5072.5_1592_S.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2047.9_924_L.</t>
+          <t>16397.3_4254_S.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>5287.4_1835_V.</t>
+          <t>8351.7_4153_C.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2004.9_754_S.</t>
+          <t>5003.2_1389_E.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>10003.1_5062_V.</t>
+          <t>5000.2_1932_E.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2556.5_1160_M.</t>
+          <t>4327.6_1237_P.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>5064.2_1636_G.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>7604.2_3303_P.</t>
+          <t>12013.5_4635_X.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>6016.7_2122_M.</t>
+          <t>5008.1_1825_M.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>5256.5_1535_S.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>5005.0_1309_M.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>8200.5_2738_M.</t>
+          <t>2558.7_905_S.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>6173.6_2865_M.</t>
+          <t>9006.5_3085_X.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>5033.4_1976_M.</t>
+          <t>2880.9_1210_L.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>4729.8_2058_P.</t>
+          <t>5008.0_2402_P.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>5904.3_2699_P.</t>
+          <t>6046.5_3239_S.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>5040.0_2971_A.</t>
+          <t>4700.4_1216_V.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>6951.4_2856_S.</t>
+          <t>4899.2_1459_A.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>5238.0_2781_F.</t>
+          <t>8004.6_2357_G.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>5049.0_2240_C.</t>
+          <t>5051.4_1993_M.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>7992.7_2506_F.</t>
+          <t>13344.7_5916_G.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>10003.8_3195_S.</t>
+          <t>8200.5_2738_M.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>1467.9_482_S.</t>
+          <t>12008.4_3832_G.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>6047.4_2816_T.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>21250.2_9506_P.</t>
+          <t>4214.8_2018_A.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>3412.3_1947_C.</t>
+          <t>2047.9_924_L.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>3059.2_956_T.</t>
+          <t>22002.4_8469_M.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>5005.4_2618_L.</t>
+          <t>5006.8_1080_M.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>56121.5_25636_F.</t>
+          <t>5013.9_1673_A.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>15200.8_10718_F.</t>
+          <t>15186.5_3866_S.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>12545.4_3039_S.</t>
+          <t>5001.9_1291_V.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>10012.3_3067_S.</t>
+          <t>15223.0_6245_P.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>7022.4_3008_L.</t>
+          <t>10174.3_3680_S.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>8024.4_2933_S.</t>
+          <t>7025.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>5086.0_1810_G.</t>
+          <t>8013.1_2082_P.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>3039.1_1013_L.</t>
+          <t>12006.1_5290_X.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>7039.1_2754_S.</t>
+          <t>5724.1_3694_S.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>10718.1_9873_S.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2558.7_905_S.</t>
+          <t>12342.9_3211_M.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2557.8_1206_V.</t>
+          <t>3005.2_1040_L.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>5064.3_1832_F.</t>
+          <t>3059.2_956_T.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>10006.9_3646_X.</t>
+          <t>18665.3_4638_S.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2880.9_1210_L.</t>
+          <t>10241.7_3826_G.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>4700.4_1216_V.</t>
+          <t>2002.2_938_P.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>4790.7_1897_F.</t>
+          <t>5451.1_1905_T.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>9555.5_5689_S.</t>
+          <t>6241.6_2497_P.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>1152.4_938_S.</t>
+          <t>4917.5_2381_T.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>1034.3_279_M.</t>
+          <t>3958.9_1777_P.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>4786.5_1898_P.</t>
+          <t>7985.2_2173_P.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>12002.7_4232_S.</t>
+          <t>7001.2_3357_M.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>4735.2_997_S.</t>
+          <t>10022.1_2875_M.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>5017.7_1147_M.</t>
+          <t>5014.8_2009_A.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>6620.4_2477_P.</t>
+          <t>4830.1_2569_C.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>4864.8_1353_E.</t>
+          <t>5093.1_1543_E.</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>10348.3_2647_S.</t>
+          <t>2510.2_1366_V.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>12006.1_5290_T.</t>
+          <t>5422.4_1911_G.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>5235.4_1766_P.</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>10005.5_2697_V.</t>
+          <t>1083.2_390_M.</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>14009.7_4401_V.</t>
+          <t>611.2_221_M.</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>1206.7_12400_M.</t>
+          <t>5049.0_2240_C.</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>10016.9_3028_M.</t>
+          <t>5296.8_1844_P.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>21106.2_7925_P.</t>
+          <t>1012.0_375_E.</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>6818.2_2036_P.</t>
+          <t>14117.6_3844_M.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>6011.5_2408_A.</t>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>10030.1_3124_M.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>6518.4_2914_A.</t>
+          <t>1885.0_952_L.</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>22002.4_8469_M.</t>
+          <t>1443.0_851_A.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>4781.2_1507_A.</t>
+          <t>10003.1_5062_V.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>5003.2_1389_E.</t>
+          <t>5581.6_3687_P.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>12521.4_4814_M.</t>
+          <t>10012.3_3067_S.</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>8978.9_3078_G.</t>
+          <t>4576.3_2084_S.</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>13344.7_5916_G.</t>
+          <t>2305.1_940_S.</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>10013.4_3721_G.</t>
+          <t>21114.4_6098_P.</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>4791.5_1524_E.</t>
+          <t>5981.9_2551_P.</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>7127.8_1843_G.</t>
+          <t>4688.1_2291_C.</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>5007.4_1601_A.</t>
+          <t>4814.5_1705_🔋.</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>5072.4_1931_S.</t>
+          <t>4850.9_2239_C.</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>5724.1_3694_S.</t>
+          <t>4678.8_1840_A.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>8899.2_2910_S.</t>
+          <t>10106.6_2889_P.</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>5008.2_1646_A.</t>
+          <t>4932.4_1545_E.</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>4028.8_1699_L.</t>
+          <t>9013.7_2337_M.</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>4768.0_1875_L.</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>7516.9_3203_A.</t>
+          <t>5904.3_2699_P.</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>4532.9_2322_L.</t>
+          <t>7390.6_2590_E.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>6035.0_2481_P.</t>
+          <t>7022.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>5004.1_1610_M.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>10027.3_2906_P.</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>5020.6_1328_M.</t>
+          <t>600.2_261_L.</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>5011.9_1594_P.</t>
+          <t>10016.9_3028_M.</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>5022.5_1222_P.</t>
+          <t>10012.1_3139_S.</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>12006.9_5463_P.</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>5451.1_1905_T.</t>
+          <t>10030.0_3041_G.</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>11005.3_5159_P.</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>10030.0_3041_G.</t>
+          <t>10003.8_3195_S.</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>5007.1_1751_T.</t>
+          <t>9005.3_4344_A.</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>4540.8_1823_A.</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>791.5_266_G.</t>
+          <t>13005.6_6018_P.</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>123.0_5992_A.</t>
+          <t>6012.3_2200_M.</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>6006.1_2236_V.</t>
+          <t>10023.3_4468_A.</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>20105.6_7766_F.</t>
+          <t>5008.2_1646_A.</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>5005.8_1527_S.</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>15057.9_8625_F.</t>
+          <t>10020.8_2989_M.</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>8200.8_2347_T.</t>
+          <t>10025.6_4018_G.</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>5144.4_2349_P.</t>
+          <t>8104.2_2652_M.</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>15637.2_5789_G.</t>
+          <t>2060.0_802_S.</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>3023.2_962_S.</t>
+          <t>4886.1_2212_V.</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>2735.8_959_S.</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>8724.4_2500_M.</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>208.3_85_P.</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>7186.5_2708_S.</t>
+          <t>3026.1_1490_A.</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>5139.2_2082_G.</t>
+          <t>1020.0_679_T.</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>657.7_273_S.</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>8618.0_2344_P.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>531.0_343_A.</t>
+          <t>5036.1_2201_C.</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>7243.5_2118_G.</t>
+          <t>7312.2_2446_G.</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>8008.0_2930_A.</t>
+          <t>773.5_238_S.</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>5224.2_2340_C.</t>
+          <t>5007.4_1601_A.</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>4153.2_3559_P.</t>
+          <t>8618.0_2344_P.</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>2504.7_703_🔋.</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>5356.1_1825_T.</t>
+          <t>10001.9_4466_P.</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>4613.1_1806_A.</t>
+          <t>7420.2_4318_C.</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>18107.4_4577_M.</t>
+          <t>2783.5_952_S.</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>7576.8_2823_P.</t>
+          <t>5100.0_2587_A.</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>37036.6_17889_F.</t>
+          <t>1206.7_12400_M.</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>10004.6_2845_V.</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>5017.7_1147_M.</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>10007.4_3588_V.</t>
+          <t>3029.5_1536_G.</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>5006.8_1080_M.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>5299.8_2406_C.</t>
+          <t>8218.3_2327_P.</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>1002.7_460_S.</t>
+          <t>21207.4_6474_V.</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>5022.0_1862_A.</t>
+          <t>7516.9_3203_A.</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>2000.0_724_A.</t>
+          <t>5770.8_2848_G.</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>4692.9_1546_P.</t>
+          <t>5002.9_1487_P.</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>26010.2_9812_F.</t>
+          <t>5064.3_1832_F.</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>12006.1_5290_X.</t>
+          <t>14019.6_6253_L.</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>10106.6_2889_P.</t>
+          <t>10001.3_4206_G.</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>5981.9_2551_P.</t>
+          <t>5014.5_1497_G.</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>9029.6_4595_P.</t>
+          <t>8978.9_3078_G.</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>5299.8_2406_C.</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>10031.8_2663_P.</t>
+          <t>10005.2_3808_G.</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>5282.8_2392_C.</t>
+          <t>2004.9_754_S.</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>12008.4_3832_G.</t>
+          <t>6518.4_2914_A.</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>8367.5_4269_C.</t>
+          <t>5043.1_2254_C.</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>4932.4_1545_E.</t>
+          <t>8008.0_2930_A.</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>10027.3_2906_P.</t>
+          <t>7604.2_3303_P.</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>8013.1_2082_P.</t>
+          <t>2051.8_860_S.</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>15504.3_3950_M.</t>
+          <t>5010.3_1888_G.</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>7012.2_4093_P.</t>
+          <t>6600.2_1915_M.</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>9507.9_2851_M.</t>
+          <t>7012.1_3931_🔋.</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>6804.1_2088_P.</t>
+          <t>4078.1_1810_A.</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>5163.5_1775_V.</t>
+          <t>1011.0_396_L.</t>
         </is>
       </c>
     </row>
@@ -3222,959 +3222,1127 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>14019.6_6253_L.</t>
+          <t>8442.5_3038_G.</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>16008.9_5968_S.</t>
+          <t>5126.8_1941_G.</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>6345.4_2376_S.</t>
+          <t>8200.8_2347_T.</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>4729.8_2058_P.</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>5000.2_1932_E.</t>
+          <t>5004.0_2103_C.</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>5256.5_1535_S.</t>
+          <t>10007.8_2668_V.</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>6005.3_2226_A.</t>
+          <t>5119.6_3153_M.</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>3010.0_1424_A.</t>
+          <t>3019.8_1453_F.</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>9791.4_3527_G.</t>
+          <t>10006.0_2772_V.</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>5010.3_1888_G.</t>
+          <t>10138.8_3268_X.</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>9012.4_2700_M.</t>
+          <t>6007.1_3172_F.</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>7569.4_2477_V.</t>
+          <t>6004.0_2559_P.</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>5009.1_2246_C.</t>
+          <t>960.0_1109_A.</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>16397.3_4254_S.</t>
+          <t>8196.1_2807_T.</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>10003.3_3845_P.</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>9020.0_2605_M.</t>
+          <t>5005.9_1755_X.</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>5010.3_3392_P.</t>
+          <t>15016.9_6221_G.</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>8351.7_4153_C.</t>
+          <t>7569.4_2477_V.</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>4821.0_1857_P.</t>
+          <t>9562.8_3145_M.</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>7090.6_3340_A.</t>
+          <t>18516.8_6699_G.</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>9007.1_3080_P.</t>
+          <t>6047.4_2816_T.</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>2783.5_952_S.</t>
+          <t>5020.6_1328_M.</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>8724.4_2500_M.</t>
+          <t>5014.3_1731_F.</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>13023.5_5156_L.</t>
+          <t>5522.8_2716_V.</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>8196.1_2807_T.</t>
+          <t>5031.8_2047_P.</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>600.2_261_L.</t>
+          <t>5000.6_1856_M.</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>6010.6_2144_A.</t>
+          <t>7230.5_2794_V.</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>10007.8_2668_V.</t>
+          <t>1884.9_866_S.</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>6005.3_2226_A.</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>8006.7_2244_V.</t>
+          <t>4797.2_1541_G.</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>5827.8_2106_S.</t>
+          <t>6779.9_2003_E.</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>7001.2_3357_M.</t>
+          <t>3010.0_1685_A.</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>6818.2_2036_P.</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>14009.0_5498_A.</t>
+          <t>7502.4_3467_P.</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>10006.5_3648_X.</t>
+          <t>8120.9_2737_G.</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>10012.1_3139_S.</t>
+          <t>5011.9_1594_P.</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>10022.1_2875_M.</t>
+          <t>8506.3_4050_C.</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>21124.1_8011_F.</t>
+          <t>2761.5_1068_S.</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>4214.8_2018_A.</t>
+          <t>15200.8_10718_F.</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>2185.4_792_S.</t>
+          <t>5018.0_1121_M.</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>3551.6_1303_S.</t>
+          <t>5580.0_2471_A.</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>2036.1_839_S.</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>4077.1_1454_S.</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>12013.5_4635_X.</t>
+          <t>9639.7_4763_P.</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>2036.1_839_S.</t>
+          <t>7006.7_5717_S.</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>419.0_180_P.</t>
+          <t>8367.5_4269_C.</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>9006.5_3085_X.</t>
+          <t>5072.4_1931_S.</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>4786.5_1898_P.</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>3757.2_1716_A.</t>
+          <t>5007.1_1751_T.</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>3138.1_1120_S.</t>
+          <t>1629.5_671_F.</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>4150.2_2042_C.</t>
+          <t>9415.9_3699_G.</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>5005.8_1527_S.</t>
+          <t>6103.6_2241_G.</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>12002.7_4232_S.</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>1020.0_679_T.</t>
+          <t>15010.8_6619_G.</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>16520.2_4844_M.</t>
+          <t>4532.9_2322_L.</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>4850.9_2239_C.</t>
+          <t>5144.4_2349_P.</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>10003.7_2721_V.</t>
+          <t>5242.7_1657_S.</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>6779.9_2003_E.</t>
+          <t>5029.4_1585_P.</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>5188.5_1799_S.</t>
+          <t>6113.5_2883_C.</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>5064.2_1636_G.</t>
+          <t>21250.2_9506_P.</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>2186.2_736_G.</t>
+          <t>7243.5_2118_G.</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>5028.5_4433_S.</t>
+          <t>4013.7_1173_V.</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>6084.1_2156_V.</t>
+          <t>17003.0_7696_P.</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>10030.5_4765_C.</t>
+          <t>5137.9_2401_C.</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>5621.6_2375_P.</t>
+          <t>9012.4_2700_M.</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>8047.1_2948_G.</t>
+          <t>5028.5_4433_S.</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>8506.3_4050_C.</t>
+          <t>56121.5_25636_F.</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>4101.5_1485_V.</t>
+          <t>7992.7_2506_F.</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>1443.0_851_A.</t>
+          <t>4731.9_1407_T.</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>11214.0_4224_V.</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>5040.0_2514_C.</t>
+          <t>401.2_179_S.</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>10006.0_2772_V.</t>
+          <t>553.2_224_S.</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>6600.2_1915_M.</t>
+          <t>5238.0_2781_F.</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>4974.4_1533_E.</t>
+          <t>8481.2_2463_🔋.</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>15186.5_3866_S.</t>
+          <t>15637.2_5789_G.</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>3010.0_1685_A.</t>
+          <t>3023.2_962_S.</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>6036.4_2875_V.</t>
+          <t>4735.2_997_S.</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>18102.7_4949_M.</t>
+          <t>5022.0_1862_A.</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>10005.2_3808_G.</t>
+          <t>5282.8_2392_C.</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>5001.9_1291_V.</t>
+          <t>1701.7_720_F.</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>8004.6_2357_G.</t>
+          <t>12545.4_3039_S.</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>8396.0_2595_S.</t>
+          <t>5287.4_1835_V.</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>10025.6_4018_G.</t>
+          <t>15010.0_6802_L.</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>21114.4_6098_P.</t>
+          <t>5010.0_1872_A.</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>1366.2_487_L.</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>7024.3_3266_L.</t>
+          <t>2557.8_1206_V.</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>4619.4_1440_S.</t>
+          <t>5033.4_1976_M.</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>4966.0_1709_G.</t>
+          <t>2064.3_708_S.</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>7598.7_2799_S.</t>
+          <t>3551.6_1303_S.</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>13008.2_4958_P.</t>
+          <t>15004.3_4718_G.</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>5126.8_1941_G.</t>
+          <t>2011.7_731_S.</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>2011.7_731_S.</t>
+          <t>5009.1_2246_C.</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>4972.5_2522_S.</t>
+          <t>21124.1_8011_F.</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>4540.8_1823_A.</t>
+          <t>4619.4_1440_S.</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>5040.0_2299_A.</t>
+          <t>10277.3_4318_L.</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>4921.0_2491_A.</t>
+          <t>6006.6_2009_P.</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>3029.5_1536_G.</t>
+          <t>4613.1_1806_A.</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>3010.0_1289_A.</t>
+          <t>25020.8_7832_V.</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>4705.5_1241_G.</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>10008.1_2966_M.</t>
+          <t>5020.4_2167_C.</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>7502.4_3467_P.</t>
+          <t>10031.8_2663_P.</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>2060.0_802_S.</t>
+          <t>7015.4_2141_T.</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>10021.0_4009_G.</t>
+          <t>7880.9_2433_E.</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>15016.9_6221_G.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>5027.8_1361_P.</t>
+          <t>26010.2_9812_F.</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>7593.7_2701_E.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>6006.6_2009_P.</t>
+          <t>10030.5_4765_C.</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>7003.6_2437_P.</t>
+          <t>5005.4_2618_L.</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>18665.3_4638_S.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>6004.0_2559_P.</t>
+          <t>1432.9_3942_M.</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>3026.1_1490_A.</t>
+          <t>7127.8_1843_G.</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>17194.0_6301_S.</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>6622.5_2224_E.</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>17003.0_7696_P.</t>
+          <t>2175.4_712_S.</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>10001.3_4206_G.</t>
+          <t>3597.6_2910_E.</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>3012.4_1258_P.</t>
+          <t>6007.1_2393_M.</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>2064.3_708_S.</t>
+          <t>3757.2_1716_A.</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>15194.4_3911_S.</t>
+          <t>9555.5_5689_S.</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>6007.1_2393_M.</t>
+          <t>10643.3_3263_S.</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>2761.5_1068_S.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>5004.0_2103_C.</t>
+          <t>10533.4_4020_F.</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>4896.8_2251_L.</t>
+          <t>4028.8_1699_L.</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>12524.7_3259_S.</t>
+          <t>2185.4_792_S.</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>12022.7_5417_L.</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>5008.0_2402_P.</t>
+          <t>6036.4_2875_V.</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>4013.7_1173_V.</t>
+          <t>4763.8_1720_P.</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>5008.1_1825_M.</t>
+          <t>8416.2_4091_P.</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>10030.1_3124_M.</t>
+          <t>6661.8_3736_P.</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>4797.2_1541_G.</t>
+          <t>10055.2_3237_T.</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>1114.9_359_S.</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>1701.7_720_F.</t>
+          <t>10348.3_2647_S.</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>5000.5_1919_P.</t>
+          <t>10006.9_3646_X.</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>6536.2_2241_P.</t>
+          <t>10003.7_2721_V.</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>10011.5_3070_S.</t>
+          <t>8132.9_2716_S.</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>7145.5_2856_E.</t>
+          <t>10062.5_2886_M.</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>3089.9_1508_C.</t>
+          <t>7083.1_2912_G.</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>3798.9_1319_S.</t>
+          <t>10002.4_5136_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>7598.7_2799_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>4781.2_1507_A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>4972.5_2522_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>4969.4_2146_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>5021.7_1930_A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>4788.2_1476_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>1467.9_482_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>10021.0_4009_G.</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>5869.6_2613_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>10013.4_3721_G.</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>2000.0_724_A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>5827.8_2106_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>2556.5_1160_M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>12524.7_3259_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>4994.4_1534_T.</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>4974.4_1533_E.</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>791.5_266_G.</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>15194.4_3911_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>6010.6_2144_A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>21141.5_8155_F.</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>7419.2_3469_F.</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>5188.5_1799_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>6610.9_1738_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>8092.0_4532_P.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_500km_2026.xlsx
+++ b/Ranking_CNB_500km_2026.xlsx
@@ -488,12 +488,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>342,0 km</t>
+          <t>345,6 km</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.382 m</t>
+          <t>3.420 m</t>
         </is>
       </c>
     </row>
@@ -522,12 +522,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>259,8 km</t>
+          <t>266,0 km</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.062 m</t>
+          <t>3.145 m</t>
         </is>
       </c>
     </row>
@@ -687,34 +687,34 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Duda X.</t>
+          <t>Naiane C.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>146,7 km</t>
+          <t>149,1 km</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.647 m</t>
+          <t>1.420 m</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Naiane C.</t>
+          <t>Duda X.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>142,1 km</t>
+          <t>146,7 km</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.363 m</t>
+          <t>1.647 m</t>
         </is>
       </c>
     </row>
@@ -760,12 +760,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>121,3 km</t>
+          <t>126,3 km</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>966 m</t>
+          <t>1.001 m</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A475"/>
+  <dimension ref="A1:A479"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1031,3318 +1031,3346 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>6084.1_2156_V.</t>
+          <t>18665.3_4638_S.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10006.9_3646_F.</t>
+          <t>6182.8_2116_G.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>6536.2_2241_P.</t>
+          <t>11214.0_4224_V.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>14119.3_5262_S.</t>
+          <t>21207.4_6474_V.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3138.1_1120_S.</t>
+          <t>6661.8_3736_P.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10005.5_2697_V.</t>
+          <t>7025.7_3094_C.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>17194.0_6301_S.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>1380.0_562_A.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>7003.6_2437_P.</t>
+          <t>15057.9_8625_F.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5301.0_2064_F.</t>
+          <t>5382.2_2690_M.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6035.0_2481_P.</t>
+          <t>4786.5_1898_P.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5040.0_2971_A.</t>
+          <t>10106.6_3354_M.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3006.0_1286_M.</t>
+          <t>3026.1_1490_A.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6038.2_2121_P.</t>
+          <t>1012.0_375_E.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>7593.7_2701_E.</t>
+          <t>8416.2_4091_P.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>9209.1_3141_E.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10011.5_3070_S.</t>
+          <t>10718.1_9873_S.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5004.4_1614_A.</t>
+          <t>8481.2_2463_🔋.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>13008.2_4958_P.</t>
+          <t>1432.9_3942_M.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4017.3_1883_C.</t>
+          <t>2305.1_940_S.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>18102.7_4949_M.</t>
+          <t>5238.0_2781_F.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>4153.2_3559_P.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6804.1_2088_P.</t>
+          <t>773.5_238_S.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>6833.7_2100_G.</t>
+          <t>5064.3_1832_F.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>3029.5_1536_G.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>4153.2_3559_P.</t>
+          <t>5020.6_1328_M.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5356.1_1825_T.</t>
+          <t>6804.1_2088_P.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1002.7_460_S.</t>
+          <t>8200.5_2738_M.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>7186.5_2708_S.</t>
+          <t>10006.0_2772_V.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>5981.9_2551_P.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5085.1_1840_G.</t>
+          <t>7003.6_2437_P.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>16008.9_5968_S.</t>
+          <t>4613.1_1806_A.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>6011.5_2408_A.</t>
+          <t>17012.6_5869_T.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>6011.8_1873_M.</t>
+          <t>5579.8_1990_E.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>6620.4_2477_P.</t>
+          <t>11005.3_5159_P.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>16520.2_4844_M.</t>
+          <t>2355.5_726_S.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>9756.3_2793_M.</t>
+          <t>7006.7_5717_S.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>4937.4_1783_A.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3004.6_746_V.</t>
+          <t>10174.3_3680_S.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>4821.0_1857_P.</t>
+          <t>5522.8_2716_V.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>5579.8_1990_E.</t>
+          <t>10010.0_2910_V.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>14009.7_4401_V.</t>
+          <t>10643.3_3263_S.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>7024.3_3266_L.</t>
+          <t>2186.2_736_G.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>5224.2_2340_C.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>18107.4_4577_M.</t>
+          <t>1443.0_851_A.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>5365.6_2437_C.</t>
+          <t>15223.0_6245_P.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>12006.1_5290_T.</t>
+          <t>6518.4_2914_A.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>6012.6_2984_P.</t>
+          <t>10003.1_5062_V.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>53755.6_36604_F.</t>
+          <t>6345.4_2376_S.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>9555.5_5689_S.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>5025.8_1214_P.</t>
+          <t>7576.8_2823_P.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>4886.1_2212_M.</t>
+          <t>10030.5_4765_C.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>123.0_5992_A.</t>
+          <t>4896.8_2251_L.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>4864.8_1353_E.</t>
+          <t>9756.3_2793_M.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>5040.0_2514_C.</t>
+          <t>8047.1_2948_G.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2629.2_1249_V.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2186.2_736_G.</t>
+          <t>8092.0_4532_P.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>10006.5_3648_X.</t>
+          <t>10023.3_4468_A.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>5010.3_3392_P.</t>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>4791.5_1524_E.</t>
+          <t>1083.2_390_M.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>5163.5_1775_V.</t>
+          <t>16397.3_4254_S.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>5004.9_1790_A.</t>
+          <t>3010.0_1289_A.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>6016.7_2122_M.</t>
+          <t>5158.6_2220_C.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>5139.2_2082_G.</t>
+          <t>16520.2_4844_M.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>6053.8_2077_M.</t>
+          <t>6103.6_2241_G.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1018.4_335_M.</t>
+          <t>5580.0_2471_A.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>4000.6_1659_S.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>6012.6_2984_P.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>3010.0_1289_A.</t>
+          <t>5009.1_2246_C.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>5086.0_1810_G.</t>
+          <t>37036.6_17889_F.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>5581.6_3687_P.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>8024.4_2933_S.</t>
+          <t>6620.4_2477_P.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>419.0_180_P.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>5027.8_1361_P.</t>
+          <t>5256.5_1535_S.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>10277.3_4318_L.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>6007.4_1804_G.</t>
+          <t>2175.4_712_S.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>4790.7_1897_F.</t>
+          <t>8978.9_3078_G.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>14004.5_5478_M.</t>
+          <t>3010.0_1424_A.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>25020.8_7832_V.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>6003.3_2987_M.</t>
+          <t>7186.5_2708_S.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>9791.4_3527_G.</t>
+          <t>5163.5_1775_V.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>3735.9_1928_V.</t>
+          <t>960.0_1109_A.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1034.3_279_M.</t>
+          <t>6007.1_2393_M.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>21106.2_7925_P.</t>
+          <t>7243.5_2118_G.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>4763.8_1720_P.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>7012.2_4093_P.</t>
+          <t>4788.2_1476_P.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>13023.5_5156_L.</t>
+          <t>6012.3_2200_M.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>8006.7_2244_V.</t>
+          <t>4729.8_2058_P.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>3010.0_1424_A.</t>
+          <t>10138.8_3268_X.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>2556.5_1160_M.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>14009.0_5498_A.</t>
+          <t>18102.7_4949_M.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>3039.1_1013_L.</t>
+          <t>3757.2_1716_A.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>5022.5_1222_P.</t>
+          <t>3059.2_956_T.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1380.0_562_A.</t>
+          <t>5072.5_1592_S.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>10503.6_3278_M.</t>
+          <t>10003.3_3845_P.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>22008.4_8412_F.</t>
+          <t>5007.4_1601_A.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>3012.4_1258_P.</t>
+          <t>1020.0_679_T.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>7039.1_2754_S.</t>
+          <t>12006.9_5463_P.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>4896.8_2251_L.</t>
+          <t>4830.1_2569_C.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1152.4_938_S.</t>
+          <t>5018.0_1121_M.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>5382.2_2690_M.</t>
+          <t>6536.2_2241_P.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>3089.9_1508_C.</t>
+          <t>7090.6_3340_A.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>22320.3_9183_F.</t>
+          <t>13005.6_6018_P.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>14009.7_4401_V.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>7114.0_2850_S.</t>
+          <t>5422.4_1911_G.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>8187.1_2322_M.</t>
+          <t>208.3_85_P.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>6006.1_2236_V.</t>
+          <t>419.0_180_P.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>6345.4_2376_S.</t>
+          <t>8396.0_2595_S.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>9007.1_3080_P.</t>
+          <t>10055.2_3237_T.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>6012.6_2984_F.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>3412.3_1947_C.</t>
+          <t>5356.1_1825_T.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>4177.9_1557_T.</t>
+          <t>4731.9_1407_T.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>14014.7_3537_S.</t>
+          <t>5004.8_1628_M.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>4921.0_2491_A.</t>
+          <t>10001.9_4466_P.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>7145.5_2856_E.</t>
+          <t>5137.9_2401_C.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>7576.8_2823_P.</t>
+          <t>2185.4_792_S.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>11527.8_4172_V.</t>
+          <t>5004.5_1548_A.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>9029.6_4595_P.</t>
+          <t>2558.7_905_S.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>15504.3_3950_M.</t>
+          <t>15194.4_3911_S.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>9507.9_2851_M.</t>
+          <t>6011.8_1873_M.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>10008.1_2966_M.</t>
+          <t>4932.4_1545_E.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>5224.2_2340_C.</t>
+          <t>7022.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>6173.6_2865_M.</t>
+          <t>10030.1_3124_M.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>4150.2_2042_C.</t>
+          <t>9005.3_4344_A.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>5040.0_2299_A.</t>
+          <t>2880.9_1210_L.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>20105.6_7766_F.</t>
+          <t>6046.5_3239_S.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>8396.0_2595_S.</t>
+          <t>6818.2_2036_P.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>10025.5_3684_F.</t>
+          <t>1701.7_720_F.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2629.2_1249_M.</t>
+          <t>4177.9_1557_T.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>5621.6_2375_P.</t>
+          <t>10241.7_3826_G.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>10007.4_3588_V.</t>
+          <t>16008.9_5968_S.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>6951.4_2856_S.</t>
+          <t>10007.4_3588_V.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>10007.8_2733_V.</t>
+          <t>10006.5_3648_X.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>10010.0_2910_V.</t>
+          <t>600.2_261_L.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>4966.0_1709_G.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>5004.8_1628_M.</t>
+          <t>5006.8_1080_M.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>611.2_221_M.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>553.2_224_S.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>6903.6_2566_G.</t>
+          <t>8253.0_2972_🔋.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>9020.0_2605_M.</t>
+          <t>6006.1_2236_V.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>4966.0_1709_G.</t>
+          <t>4150.2_2042_C.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>4101.5_1485_V.</t>
+          <t>4790.7_1897_F.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>531.0_343_A.</t>
+          <t>1152.4_938_S.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>8047.1_2948_G.</t>
+          <t>1114.9_359_S.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>15057.9_8625_F.</t>
+          <t>6833.7_2100_G.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>3798.9_1319_S.</t>
+          <t>5043.1_2254_C.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>7090.6_3340_A.</t>
+          <t>1002.7_460_S.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>5004.1_1610_M.</t>
+          <t>2047.9_924_L.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>5158.6_2220_C.</t>
+          <t>7001.2_3357_M.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>4692.9_1546_P.</t>
+          <t>6472.0_2501_S.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>5152.8_1800_G.</t>
+          <t>3019.8_1453_F.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>6028.3_2419_L.</t>
+          <t>6004.0_2559_P.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>5081.5_1647_G.</t>
+          <t>14019.6_6253_L.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>6622.5_2224_E.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>1027.7_364_S.</t>
+          <t>7604.2_3303_P.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>37036.6_17889_F.</t>
+          <t>4000.6_1659_S.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>5004.5_1548_A.</t>
+          <t>5021.7_1930_A.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>5000.5_1919_P.</t>
+          <t>3798.9_1319_S.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>7874.8_2223_M.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>8899.2_2910_S.</t>
+          <t>10006.9_3646_X.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>5072.5_1592_S.</t>
+          <t>8200.8_2347_T.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>16397.3_4254_S.</t>
+          <t>5000.6_1856_M.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>8351.7_4153_C.</t>
+          <t>10006.9_3646_F.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>5003.2_1389_E.</t>
+          <t>5770.8_2848_G.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>5000.2_1932_E.</t>
+          <t>2036.1_839_S.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>4327.6_1237_P.</t>
+          <t>21124.1_8011_F.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>5064.2_1636_G.</t>
+          <t>5008.0_2402_P.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>12013.5_4635_X.</t>
+          <t>6610.9_1738_P.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>5008.1_1825_M.</t>
+          <t>1885.0_952_L.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>5256.5_1535_S.</t>
+          <t>5036.1_2201_C.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>5005.0_1309_M.</t>
+          <t>4028.8_1699_L.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2558.7_905_S.</t>
+          <t>8004.6_2357_G.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>9006.5_3085_X.</t>
+          <t>5010.3_3392_P.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2880.9_1210_L.</t>
+          <t>56121.5_25636_F.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>5008.0_2402_P.</t>
+          <t>18107.4_4577_M.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>10020.8_2989_M.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>4700.4_1216_V.</t>
+          <t>8024.4_2933_S.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>4899.2_1459_A.</t>
+          <t>4864.8_1353_E.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>8004.6_2357_G.</t>
+          <t>22002.4_8469_M.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>5051.4_1993_M.</t>
+          <t>4814.5_1705_🔋.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>13344.7_5916_G.</t>
+          <t>4791.5_1524_E.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>8200.5_2738_M.</t>
+          <t>5152.8_1800_G.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>12008.4_3832_G.</t>
+          <t>5869.6_2613_P.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>123.0_5992_A.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>4214.8_2018_A.</t>
+          <t>10021.0_4009_G.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2047.9_924_L.</t>
+          <t>8006.7_2244_V.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>22002.4_8469_M.</t>
+          <t>6903.6_2566_G.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>5006.8_1080_M.</t>
+          <t>5100.0_2587_A.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>5013.9_1673_A.</t>
+          <t>8008.0_2930_A.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>15186.5_3866_S.</t>
+          <t>10016.9_3028_M.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>5001.9_1291_V.</t>
+          <t>7083.1_2912_G.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>15223.0_6245_P.</t>
+          <t>6010.6_2144_A.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>7025.4_3008_L.</t>
+          <t>9639.7_4763_P.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>8013.1_2082_P.</t>
+          <t>5014.8_2009_A.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>12006.1_5290_X.</t>
+          <t>4532.9_2322_L.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>5724.1_3694_S.</t>
+          <t>6241.6_2497_P.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>10718.1_9873_S.</t>
+          <t>9012.4_2700_M.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>12342.9_3211_M.</t>
+          <t>15186.5_3866_S.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>5018.2_1981_A.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>3059.2_956_T.</t>
+          <t>6016.7_2122_M.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>18665.3_4638_S.</t>
+          <t>5028.5_4433_S.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>10241.7_3826_G.</t>
+          <t>5235.4_1766_P.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2002.2_938_P.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>5451.1_1905_T.</t>
+          <t>12006.1_5290_T.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>6241.6_2497_P.</t>
+          <t>5004.9_1790_A.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>4917.5_2381_T.</t>
+          <t>10005.5_2697_V.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>3958.9_1777_P.</t>
+          <t>6035.0_2481_P.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>7985.2_2173_P.</t>
+          <t>6038.2_2121_P.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>7001.2_3357_M.</t>
+          <t>2629.2_1249_M.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>10022.1_2875_M.</t>
+          <t>12326.4_4833_S.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>5014.8_2009_A.</t>
+          <t>7025.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>4830.1_2569_C.</t>
+          <t>8367.5_4269_C.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>5093.1_1543_E.</t>
+          <t>2557.8_1206_V.</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2510.2_1366_V.</t>
+          <t>10503.6_3278_M.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>5422.4_1911_G.</t>
+          <t>9507.9_2851_M.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>5235.4_1766_P.</t>
+          <t>4101.5_1485_V.</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>1083.2_390_M.</t>
+          <t>3005.2_1040_L.</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>611.2_221_M.</t>
+          <t>5011.9_1594_P.</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>5049.0_2240_C.</t>
+          <t>5029.4_1585_P.</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>5296.8_1844_P.</t>
+          <t>5051.4_1993_M.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>1012.0_375_E.</t>
+          <t>12342.9_3211_M.</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>14117.6_3844_M.</t>
+          <t>6137.8_2406_L.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>4013.7_1173_V.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>10030.1_3124_M.</t>
+          <t>8724.4_2500_M.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>1885.0_952_L.</t>
+          <t>15504.3_3950_M.</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>1443.0_851_A.</t>
+          <t>8013.1_2082_P.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>10003.1_5062_V.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>5581.6_3687_P.</t>
+          <t>2735.8_959_S.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>10012.3_3067_S.</t>
+          <t>7114.0_2850_S.</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>4576.3_2084_S.</t>
+          <t>15010.0_6802_L.</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>21114.4_6098_P.</t>
+          <t>5093.1_1543_E.</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>5981.9_2551_P.</t>
+          <t>4899.2_1459_A.</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>4688.1_2291_C.</t>
+          <t>5005.8_1527_S.</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>10022.1_2875_M.</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>4850.9_2239_C.</t>
+          <t>21106.2_7925_P.</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>4678.8_1840_A.</t>
+          <t>7390.6_2590_E.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>10106.6_2889_P.</t>
+          <t>8442.5_3038_G.</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>4932.4_1545_E.</t>
+          <t>12006.1_5290_X.</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>3023.2_962_S.</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>5081.5_1647_G.</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>5904.3_2699_P.</t>
+          <t>15010.8_6619_G.</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>7390.6_2590_E.</t>
+          <t>4327.6_1237_P.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>7022.4_3008_L.</t>
+          <t>5008.1_1825_M.</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>4768.0_1875_L.</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>10027.3_2906_P.</t>
+          <t>10004.6_2845_V.</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>600.2_261_L.</t>
+          <t>22008.4_8412_F.</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>10016.9_3028_M.</t>
+          <t>6779.9_2003_E.</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>10012.1_3139_S.</t>
+          <t>7127.8_1843_G.</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>7419.2_3469_F.</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>10030.0_3041_G.</t>
+          <t>2004.9_754_S.</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>11005.3_5159_P.</t>
+          <t>5027.8_1361_P.</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>10003.8_3195_S.</t>
+          <t>5621.6_2375_P.</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>9005.3_4344_A.</t>
+          <t>1467.9_482_S.</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>4540.8_1823_A.</t>
+          <t>7024.3_3266_L.</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>13005.6_6018_P.</t>
+          <t>3597.6_2910_E.</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>6012.3_2200_M.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>10023.3_4468_A.</t>
+          <t>5000.5_1919_P.</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>5008.2_1646_A.</t>
+          <t>6007.1_3172_F.</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>5005.8_1527_S.</t>
+          <t>2761.5_1068_S.</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>10020.8_2989_M.</t>
+          <t>5001.9_1291_V.</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>10025.6_4018_G.</t>
+          <t>5904.3_2699_P.</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>5188.5_1799_S.</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>2060.0_802_S.</t>
+          <t>1018.4_335_M.</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>4886.1_2212_V.</t>
+          <t>9029.6_4595_P.</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>2735.8_959_S.</t>
+          <t>11527.8_4172_V.</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>8724.4_2500_M.</t>
+          <t>4678.8_1840_A.</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>9006.5_3085_X.</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>3026.1_1490_A.</t>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>1020.0_679_T.</t>
+          <t>9007.1_3080_P.</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>657.7_273_S.</t>
+          <t>10005.2_3808_G.</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>6011.5_2408_A.</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>5036.1_2201_C.</t>
+          <t>5451.1_1905_T.</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>7312.2_2446_G.</t>
+          <t>8506.3_4050_C.</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>773.5_238_S.</t>
+          <t>10007.8_2733_V.</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>5007.4_1601_A.</t>
+          <t>5827.8_2106_S.</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>8618.0_2344_P.</t>
+          <t>5004.4_1614_A.</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>2504.7_703_🔋.</t>
+          <t>5086.0_1810_G.</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>10001.9_4466_P.</t>
+          <t>7502.4_3467_P.</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>7420.2_4318_C.</t>
+          <t>4692.9_1546_P.</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>2783.5_952_S.</t>
+          <t>10007.8_2668_V.</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>5100.0_2587_A.</t>
+          <t>1027.7_364_S.</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>1206.7_12400_M.</t>
+          <t>4972.5_2522_S.</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>10004.6_2845_V.</t>
+          <t>1206.7_12400_M.</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>5017.7_1147_M.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>3029.5_1536_G.</t>
+          <t>10011.5_3070_S.</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>8120.9_2737_G.</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>8218.3_2327_P.</t>
+          <t>3735.9_1928_V.</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>21207.4_6474_V.</t>
+          <t>2510.2_1366_V.</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>7516.9_3203_A.</t>
+          <t>7039.1_2754_S.</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>5770.8_2848_G.</t>
+          <t>10012.3_3067_S.</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>5002.9_1487_P.</t>
+          <t>10001.3_4206_G.</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>5064.3_1832_F.</t>
+          <t>4921.0_2491_A.</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>14019.6_6253_L.</t>
+          <t>5287.4_1835_V.</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>10001.3_4206_G.</t>
+          <t>5040.0_2971_A.</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>5014.5_1497_G.</t>
+          <t>12008.4_3832_G.</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>8978.9_3078_G.</t>
+          <t>8899.2_2910_S.</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>5299.8_2406_C.</t>
+          <t>2060.0_802_S.</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>10005.2_3808_G.</t>
+          <t>4917.5_2381_T.</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>2004.9_754_S.</t>
+          <t>3089.9_1508_C.</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>3004.6_746_V.</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>6518.4_2914_A.</t>
+          <t>4619.4_1440_S.</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>5043.1_2254_C.</t>
+          <t>10106.6_2889_P.</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>8008.0_2930_A.</t>
+          <t>4688.1_2291_C.</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>7604.2_3303_P.</t>
+          <t>3551.6_1303_S.</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>4886.1_2212_M.</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>5010.3_1888_G.</t>
+          <t>5010.0_1872_A.</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>6600.2_1915_M.</t>
+          <t>21141.5_8155_F.</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>7012.1_3931_🔋.</t>
+          <t>401.2_179_S.</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>4078.1_1810_A.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>5022.0_1862_A.</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>2355.5_726_S.</t>
+          <t>3412.3_1947_C.</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>8442.5_3038_G.</t>
+          <t>14117.6_3844_M.</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>5126.8_1941_G.</t>
+          <t>7230.5_2794_V.</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>8200.8_2347_T.</t>
+          <t>7015.4_2141_T.</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>4729.8_2058_P.</t>
+          <t>9013.7_2337_M.</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>5004.0_2103_C.</t>
+          <t>15016.9_6221_G.</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>10007.8_2668_V.</t>
+          <t>7992.7_2506_F.</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>5007.1_1751_T.</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>2002.2_938_P.</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>10006.0_2772_V.</t>
+          <t>8351.7_4153_C.</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>10138.8_3268_X.</t>
+          <t>1034.3_279_M.</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>6007.1_3172_F.</t>
+          <t>10348.3_2647_S.</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>6004.0_2559_P.</t>
+          <t>5072.4_1931_S.</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>960.0_1109_A.</t>
+          <t>12524.7_3259_S.</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>8196.1_2807_T.</t>
+          <t>6173.6_2865_M.</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>10003.3_3845_P.</t>
+          <t>3623.3_1426_V.</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>5005.9_1755_X.</t>
+          <t>4937.4_1783_A.</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>15016.9_6221_G.</t>
+          <t>22320.3_9183_F.</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>7569.4_2477_V.</t>
+          <t>21114.4_6098_P.</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>5144.4_2349_P.</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>18516.8_6699_G.</t>
+          <t>5008.2_1646_A.</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>6047.4_2816_T.</t>
+          <t>10012.1_3139_S.</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>5020.6_1328_M.</t>
+          <t>5010.3_1888_G.</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>7516.9_3203_A.</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>5522.8_2716_V.</t>
+          <t>10058.8_3483_F.</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>5031.8_2047_P.</t>
+          <t>10003.8_3195_S.</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>5000.6_1856_M.</t>
+          <t>6084.1_2156_V.</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>7230.5_2794_V.</t>
+          <t>10002.4_5136_P.</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>12545.4_3039_S.</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>6005.3_2226_A.</t>
+          <t>2504.7_703_🔋.</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>4797.2_1541_G.</t>
+          <t>5119.6_3153_M.</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>6779.9_2003_E.</t>
+          <t>5301.0_2064_F.</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>3010.0_1685_A.</t>
+          <t>13008.2_4958_P.</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>6818.2_2036_P.</t>
+          <t>15637.2_5789_G.</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>7502.4_3467_P.</t>
+          <t>4821.0_1857_P.</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>5017.7_1147_M.</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>5011.9_1594_P.</t>
+          <t>7598.7_2799_S.</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>8506.3_4050_C.</t>
+          <t>4850.9_2239_C.</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>2761.5_1068_S.</t>
+          <t>17003.0_7696_P.</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>15200.8_10718_F.</t>
+          <t>6951.4_2856_S.</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>5018.0_1121_M.</t>
+          <t>12013.5_4635_X.</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>5580.0_2471_A.</t>
+          <t>12002.7_4232_S.</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>2036.1_839_S.</t>
+          <t>6007.4_1804_G.</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>26010.2_9812_F.</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>9639.7_4763_P.</t>
+          <t>9562.8_3145_M.</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>7006.7_5717_S.</t>
+          <t>14119.3_5262_S.</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>8367.5_4269_C.</t>
+          <t>7012.2_4093_P.</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>5072.4_1931_S.</t>
+          <t>6047.4_2816_T.</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>4786.5_1898_P.</t>
+          <t>4077.1_1454_S.</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>5007.1_1751_T.</t>
+          <t>5139.2_2082_G.</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>1629.5_671_F.</t>
+          <t>7880.9_2433_E.</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>9415.9_3699_G.</t>
+          <t>5085.1_1840_G.</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>6103.6_2241_G.</t>
+          <t>1629.5_671_F.</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>12002.7_4232_S.</t>
+          <t>10533.4_4020_F.</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>15010.8_6619_G.</t>
+          <t>8218.3_2327_P.</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>4532.9_2322_L.</t>
+          <t>7985.2_2173_P.</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>5144.4_2349_P.</t>
+          <t>12022.7_5417_L.</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>5242.7_1657_S.</t>
+          <t>5002.9_1487_P.</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>5029.4_1585_P.</t>
+          <t>3958.9_1777_P.</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>6113.5_2883_C.</t>
+          <t>7874.8_2223_M.</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>21250.2_9506_P.</t>
+          <t>8187.1_2322_M.</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>7243.5_2118_G.</t>
+          <t>5013.9_1673_A.</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>4013.7_1173_V.</t>
+          <t>8132.9_2716_S.</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>17003.0_7696_P.</t>
+          <t>4974.4_1533_E.</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>5137.9_2401_C.</t>
+          <t>14014.7_3537_S.</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>9012.4_2700_M.</t>
+          <t>6053.8_2077_M.</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>5028.5_4433_S.</t>
+          <t>9020.0_2605_M.</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>56121.5_25636_F.</t>
+          <t>15004.3_4718_G.</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>7992.7_2506_F.</t>
+          <t>531.0_343_A.</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>6006.6_2009_P.</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>11214.0_4224_V.</t>
+          <t>2783.5_952_S.</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>401.2_179_S.</t>
+          <t>5242.7_1657_S.</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>553.2_224_S.</t>
+          <t>5365.6_2437_C.</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>5238.0_2781_F.</t>
+          <t>3138.1_1120_S.</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>8481.2_2463_🔋.</t>
+          <t>6600.2_1915_M.</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>15637.2_5789_G.</t>
+          <t>4700.4_1216_V.</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>3023.2_962_S.</t>
+          <t>9209.1_3141_E.</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>4735.2_997_S.</t>
+          <t>18516.8_6699_G.</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>5022.0_1862_A.</t>
+          <t>4735.2_997_S.</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>5282.8_2392_C.</t>
+          <t>53755.6_36604_F.</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>1701.7_720_F.</t>
+          <t>6036.4_2875_V.</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>12545.4_3039_S.</t>
+          <t>14009.0_5498_A.</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>5287.4_1835_V.</t>
+          <t>9791.4_3527_G.</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>15010.0_6802_L.</t>
+          <t>4886.1_2212_V.</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>5010.0_1872_A.</t>
+          <t>3012.4_1258_P.</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>1366.2_487_L.</t>
+          <t>10062.5_2886_M.</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>2557.8_1206_V.</t>
+          <t>10025.6_4018_G.</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>5033.4_1976_M.</t>
+          <t>4078.1_1810_A.</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>2064.3_708_S.</t>
+          <t>10003.7_2721_V.</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>3551.6_1303_S.</t>
+          <t>5005.4_2618_L.</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>15004.3_4718_G.</t>
+          <t>9415.9_3699_G.</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>2011.7_731_S.</t>
+          <t>5040.0_2299_A.</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>5009.1_2246_C.</t>
+          <t>5282.8_2392_C.</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>21124.1_8011_F.</t>
+          <t>7420.2_4318_C.</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>4619.4_1440_S.</t>
+          <t>5040.0_2514_C.</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>10277.3_4318_L.</t>
+          <t>5296.8_1844_P.</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>6006.6_2009_P.</t>
+          <t>3039.1_1013_L.</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>4613.1_1806_A.</t>
+          <t>10025.5_3684_F.</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>25020.8_7832_V.</t>
+          <t>10030.0_3041_G.</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>21442.0_7959_F.</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>5020.4_2167_C.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>10031.8_2663_P.</t>
+          <t>7593.7_2701_E.</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>5724.1_3694_S.</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>7880.9_2433_E.</t>
+          <t>2629.2_1249_V.</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>5003.2_1389_E.</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>26010.2_9812_F.</t>
+          <t>657.7_273_S.</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>12521.4_4814_M.</t>
+          <t>7312.2_2446_G.</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>10030.5_4765_C.</t>
+          <t>10031.8_2663_P.</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>5005.4_2618_L.</t>
+          <t>1366.2_487_L.</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>4017.3_1883_C.</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>1432.9_3942_M.</t>
+          <t>4214.8_2018_A.</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>7127.8_1843_G.</t>
+          <t>2064.3_708_S.</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>17194.0_6301_S.</t>
+          <t>5014.5_1497_G.</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>6622.5_2224_E.</t>
+          <t>5025.8_1214_P.</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>4994.4_1534_T.</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>3597.6_2910_E.</t>
+          <t>2011.7_731_S.</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>6007.1_2393_M.</t>
+          <t>3614.8_970_🔋.</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>3757.2_1716_A.</t>
+          <t>10013.4_3721_G.</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>9555.5_5689_S.</t>
+          <t>21250.2_9506_P.</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>10643.3_3263_S.</t>
+          <t>5049.0_2240_C.</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>2000.0_724_A.</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>10533.4_4020_F.</t>
+          <t>5004.0_2103_C.</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>4028.8_1699_L.</t>
+          <t>5299.8_2406_C.</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>2185.4_792_S.</t>
+          <t>4540.8_1823_A.</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>12022.7_5417_L.</t>
+          <t>791.5_266_G.</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>6036.4_2875_V.</t>
+          <t>5022.5_1222_P.</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>5020.4_2167_C.</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>8416.2_4091_P.</t>
+          <t>6003.3_2987_M.</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>6661.8_3736_P.</t>
+          <t>7012.1_3931_🔋.</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>10055.2_3237_T.</t>
+          <t>5064.2_1636_G.</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>1114.9_359_S.</t>
+          <t>5126.8_1941_G.</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>10348.3_2647_S.</t>
+          <t>10027.3_2906_P.</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>10006.9_3646_X.</t>
+          <t>8618.0_2344_P.</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>10003.7_2721_V.</t>
+          <t>6113.5_2883_C.</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>8132.9_2716_S.</t>
+          <t>4705.5_1241_G.</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>5031.8_2047_P.</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>7083.1_2912_G.</t>
+          <t>4891.7_1690_F.</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>10002.4_5136_P.</t>
+          <t>7145.5_2856_E.</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>7598.7_2799_S.</t>
+          <t>5005.0_1309_M.</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>4781.2_1507_A.</t>
+          <t>1011.0_396_L.</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>4972.5_2522_S.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>4969.4_2146_P.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>5021.7_1930_A.</t>
+          <t>14004.5_5478_M.</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>4788.2_1476_P.</t>
+          <t>13344.7_5916_G.</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>1467.9_482_S.</t>
+          <t>5004.1_1610_M.</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>10021.0_4009_G.</t>
+          <t>20105.6_7766_F.</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>5869.6_2613_P.</t>
+          <t>3006.0_1286_M.</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>10013.4_3721_G.</t>
+          <t>6005.3_2226_A.</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>2000.0_724_A.</t>
+          <t>4576.3_2084_S.</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>5827.8_2106_S.</t>
+          <t>8196.1_2807_T.</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>2556.5_1160_M.</t>
+          <t>8104.2_2652_M.</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>12524.7_3259_S.</t>
+          <t>2051.8_860_S.</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>4994.4_1534_T.</t>
+          <t>1884.9_866_S.</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>4974.4_1533_E.</t>
+          <t>3010.0_1685_A.</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>791.5_266_G.</t>
+          <t>5033.4_1976_M.</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>15194.4_3911_S.</t>
+          <t>3580.9_1198_S.</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>6010.6_2144_A.</t>
+          <t>6028.3_2419_L.</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>21141.5_8155_F.</t>
+          <t>5005.9_1755_X.</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>7419.2_3469_F.</t>
+          <t>15200.8_10718_F.</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>5188.5_1799_S.</t>
+          <t>4797.2_1541_G.</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>6610.9_1738_P.</t>
+          <t>7569.4_2477_V.</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>8092.0_4532_P.</t>
+          <t>4781.2_1507_A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>4969.4_2146_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>13023.5_5156_L.</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>5000.2_1932_E.</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>5014.3_1731_F.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_500km_2026.xlsx
+++ b/Ranking_CNB_500km_2026.xlsx
@@ -454,12 +454,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>674,9 km</t>
+          <t>684,0 km</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>10.347 m</t>
+          <t>10.478 m</t>
         </is>
       </c>
     </row>
@@ -471,12 +471,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>525,5 km</t>
+          <t>548,9 km</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>6.976 m</t>
+          <t>7.272 m</t>
         </is>
       </c>
     </row>
@@ -488,12 +488,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>345,6 km</t>
+          <t>355,6 km</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.420 m</t>
+          <t>3.523 m</t>
         </is>
       </c>
     </row>
@@ -505,12 +505,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>306,1 km</t>
+          <t>313,9 km</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.535 m</t>
+          <t>2.572 m</t>
         </is>
       </c>
     </row>
@@ -522,12 +522,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>266,0 km</t>
+          <t>275,3 km</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.145 m</t>
+          <t>3.275 m</t>
         </is>
       </c>
     </row>
@@ -556,12 +556,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>223,5 km</t>
+          <t>232,0 km</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.833 m</t>
+          <t>2.962 m</t>
         </is>
       </c>
     </row>
@@ -573,12 +573,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>218,0 km</t>
+          <t>227,0 km</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.417 m</t>
+          <t>2.548 m</t>
         </is>
       </c>
     </row>
@@ -607,12 +607,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>190,3 km</t>
+          <t>195,3 km</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.239 m</t>
+          <t>1.282 m</t>
         </is>
       </c>
     </row>
@@ -641,12 +641,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>163,9 km</t>
+          <t>172,5 km</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.786 m</t>
+          <t>1.915 m</t>
         </is>
       </c>
     </row>
@@ -658,12 +658,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>162,1 km</t>
+          <t>167,0 km</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.961 m</t>
+          <t>2.019 m</t>
         </is>
       </c>
     </row>
@@ -675,46 +675,46 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>159,5 km</t>
+          <t>163,7 km</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.240 m</t>
+          <t>1.242 m</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Naiane C.</t>
+          <t>Duda X.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>149,1 km</t>
+          <t>155,7 km</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.420 m</t>
+          <t>1.777 m</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Duda X.</t>
+          <t>Naiane C.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>146,7 km</t>
+          <t>149,1 km</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.647 m</t>
+          <t>1.420 m</t>
         </is>
       </c>
     </row>
@@ -738,51 +738,51 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Neydrielle V.</t>
+          <t>Izac S.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>135,6 km</t>
+          <t>136,1 km</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.318 m</t>
+          <t>1.598 m</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Alexsandro A.</t>
+          <t>Neydrielle V.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>126,3 km</t>
+          <t>135,6 km</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.001 m</t>
+          <t>1.318 m</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Izac S.</t>
+          <t>Alexsandro A.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>116,1 km</t>
+          <t>126,3 km</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.346 m</t>
+          <t>1.001 m</t>
         </is>
       </c>
     </row>
@@ -794,12 +794,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>102,0 km</t>
+          <t>112,1 km</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.253 m</t>
+          <t>1.357 m</t>
         </is>
       </c>
     </row>
@@ -823,34 +823,34 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Pierre P.</t>
+          <t>Jhonny E.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>81,5 km</t>
+          <t>87,2 km</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>846 m</t>
+          <t>922 m</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Jhonny E.</t>
+          <t>Pierre P.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>78,2 km</t>
+          <t>81,5 km</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>799 m</t>
+          <t>846 m</t>
         </is>
       </c>
     </row>
@@ -874,34 +874,34 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Eduardo T.</t>
+          <t>Filipe M.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>44,1 km</t>
+          <t>51,2 km</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>496 m</t>
+          <t>726 m</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Filipe M.</t>
+          <t>Eduardo T.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>40,7 km</t>
+          <t>44,1 km</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>571 m</t>
+          <t>496 m</t>
         </is>
       </c>
     </row>
@@ -913,12 +913,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>38,1 km</t>
+          <t>43,1 km</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>537 m</t>
+          <t>608 m</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A479"/>
+  <dimension ref="A1:A498"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1031,3346 +1031,3479 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>18665.3_4638_S.</t>
+          <t>10277.3_4318_L.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>6182.8_2116_G.</t>
+          <t>9020.0_2605_M.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>11214.0_4224_V.</t>
+          <t>7390.6_2590_E.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>21207.4_6474_V.</t>
+          <t>10001.3_4206_G.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6661.8_3736_P.</t>
+          <t>4078.1_1810_A.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>7025.7_3094_C.</t>
+          <t>4899.2_1459_A.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>17194.0_6301_S.</t>
+          <t>10110.2_3737_E.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1380.0_562_A.</t>
+          <t>7001.2_3357_M.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>15057.9_8625_F.</t>
+          <t>3010.0_1424_A.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5382.2_2690_M.</t>
+          <t>7114.0_2850_S.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4786.5_1898_P.</t>
+          <t>10485.5_4164_M.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>8978.9_3078_G.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3026.1_1490_A.</t>
+          <t>6182.8_2116_G.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1012.0_375_E.</t>
+          <t>5007.4_1601_A.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>8416.2_4091_P.</t>
+          <t>15004.3_4718_G.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>7090.6_3340_A.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10718.1_9873_S.</t>
+          <t>7992.7_2506_F.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>8481.2_2463_🔋.</t>
+          <t>5040.0_2299_A.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1432.9_3942_M.</t>
+          <t>7243.5_2118_G.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>10005.5_2697_V.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5238.0_2781_F.</t>
+          <t>9791.4_3527_G.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>4153.2_3559_P.</t>
+          <t>7230.5_2794_V.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>773.5_238_S.</t>
+          <t>7880.9_2433_E.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5064.3_1832_F.</t>
+          <t>7006.7_5717_S.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3029.5_1536_G.</t>
+          <t>5152.8_1800_G.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5020.6_1328_M.</t>
+          <t>6006.6_2009_P.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>6804.1_2088_P.</t>
+          <t>6012.6_2984_P.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>8200.5_2738_M.</t>
+          <t>4688.1_2291_C.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10006.0_2772_V.</t>
+          <t>5770.8_2848_G.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5981.9_2551_P.</t>
+          <t>22002.4_8469_M.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>7003.6_2437_P.</t>
+          <t>7420.2_4318_C.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>4613.1_1806_A.</t>
+          <t>6012.3_2200_M.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>5004.8_1628_M.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>5579.8_1990_E.</t>
+          <t>1020.0_679_T.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>11005.3_5159_P.</t>
+          <t>6007.1_2393_M.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2355.5_726_S.</t>
+          <t>4729.8_2058_P.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>7006.7_5717_S.</t>
+          <t>2558.7_905_S.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>10012.3_3067_S.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5522.8_2716_V.</t>
+          <t>3012.4_1258_P.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>10010.0_2910_V.</t>
+          <t>4153.2_3559_P.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>10643.3_3263_S.</t>
+          <t>10003.8_3195_S.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2186.2_736_G.</t>
+          <t>5012.1_1375_G.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>5224.2_2340_C.</t>
+          <t>7502.4_3467_P.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1443.0_851_A.</t>
+          <t>7145.5_2856_E.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>15223.0_6245_P.</t>
+          <t>4731.9_1407_T.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>6518.4_2914_A.</t>
+          <t>21114.4_6098_P.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>10003.1_5062_V.</t>
+          <t>1380.0_562_A.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>6345.4_2376_S.</t>
+          <t>2047.9_924_L.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>9555.5_5689_S.</t>
+          <t>2011.7_731_S.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>7576.8_2823_P.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>10030.5_4765_C.</t>
+          <t>14004.5_5478_M.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>4896.8_2251_L.</t>
+          <t>7003.6_2437_P.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>9756.3_2793_M.</t>
+          <t>5100.0_2587_A.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>8047.1_2948_G.</t>
+          <t>4821.0_1857_P.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>12521.4_4814_M.</t>
+          <t>5004.9_1790_A.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>8092.0_4532_P.</t>
+          <t>6818.2_2036_P.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>10023.3_4468_A.</t>
+          <t>6036.4_2875_V.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>4896.8_2251_L.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1083.2_390_M.</t>
+          <t>7783.3_2713_S.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>16397.3_4254_S.</t>
+          <t>6903.6_2566_G.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>3010.0_1289_A.</t>
+          <t>8120.9_2737_G.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>5158.6_2220_C.</t>
+          <t>15057.9_8625_F.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>16520.2_4844_M.</t>
+          <t>9052.9_2955_M.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>6103.6_2241_G.</t>
+          <t>5238.0_2781_F.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>5580.0_2471_A.</t>
+          <t>8200.5_2738_M.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>10503.6_3278_M.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>6012.6_2984_P.</t>
+          <t>8506.3_4050_C.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>5009.1_2246_C.</t>
+          <t>8196.1_2807_T.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>37036.6_17889_F.</t>
+          <t>5005.8_1527_S.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>5581.6_3687_P.</t>
+          <t>5072.5_1592_S.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>6620.4_2477_P.</t>
+          <t>7024.3_3266_L.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>14009.0_5498_A.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>5256.5_1535_S.</t>
+          <t>17194.0_6301_S.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10277.3_4318_L.</t>
+          <t>419.0_180_P.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>791.5_266_G.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>8978.9_3078_G.</t>
+          <t>1885.0_952_L.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>3010.0_1424_A.</t>
+          <t>6007.4_1804_G.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>25020.8_7832_V.</t>
+          <t>13023.5_5156_L.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>7186.5_2708_S.</t>
+          <t>9012.4_2700_M.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>5163.5_1775_V.</t>
+          <t>6004.0_2559_P.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>960.0_1109_A.</t>
+          <t>6007.1_3172_F.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>6007.1_2393_M.</t>
+          <t>10643.3_3263_S.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>7243.5_2118_G.</t>
+          <t>15637.2_5789_G.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>10011.5_3070_S.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>4788.2_1476_P.</t>
+          <t>10062.5_2886_M.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>6012.3_2200_M.</t>
+          <t>7874.8_2223_M.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>4729.8_2058_P.</t>
+          <t>2000.0_724_A.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>10138.8_3268_X.</t>
+          <t>6016.7_2122_M.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2556.5_1160_M.</t>
+          <t>3580.9_1198_S.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>18102.7_4949_M.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>3757.2_1716_A.</t>
+          <t>5018.0_1121_M.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>3059.2_956_T.</t>
+          <t>10020.8_2989_M.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>5072.5_1592_S.</t>
+          <t>10106.6_2889_P.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>10003.3_3845_P.</t>
+          <t>15200.8_10718_F.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>5007.4_1601_A.</t>
+          <t>2761.5_1068_S.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1020.0_679_T.</t>
+          <t>1884.9_866_S.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>1701.7_720_F.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>4830.1_2569_C.</t>
+          <t>6137.8_2406_L.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>5018.0_1121_M.</t>
+          <t>14119.3_5262_S.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>6536.2_2241_P.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>7090.6_3340_A.</t>
+          <t>11214.0_4224_V.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>13005.6_6018_P.</t>
+          <t>5036.1_2201_C.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>14009.7_4401_V.</t>
+          <t>10007.8_2733_V.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>5422.4_1911_G.</t>
+          <t>10013.4_3721_G.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>1002.7_460_S.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>419.0_180_P.</t>
+          <t>5064.3_1832_F.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>8396.0_2595_S.</t>
+          <t>5126.8_1941_G.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>10055.2_3237_T.</t>
+          <t>2510.2_1366_V.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>8481.2_2463_🔋.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>5356.1_1825_T.</t>
+          <t>5008.0_2402_P.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>5001.9_1291_V.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>5004.8_1628_M.</t>
+          <t>18102.7_4949_M.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>10001.9_4466_P.</t>
+          <t>4797.2_1541_G.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>5137.9_2401_C.</t>
+          <t>4700.4_1216_V.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2185.4_792_S.</t>
+          <t>5163.5_1775_V.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>5004.5_1548_A.</t>
+          <t>6047.4_2816_T.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2558.7_905_S.</t>
+          <t>8396.0_2595_S.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>15194.4_3911_S.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>6011.8_1873_M.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>4932.4_1545_E.</t>
+          <t>5022.5_1222_P.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>7022.4_3008_L.</t>
+          <t>7604.2_3303_P.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>10030.1_3124_M.</t>
+          <t>1206.7_12400_M.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>9005.3_4344_A.</t>
+          <t>13005.6_6018_P.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2880.9_1210_L.</t>
+          <t>15010.0_6802_L.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>17012.6_5869_T.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>6818.2_2036_P.</t>
+          <t>1012.0_375_E.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>1701.7_720_F.</t>
+          <t>12006.1_5290_T.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>4177.9_1557_T.</t>
+          <t>21250.2_9506_P.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>10241.7_3826_G.</t>
+          <t>1018.4_335_M.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>16008.9_5968_S.</t>
+          <t>5224.2_2340_C.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>10007.4_3588_V.</t>
+          <t>1432.9_3942_M.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>10006.5_3648_X.</t>
+          <t>4850.9_2239_C.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>600.2_261_L.</t>
+          <t>8104.2_2652_M.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>4966.0_1709_G.</t>
+          <t>10002.4_5136_P.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>5006.8_1080_M.</t>
+          <t>1443.0_851_A.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>611.2_221_M.</t>
+          <t>6046.5_3239_S.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>553.2_224_S.</t>
+          <t>7598.7_2799_S.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>6011.8_1873_M.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>6006.1_2236_V.</t>
+          <t>3010.0_1685_A.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>4150.2_2042_C.</t>
+          <t>531.0_343_A.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>4790.7_1897_F.</t>
+          <t>5007.1_1751_T.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1152.4_938_S.</t>
+          <t>21124.1_8011_F.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1114.9_359_S.</t>
+          <t>12524.7_3259_S.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>6833.7_2100_G.</t>
+          <t>16397.3_4254_S.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>5043.1_2254_C.</t>
+          <t>4974.4_1533_E.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>1002.7_460_S.</t>
+          <t>3412.3_1947_C.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2047.9_924_L.</t>
+          <t>2064.3_708_S.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>7001.2_3357_M.</t>
+          <t>6600.2_1915_M.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>8351.7_4153_C.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>10031.8_2663_P.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>6004.0_2559_P.</t>
+          <t>5422.4_1911_G.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>14019.6_6253_L.</t>
+          <t>9006.5_3085_X.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>6622.5_2224_E.</t>
+          <t>5002.9_1487_P.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>7604.2_3303_P.</t>
+          <t>9006.6_3366_X.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>4000.6_1659_S.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>5021.7_1930_A.</t>
+          <t>5621.6_2375_P.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>3798.9_1319_S.</t>
+          <t>5014.5_1497_G.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>5040.0_2971_A.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>10006.9_3646_X.</t>
+          <t>5005.9_1755_X.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>8200.8_2347_T.</t>
+          <t>2735.8_959_S.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>5000.6_1856_M.</t>
+          <t>9001.4_3623_P.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>10006.9_3646_F.</t>
+          <t>10010.0_2910_V.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>5770.8_2848_G.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2036.1_839_S.</t>
+          <t>553.2_224_S.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>21124.1_8011_F.</t>
+          <t>6833.7_2100_G.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>5008.0_2402_P.</t>
+          <t>6951.4_2856_S.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>6610.9_1738_P.</t>
+          <t>5000.6_1856_M.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>1885.0_952_L.</t>
+          <t>8047.1_2948_G.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>5036.1_2201_C.</t>
+          <t>1152.4_938_S.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>4028.8_1699_L.</t>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>8004.6_2357_G.</t>
+          <t>5981.9_2551_P.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>5010.3_3392_P.</t>
+          <t>15010.8_6619_G.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>56121.5_25636_F.</t>
+          <t>2880.9_1210_L.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>18107.4_4577_M.</t>
+          <t>4791.5_1524_E.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>10020.8_2989_M.</t>
+          <t>5027.8_1361_P.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>8024.4_2933_S.</t>
+          <t>5235.4_1766_P.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>4864.8_1353_E.</t>
+          <t>6620.4_2477_P.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>22002.4_8469_M.</t>
+          <t>5004.4_1614_A.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>8092.0_4532_P.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>4791.5_1524_E.</t>
+          <t>8442.5_3038_G.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>5152.8_1800_G.</t>
+          <t>10006.9_3646_X.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>5869.6_2613_P.</t>
+          <t>4886.1_2212_M.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>123.0_5992_A.</t>
+          <t>3059.2_956_T.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>10021.0_4009_G.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>8006.7_2244_V.</t>
+          <t>4150.2_2042_C.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>6903.6_2566_G.</t>
+          <t>5139.2_2082_G.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>5100.0_2587_A.</t>
+          <t>3010.0_1289_A.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>8008.0_2930_A.</t>
+          <t>4864.8_1353_E.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>10016.9_3028_M.</t>
+          <t>5086.0_1810_G.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>7083.1_2912_G.</t>
+          <t>6536.2_2241_P.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>6010.6_2144_A.</t>
+          <t>12545.4_3039_S.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>8200.8_2347_T.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>9639.7_4763_P.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>5014.8_2009_A.</t>
+          <t>13008.2_4958_P.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>4532.9_2322_L.</t>
+          <t>6779.9_2003_E.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>6241.6_2497_P.</t>
+          <t>5031.8_2047_P.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>9012.4_2700_M.</t>
+          <t>21106.2_7925_P.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>15186.5_3866_S.</t>
+          <t>2175.4_712_S.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>5018.2_1981_A.</t>
+          <t>4972.5_2522_S.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>6016.7_2122_M.</t>
+          <t>12008.4_3832_G.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>5028.5_4433_S.</t>
+          <t>9029.6_4595_P.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>5235.4_1766_P.</t>
+          <t>4937.4_1783_A.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>10008.1_2966_M.</t>
+          <t>3757.2_1716_A.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>12006.1_5290_T.</t>
+          <t>5827.8_2106_S.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>5004.9_1790_A.</t>
+          <t>53755.6_36604_F.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>10005.5_2697_V.</t>
+          <t>600.2_261_L.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>6035.0_2481_P.</t>
+          <t>6804.1_2088_P.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>6038.2_2121_P.</t>
+          <t>1083.2_390_M.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2629.2_1249_M.</t>
+          <t>6084.1_2156_V.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>5085.1_1840_G.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>7025.4_3008_L.</t>
+          <t>4901.4_2376_C.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>8367.5_4269_C.</t>
+          <t>4101.5_1485_V.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2557.8_1206_V.</t>
+          <t>1011.0_396_L.</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>10503.6_3278_M.</t>
+          <t>3138.1_1120_S.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>9507.9_2851_M.</t>
+          <t>4028.8_1699_L.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>4101.5_1485_V.</t>
+          <t>15194.4_3911_S.</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>9005.3_4344_A.</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>5011.9_1594_P.</t>
+          <t>9285.3_3279_G.</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>5029.4_1585_P.</t>
+          <t>10022.1_2875_M.</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>5051.4_1993_M.</t>
+          <t>5008.2_1646_A.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>12342.9_3211_M.</t>
+          <t>10025.6_4018_G.</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>12342.9_3211_M.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>4013.7_1173_V.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>8724.4_2500_M.</t>
+          <t>10007.4_3588_V.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>15504.3_3950_M.</t>
+          <t>10003.1_5062_V.</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>8013.1_2082_P.</t>
+          <t>21442.0_7959_F.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>5093.1_1543_E.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2735.8_959_S.</t>
+          <t>7039.1_2754_S.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>7114.0_2850_S.</t>
+          <t>2002.2_938_P.</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>15010.0_6802_L.</t>
+          <t>15504.3_3950_M.</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>5081.5_1647_G.</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>5093.1_1543_E.</t>
+          <t>8008.0_2930_A.</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>4899.2_1459_A.</t>
+          <t>5010.0_1872_A.</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>5005.8_1527_S.</t>
+          <t>10006.2_2753_V.</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>10022.1_2875_M.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>21106.2_7925_P.</t>
+          <t>7593.7_2701_E.</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>7390.6_2590_E.</t>
+          <t>7186.5_2708_S.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>8442.5_3038_G.</t>
+          <t>2355.5_726_S.</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>12006.1_5290_X.</t>
+          <t>5033.4_1976_M.</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>3023.2_962_S.</t>
+          <t>14355.0_3613_M.</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>5081.5_1647_G.</t>
+          <t>12022.7_5417_L.</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>15010.8_6619_G.</t>
+          <t>4619.4_1440_S.</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>4327.6_1237_P.</t>
+          <t>10030.0_3041_G.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>5008.1_1825_M.</t>
+          <t>4177.9_1557_T.</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>10138.8_3268_X.</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>10004.6_2845_V.</t>
+          <t>5005.0_1309_M.</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>22008.4_8412_F.</t>
+          <t>6173.6_2865_M.</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>6779.9_2003_E.</t>
+          <t>8452.7_2430_M.</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>7127.8_1843_G.</t>
+          <t>3023.2_962_S.</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>7419.2_3469_F.</t>
+          <t>9562.8_3145_M.</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2004.9_754_S.</t>
+          <t>5296.8_1844_P.</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>5027.8_1361_P.</t>
+          <t>56121.5_25636_F.</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>5621.6_2375_P.</t>
+          <t>10012.1_3139_S.</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>1467.9_482_S.</t>
+          <t>10058.8_3483_F.</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>7024.3_3266_L.</t>
+          <t>10030.1_3124_M.</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>3597.6_2910_E.</t>
+          <t>6028.3_2419_L.</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>2185.4_792_S.</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>5000.5_1919_P.</t>
+          <t>5256.5_1535_S.</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>6007.1_3172_F.</t>
+          <t>611.2_221_M.</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>2761.5_1068_S.</t>
+          <t>14014.7_3537_S.</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>5001.9_1291_V.</t>
+          <t>18107.4_4577_M.</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>5904.3_2699_P.</t>
+          <t>3551.6_1303_S.</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>5188.5_1799_S.</t>
+          <t>4077.1_1454_S.</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>1018.4_335_M.</t>
+          <t>3735.9_1928_V.</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>9029.6_4595_P.</t>
+          <t>7083.1_2912_G.</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>11527.8_4172_V.</t>
+          <t>5051.4_1993_M.</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>4678.8_1840_A.</t>
+          <t>5005.4_2618_L.</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>9006.5_3085_X.</t>
+          <t>7022.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>4692.9_1546_P.</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>9007.1_3080_P.</t>
+          <t>10241.7_3826_G.</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>10005.2_3808_G.</t>
+          <t>1027.7_364_S.</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>6011.5_2408_A.</t>
+          <t>20105.6_7766_F.</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>5451.1_1905_T.</t>
+          <t>10030.5_4765_C.</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>8506.3_4050_C.</t>
+          <t>6113.5_2883_C.</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>10007.8_2733_V.</t>
+          <t>9004.5_2927_E.</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>5827.8_2106_S.</t>
+          <t>6661.8_3736_P.</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>5004.4_1614_A.</t>
+          <t>8648.9_3219_A.</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>5086.0_1810_G.</t>
+          <t>6038.2_2121_P.</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>7502.4_3467_P.</t>
+          <t>3798.9_1319_S.</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>4692.9_1546_P.</t>
+          <t>14117.6_3844_M.</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>10007.8_2668_V.</t>
+          <t>16008.9_5968_S.</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>1027.7_364_S.</t>
+          <t>8618.0_2344_P.</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>4972.5_2522_S.</t>
+          <t>22008.4_8412_F.</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>1206.7_12400_M.</t>
+          <t>5020.4_2167_C.</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>10003.7_2721_V.</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>10011.5_3070_S.</t>
+          <t>5000.5_1919_P.</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>5009.1_2246_C.</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>3735.9_1928_V.</t>
+          <t>6345.4_2376_S.</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>2510.2_1366_V.</t>
+          <t>7419.2_3469_F.</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>7039.1_2754_S.</t>
+          <t>5013.9_1673_A.</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>10012.3_3067_S.</t>
+          <t>4768.0_1875_L.</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>10001.3_4206_G.</t>
+          <t>5869.6_2613_P.</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>4921.0_2491_A.</t>
+          <t>5020.6_1328_M.</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>5287.4_1835_V.</t>
+          <t>4781.2_1507_A.</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>5040.0_2971_A.</t>
+          <t>7012.1_3931_🔋.</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>12008.4_3832_G.</t>
+          <t>18516.8_6699_G.</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>8899.2_2910_S.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>2060.0_802_S.</t>
+          <t>5007.3_2480_V.</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>4917.5_2381_T.</t>
+          <t>2305.1_940_S.</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>3089.9_1508_C.</t>
+          <t>3006.0_1286_M.</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>3004.6_746_V.</t>
+          <t>1114.9_359_S.</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>4619.4_1440_S.</t>
+          <t>6011.5_2408_A.</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>10106.6_2889_P.</t>
+          <t>5003.2_1389_E.</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>4688.1_2291_C.</t>
+          <t>6053.8_2077_M.</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>3551.6_1303_S.</t>
+          <t>2036.1_839_S.</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>4886.1_2212_M.</t>
+          <t>4969.4_2146_P.</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>5010.0_1872_A.</t>
+          <t>5724.1_3694_S.</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>21141.5_8155_F.</t>
+          <t>10106.6_3354_M.</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>401.2_179_S.</t>
+          <t>4830.1_2569_C.</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>17003.0_7696_P.</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>5022.0_1862_A.</t>
+          <t>9093.1_3374_F.</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>3412.3_1947_C.</t>
+          <t>5580.0_2471_A.</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>14117.6_3844_M.</t>
+          <t>5029.4_1585_P.</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>7230.5_2794_V.</t>
+          <t>5043.1_2254_C.</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>10001.9_4466_P.</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>15016.9_6221_G.</t>
+          <t>1629.5_671_F.</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>7992.7_2506_F.</t>
+          <t>10718.1_9873_S.</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>5007.1_1751_T.</t>
+          <t>3958.9_1777_P.</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>2002.2_938_P.</t>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>8351.7_4153_C.</t>
+          <t>5004.1_1610_M.</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>1034.3_279_M.</t>
+          <t>4705.5_1241_G.</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>10348.3_2647_S.</t>
+          <t>5021.7_1930_A.</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>5072.4_1931_S.</t>
+          <t>4214.8_2018_A.</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>12524.7_3259_S.</t>
+          <t>4763.8_1720_P.</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>6173.6_2865_M.</t>
+          <t>5018.2_1981_A.</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>3623.3_1426_V.</t>
+          <t>5382.2_2690_M.</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>4937.4_1783_A.</t>
+          <t>3005.2_1040_L.</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>22320.3_9183_F.</t>
+          <t>6518.4_2914_A.</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>21114.4_6098_P.</t>
+          <t>10174.3_3680_S.</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>5144.4_2349_P.</t>
+          <t>11527.8_4172_V.</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>5008.2_1646_A.</t>
+          <t>7015.4_2141_T.</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>10012.1_3139_S.</t>
+          <t>10025.5_3684_F.</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>5010.3_1888_G.</t>
+          <t>10533.4_4020_F.</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>7516.9_3203_A.</t>
+          <t>5522.8_2716_V.</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>4814.5_1705_🔋.</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>10003.8_3195_S.</t>
+          <t>7569.4_2477_V.</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>6084.1_2156_V.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>10002.4_5136_P.</t>
+          <t>5025.8_1214_P.</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>12545.4_3039_S.</t>
+          <t>15186.5_3866_S.</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>2504.7_703_🔋.</t>
+          <t>4886.1_2212_V.</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>2557.8_1206_V.</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>5301.0_2064_F.</t>
+          <t>10013.0_3337_S.</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>13008.2_4958_P.</t>
+          <t>14019.6_6253_L.</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>15637.2_5789_G.</t>
+          <t>5282.8_2392_C.</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>4821.0_1857_P.</t>
+          <t>9415.9_3699_G.</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>5017.7_1147_M.</t>
+          <t>773.5_238_S.</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>7598.7_2799_S.</t>
+          <t>10004.6_2845_V.</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>4850.9_2239_C.</t>
+          <t>6035.0_2481_P.</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>17003.0_7696_P.</t>
+          <t>5188.5_1799_S.</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>6951.4_2856_S.</t>
+          <t>5022.0_1862_A.</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>12013.5_4635_X.</t>
+          <t>8187.1_2322_M.</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>12002.7_4232_S.</t>
+          <t>4735.2_997_S.</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>6007.4_1804_G.</t>
+          <t>5356.1_1825_T.</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>26010.2_9812_F.</t>
+          <t>5144.4_2349_P.</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>11005.3_5159_P.</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>14119.3_5262_S.</t>
+          <t>6005.3_2226_A.</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>7012.2_4093_P.</t>
+          <t>10005.2_3808_G.</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>6047.4_2816_T.</t>
+          <t>10006.5_3648_X.</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>9507.9_2851_M.</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>5139.2_2082_G.</t>
+          <t>5000.2_1932_E.</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>7880.9_2433_E.</t>
+          <t>4790.7_1897_F.</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>5085.1_1840_G.</t>
+          <t>8218.3_2327_P.</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>1629.5_671_F.</t>
+          <t>4932.4_1545_E.</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>10533.4_4020_F.</t>
+          <t>5072.4_1931_S.</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>8218.3_2327_P.</t>
+          <t>5028.5_4433_S.</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>7985.2_2173_P.</t>
+          <t>7025.7_3094_C.</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>12022.7_5417_L.</t>
+          <t>4921.0_2491_A.</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>5002.9_1487_P.</t>
+          <t>7985.2_2173_P.</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>3958.9_1777_P.</t>
+          <t>18665.3_4638_S.</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>7874.8_2223_M.</t>
+          <t>5017.7_1147_M.</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>8187.1_2322_M.</t>
+          <t>10348.3_2647_S.</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>5013.9_1673_A.</t>
+          <t>8253.0_2972_🔋.</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>8132.9_2716_S.</t>
+          <t>5004.0_2103_C.</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>4974.4_1533_E.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>14014.7_3537_S.</t>
+          <t>4000.6_1659_S.</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>6053.8_2077_M.</t>
+          <t>4917.5_2381_T.</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>9020.0_2605_M.</t>
+          <t>4994.4_1534_T.</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>15004.3_4718_G.</t>
+          <t>8013.1_2082_P.</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>531.0_343_A.</t>
+          <t>15223.0_6245_P.</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>6006.6_2009_P.</t>
+          <t>6241.6_2497_P.</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>2783.5_952_S.</t>
+          <t>37036.6_17889_F.</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>5242.7_1657_S.</t>
+          <t>5014.8_2009_A.</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>5365.6_2437_C.</t>
+          <t>657.7_273_S.</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>3138.1_1120_S.</t>
+          <t>16520.2_4844_M.</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>6600.2_1915_M.</t>
+          <t>12002.7_4232_S.</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>4700.4_1216_V.</t>
+          <t>2783.5_952_S.</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>9209.1_3141_E.</t>
+          <t>5011.9_1594_P.</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>18516.8_6699_G.</t>
+          <t>5064.2_1636_G.</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>4735.2_997_S.</t>
+          <t>8006.7_2244_V.</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>53755.6_36604_F.</t>
+          <t>21141.5_8155_F.</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>6036.4_2875_V.</t>
+          <t>5581.6_3687_P.</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>14009.0_5498_A.</t>
+          <t>5119.6_3153_M.</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>9791.4_3527_G.</t>
+          <t>4786.5_1898_P.</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>4886.1_2212_V.</t>
+          <t>10003.3_3845_P.</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>3012.4_1258_P.</t>
+          <t>12013.5_4635_X.</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>5008.1_1825_M.</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>10025.6_4018_G.</t>
+          <t>2629.2_1249_V.</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>4078.1_1810_A.</t>
+          <t>5010.3_3392_P.</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>10003.7_2721_V.</t>
+          <t>9209.1_3141_E.</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>5005.4_2618_L.</t>
+          <t>4891.7_1690_F.</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>9415.9_3699_G.</t>
+          <t>10023.3_4468_A.</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>5040.0_2299_A.</t>
+          <t>6610.9_1738_P.</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>5282.8_2392_C.</t>
+          <t>10016.9_3028_M.</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>7420.2_4318_C.</t>
+          <t>3004.6_746_V.</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>5040.0_2514_C.</t>
+          <t>5010.3_1888_G.</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>5296.8_1844_P.</t>
+          <t>5004.5_1548_A.</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>3039.1_1013_L.</t>
+          <t>4540.8_1823_A.</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>10025.5_3684_F.</t>
+          <t>10027.3_2906_P.</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>10030.0_3041_G.</t>
+          <t>123.0_5992_A.</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>9007.1_3080_P.</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>6472.0_2501_S.</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>7593.7_2701_E.</t>
+          <t>26010.2_9812_F.</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>5724.1_3694_S.</t>
+          <t>1467.9_482_S.</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>2629.2_1249_V.</t>
+          <t>2186.2_736_G.</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>5003.2_1389_E.</t>
+          <t>3026.1_1490_A.</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>657.7_273_S.</t>
+          <t>3623.3_1426_V.</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>7312.2_2446_G.</t>
+          <t>9756.3_2793_M.</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>10031.8_2663_P.</t>
+          <t>208.3_85_P.</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>1366.2_487_L.</t>
+          <t>8416.2_4091_P.</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>4017.3_1883_C.</t>
+          <t>3019.8_1453_F.</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>4214.8_2018_A.</t>
+          <t>12006.9_5463_P.</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>2064.3_708_S.</t>
+          <t>7516.9_3203_A.</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>5014.5_1497_G.</t>
+          <t>2051.8_860_S.</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>5025.8_1214_P.</t>
+          <t>4532.9_2322_L.</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>4994.4_1534_T.</t>
+          <t>13344.7_5916_G.</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>2011.7_731_S.</t>
+          <t>960.0_1109_A.</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>4576.3_2084_S.</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>10013.4_3721_G.</t>
+          <t>10055.2_3237_T.</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>21250.2_9506_P.</t>
+          <t>6103.6_2241_G.</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>5049.0_2240_C.</t>
+          <t>5301.0_2064_F.</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>2000.0_724_A.</t>
+          <t>5158.6_2220_C.</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>5004.0_2103_C.</t>
+          <t>8367.5_4269_C.</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>5299.8_2406_C.</t>
+          <t>5040.0_2514_C.</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>4540.8_1823_A.</t>
+          <t>3614.8_970_🔋.</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>791.5_266_G.</t>
+          <t>9013.7_2337_M.</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>5022.5_1222_P.</t>
+          <t>10007.8_2668_V.</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>5020.4_2167_C.</t>
+          <t>21207.4_6474_V.</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>6003.3_2987_M.</t>
+          <t>7025.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>7012.1_3931_🔋.</t>
+          <t>15016.9_6221_G.</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>5064.2_1636_G.</t>
+          <t>5137.9_2401_C.</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>5126.8_1941_G.</t>
+          <t>7312.2_2446_G.</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>10027.3_2906_P.</t>
+          <t>6012.6_2984_F.</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>8618.0_2344_P.</t>
+          <t>10006.9_3646_F.</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>6113.5_2883_C.</t>
+          <t>4327.6_1237_P.</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>5014.3_1731_F.</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>5031.8_2047_P.</t>
+          <t>5049.0_2240_C.</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>5006.8_1080_M.</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>7145.5_2856_E.</t>
+          <t>7127.8_1843_G.</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>5005.0_1309_M.</t>
+          <t>3089.9_1508_C.</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>6622.5_2224_E.</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>5242.7_1657_S.</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>5287.4_1835_V.</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>14004.5_5478_M.</t>
+          <t>22320.3_9183_F.</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>13344.7_5916_G.</t>
+          <t>5579.8_1990_E.</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>5004.1_1610_M.</t>
+          <t>12006.1_5290_X.</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>20105.6_7766_F.</t>
+          <t>3029.5_1536_G.</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>3006.0_1286_M.</t>
+          <t>4013.7_1173_V.</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>6005.3_2226_A.</t>
+          <t>1034.3_279_M.</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>4576.3_2084_S.</t>
+          <t>8132.9_2716_S.</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>8196.1_2807_T.</t>
+          <t>6003.3_2987_M.</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>6006.1_2236_V.</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>401.2_179_S.</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>2629.2_1249_M.</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>3010.0_1685_A.</t>
+          <t>4788.2_1476_P.</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>5033.4_1976_M.</t>
+          <t>4678.8_1840_A.</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>4017.3_1883_C.</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>6028.3_2419_L.</t>
+          <t>14009.7_4401_V.</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>5005.9_1755_X.</t>
+          <t>8024.4_2933_S.</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>15200.8_10718_F.</t>
+          <t>1366.2_487_L.</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>4797.2_1541_G.</t>
+          <t>8724.4_2500_M.</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>7569.4_2477_V.</t>
+          <t>7012.2_4093_P.</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>4781.2_1507_A.</t>
+          <t>7576.8_2823_P.</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>4969.4_2146_P.</t>
+          <t>5299.8_2406_C.</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>13023.5_5156_L.</t>
+          <t>4966.0_1709_G.</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>5000.2_1932_E.</t>
+          <t>2060.0_802_S.</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>9555.5_5689_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>2556.5_1160_M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>2004.9_754_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>4613.1_1806_A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>5365.6_2437_C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>5904.3_2699_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>10004.6_3357_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>10006.0_2772_V.</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>5451.1_1905_T.</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>8004.6_2357_G.</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>8899.2_2910_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>12326.4_4833_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>3039.1_1013_L.</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>4247.7_1274_T.</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>2504.7_703_🔋.</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>6010.6_2144_A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>25020.8_7832_V.</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>10021.0_4009_G.</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>3597.6_2910_E.</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>9639.7_4763_P.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_500km_2026.xlsx
+++ b/Ranking_CNB_500km_2026.xlsx
@@ -454,12 +454,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>684,0 km</t>
+          <t>726,4 km</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>10.478 m</t>
+          <t>11.399 m</t>
         </is>
       </c>
     </row>
@@ -471,12 +471,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>561,2 km</t>
+          <t>579,1 km</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>7.448 m</t>
+          <t>7.700 m</t>
         </is>
       </c>
     </row>
@@ -488,12 +488,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>355,6 km</t>
+          <t>360,6 km</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.523 m</t>
+          <t>3.563 m</t>
         </is>
       </c>
     </row>
@@ -505,12 +505,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>313,9 km</t>
+          <t>322,6 km</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.572 m</t>
+          <t>2.715 m</t>
         </is>
       </c>
     </row>
@@ -522,12 +522,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>280,3 km</t>
+          <t>289,8 km</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.326 m</t>
+          <t>3.435 m</t>
         </is>
       </c>
     </row>
@@ -551,34 +551,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Mateus  M.</t>
+          <t>Mateus P.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>232,0 km</t>
+          <t>236,0 km</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.962 m</t>
+          <t>2.640 m</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Mateus P.</t>
+          <t>Mateus  M.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>227,0 km</t>
+          <t>232,0 km</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.548 m</t>
+          <t>2.962 m</t>
         </is>
       </c>
     </row>
@@ -590,12 +590,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>215,8 km</t>
+          <t>221,9 km</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.497 m</t>
+          <t>1.547 m</t>
         </is>
       </c>
     </row>
@@ -607,12 +607,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>195,3 km</t>
+          <t>205,3 km</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.282 m</t>
+          <t>1.372 m</t>
         </is>
       </c>
     </row>
@@ -624,12 +624,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>192,0 km</t>
+          <t>200,6 km</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.534 m</t>
+          <t>2.629 m</t>
         </is>
       </c>
     </row>
@@ -641,46 +641,46 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>172,5 km</t>
+          <t>181,5 km</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.915 m</t>
+          <t>2.007 m</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Cassia C.</t>
+          <t>Fellipe T.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>167,0 km</t>
+          <t>175,7 km</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2.019 m</t>
+          <t>1.258 m</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Fellipe T.</t>
+          <t>Cassia C.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>163,7 km</t>
+          <t>172,9 km</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.242 m</t>
+          <t>2.075 m</t>
         </is>
       </c>
     </row>
@@ -692,12 +692,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>155,7 km</t>
+          <t>169,1 km</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.777 m</t>
+          <t>1.881 m</t>
         </is>
       </c>
     </row>
@@ -726,12 +726,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>142,0 km</t>
+          <t>151,0 km</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.557 m</t>
+          <t>1.650 m</t>
         </is>
       </c>
     </row>
@@ -777,12 +777,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>126,3 km</t>
+          <t>131,3 km</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.001 m</t>
+          <t>1.031 m</t>
         </is>
       </c>
     </row>
@@ -794,12 +794,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>112,1 km</t>
+          <t>117,6 km</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.357 m</t>
+          <t>1.418 m</t>
         </is>
       </c>
     </row>
@@ -828,12 +828,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>86,5 km</t>
+          <t>91,2 km</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>887 m</t>
+          <t>894 m</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A505"/>
+  <dimension ref="A1:A525"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1014,2534 +1014,2534 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4028.8_1699_L.</t>
+          <t>18102.7_4949_M.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4013.7_1173_V.</t>
+          <t>5004.4_1614_A.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4886.1_2212_M.</t>
+          <t>4972.5_2522_S.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>9006.6_3366_X.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>7127.8_1843_G.</t>
+          <t>6113.5_2883_C.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5051.4_1993_M.</t>
+          <t>7390.6_2590_E.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5137.9_2401_C.</t>
+          <t>10012.3_3067_S.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>10012.1_3139_S.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10030.5_4765_C.</t>
+          <t>5238.0_2781_F.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>12265.3_3843_M.</t>
+          <t>10533.4_4020_F.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>9052.9_2955_M.</t>
+          <t>4917.5_2381_T.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>7576.8_2823_P.</t>
+          <t>5085.1_1840_G.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4150.2_2042_C.</t>
+          <t>8253.0_2972_🔋.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3004.6_746_V.</t>
+          <t>4028.8_1699_L.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>7039.1_2754_S.</t>
+          <t>15149.3_4051_M.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>15200.8_10718_F.</t>
+          <t>6182.8_2116_G.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6084.1_2156_V.</t>
+          <t>2709.6_926_M.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4937.4_1783_A.</t>
+          <t>10030.0_3041_G.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2011.7_731_S.</t>
+          <t>10025.5_3684_F.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10012.3_3067_S.</t>
+          <t>5158.6_2220_C.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2557.8_1206_V.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5006.8_1080_M.</t>
+          <t>5580.0_2471_A.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>13023.5_5156_L.</t>
+          <t>5002.9_1487_P.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5004.8_1628_M.</t>
+          <t>2113.3_1803_X.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>20105.6_7766_F.</t>
+          <t>6038.2_2121_P.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>4994.4_1534_T.</t>
+          <t>3089.9_1508_C.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>1114.9_359_S.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>5001.9_1291_V.</t>
+          <t>5018.0_1121_M.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5064.3_1832_F.</t>
+          <t>10030.5_4765_C.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>4781.2_1507_A.</t>
+          <t>15194.4_3911_S.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1083.2_390_M.</t>
+          <t>4729.8_2058_P.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1152.4_938_S.</t>
+          <t>4700.4_1216_V.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10023.3_4468_A.</t>
+          <t>15016.9_6221_G.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>14014.7_3537_S.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5004.1_1610_M.</t>
+          <t>8117.9_4045_E.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5040.0_2514_C.</t>
+          <t>7992.7_2506_F.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>22008.4_8412_F.</t>
+          <t>6137.8_2406_L.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>5086.0_1810_G.</t>
+          <t>6010.6_2144_A.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3059.2_956_T.</t>
+          <t>6084.1_2156_V.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>3735.9_1928_V.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2036.1_839_S.</t>
+          <t>5224.2_2340_C.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>9006.5_3085_X.</t>
+          <t>10005.2_3808_G.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>12006.1_5290_T.</t>
+          <t>17194.0_6301_S.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>4864.8_1353_E.</t>
+          <t>3004.6_746_V.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>5013.9_1673_A.</t>
+          <t>5827.8_2106_S.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>7024.3_3266_L.</t>
+          <t>1083.2_390_M.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>10025.6_4018_G.</t>
+          <t>21207.4_6474_V.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>531.0_343_A.</t>
+          <t>8013.1_2082_P.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3010.0_1685_A.</t>
+          <t>8481.2_2463_🔋.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>10030.0_3041_G.</t>
+          <t>5028.5_4433_S.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>16520.2_4844_M.</t>
+          <t>5137.9_2401_C.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>4966.6_2195_P.</t>
+          <t>5904.3_2699_P.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>6010.6_2144_A.</t>
+          <t>4540.8_1823_A.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>10020.8_2989_M.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>10006.9_3646_X.</t>
+          <t>1012.0_375_E.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>5009.1_2246_C.</t>
+          <t>9093.1_3374_F.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>6100.8_3381_P.</t>
+          <t>4797.2_1541_G.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>7502.4_3467_P.</t>
+          <t>8200.5_2738_M.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>3039.1_1013_L.</t>
+          <t>8452.7_2430_M.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>3757.2_1716_A.</t>
+          <t>56121.5_25636_F.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>7419.2_3469_F.</t>
+          <t>5365.6_2437_C.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1020.0_679_T.</t>
+          <t>12002.7_4232_S.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>4972.5_2522_S.</t>
+          <t>10003.8_3195_S.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>10002.4_5136_P.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>7880.9_2433_E.</t>
+          <t>5163.5_1775_V.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>7783.3_2713_S.</t>
+          <t>9791.4_3527_G.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>21207.4_6474_V.</t>
+          <t>9021.3_5169_P.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1432.9_3942_M.</t>
+          <t>42443.0_21763_F.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>5356.1_1825_T.</t>
+          <t>3757.2_1716_A.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>37036.6_17889_F.</t>
+          <t>6173.6_2865_M.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>4619.4_1440_S.</t>
+          <t>6818.2_2036_P.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>10022.1_2875_M.</t>
+          <t>8196.1_2807_T.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>5724.1_3694_S.</t>
+          <t>7230.5_2794_V.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10007.8_2668_V.</t>
+          <t>4966.6_2195_P.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>9093.1_3374_F.</t>
+          <t>13344.7_5916_G.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>3012.4_1258_P.</t>
+          <t>3597.6_2910_E.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>6600.2_1915_M.</t>
+          <t>791.5_266_G.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>6007.1_2393_M.</t>
+          <t>6006.1_2236_V.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>11527.8_4172_V.</t>
+          <t>7593.7_2701_E.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>4700.4_1216_V.</t>
+          <t>2051.8_860_S.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>5085.1_1840_G.</t>
+          <t>15223.0_6245_P.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>3614.8_970_🔋.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10003.1_5062_V.</t>
+          <t>21106.2_7925_P.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10106.6_2889_P.</t>
+          <t>4247.7_1274_T.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>5382.2_2690_M.</t>
+          <t>5036.1_2201_C.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>7003.6_2437_P.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>5004.5_1548_A.</t>
+          <t>12545.4_3039_S.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>3958.9_1777_P.</t>
+          <t>14355.0_3613_M.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1018.4_335_M.</t>
+          <t>7783.3_2713_S.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>21106.2_7925_P.</t>
+          <t>10006.2_2753_V.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>6003.3_2987_M.</t>
+          <t>3006.0_1286_M.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2629.2_1249_V.</t>
+          <t>4821.0_1857_P.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>4177.9_1557_T.</t>
+          <t>7516.9_3203_A.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>10020.8_2989_M.</t>
+          <t>5012.1_1375_G.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>7006.7_5717_S.</t>
+          <t>4000.6_1659_S.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>4791.5_1524_E.</t>
+          <t>7604.2_3303_P.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>8218.3_2327_P.</t>
+          <t>5005.0_1309_M.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>6035.0_2481_P.</t>
+          <t>5287.4_1835_V.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>4678.8_1840_A.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>5028.5_4433_S.</t>
+          <t>15057.9_8625_F.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>6004.0_2559_P.</t>
+          <t>1034.3_279_M.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>9029.6_4595_P.</t>
+          <t>7025.7_3094_C.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>10007.4_3588_V.</t>
+          <t>5010.9_1617_G.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>5021.7_1930_A.</t>
+          <t>4705.5_1241_G.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>5126.8_1941_G.</t>
+          <t>3029.5_1536_G.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>5522.8_2716_V.</t>
+          <t>5000.6_1856_M.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>10533.4_4020_F.</t>
+          <t>1443.0_851_A.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>10002.4_5136_P.</t>
+          <t>5004.9_1790_A.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>419.0_180_P.</t>
+          <t>21250.2_9506_P.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>5017.7_1147_M.</t>
+          <t>5903.0_2662_C.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>7025.7_3094_C.</t>
+          <t>5019.4_1823_A.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>773.5_238_S.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>6345.4_2376_S.</t>
+          <t>15010.0_6802_L.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>5152.8_1800_G.</t>
+          <t>2175.4_712_S.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>5256.5_1535_S.</t>
+          <t>10027.3_2906_P.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>8416.2_4091_P.</t>
+          <t>5014.3_1731_F.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>6012.3_2200_M.</t>
+          <t>5126.8_1941_G.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>8004.6_2357_G.</t>
+          <t>4532.9_2322_L.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>8006.7_2244_V.</t>
+          <t>8978.9_3078_G.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>5081.5_1647_G.</t>
+          <t>4688.1_2291_C.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>4891.7_1690_F.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>10005.5_2697_V.</t>
+          <t>4994.4_1534_T.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>11252.8_3966_X.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>10007.8_2733_V.</t>
+          <t>5064.3_1832_F.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>6951.4_2856_S.</t>
+          <t>1366.2_487_L.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>1012.0_375_E.</t>
+          <t>3005.2_1040_L.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>6622.5_2224_E.</t>
+          <t>10005.5_2697_V.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>8396.0_2595_S.</t>
+          <t>7874.8_2223_M.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2060.0_802_S.</t>
+          <t>7420.2_4318_C.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>6103.6_2241_G.</t>
+          <t>10174.3_3680_S.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>5007.3_2480_V.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2735.8_959_S.</t>
+          <t>2305.1_940_S.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>2557.8_1206_V.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>10030.1_3124_M.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>17003.0_7696_P.</t>
+          <t>5043.1_2254_C.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2064.3_708_S.</t>
+          <t>5022.0_1862_A.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2504.7_703_🔋.</t>
+          <t>2002.2_938_P.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>4532.9_2322_L.</t>
+          <t>1885.0_952_L.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>14019.6_6253_L.</t>
+          <t>208.3_85_P.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>9209.1_3141_E.</t>
+          <t>12326.4_4833_S.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>9020.0_2605_M.</t>
+          <t>13008.2_4958_P.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>5621.6_2375_P.</t>
+          <t>9562.8_3145_M.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>13008.2_4958_P.</t>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>7243.5_2118_G.</t>
+          <t>9004.5_2927_E.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>5296.8_1844_P.</t>
+          <t>5022.5_1222_P.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>22320.3_9183_F.</t>
+          <t>6103.6_2241_G.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>10025.5_3684_F.</t>
+          <t>4896.8_2251_L.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>4540.8_1823_A.</t>
+          <t>8618.0_2344_P.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>9004.5_2927_E.</t>
+          <t>5119.6_3153_M.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>10010.0_2910_V.</t>
+          <t>21141.5_8155_F.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>6113.5_2883_C.</t>
+          <t>6036.4_2875_V.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>5093.1_1543_E.</t>
+          <t>4763.8_1720_P.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>6012.6_2984_P.</t>
+          <t>4864.8_1353_E.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>15223.0_6245_P.</t>
+          <t>9020.0_2605_M.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>5008.2_1646_A.</t>
+          <t>6007.1_3172_F.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>8187.1_2322_M.</t>
+          <t>14004.5_5478_M.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>6006.6_2009_P.</t>
+          <t>6100.8_3381_P.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>6833.7_2100_G.</t>
+          <t>10062.5_2886_M.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>5188.5_1799_S.</t>
+          <t>6472.0_2501_S.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>5011.9_1594_P.</t>
+          <t>8442.5_3038_G.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>9285.3_3279_G.</t>
+          <t>25020.8_7832_V.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>1114.9_359_S.</t>
+          <t>3088.9_1493_C.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>5282.8_2392_C.</t>
+          <t>4974.4_1533_E.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>9791.4_3527_G.</t>
+          <t>9012.4_2700_M.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>123.0_5992_A.</t>
+          <t>9005.5_5146_A.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>18107.4_4577_M.</t>
+          <t>1432.9_3942_M.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>4821.0_1857_P.</t>
+          <t>8218.3_2327_P.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>9415.9_3699_G.</t>
+          <t>8200.8_2347_T.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>10348.3_2647_S.</t>
+          <t>11005.3_5159_P.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>7593.7_2701_E.</t>
+          <t>16397.3_4254_S.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>10006.5_3648_X.</t>
+          <t>8004.6_2357_G.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>10001.3_4206_G.</t>
+          <t>5008.2_1646_A.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>8092.0_4532_P.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>3088.9_1493_C.</t>
+          <t>9001.4_3623_P.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>6518.4_2914_A.</t>
+          <t>8506.3_4050_C.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>14117.6_3844_M.</t>
+          <t>2504.7_703_🔋.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>5025.8_1214_P.</t>
+          <t>1002.7_460_S.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>12524.7_3259_S.</t>
+          <t>5021.7_1930_A.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>5005.9_1755_X.</t>
+          <t>6833.7_2100_G.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>8442.5_3038_G.</t>
+          <t>1206.7_12400_M.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>8113.4_3006_P.</t>
+          <t>10011.2_3009_G.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>1380.0_562_A.</t>
+          <t>9494.5_3544_G.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>600.2_261_L.</t>
+          <t>9005.3_4344_A.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>17194.0_6301_S.</t>
+          <t>3023.2_962_S.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>4974.4_1533_E.</t>
+          <t>2011.7_731_S.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>5086.0_1810_G.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>8132.9_2716_S.</t>
+          <t>3019.8_1453_F.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>5770.8_2848_G.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>5014.8_2009_A.</t>
+          <t>1018.4_335_M.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>21250.2_9506_P.</t>
+          <t>4899.2_1459_A.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>3735.9_1928_V.</t>
+          <t>4078.1_1810_A.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>3010.0_1424_A.</t>
+          <t>8047.1_2948_G.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>3010.0_1289_A.</t>
+          <t>5579.8_1990_E.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>12342.9_3211_M.</t>
+          <t>10007.8_2668_V.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>5020.6_1328_M.</t>
+          <t>22002.4_8469_M.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>22320.3_9183_F.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>6661.8_3736_P.</t>
+          <t>4153.2_3559_P.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>5581.6_3687_P.</t>
+          <t>4735.2_997_S.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>3023.2_962_S.</t>
+          <t>6005.3_2226_A.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>2761.5_1068_S.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>6779.9_2003_E.</t>
+          <t>5188.5_1799_S.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>8013.1_2082_P.</t>
+          <t>3010.0_1685_A.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>611.2_221_M.</t>
+          <t>5522.8_2716_V.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2355.5_726_S.</t>
+          <t>10643.3_3263_S.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>9001.4_3623_P.</t>
+          <t>10055.2_3237_T.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>13005.6_6018_P.</t>
+          <t>14009.0_5498_A.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>25020.8_7832_V.</t>
+          <t>6028.3_2419_L.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>5013.9_1673_A.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>8978.9_3078_G.</t>
+          <t>6600.2_1915_M.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>10277.3_4318_L.</t>
+          <t>4830.1_2569_C.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>8200.8_2347_T.</t>
+          <t>17003.0_7696_P.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>10003.7_2721_V.</t>
+          <t>8113.4_3006_P.</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>5027.8_1361_P.</t>
+          <t>9639.7_4763_P.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>4576.3_2084_S.</t>
+          <t>1701.7_720_F.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>8724.4_2500_M.</t>
+          <t>5064.2_1636_G.</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>10006.0_2772_V.</t>
+          <t>2735.8_959_S.</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>6007.4_1804_G.</t>
+          <t>15004.3_4718_G.</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>8506.3_4050_C.</t>
+          <t>5451.1_1905_T.</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>7569.4_2477_V.</t>
+          <t>4682.8_2218_P.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>5033.4_1976_M.</t>
+          <t>3138.1_1120_S.</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>1011.0_396_L.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>7598.7_2799_S.</t>
+          <t>6804.1_2088_P.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>7012.1_3931_🔋.</t>
+          <t>3026.1_1490_A.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>4678.8_1840_A.</t>
+          <t>4619.4_1440_S.</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>4790.7_1897_F.</t>
+          <t>10003.7_2721_V.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>5049.0_2240_C.</t>
+          <t>6241.6_2497_P.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>5043.1_2254_C.</t>
+          <t>5869.6_2613_P.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>401.2_179_S.</t>
+          <t>4791.5_1524_E.</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>10503.6_3278_M.</t>
+          <t>5005.4_2618_L.</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>4729.8_2058_P.</t>
+          <t>2186.2_736_G.</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>7992.7_2506_F.</t>
+          <t>6006.6_2009_P.</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>6804.1_2088_P.</t>
+          <t>14117.6_3844_M.</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>5299.8_2406_C.</t>
+          <t>3412.3_1947_C.</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>3551.6_1303_S.</t>
+          <t>6345.4_2376_S.</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>5002.9_1487_P.</t>
+          <t>10001.3_4206_G.</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>6006.1_2236_V.</t>
+          <t>5029.4_1585_P.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>8117.9_4045_E.</t>
+          <t>12524.7_3259_S.</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>10004.6_3357_S.</t>
+          <t>5033.4_1976_M.</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>1885.0_952_L.</t>
+          <t>15010.8_6619_G.</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>1443.0_851_A.</t>
+          <t>5139.2_2082_G.</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>6011.8_1873_M.</t>
+          <t>10031.8_2663_P.</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>3026.1_1490_A.</t>
+          <t>9209.1_3141_E.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>15016.9_6221_G.</t>
+          <t>10004.6_3357_S.</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>4214.8_2018_A.</t>
+          <t>2880.9_1210_L.</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>5081.5_1647_G.</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>1002.7_460_S.</t>
+          <t>18107.4_4577_M.</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>8396.0_2595_S.</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>3412.3_1947_C.</t>
+          <t>5000.5_1919_P.</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>16008.9_5968_S.</t>
+          <t>20105.6_7766_F.</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>56121.5_25636_F.</t>
+          <t>3958.9_1777_P.</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>6028.3_2419_L.</t>
+          <t>7127.8_1843_G.</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>2004.9_754_S.</t>
+          <t>12006.1_5290_T.</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>4788.2_1476_P.</t>
+          <t>5282.8_2392_C.</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>10021.0_4009_G.</t>
+          <t>8008.0_2930_A.</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>7390.6_2590_E.</t>
+          <t>2064.3_708_S.</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>4613.1_1806_A.</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>10027.3_2906_P.</t>
+          <t>2000.0_724_A.</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>4786.5_1898_P.</t>
+          <t>12022.7_5417_L.</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>5008.0_2402_P.</t>
+          <t>5040.0_2971_A.</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>5010.3_3392_P.</t>
+          <t>5004.8_1628_M.</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>6241.6_2497_P.</t>
+          <t>21114.4_6098_P.</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>2000.0_724_A.</t>
+          <t>600.2_261_L.</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>10012.1_3139_S.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>5031.8_2047_P.</t>
+          <t>7012.1_3931_🔋.</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>5163.5_1775_V.</t>
+          <t>3059.2_956_T.</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>10031.8_2663_P.</t>
+          <t>5072.4_1931_S.</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>8899.2_2910_S.</t>
+          <t>5014.8_2009_A.</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>10485.5_4164_M.</t>
+          <t>13005.6_6018_P.</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>4966.0_1709_G.</t>
+          <t>5017.7_1147_M.</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>7516.9_3203_A.</t>
+          <t>10023.3_4468_A.</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>8452.7_2430_M.</t>
+          <t>10277.3_4318_L.</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>10008.1_2966_M.</t>
+          <t>5006.8_1080_M.</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>5238.0_2781_F.</t>
+          <t>7012.2_4093_P.</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>2558.7_905_S.</t>
+          <t>2004.9_754_S.</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>7312.2_2446_G.</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>7003.6_2437_P.</t>
+          <t>5296.8_1844_P.</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>5010.3_1888_G.</t>
+          <t>4901.4_2376_C.</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>791.5_266_G.</t>
+          <t>5009.1_2246_C.</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>8550.7_2328_P.</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>2047.9_924_L.</t>
+          <t>10007.4_3588_V.</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>9639.7_4763_P.</t>
+          <t>5040.0_2299_A.</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>5040.0_2971_A.</t>
+          <t>6053.8_2077_M.</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>1701.7_720_F.</t>
+          <t>9006.6_3366_X.</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>4153.2_3559_P.</t>
+          <t>7039.1_2754_S.</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>12022.7_5417_L.</t>
+          <t>773.5_238_S.</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>3029.5_1536_G.</t>
+          <t>21124.1_8011_F.</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>21114.4_6098_P.</t>
+          <t>1492.5_537_S.</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>5008.1_1825_M.</t>
+          <t>553.2_224_S.</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>5981.9_2551_P.</t>
+          <t>6661.8_3736_P.</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>2185.4_792_S.</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>2761.5_1068_S.</t>
+          <t>10022.1_2875_M.</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>5022.5_1222_P.</t>
+          <t>26010.2_9812_F.</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>6016.7_2122_M.</t>
+          <t>12013.5_4635_X.</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>5224.2_2340_C.</t>
+          <t>9029.6_4595_P.</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>8092.0_4532_P.</t>
+          <t>1467.9_482_S.</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>8196.1_2807_T.</t>
+          <t>7025.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>14014.7_3537_S.</t>
+          <t>4932.4_1545_E.</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>5005.0_1309_M.</t>
+          <t>8899.2_2910_S.</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>10013.0_3337_S.</t>
+          <t>10503.6_3278_M.</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>5018.0_1121_M.</t>
+          <t>5018.2_1981_A.</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>5005.8_1527_S.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>6903.6_2566_G.</t>
+          <t>6622.5_2224_E.</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>3798.9_1319_S.</t>
+          <t>2556.5_1160_M.</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>10718.1_9873_S.</t>
+          <t>1380.0_562_A.</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>7114.0_2850_S.</t>
+          <t>9052.9_2955_M.</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>22002.4_8469_M.</t>
+          <t>12265.3_3843_M.</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>6173.6_2865_M.</t>
+          <t>10348.3_2647_S.</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>13344.7_5916_G.</t>
+          <t>10013.4_3721_G.</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>9507.9_2851_M.</t>
+          <t>53755.6_36604_F.</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>10003.3_3845_P.</t>
+          <t>8351.7_4153_C.</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>5022.0_1862_A.</t>
+          <t>7569.4_2477_V.</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>9555.5_5689_S.</t>
+          <t>5000.7_1254_V.</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>3580.9_1198_S.</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>8367.5_4269_C.</t>
+          <t>5152.8_1800_G.</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>5010.0_1872_A.</t>
+          <t>5621.6_2375_P.</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>10055.2_3237_T.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>657.7_273_S.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>15057.9_8625_F.</t>
+          <t>2629.2_1249_V.</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>10016.9_3028_M.</t>
+          <t>4576.3_2084_S.</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>3138.1_1120_S.</t>
+          <t>1884.9_866_S.</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>5301.0_2064_F.</t>
+          <t>6951.4_2856_S.</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>7874.8_2223_M.</t>
+          <t>6004.0_2559_P.</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>15010.0_6802_L.</t>
+          <t>4850.9_2239_C.</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>5422.4_1911_G.</t>
+          <t>6012.3_2200_M.</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>5004.9_1790_A.</t>
+          <t>10006.9_3646_X.</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>10004.6_2845_V.</t>
+          <t>10110.2_3737_E.</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>10110.2_3737_E.</t>
+          <t>5031.8_2047_P.</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>7012.2_4093_P.</t>
+          <t>9555.5_5689_S.</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>8104.2_2652_M.</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>6036.4_2875_V.</t>
+          <t>14009.7_4401_V.</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>5040.0_2299_A.</t>
+          <t>10011.5_3070_S.</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>3597.6_2910_E.</t>
+          <t>1020.0_679_T.</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>4735.2_997_S.</t>
+          <t>6007.1_2393_M.</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>553.2_224_S.</t>
+          <t>5011.9_1594_P.</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>5144.4_2349_P.</t>
+          <t>21442.0_7959_F.</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>6047.4_2816_T.</t>
+          <t>8024.4_2933_S.</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>7186.5_2708_S.</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>4969.4_2146_P.</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>2510.2_1366_V.</t>
+          <t>10718.1_9873_S.</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>8416.2_4091_P.</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>1629.5_671_F.</t>
+          <t>3551.6_1303_S.</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>2060.0_802_S.</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>5451.1_1905_T.</t>
+          <t>4214.8_2018_A.</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>12014.9_4588_T.</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>12002.7_4232_S.</t>
+          <t>7114.0_2850_S.</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>14009.7_4401_V.</t>
+          <t>15200.8_10718_F.</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>8481.2_2463_🔋.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>5008.0_2402_P.</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>5365.6_2437_C.</t>
+          <t>18516.8_6699_G.</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>2629.2_1249_M.</t>
+          <t>5020.4_2167_C.</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>2002.2_938_P.</t>
+          <t>37036.6_17889_F.</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>1467.9_482_S.</t>
+          <t>5299.8_2406_C.</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>5000.5_1919_P.</t>
+          <t>3010.0_1424_A.</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>1027.7_364_S.</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>5000.6_1856_M.</t>
+          <t>7145.5_2856_E.</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>3089.9_1508_C.</t>
+          <t>10241.7_3826_G.</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>14355.0_3613_M.</t>
+          <t>5020.6_1328_M.</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>2880.9_1210_L.</t>
+          <t>10016.9_3028_M.</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>5158.6_2220_C.</t>
+          <t>5025.8_1214_P.</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>7186.5_2708_S.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
@@ -3555,987 +3555,1127 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>7420.2_4318_C.</t>
+          <t>6903.6_2566_G.</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>960.0_1109_A.</t>
+          <t>8120.9_2737_G.</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>5007.4_1601_A.</t>
+          <t>8006.7_2244_V.</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>10007.8_2733_V.</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>6038.2_2121_P.</t>
+          <t>5093.1_1543_E.</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>10030.1_3124_M.</t>
+          <t>1629.5_671_F.</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>2186.2_736_G.</t>
+          <t>12342.9_3211_M.</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>6053.8_2077_M.</t>
+          <t>7083.1_2912_G.</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>5301.0_2064_F.</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>10001.9_4466_P.</t>
+          <t>6035.0_2481_P.</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>12006.1_5290_X.</t>
+          <t>123.0_5992_A.</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>5100.0_2587_A.</t>
+          <t>401.2_179_S.</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>4017.3_1883_C.</t>
+          <t>4781.2_1507_A.</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>10006.9_3646_F.</t>
+          <t>4966.0_1709_G.</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>5004.4_1614_A.</t>
+          <t>8724.4_2500_M.</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>7025.4_3008_L.</t>
+          <t>5724.1_3694_S.</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>2783.5_952_S.</t>
+          <t>4731.9_1407_T.</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>5072.4_1931_S.</t>
+          <t>7024.3_3266_L.</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>5005.4_2618_L.</t>
+          <t>7243.5_2118_G.</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>9007.1_3080_P.</t>
+          <t>1152.4_938_S.</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>4830.1_2569_C.</t>
+          <t>7985.2_2173_P.</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>4896.8_2251_L.</t>
+          <t>4692.9_1546_P.</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>5004.0_2103_C.</t>
+          <t>6536.2_2241_P.</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>15504.3_3950_M.</t>
+          <t>2558.7_905_S.</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>6779.9_2003_E.</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>26010.2_9812_F.</t>
+          <t>5005.8_1527_S.</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>15010.8_6619_G.</t>
+          <t>16520.2_4844_M.</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>7985.2_2173_P.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>4899.2_1459_A.</t>
+          <t>6610.9_1738_P.</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>6536.2_2241_P.</t>
+          <t>4921.0_2491_A.</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>5007.1_1751_T.</t>
+          <t>611.2_221_M.</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>4921.0_2491_A.</t>
+          <t>5100.0_2587_A.</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>4327.6_1237_P.</t>
+          <t>5004.5_1548_A.</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>14119.3_5262_S.</t>
+          <t>5981.9_2551_P.</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>4692.9_1546_P.</t>
+          <t>13023.5_5156_L.</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>10006.2_2753_V.</t>
+          <t>8648.9_3219_A.</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>2556.5_1160_M.</t>
+          <t>4177.9_1557_T.</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>6011.5_2408_A.</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>8200.5_2738_M.</t>
+          <t>7015.4_2141_T.</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>1366.2_487_L.</t>
+          <t>2355.5_726_S.</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>8008.0_2930_A.</t>
+          <t>11527.8_4172_V.</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>15186.5_3866_S.</t>
+          <t>10106.6_2889_P.</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>2185.4_792_S.</t>
+          <t>9756.3_2793_M.</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>10241.7_3826_G.</t>
+          <t>5003.2_1389_E.</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>12006.1_5290_X.</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>5580.0_2471_A.</t>
+          <t>9415.9_3699_G.</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>4969.4_2146_P.</t>
+          <t>9006.5_3085_X.</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>6007.1_3172_F.</t>
+          <t>15504.3_3950_M.</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>14009.0_5498_A.</t>
+          <t>4790.7_1897_F.</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>18516.8_6699_G.</t>
+          <t>6003.3_2987_M.</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>3623.3_1426_V.</t>
+          <t>657.7_273_S.</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>5242.7_1657_S.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>5139.2_2082_G.</t>
+          <t>8132.9_2716_S.</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>9005.3_4344_A.</t>
+          <t>6518.4_2914_A.</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>6818.2_2036_P.</t>
+          <t>17012.6_5869_T.</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>6610.9_1738_P.</t>
+          <t>4327.6_1237_P.</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>7083.1_2912_G.</t>
+          <t>5008.1_1825_M.</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>8648.9_3219_A.</t>
+          <t>5010.3_3392_P.</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>5579.8_1990_E.</t>
+          <t>7880.9_2433_E.</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>1206.7_12400_M.</t>
+          <t>2036.1_839_S.</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>21141.5_8155_F.</t>
+          <t>8187.1_2322_M.</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>5004.0_2103_C.</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>6620.4_2477_P.</t>
+          <t>5382.2_2690_M.</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>12545.4_3039_S.</t>
+          <t>6047.4_2816_T.</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>5072.5_1592_S.</t>
+          <t>5010.0_1872_A.</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>10643.3_3263_S.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>5010.9_1617_G.</t>
+          <t>5014.5_1497_G.</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>6005.3_2226_A.</t>
+          <t>16008.9_5968_S.</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>10138.8_3268_X.</t>
+          <t>4788.2_1476_P.</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>7312.2_2446_G.</t>
+          <t>5040.0_2514_C.</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>53755.6_36604_F.</t>
+          <t>7247.0_2394_S.</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>4797.2_1541_G.</t>
+          <t>10006.0_2772_V.</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>15186.5_3866_S.</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>5007.3_2480_V.</t>
+          <t>419.0_180_P.</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>15194.4_3911_S.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>12008.4_3832_G.</t>
+          <t>6011.8_1873_M.</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>5064.2_1636_G.</t>
+          <t>6109.2_2608_L.</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>14004.5_5478_M.</t>
+          <t>2047.9_924_L.</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>1027.7_364_S.</t>
+          <t>10138.8_3268_X.</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>5036.1_2201_C.</t>
+          <t>4937.4_1783_A.</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>11005.3_5159_P.</t>
+          <t>6007.4_1804_G.</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>4901.4_2376_C.</t>
+          <t>5051.4_1993_M.</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>7090.6_3340_A.</t>
+          <t>10010.0_2910_V.</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>4078.1_1810_A.</t>
+          <t>5242.7_1657_S.</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>4247.7_1274_T.</t>
+          <t>4077.1_1454_S.</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>6182.8_2116_G.</t>
+          <t>7419.2_3469_F.</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>15637.2_5789_G.</t>
+          <t>4786.5_1898_P.</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>10025.6_4018_G.</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>4917.5_2381_T.</t>
+          <t>5010.3_1888_G.</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>4932.4_1545_E.</t>
+          <t>9507.9_2851_M.</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>8047.1_2948_G.</t>
+          <t>960.0_1109_A.</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>5018.2_1981_A.</t>
+          <t>10003.1_5062_V.</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>14019.6_6253_L.</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>5869.6_2613_P.</t>
+          <t>10013.0_3337_S.</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>5007.1_1751_T.</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>5000.2_1932_E.</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>7576.8_2823_P.</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>11214.0_4224_V.</t>
+          <t>5235.4_1766_P.</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>3006.0_1286_M.</t>
+          <t>14119.3_5262_S.</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>8024.4_2933_S.</t>
+          <t>5422.4_1911_G.</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>4688.1_2291_C.</t>
+          <t>5004.1_1610_M.</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>16397.3_4254_S.</t>
+          <t>5001.9_1291_V.</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>5581.6_3687_P.</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>18102.7_4949_M.</t>
+          <t>7502.4_3467_P.</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>12521.4_4814_M.</t>
+          <t>5256.5_1535_S.</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>7001.2_3357_M.</t>
+          <t>4814.5_1705_🔋.</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>10005.2_3808_G.</t>
+          <t>7001.2_3357_M.</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>5007.4_1601_A.</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>9012.4_2700_M.</t>
+          <t>9005.5_5167_M.</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>12013.5_4635_X.</t>
+          <t>2783.5_952_S.</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>5020.4_2167_C.</t>
+          <t>11214.0_4224_V.</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>5235.4_1766_P.</t>
+          <t>531.0_343_A.</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>5014.5_1497_G.</t>
+          <t>10485.5_4164_M.</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>4101.5_1485_V.</t>
+          <t>3010.0_1289_A.</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>7022.4_3008_L.</t>
+          <t>7598.7_2799_S.</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>6011.5_2408_A.</t>
+          <t>10021.0_4009_G.</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>21124.1_8011_F.</t>
+          <t>10006.9_3646_F.</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>8618.0_2344_P.</t>
+          <t>5461.3_1916_E.</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>4000.6_1659_S.</t>
+          <t>22008.4_8412_F.</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>4613.1_1806_A.</t>
+          <t>2510.2_1366_V.</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>5356.1_1825_T.</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>15004.3_4718_G.</t>
+          <t>3039.1_1013_L.</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>10013.4_3721_G.</t>
+          <t>5072.5_1592_S.</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>8351.7_4153_C.</t>
+          <t>6016.7_2122_M.</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>5287.4_1835_V.</t>
+          <t>3798.9_1319_S.</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>5003.2_1389_E.</t>
+          <t>5144.4_2349_P.</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>5029.4_1585_P.</t>
+          <t>10001.9_4466_P.</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>5000.2_1932_E.</t>
+          <t>15637.2_5789_G.</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>4850.9_2239_C.</t>
+          <t>4886.1_2212_M.</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>9756.3_2793_M.</t>
+          <t>10003.3_3845_P.</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>5904.3_2699_P.</t>
+          <t>9013.7_2337_M.</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>7145.5_2856_E.</t>
+          <t>4101.5_1485_V.</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>7604.2_3303_P.</t>
+          <t>7022.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>4886.1_2212_V.</t>
+          <t>5005.9_1755_X.</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>7230.5_2794_V.</t>
+          <t>7090.6_3340_A.</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>10003.8_3195_S.</t>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>1034.3_279_M.</t>
+          <t>12006.9_5463_P.</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>5012.1_1375_G.</t>
+          <t>9007.1_3080_P.</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>10011.5_3070_S.</t>
+          <t>10004.6_2845_V.</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>5827.8_2106_S.</t>
+          <t>6012.6_2984_P.</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>6620.4_2477_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>5049.0_2240_C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>3623.3_1426_V.</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>4017.3_1883_C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>10058.8_3483_F.</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>4013.7_1173_V.</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>6012.6_2984_F.</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>8367.5_4269_C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>4886.1_2212_V.</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>4768.0_1875_L.</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>3012.4_1258_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>9285.3_3279_G.</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>4150.2_2042_C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>2629.2_1249_M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>5770.8_2848_G.</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>5027.8_1361_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>6046.5_3239_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>10106.6_3354_M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>7006.7_5717_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>10006.5_3648_X.</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>12008.4_3832_G.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_500km_2026.xlsx
+++ b/Ranking_CNB_500km_2026.xlsx
@@ -488,12 +488,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>360,6 km</t>
+          <t>370,6 km</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.563 m</t>
+          <t>3.660 m</t>
         </is>
       </c>
     </row>
@@ -505,7 +505,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>322,6 km</t>
+          <t>329,7 km</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -522,12 +522,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>289,8 km</t>
+          <t>297,8 km</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.435 m</t>
+          <t>3.520 m</t>
         </is>
       </c>
     </row>
@@ -590,46 +590,46 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>221,9 km</t>
+          <t>224,9 km</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.547 m</t>
+          <t>1.579 m</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Gleydson G.</t>
+          <t>Jandson P.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>205,3 km</t>
+          <t>212,7 km</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.372 m</t>
+          <t>2.775 m</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Jandson P.</t>
+          <t>Gleydson G.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>200,6 km</t>
+          <t>205,3 km</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.629 m</t>
+          <t>1.372 m</t>
         </is>
       </c>
     </row>
@@ -709,12 +709,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>152,2 km</t>
+          <t>155,4 km</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.439 m</t>
+          <t>1.477 m</t>
         </is>
       </c>
     </row>
@@ -862,12 +862,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>51,2 km</t>
+          <t>52,4 km</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>726 m</t>
+          <t>747 m</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A525"/>
+  <dimension ref="A1:A533"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1014,3668 +1014,3724 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>18102.7_4949_M.</t>
+          <t>14009.0_5498_A.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5004.4_1614_A.</t>
+          <t>9005.5_5167_M.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4972.5_2522_S.</t>
+          <t>4821.0_1857_P.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>960.0_1109_A.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6113.5_2883_C.</t>
+          <t>5001.9_1291_V.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>10012.1_3139_S.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>7390.6_2590_E.</t>
+          <t>20105.6_7766_F.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10012.3_3067_S.</t>
+          <t>4101.5_1485_V.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10012.1_3139_S.</t>
+          <t>4937.4_1783_A.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5238.0_2781_F.</t>
+          <t>21141.5_8155_F.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10533.4_4020_F.</t>
+          <t>9756.3_2793_M.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>4917.5_2381_T.</t>
+          <t>22008.4_8412_F.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5085.1_1840_G.</t>
+          <t>10004.6_3357_S.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>4619.4_1440_S.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4028.8_1699_L.</t>
+          <t>10003.7_2721_V.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>15149.3_4051_M.</t>
+          <t>10106.6_3354_M.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>6182.8_2116_G.</t>
+          <t>9562.8_3145_M.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2709.6_926_M.</t>
+          <t>5006.8_1080_M.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10030.0_3041_G.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10025.5_3684_F.</t>
+          <t>15504.3_3950_M.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5158.6_2220_C.</t>
+          <t>6804.1_2088_P.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>2175.4_712_S.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5580.0_2471_A.</t>
+          <t>12524.7_3259_S.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5002.9_1487_P.</t>
+          <t>10055.2_3237_T.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2113.3_1803_X.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>6038.2_2121_P.</t>
+          <t>2305.1_940_S.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3089.9_1508_C.</t>
+          <t>5139.2_2082_G.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1114.9_359_S.</t>
+          <t>5000.2_1932_E.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>5018.0_1121_M.</t>
+          <t>10006.9_3646_X.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10030.5_4765_C.</t>
+          <t>10001.9_4466_P.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>15194.4_3911_S.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>4729.8_2058_P.</t>
+          <t>4678.8_1840_A.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>4700.4_1216_V.</t>
+          <t>2510.2_1366_V.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>15016.9_6221_G.</t>
+          <t>3623.3_1426_V.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>14014.7_3537_S.</t>
+          <t>10138.8_3268_X.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>8117.9_4045_E.</t>
+          <t>5163.5_1775_V.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>7992.7_2506_F.</t>
+          <t>3005.2_1040_L.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>9004.5_2927_E.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>6010.6_2144_A.</t>
+          <t>10016.9_3028_M.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>6084.1_2156_V.</t>
+          <t>10030.0_3041_G.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3735.9_1928_V.</t>
+          <t>6610.9_1738_P.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>5224.2_2340_C.</t>
+          <t>6536.2_2241_P.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>10005.2_3808_G.</t>
+          <t>6004.0_2559_P.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>17194.0_6301_S.</t>
+          <t>5018.2_1981_A.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3004.6_746_V.</t>
+          <t>6047.4_2816_T.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>5827.8_2106_S.</t>
+          <t>5981.9_2551_P.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1083.2_390_M.</t>
+          <t>10006.2_2753_V.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>21207.4_6474_V.</t>
+          <t>10643.3_3263_S.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>8013.1_2082_P.</t>
+          <t>791.5_266_G.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>8481.2_2463_🔋.</t>
+          <t>8550.7_2328_P.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>5028.5_4433_S.</t>
+          <t>4214.8_2018_A.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>5137.9_2401_C.</t>
+          <t>21106.2_7925_P.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>5904.3_2699_P.</t>
+          <t>8004.6_2357_G.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>4540.8_1823_A.</t>
+          <t>10503.6_3278_M.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>10020.8_2989_M.</t>
+          <t>419.0_180_P.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1012.0_375_E.</t>
+          <t>4901.4_2376_C.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>9093.1_3374_F.</t>
+          <t>1492.5_537_S.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>4797.2_1541_G.</t>
+          <t>4972.5_2522_S.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>8200.5_2738_M.</t>
+          <t>5008.0_2402_P.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>8452.7_2430_M.</t>
+          <t>18516.8_6699_G.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>56121.5_25636_F.</t>
+          <t>5010.3_1888_G.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>5365.6_2437_C.</t>
+          <t>7247.0_2394_S.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>12002.7_4232_S.</t>
+          <t>4000.6_1659_S.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>10003.8_3195_S.</t>
+          <t>5002.9_1487_P.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>10002.4_5136_P.</t>
+          <t>4028.8_1699_L.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>5163.5_1775_V.</t>
+          <t>10022.1_2875_M.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>9791.4_3527_G.</t>
+          <t>4682.8_2218_P.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>9021.3_5169_P.</t>
+          <t>5158.6_2220_C.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>42443.0_21763_F.</t>
+          <t>12006.1_5290_X.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>3757.2_1716_A.</t>
+          <t>10005.2_3808_G.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>6173.6_2865_M.</t>
+          <t>3958.9_1777_P.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>6818.2_2036_P.</t>
+          <t>3010.0_1424_A.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>8196.1_2807_T.</t>
+          <t>7003.6_2437_P.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>7230.5_2794_V.</t>
+          <t>773.5_238_S.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>4966.6_2195_P.</t>
+          <t>9093.1_3374_F.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>13344.7_5916_G.</t>
+          <t>8396.0_2595_S.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>3597.6_2910_E.</t>
+          <t>7420.2_4318_C.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>791.5_266_G.</t>
+          <t>8040.3_2996_G.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>6006.1_2236_V.</t>
+          <t>6951.4_2856_S.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>7593.7_2701_E.</t>
+          <t>6007.1_2393_M.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>1011.0_396_L.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>15223.0_6245_P.</t>
+          <t>2976.4_1213_L.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>15004.3_4718_G.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>21106.2_7925_P.</t>
+          <t>5021.7_1930_A.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>4247.7_1274_T.</t>
+          <t>1884.9_866_S.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>5036.1_2201_C.</t>
+          <t>5724.1_3694_S.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>7003.6_2437_P.</t>
+          <t>8117.9_4045_E.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>12545.4_3039_S.</t>
+          <t>5000.7_1254_V.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>14355.0_3613_M.</t>
+          <t>531.0_343_A.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>7783.3_2713_S.</t>
+          <t>15057.9_8625_F.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>10006.2_2753_V.</t>
+          <t>4150.2_2042_C.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>3006.0_1286_M.</t>
+          <t>3012.4_1258_P.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>4821.0_1857_P.</t>
+          <t>10006.5_3648_X.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>7516.9_3203_A.</t>
+          <t>5000.6_1856_M.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>5012.1_1375_G.</t>
+          <t>14014.7_3537_S.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>4000.6_1659_S.</t>
+          <t>8648.9_3219_A.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>7604.2_3303_P.</t>
+          <t>5004.0_2103_C.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>5005.0_1309_M.</t>
+          <t>3551.6_1303_S.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>5287.4_1835_V.</t>
+          <t>5238.0_2781_F.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>4678.8_1840_A.</t>
+          <t>12265.3_3843_M.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>15057.9_8625_F.</t>
+          <t>7419.2_3469_F.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>10005.5_2697_V.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1034.3_279_M.</t>
+          <t>9005.3_4344_A.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>7025.7_3094_C.</t>
+          <t>3010.0_1685_A.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>5010.9_1617_G.</t>
+          <t>4729.8_2058_P.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>2783.5_952_S.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>3029.5_1536_G.</t>
+          <t>6046.5_3239_S.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>5000.6_1856_M.</t>
+          <t>2557.8_1206_V.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1443.0_851_A.</t>
+          <t>5003.2_1389_E.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>5004.9_1790_A.</t>
+          <t>3026.1_1490_A.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>21250.2_9506_P.</t>
+          <t>8024.4_2933_S.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>5903.0_2662_C.</t>
+          <t>8978.9_3078_G.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>5019.4_1823_A.</t>
+          <t>2709.6_926_M.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>10008.1_2966_M.</t>
+          <t>6620.4_2477_P.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>15010.0_6802_L.</t>
+          <t>7083.1_2912_G.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>9021.3_5169_P.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>10027.3_2906_P.</t>
+          <t>4899.2_1459_A.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>5004.4_1614_A.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>5126.8_1941_G.</t>
+          <t>13344.7_5916_G.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>4532.9_2322_L.</t>
+          <t>3023.2_962_S.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>8978.9_3078_G.</t>
+          <t>5036.1_2201_C.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>4688.1_2291_C.</t>
+          <t>401.2_179_S.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>18665.3_4638_S.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>4994.4_1534_T.</t>
+          <t>5827.8_2106_S.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>11252.8_3966_X.</t>
+          <t>21207.4_6474_V.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>5064.3_1832_F.</t>
+          <t>8253.0_2972_🔋.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>1366.2_487_L.</t>
+          <t>7186.5_2708_S.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>4177.9_1557_T.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>10005.5_2697_V.</t>
+          <t>15194.4_3911_S.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>7874.8_2223_M.</t>
+          <t>2558.7_905_S.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>7420.2_4318_C.</t>
+          <t>12008.4_3832_G.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>4886.1_2212_M.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>5007.3_2480_V.</t>
+          <t>10110.2_3737_E.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>5007.1_1751_T.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2557.8_1206_V.</t>
+          <t>7145.5_2856_E.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>10030.1_3124_M.</t>
+          <t>5005.9_1755_X.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>5043.1_2254_C.</t>
+          <t>5072.4_1931_S.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>5022.0_1862_A.</t>
+          <t>5081.5_1647_G.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2002.2_938_P.</t>
+          <t>14019.6_6253_L.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1885.0_952_L.</t>
+          <t>8047.1_2948_G.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>5903.0_2662_C.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>7604.2_3303_P.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>13008.2_4958_P.</t>
+          <t>5296.8_1844_P.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>15223.0_6245_P.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>7230.5_2794_V.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>9004.5_2927_E.</t>
+          <t>6012.6_2984_F.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>5022.5_1222_P.</t>
+          <t>15637.2_5789_G.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>6103.6_2241_G.</t>
+          <t>6007.1_3172_F.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>4896.8_2251_L.</t>
+          <t>8351.7_4153_C.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>8618.0_2344_P.</t>
+          <t>5004.5_1548_A.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>2004.9_754_S.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>21141.5_8155_F.</t>
+          <t>8092.0_4532_P.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>6036.4_2875_V.</t>
+          <t>8132.9_2716_S.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>2185.4_792_S.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>4864.8_1353_E.</t>
+          <t>5869.6_2613_P.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>9020.0_2605_M.</t>
+          <t>4994.4_1534_T.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>6007.1_3172_F.</t>
+          <t>7012.1_3931_🔋.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>14004.5_5478_M.</t>
+          <t>6006.1_2236_V.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>6100.8_3381_P.</t>
+          <t>5072.5_1592_S.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>9013.7_2337_M.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>6011.8_1873_M.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>8442.5_3038_G.</t>
+          <t>7090.6_3340_A.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>25020.8_7832_V.</t>
+          <t>4788.2_1476_P.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>3088.9_1493_C.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>4974.4_1533_E.</t>
+          <t>10241.7_3826_G.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>9012.4_2700_M.</t>
+          <t>4017.3_1883_C.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>9005.5_5146_A.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>1432.9_3942_M.</t>
+          <t>10004.6_2845_V.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>8218.3_2327_P.</t>
+          <t>10277.3_4318_L.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>8200.8_2347_T.</t>
+          <t>4078.1_1810_A.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>11005.3_5159_P.</t>
+          <t>10025.5_3684_F.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>16397.3_4254_S.</t>
+          <t>5522.8_2716_V.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>8004.6_2357_G.</t>
+          <t>1467.9_482_S.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>5008.2_1646_A.</t>
+          <t>9005.5_5146_A.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>8092.0_4532_P.</t>
+          <t>8113.4_3006_P.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>9001.4_3623_P.</t>
+          <t>18102.7_4949_M.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>8506.3_4050_C.</t>
+          <t>6006.6_2009_P.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2504.7_703_🔋.</t>
+          <t>22320.3_9183_F.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>1002.7_460_S.</t>
+          <t>7874.8_2223_M.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>5021.7_1930_A.</t>
+          <t>6833.7_2100_G.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>6833.7_2100_G.</t>
+          <t>611.2_221_M.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>1206.7_12400_M.</t>
+          <t>5014.3_1731_F.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>10011.2_3009_G.</t>
+          <t>5242.7_1657_S.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>9494.5_3544_G.</t>
+          <t>3798.9_1319_S.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>9005.3_4344_A.</t>
+          <t>5008.2_1646_A.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>3023.2_962_S.</t>
+          <t>8618.0_2344_P.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2011.7_731_S.</t>
+          <t>9494.5_3544_G.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>5086.0_1810_G.</t>
+          <t>15149.3_4051_M.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>17012.6_5869_T.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>6053.8_2077_M.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>1018.4_335_M.</t>
+          <t>1152.4_938_S.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>4899.2_1459_A.</t>
+          <t>12138.7_3727_P.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>4078.1_1810_A.</t>
+          <t>8416.2_4091_P.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>8047.1_2948_G.</t>
+          <t>5152.8_1800_G.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>5579.8_1990_E.</t>
+          <t>5004.8_1628_M.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>10007.8_2668_V.</t>
+          <t>8481.2_2463_🔋.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>22002.4_8469_M.</t>
+          <t>2002.2_938_P.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>22320.3_9183_F.</t>
+          <t>2036.1_839_S.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>4153.2_3559_P.</t>
+          <t>5040.0_2299_A.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>4735.2_997_S.</t>
+          <t>21250.2_9506_P.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>6005.3_2226_A.</t>
+          <t>11252.8_3966_X.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2761.5_1068_S.</t>
+          <t>9285.3_3279_G.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>5188.5_1799_S.</t>
+          <t>5086.0_1810_G.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>3010.0_1685_A.</t>
+          <t>4613.1_1806_A.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>5522.8_2716_V.</t>
+          <t>5422.4_1911_G.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>10643.3_3263_S.</t>
+          <t>13023.5_5156_L.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>10055.2_3237_T.</t>
+          <t>8008.0_2930_A.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>14009.0_5498_A.</t>
+          <t>5011.9_1594_P.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>6028.3_2419_L.</t>
+          <t>5013.9_1673_A.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>5013.9_1673_A.</t>
+          <t>42443.0_21763_F.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>6600.2_1915_M.</t>
+          <t>10020.8_2989_M.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>4830.1_2569_C.</t>
+          <t>8452.7_2430_M.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>17003.0_7696_P.</t>
+          <t>5031.8_2047_P.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>8113.4_3006_P.</t>
+          <t>6109.2_2608_L.</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>9639.7_4763_P.</t>
+          <t>7598.7_2799_S.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>1701.7_720_F.</t>
+          <t>8200.5_2738_M.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>5064.2_1636_G.</t>
+          <t>9791.4_3527_G.</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2735.8_959_S.</t>
+          <t>10030.1_3124_M.</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>15004.3_4718_G.</t>
+          <t>5119.6_3153_M.</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>5451.1_1905_T.</t>
+          <t>5580.0_2471_A.</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>4682.8_2218_P.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>3138.1_1120_S.</t>
+          <t>4735.2_997_S.</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>22002.4_8469_M.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>6804.1_2088_P.</t>
+          <t>21114.4_6098_P.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>3026.1_1490_A.</t>
+          <t>3580.9_1198_S.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>4619.4_1440_S.</t>
+          <t>10007.8_2733_V.</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>10003.7_2721_V.</t>
+          <t>5010.9_1617_G.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>6241.6_2497_P.</t>
+          <t>10003.8_3195_S.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>5869.6_2613_P.</t>
+          <t>5019.4_1823_A.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>4791.5_1524_E.</t>
+          <t>5012.1_1375_G.</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>5005.4_2618_L.</t>
+          <t>5018.0_1121_M.</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2186.2_736_G.</t>
+          <t>6173.6_2865_M.</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>6006.6_2009_P.</t>
+          <t>4576.3_2084_S.</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>14117.6_3844_M.</t>
+          <t>6622.5_2224_E.</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>3412.3_1947_C.</t>
+          <t>8120.9_2737_G.</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>6345.4_2376_S.</t>
+          <t>3088.9_1493_C.</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>10001.3_4206_G.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>5029.4_1585_P.</t>
+          <t>9555.5_5689_S.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>12524.7_3259_S.</t>
+          <t>5356.1_1825_T.</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>5033.4_1976_M.</t>
+          <t>7024.3_3266_L.</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>15010.8_6619_G.</t>
+          <t>1432.9_3942_M.</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>5139.2_2082_G.</t>
+          <t>7985.2_2173_P.</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>10031.8_2663_P.</t>
+          <t>2047.9_924_L.</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>9209.1_3141_E.</t>
+          <t>1206.7_12400_M.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>10004.6_3357_S.</t>
+          <t>657.7_273_S.</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>2880.9_1210_L.</t>
+          <t>123.0_5992_A.</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>5081.5_1647_G.</t>
+          <t>8187.1_2322_M.</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>18107.4_4577_M.</t>
+          <t>5033.4_1976_M.</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>8396.0_2595_S.</t>
+          <t>26010.2_9812_F.</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>5000.5_1919_P.</t>
+          <t>9209.1_3141_E.</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>20105.6_7766_F.</t>
+          <t>6518.4_2914_A.</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>3958.9_1777_P.</t>
+          <t>5126.8_1941_G.</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>7127.8_1843_G.</t>
+          <t>10025.6_4018_G.</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>12006.1_5290_T.</t>
+          <t>1701.7_720_F.</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>5282.8_2392_C.</t>
+          <t>14355.0_3613_M.</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>8008.0_2930_A.</t>
+          <t>6038.2_2121_P.</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>2064.3_708_S.</t>
+          <t>4932.4_1545_E.</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>4613.1_1806_A.</t>
+          <t>3757.2_1716_A.</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>2000.0_724_A.</t>
+          <t>10027.3_2906_P.</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>12022.7_5417_L.</t>
+          <t>6241.6_2497_P.</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>5040.0_2971_A.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>5004.8_1628_M.</t>
+          <t>7001.2_3357_M.</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>21114.4_6098_P.</t>
+          <t>1012.0_375_E.</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>600.2_261_L.</t>
+          <t>4891.7_1690_F.</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>5144.4_2349_P.</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>7012.1_3931_🔋.</t>
+          <t>6345.4_2376_S.</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>3059.2_956_T.</t>
+          <t>25020.8_7832_V.</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>5072.4_1931_S.</t>
+          <t>5004.9_1790_A.</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>5014.8_2009_A.</t>
+          <t>16397.3_4254_S.</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>13005.6_6018_P.</t>
+          <t>6137.8_2406_L.</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>5017.7_1147_M.</t>
+          <t>3089.9_1508_C.</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>10023.3_4468_A.</t>
+          <t>5224.2_2340_C.</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>10277.3_4318_L.</t>
+          <t>4705.5_1241_G.</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>5006.8_1080_M.</t>
+          <t>53755.6_36604_F.</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>7012.2_4093_P.</t>
+          <t>5049.0_2240_C.</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>2004.9_754_S.</t>
+          <t>7576.8_2823_P.</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>7312.2_2446_G.</t>
+          <t>4896.8_2251_L.</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>5296.8_1844_P.</t>
+          <t>4974.4_1533_E.</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>4901.4_2376_C.</t>
+          <t>7006.7_5717_S.</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>5009.1_2246_C.</t>
+          <t>8006.7_2244_V.</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>8550.7_2328_P.</t>
+          <t>10030.5_4765_C.</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>10007.4_3588_V.</t>
+          <t>5022.0_1862_A.</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>5040.0_2299_A.</t>
+          <t>5043.1_2254_C.</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>6053.8_2077_M.</t>
+          <t>9639.7_4763_P.</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>9006.6_3366_X.</t>
+          <t>10021.0_4009_G.</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>7039.1_2754_S.</t>
+          <t>5004.1_1610_M.</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>773.5_238_S.</t>
+          <t>2000.0_724_A.</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>21124.1_8011_F.</t>
+          <t>4731.9_1407_T.</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>1492.5_537_S.</t>
+          <t>10023.3_4468_A.</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>553.2_224_S.</t>
+          <t>6007.4_1804_G.</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>6661.8_3736_P.</t>
+          <t>12014.9_4588_T.</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>2185.4_792_S.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>10022.1_2875_M.</t>
+          <t>2629.2_1249_M.</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>26010.2_9812_F.</t>
+          <t>56121.5_25636_F.</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>12013.5_4635_X.</t>
+          <t>5301.0_2064_F.</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>9029.6_4595_P.</t>
+          <t>4763.8_1720_P.</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>1467.9_482_S.</t>
+          <t>2504.7_703_🔋.</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>7025.4_3008_L.</t>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>4932.4_1545_E.</t>
+          <t>5919.7_1982_S.</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>8899.2_2910_S.</t>
+          <t>5040.0_2971_A.</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>10503.6_3278_M.</t>
+          <t>1083.2_390_M.</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>5018.2_1981_A.</t>
+          <t>5008.1_1825_M.</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>5009.1_2246_C.</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>6622.5_2224_E.</t>
+          <t>10002.4_5136_P.</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>2556.5_1160_M.</t>
+          <t>5020.6_1328_M.</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>1380.0_562_A.</t>
+          <t>12006.9_5463_P.</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>9052.9_2955_M.</t>
+          <t>9012.4_2700_M.</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>12265.3_3843_M.</t>
+          <t>6818.2_2036_P.</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>10348.3_2647_S.</t>
+          <t>1885.0_952_L.</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>10013.4_3721_G.</t>
+          <t>17194.0_6301_S.</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>53755.6_36604_F.</t>
+          <t>5017.7_1147_M.</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>8351.7_4153_C.</t>
+          <t>10010.0_2910_V.</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>7569.4_2477_V.</t>
+          <t>9020.0_2605_M.</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>5000.7_1254_V.</t>
+          <t>6182.8_2116_G.</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>14117.6_3844_M.</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>5152.8_1800_G.</t>
+          <t>10006.0_2772_V.</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>5621.6_2375_P.</t>
+          <t>14004.5_5478_M.</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>21442.0_7959_F.</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>5051.4_1993_M.</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>2629.2_1249_V.</t>
+          <t>15016.9_6221_G.</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>4576.3_2084_S.</t>
+          <t>6113.5_2883_C.</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>3010.0_1289_A.</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>6951.4_2856_S.</t>
+          <t>4864.8_1353_E.</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>6004.0_2559_P.</t>
+          <t>11005.3_5159_P.</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>4850.9_2239_C.</t>
+          <t>6779.9_2003_E.</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>6012.3_2200_M.</t>
+          <t>8013.1_2082_P.</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>10006.9_3646_X.</t>
+          <t>10006.9_3646_F.</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>10110.2_3737_E.</t>
+          <t>208.3_85_P.</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>5031.8_2047_P.</t>
+          <t>6903.6_2566_G.</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>9555.5_5689_S.</t>
+          <t>7015.4_2141_T.</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>4781.2_1507_A.</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>14009.7_4401_V.</t>
+          <t>10012.3_3067_S.</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>10011.5_3070_S.</t>
+          <t>5093.1_1543_E.</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>1020.0_679_T.</t>
+          <t>10058.8_3483_F.</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>6007.1_2393_M.</t>
+          <t>14009.7_4401_V.</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>5011.9_1594_P.</t>
+          <t>4540.8_1823_A.</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>6600.2_1915_M.</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>8024.4_2933_S.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>7186.5_2708_S.</t>
+          <t>8899.2_2910_S.</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>4969.4_2146_P.</t>
+          <t>1020.0_679_T.</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>10718.1_9873_S.</t>
+          <t>6035.0_2481_P.</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>8416.2_4091_P.</t>
+          <t>4917.5_2381_T.</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>3551.6_1303_S.</t>
+          <t>3735.9_1928_V.</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>2060.0_802_S.</t>
+          <t>5025.8_1214_P.</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>4214.8_2018_A.</t>
+          <t>7127.8_1843_G.</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>12014.9_4588_T.</t>
+          <t>3059.2_956_T.</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>7114.0_2850_S.</t>
+          <t>8506.3_4050_C.</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>15200.8_10718_F.</t>
+          <t>3029.5_1536_G.</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>6100.8_3381_P.</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>5008.0_2402_P.</t>
+          <t>2113.3_1803_X.</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>18516.8_6699_G.</t>
+          <t>5137.9_2401_C.</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>5020.4_2167_C.</t>
+          <t>4153.2_3559_P.</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>37036.6_17889_F.</t>
+          <t>2556.5_1160_M.</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>5299.8_2406_C.</t>
+          <t>5000.5_1919_P.</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>3010.0_1424_A.</t>
+          <t>9507.9_2851_M.</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>1027.7_364_S.</t>
+          <t>5005.4_2618_L.</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>7145.5_2856_E.</t>
+          <t>10348.3_2647_S.</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>10241.7_3826_G.</t>
+          <t>4814.5_1705_🔋.</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>5020.6_1328_M.</t>
+          <t>13005.6_6018_P.</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>10016.9_3028_M.</t>
+          <t>1002.7_460_S.</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>5025.8_1214_P.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>10007.4_3588_V.</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>18665.3_4638_S.</t>
+          <t>6003.3_2987_M.</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>6903.6_2566_G.</t>
+          <t>7516.9_3203_A.</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>7593.7_2701_E.</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>8006.7_2244_V.</t>
+          <t>7025.7_3094_C.</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>10007.8_2733_V.</t>
+          <t>16520.2_4844_M.</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>5093.1_1543_E.</t>
+          <t>6036.4_2875_V.</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>1629.5_671_F.</t>
+          <t>1018.4_335_M.</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>12342.9_3211_M.</t>
+          <t>18107.4_4577_M.</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>7083.1_2912_G.</t>
+          <t>9006.5_3085_X.</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>5301.0_2064_F.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>6035.0_2481_P.</t>
+          <t>6010.6_2144_A.</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>123.0_5992_A.</t>
+          <t>10718.1_9873_S.</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>401.2_179_S.</t>
+          <t>17003.0_7696_P.</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>4781.2_1507_A.</t>
+          <t>5005.8_1527_S.</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>4966.0_1709_G.</t>
+          <t>6005.3_2226_A.</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>8724.4_2500_M.</t>
+          <t>5451.1_1905_T.</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>5724.1_3694_S.</t>
+          <t>14119.3_5262_S.</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>4077.1_1454_S.</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>7024.3_3266_L.</t>
+          <t>4969.4_2146_P.</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>7243.5_2118_G.</t>
+          <t>8200.8_2347_T.</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>1152.4_938_S.</t>
+          <t>10013.0_3337_S.</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>7985.2_2173_P.</t>
+          <t>5028.5_4433_S.</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>4692.9_1546_P.</t>
+          <t>10005.5_2708_V.</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>6536.2_2241_P.</t>
+          <t>2060.0_802_S.</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>2558.7_905_S.</t>
+          <t>5022.5_1222_P.</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>6779.9_2003_E.</t>
+          <t>2011.7_731_S.</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>5005.8_1527_S.</t>
+          <t>15186.5_3866_S.</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>16520.2_4844_M.</t>
+          <t>5579.8_1990_E.</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>5014.8_2009_A.</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>6610.9_1738_P.</t>
+          <t>5100.0_2587_A.</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>4921.0_2491_A.</t>
+          <t>10011.2_3009_G.</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>611.2_221_M.</t>
+          <t>4886.1_2212_V.</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>5100.0_2587_A.</t>
+          <t>5256.5_1535_S.</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>5004.5_1548_A.</t>
+          <t>7502.4_3467_P.</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>5981.9_2551_P.</t>
+          <t>7880.9_2433_E.</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>13023.5_5156_L.</t>
+          <t>5040.0_2514_C.</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>8648.9_3219_A.</t>
+          <t>3004.6_746_V.</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>4177.9_1557_T.</t>
+          <t>10003.1_5062_V.</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>6011.5_2408_A.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>7025.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>2355.5_726_S.</t>
+          <t>10007.8_2668_V.</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>11527.8_4172_V.</t>
+          <t>10062.5_2886_M.</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>10106.6_2889_P.</t>
+          <t>7022.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>9756.3_2793_M.</t>
+          <t>4700.4_1216_V.</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>5003.2_1389_E.</t>
+          <t>5299.8_2406_C.</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>12006.1_5290_X.</t>
+          <t>1380.0_562_A.</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>9415.9_3699_G.</t>
+          <t>4247.7_1274_T.</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>9006.5_3085_X.</t>
+          <t>5029.4_1585_P.</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>15504.3_3950_M.</t>
+          <t>7243.5_2118_G.</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>4790.7_1897_F.</t>
+          <t>6011.5_2408_A.</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>6003.3_2987_M.</t>
+          <t>4688.1_2291_C.</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>657.7_273_S.</t>
+          <t>7783.3_2713_S.</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>21124.1_8011_F.</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>8132.9_2716_S.</t>
+          <t>2355.5_726_S.</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>6518.4_2914_A.</t>
+          <t>5010.3_3392_P.</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>4013.7_1173_V.</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>4327.6_1237_P.</t>
+          <t>4966.6_2195_P.</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>5008.1_1825_M.</t>
+          <t>7569.4_2477_V.</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>5010.3_3392_P.</t>
+          <t>12013.5_4635_X.</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>7880.9_2433_E.</t>
+          <t>9029.6_4595_P.</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>2036.1_839_S.</t>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>8187.1_2322_M.</t>
+          <t>5020.4_2167_C.</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>5004.0_2103_C.</t>
+          <t>1114.9_359_S.</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>5382.2_2690_M.</t>
+          <t>6472.0_2501_S.</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>6047.4_2816_T.</t>
+          <t>15010.0_6802_L.</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>5010.0_1872_A.</t>
+          <t>10106.6_2889_P.</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>9001.4_3623_P.</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>5014.5_1497_G.</t>
+          <t>3614.8_970_🔋.</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>16008.9_5968_S.</t>
+          <t>5382.2_2690_M.</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>4788.2_1476_P.</t>
+          <t>2761.5_1068_S.</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>5040.0_2514_C.</t>
+          <t>12002.7_4232_S.</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>7247.0_2394_S.</t>
+          <t>12022.7_5417_L.</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>10006.0_2772_V.</t>
+          <t>8196.1_2807_T.</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>15186.5_3866_S.</t>
+          <t>1629.5_671_F.</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>419.0_180_P.</t>
+          <t>7114.0_2850_S.</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>12521.4_4814_M.</t>
+          <t>5461.3_1916_E.</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>6011.8_1873_M.</t>
+          <t>5085.1_1840_G.</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>6109.2_2608_L.</t>
+          <t>6084.1_2156_V.</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>2047.9_924_L.</t>
+          <t>5064.3_1832_F.</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>10138.8_3268_X.</t>
+          <t>6012.3_2200_M.</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>4937.4_1783_A.</t>
+          <t>9006.6_3366_X.</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>6007.4_1804_G.</t>
+          <t>8104.2_2652_M.</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>5051.4_1993_M.</t>
+          <t>4921.0_2491_A.</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>10010.0_2910_V.</t>
+          <t>2735.8_959_S.</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>5242.7_1657_S.</t>
+          <t>10174.3_3680_S.</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>6016.7_2122_M.</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>7419.2_3469_F.</t>
+          <t>1443.0_851_A.</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>4786.5_1898_P.</t>
+          <t>2051.8_860_S.</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>10025.6_4018_G.</t>
+          <t>2880.9_1210_L.</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>5010.3_1888_G.</t>
+          <t>4966.0_1709_G.</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>9507.9_2851_M.</t>
+          <t>5621.6_2375_P.</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>960.0_1109_A.</t>
+          <t>11527.8_4172_V.</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>10003.1_5062_V.</t>
+          <t>3173.3_1251_C.</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>14019.6_6253_L.</t>
+          <t>6012.6_2984_P.</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>10013.0_3337_S.</t>
+          <t>4790.7_1897_F.</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>5007.1_1751_T.</t>
+          <t>600.2_261_L.</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>5000.2_1932_E.</t>
+          <t>3019.8_1453_F.</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>7576.8_2823_P.</t>
+          <t>3138.1_1120_S.</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>5235.4_1766_P.</t>
+          <t>8218.3_2327_P.</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>14119.3_5262_S.</t>
+          <t>5770.8_2848_G.</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>5422.4_1911_G.</t>
+          <t>37036.6_17889_F.</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>5004.1_1610_M.</t>
+          <t>2186.2_736_G.</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>5001.9_1291_V.</t>
+          <t>1222.2_429_M.</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>5581.6_3687_P.</t>
+          <t>10485.5_4164_M.</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>7502.4_3467_P.</t>
+          <t>4791.5_1524_E.</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>5256.5_1535_S.</t>
+          <t>9415.9_3699_G.</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>10001.3_4206_G.</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>7001.2_3357_M.</t>
+          <t>6661.8_3736_P.</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>5007.4_1601_A.</t>
+          <t>7390.6_2590_E.</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>9005.5_5167_M.</t>
+          <t>4797.2_1541_G.</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>2783.5_952_S.</t>
+          <t>12326.4_4833_S.</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>11214.0_4224_V.</t>
+          <t>5005.0_1309_M.</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>531.0_343_A.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>10485.5_4164_M.</t>
+          <t>5007.3_2480_V.</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>3010.0_1289_A.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>7598.7_2799_S.</t>
+          <t>5287.4_1835_V.</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>10021.0_4009_G.</t>
+          <t>9007.1_3080_P.</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>10006.9_3646_F.</t>
+          <t>12006.1_5290_T.</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>5461.3_1916_E.</t>
+          <t>10013.4_3721_G.</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>22008.4_8412_F.</t>
+          <t>4768.0_1875_L.</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>2510.2_1366_V.</t>
+          <t>7039.1_2754_S.</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>5356.1_1825_T.</t>
+          <t>553.2_224_S.</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>3039.1_1013_L.</t>
+          <t>3412.3_1947_C.</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>5072.5_1592_S.</t>
+          <t>6103.6_2241_G.</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>6016.7_2122_M.</t>
+          <t>4786.5_1898_P.</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>3798.9_1319_S.</t>
+          <t>3006.0_1286_M.</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>5144.4_2349_P.</t>
+          <t>4830.1_2569_C.</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>10001.9_4466_P.</t>
+          <t>10031.8_2663_P.</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>15637.2_5789_G.</t>
+          <t>5282.8_2392_C.</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>4886.1_2212_M.</t>
+          <t>5581.6_3687_P.</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>10003.3_3845_P.</t>
+          <t>8367.5_4269_C.</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>5235.4_1766_P.</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>4101.5_1485_V.</t>
+          <t>5010.0_1872_A.</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>7022.4_3008_L.</t>
+          <t>5007.4_1601_A.</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>5005.9_1755_X.</t>
+          <t>3597.6_2910_E.</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>7090.6_3340_A.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>8442.5_3038_G.</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>4850.9_2239_C.</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>9007.1_3080_P.</t>
+          <t>7992.7_2506_F.</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>10004.6_2845_V.</t>
+          <t>1366.2_487_L.</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>6012.6_2984_P.</t>
+          <t>2629.2_1249_V.</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>6620.4_2477_P.</t>
+          <t>15200.8_10718_F.</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>5049.0_2240_C.</t>
+          <t>3039.1_1013_L.</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>3623.3_1426_V.</t>
+          <t>5027.8_1361_P.</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>4017.3_1883_C.</t>
+          <t>11214.0_4224_V.</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>9052.9_2955_M.</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>4013.7_1173_V.</t>
+          <t>16008.9_5968_S.</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>10533.4_4020_F.</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>8367.5_4269_C.</t>
+          <t>4532.9_2322_L.</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>4886.1_2212_V.</t>
+          <t>5904.3_2699_P.</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>2064.3_708_S.</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>3012.4_1258_P.</t>
+          <t>8724.4_2500_M.</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>9285.3_3279_G.</t>
+          <t>10011.5_3070_S.</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>4150.2_2042_C.</t>
+          <t>1027.7_364_S.</t>
         </is>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>2629.2_1249_M.</t>
+          <t>5064.2_1636_G.</t>
         </is>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>5770.8_2848_G.</t>
+          <t>7012.2_4093_P.</t>
         </is>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>5027.8_1361_P.</t>
+          <t>12342.9_3211_M.</t>
         </is>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>5188.5_1799_S.</t>
         </is>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>5014.5_1497_G.</t>
         </is>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>7006.7_5717_S.</t>
+          <t>15010.8_6619_G.</t>
         </is>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>10006.5_3648_X.</t>
+          <t>12545.4_3039_S.</t>
         </is>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>12008.4_3832_G.</t>
+          <t>4692.9_1546_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>5365.6_2437_C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>1135.5_361_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>4327.6_1237_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>13008.2_4958_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>7312.2_2446_G.</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>10003.3_3845_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>1034.3_279_M.</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>6028.3_2419_L.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_500km_2026.xlsx
+++ b/Ranking_CNB_500km_2026.xlsx
@@ -539,12 +539,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>261,3 km</t>
+          <t>263,3 km</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.455 m</t>
+          <t>2.472 m</t>
         </is>
       </c>
     </row>
@@ -641,12 +641,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>181,5 km</t>
+          <t>198,5 km</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2.007 m</t>
+          <t>2.188 m</t>
         </is>
       </c>
     </row>
@@ -704,85 +704,85 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Naiane C.</t>
+          <t>Edivânia M.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>155,4 km</t>
+          <t>168,0 km</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.477 m</t>
+          <t>1.822 m</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Edivânia M.</t>
+          <t>Naiane C.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>151,0 km</t>
+          <t>155,4 km</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.650 m</t>
+          <t>1.477 m</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Izac S.</t>
+          <t>Alexsandro A.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>136,1 km</t>
+          <t>136,5 km</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.598 m</t>
+          <t>1.093 m</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Neydrielle V.</t>
+          <t>Izac S.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>135,6 km</t>
+          <t>136,1 km</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.318 m</t>
+          <t>1.598 m</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Alexsandro A.</t>
+          <t>Neydrielle V.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>131,3 km</t>
+          <t>135,6 km</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.031 m</t>
+          <t>1.318 m</t>
         </is>
       </c>
     </row>
@@ -862,46 +862,46 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>52,4 km</t>
+          <t>55,0 km</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>747 m</t>
+          <t>793 m</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Eduardo T.</t>
+          <t>Thaisa V.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>44,1 km</t>
+          <t>45,5 km</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>496 m</t>
+          <t>652 m</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Thaisa V.</t>
+          <t>Eduardo T.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>43,1 km</t>
+          <t>44,1 km</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>608 m</t>
+          <t>496 m</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A533"/>
+  <dimension ref="A1:A539"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1014,1372 +1014,1372 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>14009.0_5498_A.</t>
+          <t>10007.8_2733_V.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>9005.5_5167_M.</t>
+          <t>9052.9_2955_M.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4821.0_1857_P.</t>
+          <t>7003.6_2437_P.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>960.0_1109_A.</t>
+          <t>10106.6_3354_M.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5001.9_1291_V.</t>
+          <t>3004.6_746_V.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10012.1_3139_S.</t>
+          <t>5005.0_1309_M.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20105.6_7766_F.</t>
+          <t>6518.4_2914_A.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>4101.5_1485_V.</t>
+          <t>6833.7_2100_G.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4937.4_1783_A.</t>
+          <t>600.2_261_L.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>21141.5_8155_F.</t>
+          <t>5005.9_1755_X.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>9756.3_2793_M.</t>
+          <t>5009.1_2246_C.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>22008.4_8412_F.</t>
+          <t>21106.2_7925_P.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10004.6_3357_S.</t>
+          <t>3079.4_1056_L.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4619.4_1440_S.</t>
+          <t>7022.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10003.7_2721_V.</t>
+          <t>14119.3_5262_S.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>7880.9_2433_E.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>9562.8_3145_M.</t>
+          <t>8013.1_2082_P.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5006.8_1080_M.</t>
+          <t>10030.5_4765_C.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>12521.4_4814_M.</t>
+          <t>5072.5_1592_S.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>15504.3_3950_M.</t>
+          <t>5008.1_1825_M.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>6804.1_2088_P.</t>
+          <t>1206.7_12400_M.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2175.4_712_S.</t>
+          <t>8899.2_2910_S.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>12524.7_3259_S.</t>
+          <t>5580.0_2471_A.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10055.2_3237_T.</t>
+          <t>10058.8_3483_F.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>8200.0_2760_F.</t>
+          <t>6951.4_2856_S.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2305.1_940_S.</t>
+          <t>7098.4_4003_P.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5139.2_2082_G.</t>
+          <t>22320.3_9183_F.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5000.2_1932_E.</t>
+          <t>8367.5_4269_C.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10006.9_3646_X.</t>
+          <t>7992.7_2506_F.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10001.9_4466_P.</t>
+          <t>10174.3_3680_S.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>9005.5_5167_M.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>4678.8_1840_A.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2510.2_1366_V.</t>
+          <t>5282.8_2392_C.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3623.3_1426_V.</t>
+          <t>9006.5_3085_X.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10138.8_3268_X.</t>
+          <t>6779.9_2003_E.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5163.5_1775_V.</t>
+          <t>5903.0_2662_C.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3005.2_1040_L.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>9004.5_2927_E.</t>
+          <t>5014.3_1731_F.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10016.9_3028_M.</t>
+          <t>5007.1_1751_T.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10030.0_3041_G.</t>
+          <t>401.2_179_S.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>6610.9_1738_P.</t>
+          <t>1002.7_460_S.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>6536.2_2241_P.</t>
+          <t>9021.3_5169_P.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>6004.0_2559_P.</t>
+          <t>5770.8_2848_G.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>5018.2_1981_A.</t>
+          <t>4692.9_1546_P.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>6047.4_2816_T.</t>
+          <t>5017.7_1147_M.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>5981.9_2551_P.</t>
+          <t>21250.2_9506_P.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>10006.2_2753_V.</t>
+          <t>3138.1_1120_S.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>10643.3_3263_S.</t>
+          <t>4028.8_1699_L.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>791.5_266_G.</t>
+          <t>4994.4_1534_T.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>8550.7_2328_P.</t>
+          <t>2000.0_724_A.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>4214.8_2018_A.</t>
+          <t>10643.3_3263_S.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>21106.2_7925_P.</t>
+          <t>5238.0_2781_F.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>8004.6_2357_G.</t>
+          <t>5004.9_1790_A.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>10503.6_3278_M.</t>
+          <t>9415.9_3699_G.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>419.0_180_P.</t>
+          <t>4101.5_1485_V.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>4901.4_2376_C.</t>
+          <t>56121.5_25636_F.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1492.5_537_S.</t>
+          <t>7025.7_3094_C.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>4972.5_2522_S.</t>
+          <t>3958.9_1777_P.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>5008.0_2402_P.</t>
+          <t>15223.0_6245_P.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>18516.8_6699_G.</t>
+          <t>4153.2_3559_P.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>5010.3_1888_G.</t>
+          <t>6007.1_2393_M.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>7247.0_2394_S.</t>
+          <t>2735.8_959_S.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>4000.6_1659_S.</t>
+          <t>4891.7_1690_F.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>5002.9_1487_P.</t>
+          <t>8506.3_4050_C.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>4028.8_1699_L.</t>
+          <t>8452.7_2430_M.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>10022.1_2875_M.</t>
+          <t>2709.6_926_M.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>4682.8_2218_P.</t>
+          <t>1443.0_851_A.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>5158.6_2220_C.</t>
+          <t>2186.2_736_G.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>12006.1_5290_X.</t>
+          <t>11214.0_4224_V.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>10005.2_3808_G.</t>
+          <t>12524.7_3259_S.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>3958.9_1777_P.</t>
+          <t>1114.9_359_S.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>3010.0_1424_A.</t>
+          <t>10022.1_2875_M.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>7003.6_2437_P.</t>
+          <t>7576.8_2823_P.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>773.5_238_S.</t>
+          <t>53755.6_36604_F.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>9093.1_3374_F.</t>
+          <t>5008.0_2402_P.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>8396.0_2595_S.</t>
+          <t>8618.0_2344_P.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>7420.2_4318_C.</t>
+          <t>9494.5_3544_G.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>8040.3_2996_G.</t>
+          <t>5382.2_2690_M.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>6951.4_2856_S.</t>
+          <t>5019.4_1823_A.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>6007.1_2393_M.</t>
+          <t>9007.1_3080_P.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>4729.8_2058_P.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2976.4_1213_L.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>15004.3_4718_G.</t>
+          <t>3623.3_1426_V.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>5021.7_1930_A.</t>
+          <t>17005.3_7545_M.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1884.9_866_S.</t>
+          <t>4619.4_1440_S.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>5724.1_3694_S.</t>
+          <t>6109.2_2608_L.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>8117.9_4045_E.</t>
+          <t>4214.8_2018_A.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>5000.7_1254_V.</t>
+          <t>15637.2_5789_G.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>531.0_343_A.</t>
+          <t>14004.5_5478_M.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>15057.9_8625_F.</t>
+          <t>6818.2_2036_P.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>4150.2_2042_C.</t>
+          <t>3023.2_962_S.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>3012.4_1258_P.</t>
+          <t>3089.9_1508_C.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>10006.5_3648_X.</t>
+          <t>10005.2_3808_G.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>5000.6_1856_M.</t>
+          <t>5137.9_2401_C.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>14014.7_3537_S.</t>
+          <t>6006.6_2009_P.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>8648.9_3219_A.</t>
+          <t>7390.6_2590_E.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>5004.0_2103_C.</t>
+          <t>7420.2_4318_C.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>3551.6_1303_S.</t>
+          <t>5724.1_3694_S.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>5238.0_2781_F.</t>
+          <t>5522.8_2716_V.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>12265.3_3843_M.</t>
+          <t>7502.4_3467_P.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>7419.2_3469_F.</t>
+          <t>14009.0_5498_A.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>10005.5_2697_V.</t>
+          <t>4077.1_1454_S.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>9005.3_4344_A.</t>
+          <t>2004.9_754_S.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>3010.0_1685_A.</t>
+          <t>10007.4_3588_V.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>4729.8_2058_P.</t>
+          <t>5299.8_2406_C.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2783.5_952_S.</t>
+          <t>5085.1_1840_G.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>6046.5_3239_S.</t>
+          <t>5144.4_2349_P.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2557.8_1206_V.</t>
+          <t>3597.6_2910_E.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>5003.2_1389_E.</t>
+          <t>8092.0_4532_P.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>3026.1_1490_A.</t>
+          <t>10027.3_2906_P.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>8024.4_2933_S.</t>
+          <t>1012.0_375_E.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>8978.9_3078_G.</t>
+          <t>12342.9_3211_M.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2709.6_926_M.</t>
+          <t>10011.2_3009_G.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>6620.4_2477_P.</t>
+          <t>37036.6_17889_F.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>7083.1_2912_G.</t>
+          <t>10106.6_2889_P.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>9021.3_5169_P.</t>
+          <t>6610.9_1738_P.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>4899.2_1459_A.</t>
+          <t>10533.4_4020_F.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>5004.4_1614_A.</t>
+          <t>10055.2_3237_T.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>13344.7_5916_G.</t>
+          <t>5011.9_1594_P.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>3023.2_962_S.</t>
+          <t>4937.4_1783_A.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>5036.1_2201_C.</t>
+          <t>9791.4_3527_G.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>401.2_179_S.</t>
+          <t>16008.9_5968_S.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>18665.3_4638_S.</t>
+          <t>6035.0_2481_P.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>5827.8_2106_S.</t>
+          <t>2880.9_1210_L.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>21207.4_6474_V.</t>
+          <t>1432.9_3942_M.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>8442.5_3038_G.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>7186.5_2708_S.</t>
+          <t>1018.4_335_M.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>4177.9_1557_T.</t>
+          <t>6661.8_3736_P.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>15194.4_3911_S.</t>
+          <t>5174.8_2372_A.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2558.7_905_S.</t>
+          <t>6016.7_2122_M.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>12008.4_3832_G.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>4886.1_2212_M.</t>
+          <t>21442.0_7959_F.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>10110.2_3737_E.</t>
+          <t>5004.5_1548_A.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>5007.1_1751_T.</t>
+          <t>10012.1_3139_S.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>7145.5_2856_E.</t>
+          <t>5301.0_2064_F.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>5005.9_1755_X.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>5072.4_1931_S.</t>
+          <t>7598.7_2799_S.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>5081.5_1647_G.</t>
+          <t>4768.0_1875_L.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>14019.6_6253_L.</t>
+          <t>8416.2_4091_P.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>8047.1_2948_G.</t>
+          <t>3019.8_1453_F.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>5903.0_2662_C.</t>
+          <t>15004.3_4718_G.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>7604.2_3303_P.</t>
+          <t>4247.7_1274_T.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>5296.8_1844_P.</t>
+          <t>4896.8_2251_L.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>15223.0_6245_P.</t>
+          <t>17003.0_7696_P.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>7230.5_2794_V.</t>
+          <t>22008.4_8412_F.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>6012.6_2984_F.</t>
+          <t>5018.2_1981_A.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>15637.2_5789_G.</t>
+          <t>22002.4_8469_M.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>6007.1_3172_F.</t>
+          <t>5126.8_1941_G.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>8351.7_4153_C.</t>
+          <t>553.2_224_S.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>5004.5_1548_A.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2004.9_754_S.</t>
+          <t>5022.0_1862_A.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>8092.0_4532_P.</t>
+          <t>18102.7_4949_M.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>8132.9_2716_S.</t>
+          <t>5000.5_1919_P.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2185.4_792_S.</t>
+          <t>10005.5_2708_V.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>5869.6_2613_P.</t>
+          <t>12013.5_4635_X.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>4994.4_1534_T.</t>
+          <t>7604.2_3303_P.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>7012.1_3931_🔋.</t>
+          <t>10006.2_2753_V.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>6006.1_2236_V.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>5072.5_1592_S.</t>
+          <t>17012.6_5869_T.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>7114.0_2850_S.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>6011.8_1873_M.</t>
+          <t>5013.9_1673_A.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>7090.6_3340_A.</t>
+          <t>6010.6_2144_A.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>4788.2_1476_P.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>3997.6_2695_M.</t>
+          <t>8253.0_2972_🔋.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>10241.7_3826_G.</t>
+          <t>6007.1_3172_F.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>4017.3_1883_C.</t>
+          <t>1222.2_429_M.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>8024.4_2933_S.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>10004.6_2845_V.</t>
+          <t>5010.9_1617_G.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>10277.3_4318_L.</t>
+          <t>1083.2_390_M.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>4078.1_1810_A.</t>
+          <t>1885.0_952_L.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>10025.5_3684_F.</t>
+          <t>5004.8_1628_M.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>5522.8_2716_V.</t>
+          <t>8218.3_2327_P.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>1467.9_482_S.</t>
+          <t>10023.3_4468_A.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>9005.5_5146_A.</t>
+          <t>5919.7_1982_S.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>8113.4_3006_P.</t>
+          <t>10013.4_3721_G.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>18102.7_4949_M.</t>
+          <t>5003.2_1389_E.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>6006.6_2009_P.</t>
+          <t>9029.6_4595_P.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>22320.3_9183_F.</t>
+          <t>5000.2_1932_E.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>7874.8_2223_M.</t>
+          <t>15186.5_3866_S.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>6833.7_2100_G.</t>
+          <t>7186.5_2708_S.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>611.2_221_M.</t>
+          <t>1152.4_938_S.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>10030.0_3041_G.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>5242.7_1657_S.</t>
+          <t>9004.5_2927_E.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>3798.9_1319_S.</t>
+          <t>6006.1_2236_V.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>5008.2_1646_A.</t>
+          <t>5981.9_2551_P.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>8618.0_2344_P.</t>
+          <t>6472.0_2501_S.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>9494.5_3544_G.</t>
+          <t>6536.2_2241_P.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>15149.3_4051_M.</t>
+          <t>5072.4_1931_S.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>3551.6_1303_S.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>6053.8_2077_M.</t>
+          <t>5869.6_2613_P.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>1152.4_938_S.</t>
+          <t>8008.0_2930_A.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>12138.7_3727_P.</t>
+          <t>18665.3_4638_S.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>8416.2_4091_P.</t>
+          <t>5296.8_1844_P.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>5152.8_1800_G.</t>
+          <t>3173.3_1251_C.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>5004.8_1628_M.</t>
+          <t>10031.8_2663_P.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>8481.2_2463_🔋.</t>
+          <t>3010.0_1289_A.</t>
         </is>
       </c>
     </row>
@@ -2393,2345 +2393,2387 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2036.1_839_S.</t>
+          <t>3012.4_1258_P.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>5040.0_2299_A.</t>
+          <t>5422.4_1911_G.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>21250.2_9506_P.</t>
+          <t>4532.9_2322_L.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>11252.8_3966_X.</t>
+          <t>10004.6_3357_S.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>9285.3_3279_G.</t>
+          <t>5020.6_1328_M.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>5086.0_1810_G.</t>
+          <t>2557.8_1206_V.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>4613.1_1806_A.</t>
+          <t>1467.9_482_S.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>5422.4_1911_G.</t>
+          <t>8040.3_2996_G.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>13023.5_5156_L.</t>
+          <t>3010.0_1424_A.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>8008.0_2930_A.</t>
+          <t>6113.5_2883_C.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>5011.9_1594_P.</t>
+          <t>2558.7_905_S.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>5013.9_1673_A.</t>
+          <t>26010.2_9812_F.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>42443.0_21763_F.</t>
+          <t>9020.0_2605_M.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>10020.8_2989_M.</t>
+          <t>7015.4_2141_T.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>8452.7_2430_M.</t>
+          <t>6182.8_2116_G.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>5031.8_2047_P.</t>
+          <t>4017.3_1883_C.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>6109.2_2608_L.</t>
+          <t>4814.5_1705_🔋.</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>7598.7_2799_S.</t>
+          <t>5365.6_2437_C.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>8200.5_2738_M.</t>
+          <t>7127.8_1843_G.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>9791.4_3527_G.</t>
+          <t>4705.5_1241_G.</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>10030.1_3124_M.</t>
+          <t>3039.1_1013_L.</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>5119.6_3153_M.</t>
+          <t>2064.3_708_S.</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>5580.0_2471_A.</t>
+          <t>4781.2_1507_A.</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>5188.5_1799_S.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>4735.2_997_S.</t>
+          <t>10007.8_2668_V.</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>22002.4_8469_M.</t>
+          <t>4921.0_2491_A.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>21114.4_6098_P.</t>
+          <t>7024.3_3266_L.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>3580.9_1198_S.</t>
+          <t>21114.4_6098_P.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>10007.8_2733_V.</t>
+          <t>10005.5_2697_V.</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>5010.9_1617_G.</t>
+          <t>14019.6_6253_L.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>10003.8_3195_S.</t>
+          <t>5004.4_1614_A.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>5019.4_1823_A.</t>
+          <t>10485.5_4164_M.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>5012.1_1375_G.</t>
+          <t>8113.4_3006_P.</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>5018.0_1121_M.</t>
+          <t>5002.9_1487_P.</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>6173.6_2865_M.</t>
+          <t>4763.8_1720_P.</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>4576.3_2084_S.</t>
+          <t>5040.0_2514_C.</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>6622.5_2224_E.</t>
+          <t>16397.3_4254_S.</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>8120.9_2737_G.</t>
+          <t>5010.3_1888_G.</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>3088.9_1493_C.</t>
+          <t>5081.5_1647_G.</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>10008.1_2966_M.</t>
+          <t>6804.1_2088_P.</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>9555.5_5689_S.</t>
+          <t>4974.4_1533_E.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>5356.1_1825_T.</t>
+          <t>5008.2_1646_A.</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>7024.3_3266_L.</t>
+          <t>8396.0_2595_S.</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>1432.9_3942_M.</t>
+          <t>5461.3_1916_E.</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>7985.2_2173_P.</t>
+          <t>1011.0_396_L.</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2047.9_924_L.</t>
+          <t>9013.7_2337_M.</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>1206.7_12400_M.</t>
+          <t>1366.2_487_L.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>657.7_273_S.</t>
+          <t>3088.9_1493_C.</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>123.0_5992_A.</t>
+          <t>5064.3_1832_F.</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>8187.1_2322_M.</t>
+          <t>8104.2_2652_M.</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>5033.4_1976_M.</t>
+          <t>611.2_221_M.</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>26010.2_9812_F.</t>
+          <t>10011.5_3070_S.</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>9209.1_3141_E.</t>
+          <t>10348.3_2647_S.</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>6518.4_2914_A.</t>
+          <t>4788.2_1476_P.</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>5126.8_1941_G.</t>
+          <t>9001.4_3623_P.</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>10025.6_4018_G.</t>
+          <t>6620.4_2477_P.</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>1701.7_720_F.</t>
+          <t>5012.1_1375_G.</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>14355.0_3613_M.</t>
+          <t>2556.5_1160_M.</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>6038.2_2121_P.</t>
+          <t>4540.8_1823_A.</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>4932.4_1545_E.</t>
+          <t>3412.3_1947_C.</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>3757.2_1716_A.</t>
+          <t>3010.0_1685_A.</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>10027.3_2906_P.</t>
+          <t>2051.8_860_S.</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>6241.6_2497_P.</t>
+          <t>5004.1_1610_M.</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>4777.4_1215_M.</t>
+          <t>5025.8_1214_P.</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>7001.2_3357_M.</t>
+          <t>16520.2_4844_M.</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>1012.0_375_E.</t>
+          <t>773.5_238_S.</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>10025.5_3684_F.</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>5144.4_2349_P.</t>
+          <t>5010.3_3392_P.</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>6345.4_2376_S.</t>
+          <t>5000.6_1856_M.</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>25020.8_7832_V.</t>
+          <t>2629.2_1249_V.</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>5004.9_1790_A.</t>
+          <t>6622.5_2224_E.</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>16397.3_4254_S.</t>
+          <t>5235.4_1766_P.</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>6137.8_2406_L.</t>
+          <t>15010.0_6802_L.</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>3089.9_1508_C.</t>
+          <t>5018.0_1121_M.</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>5224.2_2340_C.</t>
+          <t>5020.4_2167_C.</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>4786.5_1898_P.</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>53755.6_36604_F.</t>
+          <t>12138.7_3727_P.</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>5049.0_2240_C.</t>
+          <t>9639.7_4763_P.</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>7576.8_2823_P.</t>
+          <t>7001.2_3357_M.</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>4896.8_2251_L.</t>
+          <t>4886.1_2212_V.</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>4974.4_1533_E.</t>
+          <t>5086.0_1810_G.</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>7006.7_5717_S.</t>
+          <t>10110.2_3737_E.</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>8006.7_2244_V.</t>
+          <t>13008.2_4958_P.</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>10030.5_4765_C.</t>
+          <t>4850.9_2239_C.</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>5022.0_1862_A.</t>
+          <t>123.0_5992_A.</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>5043.1_2254_C.</t>
+          <t>10025.6_4018_G.</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>9639.7_4763_P.</t>
+          <t>6053.8_2077_M.</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>10021.0_4009_G.</t>
+          <t>6012.3_2200_M.</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>5004.1_1610_M.</t>
+          <t>2448.6_1233_V.</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>2000.0_724_A.</t>
+          <t>2355.5_726_S.</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>4731.9_1407_T.</t>
+          <t>5004.0_2103_C.</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>10023.3_4468_A.</t>
+          <t>6103.6_2241_G.</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>6007.4_1804_G.</t>
+          <t>10010.0_2910_V.</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>12014.9_4588_T.</t>
+          <t>3735.9_1928_V.</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>6173.6_2865_M.</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>2629.2_1249_M.</t>
+          <t>1027.7_364_S.</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>56121.5_25636_F.</t>
+          <t>5051.4_1993_M.</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>5301.0_2064_F.</t>
+          <t>5014.8_2009_A.</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>7039.1_2754_S.</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>2504.7_703_🔋.</t>
+          <t>2629.2_1249_M.</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>7419.2_3469_F.</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>5919.7_1982_S.</t>
+          <t>5007.4_1601_A.</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>5040.0_2971_A.</t>
+          <t>5005.4_2618_L.</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>1083.2_390_M.</t>
+          <t>6028.3_2419_L.</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>5008.1_1825_M.</t>
+          <t>6004.0_2559_P.</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>5009.1_2246_C.</t>
+          <t>21207.4_6474_V.</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>10002.4_5136_P.</t>
+          <t>21141.5_8155_F.</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>5020.6_1328_M.</t>
+          <t>2004.2_969_P.</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>12006.9_5463_P.</t>
+          <t>9093.1_3374_F.</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>9012.4_2700_M.</t>
+          <t>7593.7_2701_E.</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>6818.2_2036_P.</t>
+          <t>14014.7_3537_S.</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>1885.0_952_L.</t>
+          <t>5100.0_2587_A.</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>17194.0_6301_S.</t>
+          <t>18516.8_6699_G.</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>5017.7_1147_M.</t>
+          <t>10002.4_5136_P.</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>10010.0_2910_V.</t>
+          <t>4966.6_2195_P.</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>9020.0_2605_M.</t>
+          <t>4932.4_1545_E.</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>6182.8_2116_G.</t>
+          <t>4821.0_1857_P.</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>14117.6_3844_M.</t>
+          <t>4899.2_1459_A.</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>10006.0_2772_V.</t>
+          <t>20105.6_7766_F.</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>14004.5_5478_M.</t>
+          <t>5028.5_4433_S.</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>9006.6_3366_X.</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>5051.4_1993_M.</t>
+          <t>6345.4_2376_S.</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>15016.9_6221_G.</t>
+          <t>5158.6_2220_C.</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>6113.5_2883_C.</t>
+          <t>9285.3_3279_G.</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>3010.0_1289_A.</t>
+          <t>5287.4_1835_V.</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>4864.8_1353_E.</t>
+          <t>8117.9_4045_E.</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>11005.3_5159_P.</t>
+          <t>12006.1_5290_X.</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>6779.9_2003_E.</t>
+          <t>12545.4_3039_S.</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>8013.1_2082_P.</t>
+          <t>10030.1_3124_M.</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>10006.9_3646_F.</t>
+          <t>4735.2_997_S.</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>208.3_85_P.</t>
+          <t>13344.7_5916_G.</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>6903.6_2566_G.</t>
+          <t>9562.8_3145_M.</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>5093.1_1543_E.</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>4781.2_1507_A.</t>
+          <t>8550.7_2328_P.</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>10012.3_3067_S.</t>
+          <t>1884.9_866_S.</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>5093.1_1543_E.</t>
+          <t>2783.5_952_S.</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>8120.9_2737_G.</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>14009.7_4401_V.</t>
+          <t>7312.2_2446_G.</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>4540.8_1823_A.</t>
+          <t>11527.8_4172_V.</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>6600.2_1915_M.</t>
+          <t>5904.3_2699_P.</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>3378.9_1292_🔋.</t>
+          <t>7516.9_3203_A.</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>8899.2_2910_S.</t>
+          <t>10718.1_9873_S.</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>1020.0_679_T.</t>
+          <t>7006.7_5717_S.</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>6035.0_2481_P.</t>
+          <t>4966.0_1709_G.</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>4917.5_2381_T.</t>
+          <t>6084.1_2156_V.</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>3735.9_1928_V.</t>
+          <t>15200.8_10718_F.</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>5025.8_1214_P.</t>
+          <t>4678.8_1840_A.</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>7127.8_1843_G.</t>
+          <t>21124.1_8011_F.</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>3059.2_956_T.</t>
+          <t>6011.5_2408_A.</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>8506.3_4050_C.</t>
+          <t>5010.0_1872_A.</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>3029.5_1536_G.</t>
+          <t>8724.4_2500_M.</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>6100.8_3381_P.</t>
+          <t>9555.5_5689_S.</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>2113.3_1803_X.</t>
+          <t>9756.3_2793_M.</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>5137.9_2401_C.</t>
+          <t>7247.0_2394_S.</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>4153.2_3559_P.</t>
+          <t>7012.1_3931_🔋.</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>2556.5_1160_M.</t>
+          <t>5049.0_2240_C.</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>5000.5_1919_P.</t>
+          <t>10277.3_4318_L.</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>9507.9_2851_M.</t>
+          <t>10003.7_2721_V.</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>5005.4_2618_L.</t>
+          <t>9012.4_2700_M.</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>10348.3_2647_S.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>3029.5_1536_G.</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>13005.6_6018_P.</t>
+          <t>15016.9_6221_G.</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>1002.7_460_S.</t>
+          <t>6903.6_2566_G.</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>2213.2_1662_P.</t>
+          <t>5006.8_1080_M.</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>10007.4_3588_V.</t>
+          <t>10020.8_2989_M.</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>6003.3_2987_M.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>7516.9_3203_A.</t>
+          <t>4797.2_1541_G.</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>7593.7_2701_E.</t>
+          <t>10003.8_3195_S.</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>7025.7_3094_C.</t>
+          <t>6036.4_2875_V.</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>16520.2_4844_M.</t>
+          <t>2504.7_703_🔋.</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>6036.4_2875_V.</t>
+          <t>4682.8_2218_P.</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>1018.4_335_M.</t>
+          <t>18107.4_4577_M.</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>18107.4_4577_M.</t>
+          <t>9209.1_3141_E.</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>9006.5_3085_X.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>7012.2_4093_P.</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>6010.6_2144_A.</t>
+          <t>7230.5_2794_V.</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>10718.1_9873_S.</t>
+          <t>10241.7_3826_G.</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>17003.0_7696_P.</t>
+          <t>12014.9_4588_T.</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>5005.8_1527_S.</t>
+          <t>3059.2_956_T.</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>6005.3_2226_A.</t>
+          <t>10003.3_3845_P.</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>5451.1_1905_T.</t>
+          <t>10004.6_2845_V.</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>14119.3_5262_S.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>1492.5_537_S.</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>4969.4_2146_P.</t>
+          <t>25020.8_7832_V.</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>8200.8_2347_T.</t>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>10013.0_3337_S.</t>
+          <t>6011.8_1873_M.</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>5028.5_4433_S.</t>
+          <t>4613.1_1806_A.</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>10005.5_2708_V.</t>
+          <t>6003.3_2987_M.</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>2060.0_802_S.</t>
+          <t>12002.7_4232_S.</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>5022.5_1222_P.</t>
+          <t>11005.3_5159_P.</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>2011.7_731_S.</t>
+          <t>4700.4_1216_V.</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>15186.5_3866_S.</t>
+          <t>4731.9_1407_T.</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>5579.8_1990_E.</t>
+          <t>9005.5_5146_A.</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>5014.8_2009_A.</t>
+          <t>6137.8_2406_L.</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>5100.0_2587_A.</t>
+          <t>4886.1_2212_M.</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>10011.2_3009_G.</t>
+          <t>4901.4_2376_C.</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>4886.1_2212_V.</t>
+          <t>3614.8_970_🔋.</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>5256.5_1535_S.</t>
+          <t>9507.9_2851_M.</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>7502.4_3467_P.</t>
+          <t>10006.5_3648_X.</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>7880.9_2433_E.</t>
+          <t>2047.9_924_L.</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>5040.0_2514_C.</t>
+          <t>4917.5_2381_T.</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>3004.6_746_V.</t>
+          <t>5579.8_1990_E.</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>10003.1_5062_V.</t>
+          <t>2036.1_839_S.</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>7874.8_2223_M.</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>7025.4_3008_L.</t>
+          <t>7145.5_2856_E.</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>10007.8_2668_V.</t>
+          <t>5021.7_1930_A.</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>10062.5_2886_M.</t>
+          <t>2305.1_940_S.</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>7022.4_3008_L.</t>
+          <t>960.0_1109_A.</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>4700.4_1216_V.</t>
+          <t>4177.9_1557_T.</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>5299.8_2406_C.</t>
+          <t>8351.7_4153_C.</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>1380.0_562_A.</t>
+          <t>42443.0_21763_F.</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>4247.7_1274_T.</t>
+          <t>3026.1_1490_A.</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>5029.4_1585_P.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>7243.5_2118_G.</t>
+          <t>5043.1_2254_C.</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>6011.5_2408_A.</t>
+          <t>6005.3_2226_A.</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>4688.1_2291_C.</t>
+          <t>4790.7_1897_F.</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>7783.3_2713_S.</t>
+          <t>1629.5_671_F.</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>21124.1_8011_F.</t>
+          <t>5064.2_1636_G.</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>2355.5_726_S.</t>
+          <t>10016.9_3028_M.</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>5010.3_3392_P.</t>
+          <t>6012.6_2984_F.</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>4013.7_1173_V.</t>
+          <t>6600.2_1915_M.</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>4966.6_2195_P.</t>
+          <t>4864.8_1353_E.</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>7569.4_2477_V.</t>
+          <t>15504.3_3950_M.</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>12013.5_4635_X.</t>
+          <t>2649.1_1164_M.</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>9029.6_4595_P.</t>
+          <t>7985.2_2173_P.</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>5533.2_1998_S.</t>
+          <t>7083.1_2912_G.</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>5020.4_2167_C.</t>
+          <t>11252.8_3966_X.</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>1114.9_359_S.</t>
+          <t>8200.5_2738_M.</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>14009.7_4401_V.</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>15010.0_6802_L.</t>
+          <t>8132.9_2716_S.</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>10106.6_2889_P.</t>
+          <t>5007.3_2480_V.</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>9001.4_3623_P.</t>
+          <t>5224.2_2340_C.</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>3614.8_970_🔋.</t>
+          <t>5621.6_2375_P.</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>5382.2_2690_M.</t>
+          <t>6012.6_2984_P.</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>2761.5_1068_S.</t>
+          <t>6100.8_3381_P.</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>12002.7_4232_S.</t>
+          <t>5356.1_1825_T.</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>12022.7_5417_L.</t>
+          <t>4972.5_2522_S.</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>8196.1_2807_T.</t>
+          <t>5001.9_1291_V.</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>1629.5_671_F.</t>
+          <t>9005.3_4344_A.</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>7114.0_2850_S.</t>
+          <t>13005.6_6018_P.</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>5461.3_1916_E.</t>
+          <t>3580.9_1198_S.</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>5085.1_1840_G.</t>
+          <t>5040.0_2299_A.</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>6084.1_2156_V.</t>
+          <t>4969.4_2146_P.</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>5064.3_1832_F.</t>
+          <t>15149.3_4051_M.</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>6012.3_2200_M.</t>
+          <t>12326.4_4833_S.</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>9006.6_3366_X.</t>
+          <t>10021.0_4009_G.</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>5022.5_1222_P.</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>4921.0_2491_A.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>2735.8_959_S.</t>
+          <t>208.3_85_P.</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>5256.5_1535_S.</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>6016.7_2122_M.</t>
+          <t>5152.8_1800_G.</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>1443.0_851_A.</t>
+          <t>10012.3_3067_S.</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>1020.0_679_T.</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>2880.9_1210_L.</t>
+          <t>791.5_266_G.</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>4966.0_1709_G.</t>
+          <t>2113.3_1803_X.</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>5621.6_2375_P.</t>
+          <t>5036.1_2201_C.</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>11527.8_4172_V.</t>
+          <t>10062.5_2886_M.</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>3173.3_1251_C.</t>
+          <t>5033.4_1976_M.</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>6012.6_2984_P.</t>
+          <t>10003.1_5062_V.</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>4790.7_1897_F.</t>
+          <t>10001.3_4206_G.</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>600.2_261_L.</t>
+          <t>12265.3_3843_M.</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>2976.4_1213_L.</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>3138.1_1120_S.</t>
+          <t>3757.2_1716_A.</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>8218.3_2327_P.</t>
+          <t>657.7_273_S.</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>5770.8_2848_G.</t>
+          <t>4327.6_1237_P.</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>37036.6_17889_F.</t>
+          <t>6046.5_3239_S.</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>2186.2_736_G.</t>
+          <t>2510.2_1366_V.</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>1222.2_429_M.</t>
+          <t>8978.9_3078_G.</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>10485.5_4164_M.</t>
+          <t>1135.5_361_S.</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>4791.5_1524_E.</t>
+          <t>5139.2_2082_G.</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>9415.9_3699_G.</t>
+          <t>5029.4_1585_P.</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>10001.3_4206_G.</t>
+          <t>5027.8_1361_P.</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>6661.8_3736_P.</t>
+          <t>15057.9_8625_F.</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>7390.6_2590_E.</t>
+          <t>7243.5_2118_G.</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>4797.2_1541_G.</t>
+          <t>12006.9_5463_P.</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>12326.4_4833_S.</t>
+          <t>5451.1_1905_T.</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>5005.0_1309_M.</t>
+          <t>17194.0_6301_S.</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>8481.2_2463_🔋.</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>5007.3_2480_V.</t>
+          <t>14355.0_3613_M.</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>5040.0_2971_A.</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>5287.4_1835_V.</t>
+          <t>4688.1_2291_C.</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>9007.1_3080_P.</t>
+          <t>6007.4_1804_G.</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>12006.1_5290_T.</t>
+          <t>7025.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>10013.4_3721_G.</t>
+          <t>10006.9_3646_F.</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>8648.9_3219_A.</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>7039.1_2754_S.</t>
+          <t>5119.6_3153_M.</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>553.2_224_S.</t>
+          <t>1034.3_279_M.</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>3412.3_1947_C.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>6103.6_2241_G.</t>
+          <t>12008.4_3832_G.</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>4786.5_1898_P.</t>
+          <t>2011.7_731_S.</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>3006.0_1286_M.</t>
+          <t>4000.6_1659_S.</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>4830.1_2569_C.</t>
+          <t>5000.7_1254_V.</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>10031.8_2663_P.</t>
+          <t>2761.5_1068_S.</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>5282.8_2392_C.</t>
+          <t>5242.7_1657_S.</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>5581.6_3687_P.</t>
+          <t>4078.1_1810_A.</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>8367.5_4269_C.</t>
+          <t>8006.7_2244_V.</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>5235.4_1766_P.</t>
+          <t>12006.1_5290_T.</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>5010.0_1872_A.</t>
+          <t>4830.1_2569_C.</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>5007.4_1601_A.</t>
+          <t>5163.5_1775_V.</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>3597.6_2910_E.</t>
+          <t>2175.4_712_S.</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>12022.7_5417_L.</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>8442.5_3038_G.</t>
+          <t>10001.9_4466_P.</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>4850.9_2239_C.</t>
+          <t>8196.1_2807_T.</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>7992.7_2506_F.</t>
+          <t>5827.8_2106_S.</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>1366.2_487_L.</t>
+          <t>7569.4_2477_V.</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>2629.2_1249_V.</t>
+          <t>2060.0_802_S.</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>15200.8_10718_F.</t>
+          <t>2185.4_792_S.</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>3039.1_1013_L.</t>
+          <t>8200.8_2347_T.</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>5027.8_1361_P.</t>
+          <t>6047.4_2816_T.</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>11214.0_4224_V.</t>
+          <t>6241.6_2497_P.</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>9052.9_2955_M.</t>
+          <t>5014.5_1497_G.</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>16008.9_5968_S.</t>
+          <t>7090.6_3340_A.</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>10533.4_4020_F.</t>
+          <t>1701.7_720_F.</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>4532.9_2322_L.</t>
+          <t>10006.0_2772_V.</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>5904.3_2699_P.</t>
+          <t>15194.4_3911_S.</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>2064.3_708_S.</t>
+          <t>5005.8_1527_S.</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>8724.4_2500_M.</t>
+          <t>8187.1_2322_M.</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>10011.5_3070_S.</t>
+          <t>4576.3_2084_S.</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>1027.7_364_S.</t>
+          <t>4013.7_1173_V.</t>
         </is>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>5064.2_1636_G.</t>
+          <t>14117.6_3844_M.</t>
         </is>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>7012.2_4093_P.</t>
+          <t>4791.5_1524_E.</t>
         </is>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>12342.9_3211_M.</t>
+          <t>10503.6_3278_M.</t>
         </is>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>5188.5_1799_S.</t>
+          <t>419.0_180_P.</t>
         </is>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>5014.5_1497_G.</t>
+          <t>10138.8_3268_X.</t>
         </is>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>15010.8_6619_G.</t>
+          <t>13023.5_5156_L.</t>
         </is>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>12545.4_3039_S.</t>
+          <t>3006.0_1286_M.</t>
         </is>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>4692.9_1546_P.</t>
+          <t>15010.8_6619_G.</t>
         </is>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>5365.6_2437_C.</t>
+          <t>7783.3_2713_S.</t>
         </is>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>1135.5_361_S.</t>
+          <t>10006.9_3646_X.</t>
         </is>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>4327.6_1237_P.</t>
+          <t>5031.8_2047_P.</t>
         </is>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>13008.2_4958_P.</t>
+          <t>3005.2_1040_L.</t>
         </is>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>7312.2_2446_G.</t>
+          <t>531.0_343_A.</t>
         </is>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>10003.3_3845_P.</t>
+          <t>3798.9_1319_S.</t>
         </is>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>1034.3_279_M.</t>
+          <t>1380.0_562_A.</t>
         </is>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>6028.3_2419_L.</t>
+          <t>6038.2_2121_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>10013.0_3337_S.</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>8047.1_2948_G.</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>4150.2_2042_C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>5581.6_3687_P.</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>17003.4_7817_A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>8004.6_2357_G.</t>
         </is>
       </c>
     </row>

--- a/Ranking_CNB_500km_2026.xlsx
+++ b/Ranking_CNB_500km_2026.xlsx
@@ -454,12 +454,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>726,4 km</t>
+          <t>768,7 km</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>11.399 m</t>
+          <t>12.064 m</t>
         </is>
       </c>
     </row>
@@ -471,12 +471,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>579,1 km</t>
+          <t>603,1 km</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>7.700 m</t>
+          <t>7.919 m</t>
         </is>
       </c>
     </row>
@@ -505,12 +505,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>329,7 km</t>
+          <t>345,7 km</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.715 m</t>
+          <t>2.992 m</t>
         </is>
       </c>
     </row>
@@ -522,12 +522,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>297,8 km</t>
+          <t>304,9 km</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.520 m</t>
+          <t>3.571 m</t>
         </is>
       </c>
     </row>
@@ -539,97 +539,97 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>263,3 km</t>
+          <t>272,6 km</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.472 m</t>
+          <t>2.541 m</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Mateus P.</t>
+          <t>Mateus  M.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>236,0 km</t>
+          <t>253,1 km</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.640 m</t>
+          <t>3.169 m</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Mateus  M.</t>
+          <t>Gabriele L.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>232,0 km</t>
+          <t>240,9 km</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.962 m</t>
+          <t>1.738 m</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Gabriele L.</t>
+          <t>Mateus P.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>224,9 km</t>
+          <t>236,0 km</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.579 m</t>
+          <t>2.640 m</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Jandson P.</t>
+          <t>Gleydson G.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>212,7 km</t>
+          <t>221,3 km</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.775 m</t>
+          <t>1.556 m</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Gleydson G.</t>
+          <t>Jandson P.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>205,3 km</t>
+          <t>212,7 km</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.372 m</t>
+          <t>2.775 m</t>
         </is>
       </c>
     </row>
@@ -653,34 +653,34 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Fellipe T.</t>
+          <t>Cassia C.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>175,7 km</t>
+          <t>177,8 km</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.258 m</t>
+          <t>2.125 m</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Cassia C.</t>
+          <t>Fellipe T.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>172,9 km</t>
+          <t>175,7 km</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2.075 m</t>
+          <t>1.258 m</t>
         </is>
       </c>
     </row>
@@ -726,12 +726,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>155,4 km</t>
+          <t>160,4 km</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.477 m</t>
+          <t>1.488 m</t>
         </is>
       </c>
     </row>
@@ -794,12 +794,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>117,6 km</t>
+          <t>122,6 km</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.418 m</t>
+          <t>1.486 m</t>
         </is>
       </c>
     </row>
@@ -811,12 +811,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>95,3 km</t>
+          <t>116,5 km</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.027 m</t>
+          <t>1.234 m</t>
         </is>
       </c>
     </row>
@@ -857,51 +857,51 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Filipe M.</t>
+          <t>Eduardo T.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>55,0 km</t>
+          <t>62,2 km</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>793 m</t>
+          <t>675 m</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Thaisa V.</t>
+          <t>Filipe M.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>45,5 km</t>
+          <t>55,0 km</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>652 m</t>
+          <t>793 m</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Eduardo T.</t>
+          <t>Thaisa V.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>44,1 km</t>
+          <t>45,5 km</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>496 m</t>
+          <t>652 m</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A539"/>
+  <dimension ref="A1:A554"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1014,3766 +1014,3871 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10007.8_2733_V.</t>
+          <t>12008.4_3832_G.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>9052.9_2955_M.</t>
+          <t>6007.1_2393_M.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>7003.6_2437_P.</t>
+          <t>7598.7_2799_S.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10106.6_3354_M.</t>
+          <t>5072.4_1931_S.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3004.6_746_V.</t>
+          <t>21442.0_7959_F.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5005.0_1309_M.</t>
+          <t>2213.2_1662_P.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6518.4_2914_A.</t>
+          <t>15637.2_5789_G.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6833.7_2100_G.</t>
+          <t>6007.1_3172_F.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>600.2_261_L.</t>
+          <t>5010.3_3392_P.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5005.9_1755_X.</t>
+          <t>10021.0_4009_G.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5009.1_2246_C.</t>
+          <t>4790.7_1897_F.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>21106.2_7925_P.</t>
+          <t>419.0_180_P.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3079.4_1056_L.</t>
+          <t>5007.4_1601_A.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>7022.4_3008_L.</t>
+          <t>6109.2_2608_L.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>14119.3_5262_S.</t>
+          <t>10030.5_4765_C.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>7880.9_2433_E.</t>
+          <t>8132.9_2716_S.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>8013.1_2082_P.</t>
+          <t>4928.0_2454_C.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10030.5_4765_C.</t>
+          <t>15995.0_5344_S.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5072.5_1592_S.</t>
+          <t>6028.3_2419_L.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5008.1_1825_M.</t>
+          <t>5144.4_2349_P.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1206.7_12400_M.</t>
+          <t>2783.5_952_S.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>8899.2_2910_S.</t>
+          <t>15223.0_6245_P.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5580.0_2471_A.</t>
+          <t>2000.0_724_A.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10058.8_3483_F.</t>
+          <t>4153.2_3559_P.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>6951.4_2856_S.</t>
+          <t>10485.5_4164_M.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>7098.4_4003_P.</t>
+          <t>7025.4_3008_L.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>22320.3_9183_F.</t>
+          <t>80.0_22_P.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>8367.5_4269_C.</t>
+          <t>6004.0_2559_P.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>7992.7_2506_F.</t>
+          <t>4678.8_1840_A.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10174.3_3680_S.</t>
+          <t>12002.7_4232_S.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>9005.5_5167_M.</t>
+          <t>8200.5_2738_M.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5079.1_1762_L.</t>
+          <t>7006.7_5717_S.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5282.8_2392_C.</t>
+          <t>12342.9_3211_M.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>9006.5_3085_X.</t>
+          <t>10012.1_3139_S.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>6779.9_2003_E.</t>
+          <t>5007.1_1751_T.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5903.0_2662_C.</t>
+          <t>4729.8_2058_P.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>47036.4_21887_F.</t>
+          <t>8724.4_2500_M.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>5014.3_1731_F.</t>
+          <t>5064.2_1636_G.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>5007.1_1751_T.</t>
+          <t>5981.9_2551_P.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>401.2_179_S.</t>
+          <t>16008.9_5968_S.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1002.7_460_S.</t>
+          <t>8506.3_4050_C.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>9021.3_5169_P.</t>
+          <t>15010.0_6802_L.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>5770.8_2848_G.</t>
+          <t>14119.3_5262_S.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>4692.9_1546_P.</t>
+          <t>5008.2_1646_A.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>5017.7_1147_M.</t>
+          <t>5014.5_1497_G.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>21250.2_9506_P.</t>
+          <t>24004.5_6492_M.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3138.1_1120_S.</t>
+          <t>3010.0_1685_A.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>4028.8_1699_L.</t>
+          <t>7039.1_2754_S.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>4994.4_1534_T.</t>
+          <t>4013.7_1173_V.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2000.0_724_A.</t>
+          <t>4896.8_2251_L.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>10643.3_3263_S.</t>
+          <t>1629.5_671_F.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>5238.0_2781_F.</t>
+          <t>4966.6_2195_P.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>5004.9_1790_A.</t>
+          <t>10012.3_3067_S.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>9415.9_3699_G.</t>
+          <t>4101.5_1485_V.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>4101.5_1485_V.</t>
+          <t>3010.0_1289_A.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>56121.5_25636_F.</t>
+          <t>9005.5_5146_A.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>7025.7_3094_C.</t>
+          <t>3580.9_1198_S.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>3958.9_1777_P.</t>
+          <t>1432.9_3942_M.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>15223.0_6245_P.</t>
+          <t>4901.4_2376_C.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>4153.2_3559_P.</t>
+          <t>5533.2_1998_S.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>6007.1_2393_M.</t>
+          <t>5005.9_1755_X.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2735.8_959_S.</t>
+          <t>4797.2_1541_G.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>4891.7_1690_F.</t>
+          <t>21250.2_9506_P.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>8506.3_4050_C.</t>
+          <t>7186.5_2708_S.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>8452.7_2430_M.</t>
+          <t>6084.1_2156_V.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2709.6_926_M.</t>
+          <t>4830.1_2569_C.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1443.0_851_A.</t>
+          <t>8442.5_3038_G.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2186.2_736_G.</t>
+          <t>5010.3_1888_G.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>11214.0_4224_V.</t>
+          <t>4247.7_1274_T.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>12524.7_3259_S.</t>
+          <t>10005.5_2708_V.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1114.9_359_S.</t>
+          <t>12521.4_4814_M.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>10022.1_2875_M.</t>
+          <t>11005.3_5159_P.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>7576.8_2823_P.</t>
+          <t>8008.0_2930_A.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>53755.6_36604_F.</t>
+          <t>17003.4_7817_A.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>5008.0_2402_P.</t>
+          <t>5072.5_1592_S.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>8618.0_2344_P.</t>
+          <t>5028.5_4433_S.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>9494.5_3544_G.</t>
+          <t>15186.5_3866_S.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>5382.2_2690_M.</t>
+          <t>7098.1_2142_G.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>5019.4_1823_A.</t>
+          <t>6007.4_1804_G.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>9007.1_3080_P.</t>
+          <t>9006.5_3085_X.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>4729.8_2058_P.</t>
+          <t>21114.5_6969_M.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>5007.5_3389_P.</t>
+          <t>3138.1_1120_S.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>3623.3_1426_V.</t>
+          <t>5013.9_1673_A.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>17005.3_7545_M.</t>
+          <t>3005.2_1040_L.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>4619.4_1440_S.</t>
+          <t>17194.0_6301_S.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>6109.2_2608_L.</t>
+          <t>10001.3_4206_G.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>4214.8_2018_A.</t>
+          <t>3614.8_970_🔋.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>15637.2_5789_G.</t>
+          <t>5004.8_1628_M.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>14004.5_5478_M.</t>
+          <t>5040.0_2299_A.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>6818.2_2036_P.</t>
+          <t>5029.4_1585_P.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>3023.2_962_S.</t>
+          <t>5079.1_1762_L.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>3089.9_1508_C.</t>
+          <t>4899.2_1459_A.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>10005.2_3808_G.</t>
+          <t>5919.7_1982_S.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>5137.9_2401_C.</t>
+          <t>2735.8_959_S.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>6006.6_2009_P.</t>
+          <t>1002.7_460_S.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>7390.6_2590_E.</t>
+          <t>4327.6_1237_P.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>7420.2_4318_C.</t>
+          <t>7247.0_2394_S.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>5724.1_3694_S.</t>
+          <t>5000.7_1254_V.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>5522.8_2716_V.</t>
+          <t>2510.2_1366_V.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>7502.4_3467_P.</t>
+          <t>13008.2_4958_P.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>14009.0_5498_A.</t>
+          <t>15200.8_10718_F.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>4077.1_1454_S.</t>
+          <t>5903.0_2662_C.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2004.9_754_S.</t>
+          <t>6012.6_2984_F.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>10007.4_3588_V.</t>
+          <t>9005.3_4344_A.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>5299.8_2406_C.</t>
+          <t>4078.1_1810_A.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>5085.1_1840_G.</t>
+          <t>1380.0_562_A.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>5144.4_2349_P.</t>
+          <t>3958.9_1777_P.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>3597.6_2910_E.</t>
+          <t>10174.3_3680_S.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>8092.0_4532_P.</t>
+          <t>21207.4_6474_V.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>10027.3_2906_P.</t>
+          <t>9415.9_3699_G.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1012.0_375_E.</t>
+          <t>7015.4_2141_T.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>12342.9_3211_M.</t>
+          <t>12545.4_3039_S.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>10011.2_3009_G.</t>
+          <t>2649.1_1164_M.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>37036.6_17889_F.</t>
+          <t>1443.0_851_A.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>10106.6_2889_P.</t>
+          <t>6006.6_2009_P.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>6610.9_1738_P.</t>
+          <t>6011.5_2408_A.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>10533.4_4020_F.</t>
+          <t>11214.0_4224_V.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>10055.2_3237_T.</t>
+          <t>4932.4_1545_E.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>5011.9_1594_P.</t>
+          <t>7593.7_2701_E.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>4937.4_1783_A.</t>
+          <t>7114.0_2850_S.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>9791.4_3527_G.</t>
+          <t>9045.2_4937_P.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>16008.9_5968_S.</t>
+          <t>8648.9_3219_A.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>6035.0_2481_P.</t>
+          <t>173.3_68_P.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2880.9_1210_L.</t>
+          <t>5010.0_1872_A.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1432.9_3942_M.</t>
+          <t>5137.9_2401_C.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>8442.5_3038_G.</t>
+          <t>3006.0_1286_M.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>1018.4_335_M.</t>
+          <t>5522.8_2716_V.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>6661.8_3736_P.</t>
+          <t>5012.1_1375_G.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>5174.8_2372_A.</t>
+          <t>10016.9_3028_M.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>6016.7_2122_M.</t>
+          <t>5014.8_2009_A.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>5002.1_1441_G.</t>
+          <t>6241.6_2497_P.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>21442.0_7959_F.</t>
+          <t>17005.3_7545_M.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>5004.5_1548_A.</t>
+          <t>515.9_237_S.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>10012.1_3139_S.</t>
+          <t>7003.6_2437_P.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>5301.0_2064_F.</t>
+          <t>4619.4_1440_S.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2006.0_811_P.</t>
+          <t>5461.3_1916_E.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>7598.7_2799_S.</t>
+          <t>4891.7_1690_F.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>4768.0_1875_L.</t>
+          <t>1011.0_396_L.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>8416.2_4091_P.</t>
+          <t>4000.6_1659_S.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>3019.8_1453_F.</t>
+          <t>5904.3_2699_P.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>15004.3_4718_G.</t>
+          <t>7783.3_2713_S.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>4247.7_1274_T.</t>
+          <t>960.0_1109_A.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>4896.8_2251_L.</t>
+          <t>4966.0_1709_G.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>17003.0_7696_P.</t>
+          <t>5040.0_2514_C.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>22008.4_8412_F.</t>
+          <t>9012.4_2700_M.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>5018.2_1981_A.</t>
+          <t>4850.9_2239_C.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>22002.4_8469_M.</t>
+          <t>9093.1_3374_F.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>5126.8_1941_G.</t>
+          <t>4017.3_1883_C.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>553.2_224_S.</t>
+          <t>10008.1_2966_M.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>515.9_237_S.</t>
+          <t>56121.5_25636_F.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>5022.0_1862_A.</t>
+          <t>10062.5_2886_M.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>18102.7_4949_M.</t>
+          <t>4788.2_1476_P.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>5000.5_1919_P.</t>
+          <t>25020.8_7832_V.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>10005.5_2708_V.</t>
+          <t>13023.5_5156_L.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>12013.5_4635_X.</t>
+          <t>5036.1_2201_C.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>7604.2_3303_P.</t>
+          <t>5724.1_3694_S.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>10006.2_2753_V.</t>
+          <t>1135.5_361_S.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>5601.8_2355_M.</t>
+          <t>10003.7_2721_V.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>17012.6_5869_T.</t>
+          <t>5002.9_1487_P.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>7114.0_2850_S.</t>
+          <t>9562.8_3145_M.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>5013.9_1673_A.</t>
+          <t>4763.8_1720_P.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>6010.6_2144_A.</t>
+          <t>10277.3_4318_L.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>21202.9_7130_🔋.</t>
+          <t>1034.3_279_M.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>8253.0_2972_🔋.</t>
+          <t>4974.4_1533_E.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>6007.1_3172_F.</t>
+          <t>7230.5_2794_V.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1222.2_429_M.</t>
+          <t>7516.9_3203_A.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>8024.4_2933_S.</t>
+          <t>6012.6_2984_P.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>5010.9_1617_G.</t>
+          <t>5005.8_1527_S.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>1083.2_390_M.</t>
+          <t>2113.3_1803_X.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>1885.0_952_L.</t>
+          <t>10006.9_3646_F.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>5004.8_1628_M.</t>
+          <t>5188.5_1799_S.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>8218.3_2327_P.</t>
+          <t>5081.5_1647_G.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>10023.3_4468_A.</t>
+          <t>10007.8_2733_V.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>5919.7_1982_S.</t>
+          <t>2064.3_708_S.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>10013.4_3721_G.</t>
+          <t>7001.2_3357_M.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>5003.2_1389_E.</t>
+          <t>2004.2_969_P.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>9029.6_4595_P.</t>
+          <t>10241.7_3826_G.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>5000.2_1932_E.</t>
+          <t>5003.2_1389_E.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>15186.5_3866_S.</t>
+          <t>10106.6_2889_P.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>7186.5_2708_S.</t>
+          <t>10004.6_2845_V.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>1152.4_938_S.</t>
+          <t>47036.4_21887_F.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>10030.0_3041_G.</t>
+          <t>5000.6_1856_M.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>9004.5_2927_E.</t>
+          <t>21141.5_8155_F.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>6006.1_2236_V.</t>
+          <t>4700.4_1216_V.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>5981.9_2551_P.</t>
+          <t>4177.9_1557_T.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>6472.0_2501_S.</t>
+          <t>5299.8_2406_C.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>6536.2_2241_P.</t>
+          <t>3026.1_1490_A.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>5072.4_1931_S.</t>
+          <t>3039.1_1013_L.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>3551.6_1303_S.</t>
+          <t>9007.1_3080_P.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>5869.6_2613_P.</t>
+          <t>12014.9_4588_T.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>8008.0_2930_A.</t>
+          <t>5020.6_1328_M.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>18665.3_4638_S.</t>
+          <t>4735.2_997_S.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>5296.8_1844_P.</t>
+          <t>611.2_221_M.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>3173.3_1251_C.</t>
+          <t>773.5_238_S.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>10031.8_2663_P.</t>
+          <t>6137.8_2406_L.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>3010.0_1289_A.</t>
+          <t>10027.3_2906_P.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2002.2_938_P.</t>
+          <t>7502.4_3467_P.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>3012.4_1258_P.</t>
+          <t>15010.8_6619_G.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>5422.4_1911_G.</t>
+          <t>600.2_261_L.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>4532.9_2322_L.</t>
+          <t>9021.3_5169_P.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>10004.6_3357_S.</t>
+          <t>5256.5_1535_S.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>5020.6_1328_M.</t>
+          <t>5004.0_2103_C.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2557.8_1206_V.</t>
+          <t>22008.4_8412_F.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>1467.9_482_S.</t>
+          <t>9005.5_5167_M.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>8040.3_2996_G.</t>
+          <t>5009.1_2246_C.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>3010.0_1424_A.</t>
+          <t>9013.7_2337_M.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>6113.5_2883_C.</t>
+          <t>5002.1_1441_G.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2558.7_905_S.</t>
+          <t>5119.6_3153_M.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>26010.2_9812_F.</t>
+          <t>5621.6_2375_P.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>9020.0_2605_M.</t>
+          <t>14009.7_4401_V.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>7015.4_2141_T.</t>
+          <t>5031.8_2047_P.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>6182.8_2116_G.</t>
+          <t>5093.1_1543_E.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>4017.3_1883_C.</t>
+          <t>5580.0_2471_A.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>4814.5_1705_🔋.</t>
+          <t>8218.3_2327_P.</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>5365.6_2437_C.</t>
+          <t>3412.3_1947_C.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>7127.8_1843_G.</t>
+          <t>6345.4_2376_S.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>4705.5_1241_G.</t>
+          <t>5235.4_1766_P.</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>3039.1_1013_L.</t>
+          <t>12326.4_4833_S.</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2064.3_708_S.</t>
+          <t>2011.7_731_S.</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>4781.2_1507_A.</t>
+          <t>7420.2_4318_C.</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>5188.5_1799_S.</t>
+          <t>10106.6_3354_M.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>10007.8_2668_V.</t>
+          <t>4214.8_2018_A.</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>4921.0_2491_A.</t>
+          <t>15194.4_3911_S.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>7024.3_3266_L.</t>
+          <t>10003.3_3845_P.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>21114.4_6098_P.</t>
+          <t>4613.1_1806_A.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>10005.5_2697_V.</t>
+          <t>1083.2_390_M.</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>14019.6_6253_L.</t>
+          <t>2175.4_712_S.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>5004.4_1614_A.</t>
+          <t>8113.4_3006_P.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>10485.5_4164_M.</t>
+          <t>10006.9_3646_X.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>8113.4_3006_P.</t>
+          <t>3023.2_962_S.</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>5002.9_1487_P.</t>
+          <t>4768.0_1875_L.</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>4763.8_1720_P.</t>
+          <t>5025.8_1214_P.</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>5040.0_2514_C.</t>
+          <t>3798.9_1319_S.</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>16397.3_4254_S.</t>
+          <t>18102.7_4949_M.</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>5010.3_1888_G.</t>
+          <t>5004.9_1790_A.</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>5081.5_1647_G.</t>
+          <t>9001.4_3623_P.</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>6804.1_2088_P.</t>
+          <t>5296.8_1844_P.</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>4974.4_1533_E.</t>
+          <t>10110.2_3737_E.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>5008.2_1646_A.</t>
+          <t>5017.7_1147_M.</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>8396.0_2595_S.</t>
+          <t>8117.9_4045_E.</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>5461.3_1916_E.</t>
+          <t>2006.0_811_P.</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>1011.0_396_L.</t>
+          <t>7243.5_2118_G.</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>9013.7_2337_M.</t>
+          <t>16397.3_4254_S.</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>1366.2_487_L.</t>
+          <t>5152.8_1800_G.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>3088.9_1493_C.</t>
+          <t>6818.2_2036_P.</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>5064.3_1832_F.</t>
+          <t>2004.9_754_S.</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>8104.2_2652_M.</t>
+          <t>10030.0_3041_G.</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>611.2_221_M.</t>
+          <t>6003.3_2987_M.</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>10011.5_3070_S.</t>
+          <t>3378.9_1292_🔋.</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>10348.3_2647_S.</t>
+          <t>5356.1_1825_T.</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>4788.2_1476_P.</t>
+          <t>5027.8_1361_P.</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>9001.4_3623_P.</t>
+          <t>21202.9_7130_🔋.</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>6620.4_2477_P.</t>
+          <t>10348.3_2647_S.</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>5012.1_1375_G.</t>
+          <t>5005.0_1309_M.</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>2556.5_1160_M.</t>
+          <t>22320.3_9183_F.</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>4540.8_1823_A.</t>
+          <t>7012.2_4093_P.</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>3412.3_1947_C.</t>
+          <t>10643.3_3263_S.</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>3010.0_1685_A.</t>
+          <t>4864.8_1353_E.</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>2051.8_860_S.</t>
+          <t>5064.3_1832_F.</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>5004.1_1610_M.</t>
+          <t>5581.6_3687_P.</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>5025.8_1214_P.</t>
+          <t>6661.8_3736_P.</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>16520.2_4844_M.</t>
+          <t>10058.8_3483_F.</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>773.5_238_S.</t>
+          <t>22002.4_8469_M.</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>10025.5_3684_F.</t>
+          <t>21165.3_7815_E.</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>5010.3_3392_P.</t>
+          <t>4969.4_2146_P.</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>5000.6_1856_M.</t>
+          <t>5004.1_1610_M.</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>2629.2_1249_V.</t>
+          <t>9285.3_3279_G.</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>6622.5_2224_E.</t>
+          <t>5869.6_2613_P.</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>5235.4_1766_P.</t>
+          <t>6600.2_1915_M.</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>15010.0_6802_L.</t>
+          <t>12022.7_5417_L.</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>5018.0_1121_M.</t>
+          <t>5007.3_2480_V.</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>5020.4_2167_C.</t>
+          <t>4814.5_1705_🔋.</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>4786.5_1898_P.</t>
+          <t>5014.3_1731_F.</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>12138.7_3727_P.</t>
+          <t>9639.7_4763_P.</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>9639.7_4763_P.</t>
+          <t>8351.7_4153_C.</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>7001.2_3357_M.</t>
+          <t>3997.6_2695_M.</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>4886.1_2212_V.</t>
+          <t>10003.1_5062_V.</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>5086.0_1810_G.</t>
+          <t>1492.5_537_S.</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>10110.2_3737_E.</t>
+          <t>5007.5_3389_P.</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>13008.2_4958_P.</t>
+          <t>12006.9_5463_P.</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>4850.9_2239_C.</t>
+          <t>3597.6_2910_E.</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>123.0_5992_A.</t>
+          <t>10004.6_3357_S.</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>10025.6_4018_G.</t>
+          <t>7024.3_3266_L.</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>6053.8_2077_M.</t>
+          <t>3623.3_1426_V.</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>6012.3_2200_M.</t>
+          <t>10007.4_3588_V.</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>2448.6_1233_V.</t>
+          <t>6016.7_2122_M.</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>2355.5_726_S.</t>
+          <t>10031.8_2663_P.</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>5004.0_2103_C.</t>
+          <t>4937.4_1783_A.</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>6103.6_2241_G.</t>
+          <t>5022.5_1222_P.</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>10010.0_2910_V.</t>
+          <t>5451.1_1905_T.</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>3735.9_1928_V.</t>
+          <t>6833.7_2100_G.</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>6173.6_2865_M.</t>
+          <t>10718.1_9873_S.</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>1027.7_364_S.</t>
+          <t>8978.9_3078_G.</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>5051.4_1993_M.</t>
+          <t>7569.4_2477_V.</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>5014.8_2009_A.</t>
+          <t>9555.5_5689_S.</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>7039.1_2754_S.</t>
+          <t>4532.9_2322_L.</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>2629.2_1249_M.</t>
+          <t>8550.7_2328_P.</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>7419.2_3469_F.</t>
+          <t>5020.4_2167_C.</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>5007.4_1601_A.</t>
+          <t>4077.1_1454_S.</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>5005.4_2618_L.</t>
+          <t>5006.6_1780_E.</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>6028.3_2419_L.</t>
+          <t>9004.5_2927_E.</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>6004.0_2559_P.</t>
+          <t>15149.3_4051_M.</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>21207.4_6474_V.</t>
+          <t>5049.0_2240_C.</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>21141.5_8155_F.</t>
+          <t>3089.9_1508_C.</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>2004.2_969_P.</t>
+          <t>12524.7_3259_S.</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>9093.1_3374_F.</t>
+          <t>5086.0_1810_G.</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>7593.7_2701_E.</t>
+          <t>42443.0_21763_F.</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>14014.7_3537_S.</t>
+          <t>1012.0_375_E.</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>5100.0_2587_A.</t>
+          <t>6011.8_1873_M.</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>18516.8_6699_G.</t>
+          <t>6113.5_2883_C.</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>10002.4_5136_P.</t>
+          <t>5163.5_1775_V.</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>4966.6_2195_P.</t>
+          <t>10055.2_3237_T.</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>4932.4_1545_E.</t>
+          <t>4994.4_1534_T.</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>4821.0_1857_P.</t>
+          <t>8200.0_2760_F.</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>4899.2_1459_A.</t>
+          <t>4777.4_1215_M.</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>20105.6_7766_F.</t>
+          <t>5601.8_2355_M.</t>
         </is>
       </c>
     </ro